--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1237"/>
+  <dimension ref="A1:H1277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>7090000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="E1214" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="F1214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1214" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>15500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="E1215" t="n">
-        <v>350</v>
+        <v>598</v>
       </c>
       <c r="F1215" t="n">
         <v>3</v>
       </c>
       <c r="G1215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>17000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="E1216" t="n">
-        <v>598</v>
+        <v>260</v>
       </c>
       <c r="F1216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1216" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>11000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>310</v>
+        <v>431</v>
       </c>
       <c r="E1217" t="n">
-        <v>260</v>
+        <v>874</v>
       </c>
       <c r="F1217" t="n">
         <v>4</v>
       </c>
       <c r="G1217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,20 +34524,20 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>15000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E1218" t="n">
-        <v>874</v>
+        <v>202</v>
       </c>
       <c r="F1218" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1218" t="n">
         <v>4</v>
@@ -34552,7 +34552,7 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1219" t="n">
@@ -34562,13 +34562,13 @@
         <v>440</v>
       </c>
       <c r="E1219" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F1219" t="n">
         <v>7</v>
       </c>
       <c r="G1219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1219" t="n">
         <v>2</v>
@@ -34580,7 +34580,7 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1220" t="n">
@@ -34590,13 +34590,13 @@
         <v>440</v>
       </c>
       <c r="E1220" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F1220" t="n">
         <v>7</v>
       </c>
       <c r="G1220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1220" t="n">
         <v>2</v>
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>2600000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E1221" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="F1221" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1221" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>8500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>440</v>
+        <v>135</v>
       </c>
       <c r="E1222" t="n">
-        <v>202</v>
+        <v>30</v>
       </c>
       <c r="F1222" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>76000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>800</v>
+        <v>240</v>
       </c>
       <c r="E1223" t="n">
-        <v>700</v>
+        <v>310</v>
       </c>
       <c r="F1223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,23 +34692,23 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>2600000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="E1224" t="n">
-        <v>30</v>
+        <v>515</v>
       </c>
       <c r="F1224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1224" t="n">
         <v>1</v>
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>2830000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>60</v>
+        <v>636</v>
       </c>
       <c r="E1225" t="n">
-        <v>60</v>
+        <v>938</v>
       </c>
       <c r="F1225" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1225" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1225" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,20 +34748,20 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>15000000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E1226" t="n">
-        <v>310</v>
+        <v>160</v>
       </c>
       <c r="F1226" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1226" t="n">
         <v>4</v>
@@ -34776,17 +34776,17 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>15000000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1227" t="n">
-        <v>515</v>
+        <v>205</v>
       </c>
       <c r="F1227" t="n">
         <v>4</v>
@@ -34795,7 +34795,7 @@
         <v>4</v>
       </c>
       <c r="H1227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>40000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>636</v>
+        <v>355</v>
       </c>
       <c r="E1228" t="n">
-        <v>938</v>
+        <v>648</v>
       </c>
       <c r="F1228" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1228" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>2600000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="E1229" t="n">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="F1229" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1229" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>6750000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E1230" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="F1230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1230" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>3700000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1231" t="n">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="F1231" t="n">
         <v>4</v>
       </c>
       <c r="G1231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>10000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="E1232" t="n">
-        <v>648</v>
+        <v>231</v>
       </c>
       <c r="F1232" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>15000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="E1233" t="n">
-        <v>307</v>
+        <v>104</v>
       </c>
       <c r="F1233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>2600000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E1234" t="n">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="F1234" t="n">
         <v>2</v>
       </c>
       <c r="G1234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,23 +35000,23 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>6950000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="E1235" t="n">
-        <v>322</v>
+        <v>161</v>
       </c>
       <c r="F1235" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1235" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1235" t="n">
         <v>2</v>
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>4500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="E1236" t="n">
-        <v>231</v>
+        <v>350</v>
       </c>
       <c r="F1236" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1236" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H1236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,1146 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1237" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>135</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>582</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1238" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>209</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>1239</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>181</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>182</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>1240</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>1241</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>16000000000</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>909</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>1242</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>432</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>1243</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>10300000000</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>186</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>1950000000</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>130</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>1246</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>563</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>1248</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>1249</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1250" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1251" t="n">
         <v>4900000000</v>
       </c>
-      <c r="D1237" t="n">
-        <v>160</v>
-      </c>
-      <c r="E1237" t="n">
-        <v>104</v>
-      </c>
-      <c r="F1237" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1237" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1237" t="n">
-        <v>1</v>
+      <c r="D1251" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1252" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>283</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>1252</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1253" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>310</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>260</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>1253</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>18500000000</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>503</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>421</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>1254</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>20500000000</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>543</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>1255</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>5550000000</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>304</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+        </is>
+      </c>
+      <c r="C1257" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>64</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+        </is>
+      </c>
+      <c r="C1258" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>559</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>572</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>1258</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1259" t="n">
+        <v>16899999999</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>408</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1260" t="n">
+        <v>45000000000</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>620</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1261" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>10500000000</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>407</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>1262</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>68000000000</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>1263</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>7500000000</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>348</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>American Classic House Dalam Town House Di Kemang</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>380</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>247</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>260</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>38900000000</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>932</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>6350000000</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>230</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>752</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>1269</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>1270</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>900</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>57000000000</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>936</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>123</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>588</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>1250000000</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>70</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1277"/>
+  <dimension ref="A1:H1303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31976,26 +31976,26 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>21000000000</v>
+        <v>60600000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>700</v>
+        <v>1130</v>
       </c>
       <c r="E1127" t="n">
-        <v>960</v>
+        <v>4041</v>
       </c>
       <c r="F1127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1127" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1128">
@@ -32004,26 +32004,26 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>60600000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>1130</v>
+        <v>350</v>
       </c>
       <c r="E1128" t="n">
-        <v>4041</v>
+        <v>534</v>
       </c>
       <c r="F1128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1128" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,26 +32032,26 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>40500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="E1129" t="n">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="F1129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1130">
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>12000000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E1130" t="n">
-        <v>550</v>
+        <v>850</v>
       </c>
       <c r="F1130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,26 +32088,26 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>61000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E1131" t="n">
-        <v>850</v>
+        <v>1235</v>
       </c>
       <c r="F1131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1131" t="n">
         <v>4</v>
       </c>
       <c r="H1131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1132">
@@ -32116,26 +32116,26 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>15000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>1000</v>
+        <v>195</v>
       </c>
       <c r="E1132" t="n">
-        <v>1153</v>
+        <v>252</v>
       </c>
       <c r="F1132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1132" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1133">
@@ -32144,26 +32144,26 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
+          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>45000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1133" t="n">
-        <v>1235</v>
+        <v>379</v>
       </c>
       <c r="F1133" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,26 +32172,26 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
+          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>14000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="E1134" t="n">
-        <v>252</v>
+        <v>604</v>
       </c>
       <c r="F1134" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1135">
@@ -32200,26 +32200,26 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>12800000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E1135" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F1135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,23 +32228,23 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>21000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1136" t="n">
-        <v>379</v>
+        <v>76</v>
       </c>
       <c r="F1136" t="n">
         <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1136" t="n">
         <v>2</v>
@@ -32256,23 +32256,23 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
+          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>40000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E1137" t="n">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="F1137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1137" t="n">
         <v>4</v>
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
+          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>15000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1138" t="n">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="F1138" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1138" t="n">
         <v>3</v>
       </c>
       <c r="H1138" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>6900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1139" t="n">
-        <v>76</v>
+        <v>630</v>
       </c>
       <c r="F1139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,26 +32340,26 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>13500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1140" t="n">
-        <v>325</v>
+        <v>850</v>
       </c>
       <c r="E1140" t="n">
-        <v>696</v>
+        <v>1925</v>
       </c>
       <c r="F1140" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1140" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1140" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1141">
@@ -32368,26 +32368,26 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>27000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>301</v>
+        <v>882</v>
       </c>
       <c r="E1141" t="n">
-        <v>469</v>
+        <v>1845</v>
       </c>
       <c r="F1141" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1142">
@@ -32396,26 +32396,26 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>21000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1142" t="n">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="F1142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -32452,26 +32452,26 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>71900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>882</v>
+        <v>1100</v>
       </c>
       <c r="E1144" t="n">
-        <v>1845</v>
+        <v>540</v>
       </c>
       <c r="F1144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1144" t="n">
         <v>4</v>
       </c>
       <c r="H1144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1145">
@@ -32480,17 +32480,17 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>6500000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1145" t="n">
-        <v>140</v>
+        <v>696</v>
       </c>
       <c r="F1145" t="n">
         <v>3</v>
@@ -32499,7 +32499,7 @@
         <v>3</v>
       </c>
       <c r="H1145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,20 +32508,20 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>42000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>850</v>
+        <v>880</v>
       </c>
       <c r="E1146" t="n">
-        <v>1925</v>
+        <v>1000</v>
       </c>
       <c r="F1146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1146" t="n">
         <v>6</v>
@@ -32536,17 +32536,17 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>49000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1147" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1147" t="n">
-        <v>540</v>
+        <v>187</v>
       </c>
       <c r="F1147" t="n">
         <v>4</v>
@@ -32555,7 +32555,7 @@
         <v>4</v>
       </c>
       <c r="H1147" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1148">
@@ -32564,26 +32564,26 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>13000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="E1148" t="n">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F1148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1148" t="n">
         <v>3</v>
       </c>
       <c r="H1148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1149">
@@ -32592,26 +32592,26 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>62000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>880</v>
+        <v>500</v>
       </c>
       <c r="E1149" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="F1149" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1149" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1149" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,26 +32620,26 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>4990000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>250</v>
+        <v>1050</v>
       </c>
       <c r="E1150" t="n">
-        <v>187</v>
+        <v>627</v>
       </c>
       <c r="F1150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1151">
@@ -32648,23 +32648,23 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>13800000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E1151" t="n">
-        <v>692</v>
+        <v>350</v>
       </c>
       <c r="F1151" t="n">
         <v>5</v>
       </c>
       <c r="G1151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1151" t="n">
         <v>4</v>
@@ -32676,17 +32676,17 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>13900000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1152" t="n">
-        <v>340</v>
+        <v>696</v>
       </c>
       <c r="F1152" t="n">
         <v>3</v>
@@ -32695,7 +32695,7 @@
         <v>3</v>
       </c>
       <c r="H1152" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1153">
@@ -32704,26 +32704,26 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>44000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>1050</v>
+        <v>375</v>
       </c>
       <c r="E1153" t="n">
-        <v>627</v>
+        <v>76</v>
       </c>
       <c r="F1153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1153" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1154">
@@ -32732,26 +32732,26 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>31900000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1154" t="n">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="F1154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1154" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1155">
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>13000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1155" t="n">
-        <v>696</v>
+        <v>510</v>
       </c>
       <c r="F1155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1155" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,23 +32788,23 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>7090000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>375</v>
+        <v>64</v>
       </c>
       <c r="E1156" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F1156" t="n">
         <v>2</v>
       </c>
       <c r="G1156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1156" t="n">
         <v>1</v>
@@ -32816,23 +32816,23 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>7500000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E1157" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="F1157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1157" t="n">
         <v>1</v>
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>7300000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>600</v>
+        <v>260</v>
       </c>
       <c r="E1158" t="n">
-        <v>510</v>
+        <v>172</v>
       </c>
       <c r="F1158" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1158" t="n">
         <v>5</v>
       </c>
       <c r="H1158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,23 +32872,23 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>998000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="E1159" t="n">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="F1159" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1159" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H1159" t="n">
         <v>1</v>
@@ -32900,23 +32900,23 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>22000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>232</v>
+        <v>88</v>
       </c>
       <c r="E1160" t="n">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="F1160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1160" t="n">
         <v>1</v>
@@ -32928,26 +32928,26 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>6250000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="E1161" t="n">
-        <v>172</v>
+        <v>675</v>
       </c>
       <c r="F1161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1161" t="n">
         <v>5</v>
       </c>
       <c r="H1161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1162">
@@ -32956,26 +32956,26 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>7200000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E1162" t="n">
-        <v>196</v>
+        <v>534</v>
       </c>
       <c r="F1162" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G1162" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H1162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,23 +32984,23 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>2600000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>88</v>
+        <v>928</v>
       </c>
       <c r="E1163" t="n">
-        <v>55</v>
+        <v>378</v>
       </c>
       <c r="F1163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1163" t="n">
         <v>1</v>
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>65000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>1000</v>
+        <v>112</v>
       </c>
       <c r="E1164" t="n">
-        <v>675</v>
+        <v>70</v>
       </c>
       <c r="F1164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1164" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>23000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>375</v>
+        <v>1350</v>
       </c>
       <c r="E1165" t="n">
-        <v>534</v>
+        <v>863</v>
       </c>
       <c r="F1165" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1165" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,23 +33068,23 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>15500000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>928</v>
+        <v>280</v>
       </c>
       <c r="E1166" t="n">
-        <v>378</v>
+        <v>120</v>
       </c>
       <c r="F1166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1166" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1166" t="n">
         <v>1</v>
@@ -33096,17 +33096,17 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>2830000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E1167" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F1167" t="n">
         <v>2</v>
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>38000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="E1168" t="n">
-        <v>863</v>
+        <v>1050</v>
       </c>
       <c r="F1168" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1168" t="n">
         <v>6</v>
-      </c>
-      <c r="G1168" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1168" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,26 +33152,26 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>8800000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="E1169" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="F1169" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1169" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1170">
@@ -33180,26 +33180,26 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>2600000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="E1170" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F1170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1171">
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>68000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E1171" t="n">
-        <v>1050</v>
+        <v>304</v>
       </c>
       <c r="F1171" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1171" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1171" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,17 +33236,17 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>22000000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="E1172" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="F1172" t="n">
         <v>3</v>
@@ -33255,7 +33255,7 @@
         <v>3</v>
       </c>
       <c r="H1172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,23 +33264,23 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>4800000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="E1173" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F1173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1173" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1173" t="n">
         <v>2</v>
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>13500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E1174" t="n">
-        <v>304</v>
+        <v>1554</v>
       </c>
       <c r="F1174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1174" t="n">
         <v>5</v>
       </c>
       <c r="H1174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>14500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E1175" t="n">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="F1175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>New House Full Furnished Kemang Selatan</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>8500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>262</v>
+        <v>760</v>
       </c>
       <c r="E1176" t="n">
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="F1176" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1176" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>52500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1177" t="n">
-        <v>1554</v>
+        <v>160</v>
       </c>
       <c r="F1177" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,17 +33404,17 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>6900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>375</v>
+        <v>810</v>
       </c>
       <c r="E1178" t="n">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="F1178" t="n">
         <v>4</v>
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>New House Full Furnished Kemang Selatan</t>
+          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>38000000000</v>
+        <v>2950000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>760</v>
+        <v>200</v>
       </c>
       <c r="E1179" t="n">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="F1179" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1179" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,26 +33460,26 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>7800000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1180" t="n">
-        <v>160</v>
+        <v>351</v>
       </c>
       <c r="F1180" t="n">
         <v>4</v>
       </c>
       <c r="G1180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1181">
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>48000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>810</v>
+        <v>120</v>
       </c>
       <c r="E1181" t="n">
-        <v>370</v>
+        <v>50</v>
       </c>
       <c r="F1181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
+          <t>Brand New House Modern Design With Pool Cilandak</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>2950000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>200</v>
+        <v>428</v>
       </c>
       <c r="E1182" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F1182" t="n">
         <v>4</v>
       </c>
       <c r="G1182" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>34500000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>500</v>
+        <v>588</v>
       </c>
       <c r="E1183" t="n">
-        <v>351</v>
+        <v>866</v>
       </c>
       <c r="F1183" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1183" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>2500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E1184" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F1184" t="n">
         <v>3</v>
       </c>
       <c r="G1184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,26 +33600,26 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Brand New House Modern Design With Pool Cilandak</t>
+          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>9800000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>428</v>
+        <v>600</v>
       </c>
       <c r="E1185" t="n">
-        <v>204</v>
+        <v>650</v>
       </c>
       <c r="F1185" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1185" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1186">
@@ -33628,23 +33628,23 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
+          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>37000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>588</v>
+        <v>1115</v>
       </c>
       <c r="E1186" t="n">
-        <v>866</v>
+        <v>759</v>
       </c>
       <c r="F1186" t="n">
         <v>6</v>
       </c>
       <c r="G1186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1186" t="n">
         <v>2</v>
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>2400000000</v>
+        <v>4550000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="E1187" t="n">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="F1187" t="n">
         <v>3</v>
       </c>
       <c r="G1187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>45000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="E1188" t="n">
-        <v>650</v>
+        <v>344</v>
       </c>
       <c r="F1188" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G1188" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H1188" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
+          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>60000000000</v>
+        <v>31200000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>1115</v>
+        <v>1000</v>
       </c>
       <c r="E1189" t="n">
-        <v>759</v>
+        <v>1200</v>
       </c>
       <c r="F1189" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G1189" t="n">
         <v>6</v>
       </c>
       <c r="H1189" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
+          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>4550000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E1190" t="n">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="F1190" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1190" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>8000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>580</v>
+        <v>301</v>
       </c>
       <c r="E1191" t="n">
-        <v>344</v>
+        <v>469</v>
       </c>
       <c r="F1191" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H1191" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
+          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>31200000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>1000</v>
+        <v>616</v>
       </c>
       <c r="E1192" t="n">
-        <v>1200</v>
+        <v>383</v>
       </c>
       <c r="F1192" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G1192" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,20 +33824,20 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>3850000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>198</v>
+        <v>350</v>
       </c>
       <c r="E1193" t="n">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="F1193" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1193" t="n">
         <v>4</v>
@@ -33852,26 +33852,26 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>27000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="E1194" t="n">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="F1194" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1194" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1195">
@@ -33880,23 +33880,23 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
+          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>16000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>616</v>
+        <v>500</v>
       </c>
       <c r="E1195" t="n">
-        <v>383</v>
+        <v>1028</v>
       </c>
       <c r="F1195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1195" t="n">
         <v>2</v>
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>5500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1196" t="n">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="F1196" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>21000000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1197" t="n">
-        <v>543</v>
+        <v>793</v>
       </c>
       <c r="F1197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1197" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,17 +33964,17 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>18500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>500</v>
+        <v>559</v>
       </c>
       <c r="E1198" t="n">
-        <v>1028</v>
+        <v>572</v>
       </c>
       <c r="F1198" t="n">
         <v>5</v>
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>5550000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1199" t="n">
-        <v>304</v>
+        <v>1000</v>
       </c>
       <c r="F1199" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1199" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
+          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>15300000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="E1200" t="n">
-        <v>793</v>
+        <v>260</v>
       </c>
       <c r="F1200" t="n">
         <v>4</v>
       </c>
       <c r="G1200" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1200" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,26 +34048,26 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>24000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>559</v>
+        <v>760</v>
       </c>
       <c r="E1201" t="n">
-        <v>572</v>
+        <v>517</v>
       </c>
       <c r="F1201" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1201" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
+          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>35000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E1202" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="F1202" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1202" t="n">
         <v>4</v>
       </c>
       <c r="H1202" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>11000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E1203" t="n">
-        <v>260</v>
+        <v>497</v>
       </c>
       <c r="F1203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
+          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>38000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>760</v>
+        <v>650</v>
       </c>
       <c r="E1204" t="n">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="F1204" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1204" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
+          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>13900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1205" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F1205" t="n">
         <v>4</v>
       </c>
       <c r="G1205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,26 +34188,26 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>12500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="E1206" t="n">
-        <v>497</v>
+        <v>230</v>
       </c>
       <c r="F1206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>12500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>650</v>
+        <v>147</v>
       </c>
       <c r="E1207" t="n">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="F1207" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1207" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,17 +34244,17 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
+          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>12000000000</v>
+        <v>990000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="E1208" t="n">
-        <v>348</v>
+        <v>72</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
@@ -34263,7 +34263,7 @@
         <v>3</v>
       </c>
       <c r="H1208" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>9800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E1209" t="n">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="F1209" t="n">
         <v>4</v>
       </c>
       <c r="G1209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>3500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E1210" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="F1210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>990000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="E1211" t="n">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="F1211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,23 +34356,23 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>10000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="E1212" t="n">
-        <v>347</v>
+        <v>598</v>
       </c>
       <c r="F1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1212" t="n">
         <v>2</v>
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>1900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="E1213" t="n">
-        <v>105</v>
+        <v>260</v>
       </c>
       <c r="F1213" t="n">
         <v>4</v>
       </c>
       <c r="G1213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>15500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>340</v>
+        <v>431</v>
       </c>
       <c r="E1214" t="n">
-        <v>350</v>
+        <v>874</v>
       </c>
       <c r="F1214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1214" t="n">
         <v>4</v>
       </c>
       <c r="H1214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,20 +34440,20 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>17000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>288</v>
+        <v>440</v>
       </c>
       <c r="E1215" t="n">
-        <v>598</v>
+        <v>200</v>
       </c>
       <c r="F1215" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1215" t="n">
         <v>3</v>
@@ -34468,23 +34468,23 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>11000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="E1216" t="n">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="F1216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1216" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1216" t="n">
         <v>1</v>
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1217" t="n">
         <v>15000000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>431</v>
+        <v>240</v>
       </c>
       <c r="E1217" t="n">
-        <v>874</v>
+        <v>310</v>
       </c>
       <c r="F1217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1217" t="n">
         <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>8500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="E1218" t="n">
-        <v>202</v>
+        <v>515</v>
       </c>
       <c r="F1218" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1218" t="n">
         <v>4</v>
       </c>
       <c r="H1218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>8500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>440</v>
+        <v>636</v>
       </c>
       <c r="E1219" t="n">
-        <v>200</v>
+        <v>938</v>
       </c>
       <c r="F1219" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1219" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>8500000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="E1220" t="n">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="F1220" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1220" t="n">
         <v>4</v>
       </c>
       <c r="H1220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>76000000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1221" t="n">
-        <v>700</v>
+        <v>205</v>
       </c>
       <c r="F1221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>2600000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>135</v>
+        <v>355</v>
       </c>
       <c r="E1222" t="n">
-        <v>30</v>
+        <v>648</v>
       </c>
       <c r="F1222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1223" t="n">
         <v>15000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="E1223" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1223" t="n">
         <v>4</v>
       </c>
       <c r="H1223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>15000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E1224" t="n">
-        <v>515</v>
+        <v>113</v>
       </c>
       <c r="F1224" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1224" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>40000000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>636</v>
+        <v>400</v>
       </c>
       <c r="E1225" t="n">
-        <v>938</v>
+        <v>322</v>
       </c>
       <c r="F1225" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1225" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,23 +34748,23 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>6750000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1226" t="n">
         <v>200</v>
       </c>
       <c r="E1226" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="F1226" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1226" t="n">
         <v>1</v>
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>3700000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="E1227" t="n">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="F1227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1227" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>10000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="E1228" t="n">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="F1228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1228" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>15000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="E1229" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="F1229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1229" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1229" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>2600000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="E1230" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="F1230" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1230" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>6950000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="E1231" t="n">
-        <v>322</v>
+        <v>909</v>
       </c>
       <c r="F1231" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1231" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1231" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>4500000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>200</v>
+        <v>432</v>
       </c>
       <c r="E1232" t="n">
-        <v>231</v>
+        <v>600</v>
       </c>
       <c r="F1232" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G1232" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>4900000000</v>
+        <v>10300000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="E1233" t="n">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="F1233" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1233" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1233" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,23 +34972,23 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>7090000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="E1234" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="F1234" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1234" t="n">
         <v>1</v>
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>8500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="E1235" t="n">
-        <v>161</v>
+        <v>563</v>
       </c>
       <c r="F1235" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1235" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H1235" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>15500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>340</v>
+        <v>193</v>
       </c>
       <c r="E1236" t="n">
-        <v>350</v>
+        <v>283</v>
       </c>
       <c r="F1236" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1236" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1236" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,23 +35056,23 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>2500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>135</v>
+        <v>310</v>
       </c>
       <c r="E1237" t="n">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="F1237" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G1237" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1237" t="n">
         <v>1</v>
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>400</v>
+        <v>503</v>
       </c>
       <c r="E1238" t="n">
-        <v>582</v>
+        <v>421</v>
       </c>
       <c r="F1238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1238" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>12900000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1239" t="n">
-        <v>209</v>
+        <v>543</v>
       </c>
       <c r="F1239" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1239" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H1239" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,20 +35140,20 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>4000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="E1240" t="n">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="F1240" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1240" t="n">
         <v>31</v>
@@ -35168,23 +35168,23 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>2600000000</v>
+        <v>1050000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1241" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F1241" t="n">
         <v>2</v>
       </c>
       <c r="G1241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1241" t="n">
         <v>1</v>
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>16000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>320</v>
+        <v>559</v>
       </c>
       <c r="E1242" t="n">
-        <v>909</v>
+        <v>572</v>
       </c>
       <c r="F1242" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G1242" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H1242" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>28000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1243" t="n">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="E1243" t="n">
-        <v>600</v>
+        <v>408</v>
       </c>
       <c r="F1243" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1243" t="n">
         <v>31</v>
       </c>
       <c r="H1243" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>10300000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E1244" t="n">
-        <v>186</v>
+        <v>620</v>
       </c>
       <c r="F1244" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1244" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1244" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>2600000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>60</v>
+        <v>850</v>
       </c>
       <c r="E1245" t="n">
-        <v>60</v>
+        <v>1925</v>
       </c>
       <c r="F1245" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G1245" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H1245" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>1950000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="E1246" t="n">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="F1246" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1246" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1246" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>55000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="E1247" t="n">
-        <v>563</v>
+        <v>1050</v>
       </c>
       <c r="F1247" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="G1247" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="H1247" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>2000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>85</v>
+        <v>325</v>
       </c>
       <c r="E1248" t="n">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="F1248" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1248" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1248" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>American Classic House Dalam Town House Di Kemang</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>2830000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="E1249" t="n">
-        <v>60</v>
+        <v>247</v>
       </c>
       <c r="F1249" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1249" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1249" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>2000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E1250" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="F1250" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1250" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1250" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>4900000000</v>
+        <v>38900000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>360</v>
+        <v>650</v>
       </c>
       <c r="E1251" t="n">
-        <v>127</v>
+        <v>932</v>
       </c>
       <c r="F1251" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1251" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="H1251" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>22500000000</v>
+        <v>6350000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="E1252" t="n">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="F1252" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1252" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>11000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="E1253" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="F1253" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G1253" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H1253" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>18500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>503</v>
+        <v>800</v>
       </c>
       <c r="E1254" t="n">
-        <v>421</v>
+        <v>1335</v>
       </c>
       <c r="F1254" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1254" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1254" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>20500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E1255" t="n">
-        <v>543</v>
+        <v>1098</v>
       </c>
       <c r="F1255" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="G1255" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H1255" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>5550000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="E1256" t="n">
-        <v>304</v>
+        <v>936</v>
       </c>
       <c r="F1256" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1256" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1256" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,17 +35616,17 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>1050000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="E1257" t="n">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F1257" t="n">
         <v>2</v>
@@ -35635,7 +35635,7 @@
         <v>2</v>
       </c>
       <c r="H1257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,23 +35644,23 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>24000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>559</v>
+        <v>400</v>
       </c>
       <c r="E1258" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="F1258" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1258" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1258" t="n">
         <v>22</v>
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>16899999999</v>
+        <v>1250000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="E1259" t="n">
-        <v>408</v>
+        <v>87</v>
       </c>
       <c r="F1259" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1259" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1259" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>45000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="E1260" t="n">
-        <v>620</v>
+        <v>60</v>
       </c>
       <c r="F1260" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1260" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1260" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>42000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>850</v>
+        <v>262</v>
       </c>
       <c r="E1261" t="n">
-        <v>1925</v>
+        <v>161</v>
       </c>
       <c r="F1261" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G1261" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H1261" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>10500000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1262" t="n">
-        <v>407</v>
+        <v>1980</v>
       </c>
       <c r="F1262" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G1262" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H1262" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>68000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="E1263" t="n">
-        <v>1050</v>
+        <v>515</v>
       </c>
       <c r="F1263" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="G1263" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="H1263" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>7500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>325</v>
+        <v>135</v>
       </c>
       <c r="E1264" t="n">
-        <v>348</v>
+        <v>30</v>
       </c>
       <c r="F1264" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1264" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1264" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>American Classic House Dalam Town House Di Kemang</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>8500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="E1265" t="n">
-        <v>247</v>
+        <v>350</v>
       </c>
       <c r="F1265" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1265" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1265" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>7000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1266" t="n">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="F1266" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1266" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1266" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>38900000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="E1267" t="n">
-        <v>932</v>
+        <v>60</v>
       </c>
       <c r="F1267" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1267" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H1267" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>6350000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E1268" t="n">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="F1268" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1268" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1268" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,23 +35952,23 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>13500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>230</v>
+        <v>440</v>
       </c>
       <c r="E1269" t="n">
-        <v>752</v>
+        <v>202</v>
       </c>
       <c r="F1269" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G1269" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1269" t="n">
         <v>22</v>
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>13500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>200</v>
+        <v>440</v>
       </c>
       <c r="E1270" t="n">
-        <v>500</v>
+        <v>202</v>
       </c>
       <c r="F1270" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1270" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1270" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>10000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E1271" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1271" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1271" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>27000000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1272" t="n">
         <v>800</v>
       </c>
       <c r="E1272" t="n">
-        <v>1335</v>
+        <v>700</v>
       </c>
       <c r="F1272" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1272" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>20000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>900</v>
+        <v>1280</v>
       </c>
       <c r="E1273" t="n">
-        <v>1098</v>
+        <v>600</v>
       </c>
       <c r="F1273" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="G1273" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H1273" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>57000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="E1274" t="n">
-        <v>936</v>
+        <v>165</v>
       </c>
       <c r="F1274" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1274" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1274" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>2900000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1275" t="n">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="F1275" t="n">
         <v>2</v>
       </c>
       <c r="G1275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>11500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="E1276" t="n">
-        <v>588</v>
+        <v>60</v>
       </c>
       <c r="F1276" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1276" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1276" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,754 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>1250000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>70</v>
+        <v>325</v>
       </c>
       <c r="E1277" t="n">
-        <v>87</v>
+        <v>340</v>
       </c>
       <c r="F1277" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1277" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1277" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1278" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>703</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>130</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>72</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>18500000000</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>317</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>419</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>2450000000</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>285</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>177</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>230</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>752</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>23000000000</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>23000000000</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>174</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>1420000000</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>35800000000</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>185000000000</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>61000000000</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>900</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>850</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>21000000000</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>960</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>584</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>182</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>49000000000</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>1153</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1303"/>
+  <dimension ref="A1:H1330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30968,23 +30968,23 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>3000000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1091" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="E1091" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F1091" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1091" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1091" t="n">
         <v>2</v>
@@ -30996,23 +30996,23 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>1800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1092" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E1092" t="n">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="F1092" t="n">
         <v>4</v>
       </c>
       <c r="G1092" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1092" t="n">
         <v>2</v>
@@ -31024,20 +31024,20 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
+          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2400000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1093" t="n">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="E1093" t="n">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="F1093" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1093" t="n">
         <v>4</v>
@@ -31052,23 +31052,23 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
+          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>3850000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1094" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E1094" t="n">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="F1094" t="n">
         <v>5</v>
       </c>
       <c r="G1094" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1094" t="n">
         <v>2</v>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
+          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -31090,7 +31090,7 @@
         <v>180</v>
       </c>
       <c r="E1095" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1095" t="n">
         <v>5</v>
@@ -31108,7 +31108,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
+          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -31136,20 +31136,20 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
+          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>3950000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1097" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E1097" t="n">
-        <v>162</v>
+        <v>446</v>
       </c>
       <c r="F1097" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1097" t="n">
         <v>3</v>
@@ -31164,26 +31164,26 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
+          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>11500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1098" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1098" t="n">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="F1098" t="n">
         <v>4</v>
       </c>
       <c r="G1098" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1098" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1099">
@@ -31192,26 +31192,26 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
+          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>9500000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1099" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E1099" t="n">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="F1099" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1099" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1099" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1100">
@@ -31220,26 +31220,26 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
+          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>35000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1100" t="n">
-        <v>650</v>
+        <v>274</v>
       </c>
       <c r="E1100" t="n">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="F1100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1101">
@@ -31248,26 +31248,26 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>30000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1101" t="n">
-        <v>274</v>
+        <v>1374</v>
       </c>
       <c r="E1101" t="n">
-        <v>448</v>
+        <v>1493</v>
       </c>
       <c r="F1101" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1101" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H1101" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1102">
@@ -31276,26 +31276,26 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
+          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>26000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1102" t="n">
-        <v>1374</v>
+        <v>467</v>
       </c>
       <c r="E1102" t="n">
-        <v>1493</v>
+        <v>899</v>
       </c>
       <c r="F1102" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G1102" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H1102" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1103">
@@ -31304,26 +31304,26 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
+          <t>Rumah Mewah Baru di Jagakarsa</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>18000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1103" t="n">
-        <v>467</v>
+        <v>520</v>
       </c>
       <c r="E1103" t="n">
-        <v>899</v>
+        <v>720</v>
       </c>
       <c r="F1103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1104">
@@ -31332,26 +31332,26 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Rumah Mewah Baru di Jagakarsa</t>
+          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>12500000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1104" t="n">
-        <v>520</v>
+        <v>150</v>
       </c>
       <c r="E1104" t="n">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="F1104" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1104" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1105">
@@ -31360,26 +31360,26 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
+          <t>Dijual Bawah Njop Kemang Rp 13.3juta/m2 Luas 2028m2 Bebas Banjir</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>13000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1105" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="E1105" t="n">
-        <v>300</v>
+        <v>2028</v>
       </c>
       <c r="F1105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1106">
@@ -31388,26 +31388,26 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Dijual Bawah Njop Kemang Rp 13.3juta/m2 Luas 2028m2 Bebas Banjir</t>
+          <t>Baru Akses Jalan Utama Khafi 1 Siap Huni Tanah Luas Free Canopy Bata Merah</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>27000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1106" t="n">
-        <v>550</v>
+        <v>185</v>
       </c>
       <c r="E1106" t="n">
-        <v>2028</v>
+        <v>128</v>
       </c>
       <c r="F1106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1106" t="n">
         <v>4</v>
       </c>
       <c r="H1106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1107">
@@ -31416,26 +31416,26 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Baru Akses Jalan Utama Khafi 1 Siap Huni Tanah Luas Free Canopy Bata Merah</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>2500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1107" t="n">
-        <v>185</v>
+        <v>430</v>
       </c>
       <c r="E1107" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F1107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1108">
@@ -31444,17 +31444,17 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>8000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1108" t="n">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="E1108" t="n">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="F1108" t="n">
         <v>5</v>
@@ -31463,7 +31463,7 @@
         <v>5</v>
       </c>
       <c r="H1108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1109">
@@ -31472,26 +31472,26 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>5500000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1109" t="n">
-        <v>320</v>
+        <v>850</v>
       </c>
       <c r="E1109" t="n">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="F1109" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1110">
@@ -31500,26 +31500,26 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>14000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1110" t="n">
-        <v>850</v>
+        <v>258</v>
       </c>
       <c r="E1110" t="n">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="F1110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1110" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1111">
@@ -31528,26 +31528,26 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>4800000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1111" t="n">
-        <v>258</v>
+        <v>409</v>
       </c>
       <c r="E1111" t="n">
-        <v>108</v>
+        <v>520</v>
       </c>
       <c r="F1111" t="n">
         <v>5</v>
       </c>
       <c r="G1111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1112">
@@ -31556,26 +31556,26 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
+          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>19000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1112" t="n">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="E1112" t="n">
-        <v>520</v>
+        <v>202</v>
       </c>
       <c r="F1112" t="n">
         <v>5</v>
       </c>
       <c r="G1112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1113">
@@ -31584,26 +31584,26 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>9000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1113" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="E1113" t="n">
-        <v>202</v>
+        <v>620</v>
       </c>
       <c r="F1113" t="n">
         <v>5</v>
       </c>
       <c r="G1113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1114">
@@ -31612,26 +31612,26 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
+          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>45000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1114" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E1114" t="n">
-        <v>620</v>
+        <v>1050</v>
       </c>
       <c r="F1114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1115">
@@ -31640,26 +31640,26 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>68000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1115" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="E1115" t="n">
-        <v>1050</v>
+        <v>768</v>
       </c>
       <c r="F1115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1116">
@@ -31668,23 +31668,23 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
+          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>32000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1116" t="n">
-        <v>825</v>
+        <v>380</v>
       </c>
       <c r="E1116" t="n">
-        <v>768</v>
+        <v>300</v>
       </c>
       <c r="F1116" t="n">
         <v>6</v>
       </c>
       <c r="G1116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1116" t="n">
         <v>2</v>
@@ -31696,26 +31696,26 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
+          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>14000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1117" t="n">
-        <v>380</v>
+        <v>850</v>
       </c>
       <c r="E1117" t="n">
-        <v>300</v>
+        <v>1925</v>
       </c>
       <c r="F1117" t="n">
         <v>6</v>
       </c>
       <c r="G1117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1118">
@@ -31724,26 +31724,26 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
+          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>42000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1118" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="E1118" t="n">
-        <v>1925</v>
+        <v>1000</v>
       </c>
       <c r="F1118" t="n">
         <v>6</v>
       </c>
       <c r="G1118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H1118" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1119">
@@ -31752,26 +31752,26 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>6900000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1119" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="E1119" t="n">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="F1119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1119" t="n">
         <v>4</v>
       </c>
       <c r="H1119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1120">
@@ -31780,26 +31780,26 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>45000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1120" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1120" t="n">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="F1120" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1120" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H1120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1121">
@@ -31808,23 +31808,23 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>15800000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1121" t="n">
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="E1121" t="n">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="F1121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1121" t="n">
         <v>1</v>
@@ -31836,17 +31836,17 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>17000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1122" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E1122" t="n">
-        <v>1070</v>
+        <v>1250</v>
       </c>
       <c r="F1122" t="n">
         <v>4</v>
@@ -31855,7 +31855,7 @@
         <v>3</v>
       </c>
       <c r="H1122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1123">
@@ -31864,26 +31864,26 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
+          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>9700000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1123" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="E1123" t="n">
-        <v>216</v>
+        <v>467</v>
       </c>
       <c r="F1123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1124">
@@ -31892,26 +31892,26 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>23000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1124" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="E1124" t="n">
-        <v>1250</v>
+        <v>620</v>
       </c>
       <c r="F1124" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G1124" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H1124" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1125">
@@ -31920,26 +31920,26 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
+          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>12000000000</v>
+        <v>60600000000</v>
       </c>
       <c r="D1125" t="n">
-        <v>580</v>
+        <v>1130</v>
       </c>
       <c r="E1125" t="n">
-        <v>467</v>
+        <v>4041</v>
       </c>
       <c r="F1125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1125" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1126">
@@ -31948,26 +31948,26 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>42000000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1126" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1126" t="n">
-        <v>620</v>
+        <v>534</v>
       </c>
       <c r="F1126" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G1126" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H1126" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1127">
@@ -31976,26 +31976,26 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>60600000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>1130</v>
+        <v>600</v>
       </c>
       <c r="E1127" t="n">
-        <v>4041</v>
+        <v>550</v>
       </c>
       <c r="F1127" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1128">
@@ -32004,26 +32004,26 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>40500000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="E1128" t="n">
-        <v>534</v>
+        <v>850</v>
       </c>
       <c r="F1128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,26 +32032,26 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>12000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1129" t="n">
-        <v>550</v>
+        <v>1235</v>
       </c>
       <c r="F1129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1130">
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>61000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>900</v>
+        <v>195</v>
       </c>
       <c r="E1130" t="n">
-        <v>850</v>
+        <v>252</v>
       </c>
       <c r="F1130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,26 +32088,26 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
+          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>45000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1131" t="n">
-        <v>1235</v>
+        <v>379</v>
       </c>
       <c r="F1131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1132">
@@ -32116,26 +32116,26 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
+          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>14000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="E1132" t="n">
-        <v>252</v>
+        <v>604</v>
       </c>
       <c r="F1132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1133">
@@ -32144,17 +32144,17 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
+          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>21000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1133" t="n">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="F1133" t="n">
         <v>4</v>
@@ -32163,7 +32163,7 @@
         <v>3</v>
       </c>
       <c r="H1133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,23 +32172,23 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
+          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>40000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E1134" t="n">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="F1134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1134" t="n">
         <v>4</v>
@@ -32200,26 +32200,26 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
+          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>15000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1135" t="n">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="F1135" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1135" t="n">
         <v>3</v>
       </c>
       <c r="H1135" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,26 +32228,26 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>6900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1136" t="n">
-        <v>76</v>
+        <v>630</v>
       </c>
       <c r="F1136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1137">
@@ -32256,26 +32256,26 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>13500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>325</v>
+        <v>850</v>
       </c>
       <c r="E1137" t="n">
-        <v>696</v>
+        <v>1925</v>
       </c>
       <c r="F1137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1137" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1138">
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>27000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>301</v>
+        <v>882</v>
       </c>
       <c r="E1138" t="n">
-        <v>469</v>
+        <v>1845</v>
       </c>
       <c r="F1138" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>21000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1139" t="n">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="F1139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,7 +32340,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -32368,26 +32368,26 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>71900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>882</v>
+        <v>1100</v>
       </c>
       <c r="E1141" t="n">
-        <v>1845</v>
+        <v>540</v>
       </c>
       <c r="F1141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1141" t="n">
         <v>4</v>
       </c>
       <c r="H1141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1142">
@@ -32396,17 +32396,17 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>6500000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1142" t="n">
-        <v>140</v>
+        <v>696</v>
       </c>
       <c r="F1142" t="n">
         <v>3</v>
@@ -32415,7 +32415,7 @@
         <v>3</v>
       </c>
       <c r="H1142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,20 +32424,20 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>42000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1143" t="n">
-        <v>850</v>
+        <v>880</v>
       </c>
       <c r="E1143" t="n">
-        <v>1925</v>
+        <v>1000</v>
       </c>
       <c r="F1143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1143" t="n">
         <v>6</v>
@@ -32452,17 +32452,17 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>49000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1144" t="n">
-        <v>540</v>
+        <v>187</v>
       </c>
       <c r="F1144" t="n">
         <v>4</v>
@@ -32471,7 +32471,7 @@
         <v>4</v>
       </c>
       <c r="H1144" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1145">
@@ -32480,26 +32480,26 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>13000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="E1145" t="n">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F1145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1145" t="n">
         <v>3</v>
       </c>
       <c r="H1145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,26 +32508,26 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>62000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>880</v>
+        <v>500</v>
       </c>
       <c r="E1146" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="F1146" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1146" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1147">
@@ -32536,26 +32536,26 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>4990000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1147" t="n">
-        <v>250</v>
+        <v>1050</v>
       </c>
       <c r="E1147" t="n">
-        <v>187</v>
+        <v>627</v>
       </c>
       <c r="F1147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1147" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1148">
@@ -32564,23 +32564,23 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>13800000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E1148" t="n">
-        <v>692</v>
+        <v>350</v>
       </c>
       <c r="F1148" t="n">
         <v>5</v>
       </c>
       <c r="G1148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1148" t="n">
         <v>4</v>
@@ -32592,17 +32592,17 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>13900000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1149" t="n">
-        <v>340</v>
+        <v>696</v>
       </c>
       <c r="F1149" t="n">
         <v>3</v>
@@ -32611,7 +32611,7 @@
         <v>3</v>
       </c>
       <c r="H1149" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,26 +32620,26 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>44000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>1050</v>
+        <v>375</v>
       </c>
       <c r="E1150" t="n">
-        <v>627</v>
+        <v>76</v>
       </c>
       <c r="F1150" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1150" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1151">
@@ -32648,26 +32648,26 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>31900000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1151" t="n">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="F1151" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1152">
@@ -32676,26 +32676,26 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>13000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1152" t="n">
-        <v>696</v>
+        <v>510</v>
       </c>
       <c r="F1152" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1153">
@@ -32704,23 +32704,23 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>7090000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>375</v>
+        <v>64</v>
       </c>
       <c r="E1153" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F1153" t="n">
         <v>2</v>
       </c>
       <c r="G1153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1153" t="n">
         <v>1</v>
@@ -32732,23 +32732,23 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>7500000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E1154" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="F1154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1154" t="n">
         <v>1</v>
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>7300000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>600</v>
+        <v>260</v>
       </c>
       <c r="E1155" t="n">
-        <v>510</v>
+        <v>172</v>
       </c>
       <c r="F1155" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1155" t="n">
         <v>5</v>
       </c>
       <c r="H1155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,23 +32788,23 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>998000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>64</v>
+        <v>380</v>
       </c>
       <c r="E1156" t="n">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="F1156" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1156" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H1156" t="n">
         <v>1</v>
@@ -32816,23 +32816,23 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>22000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>232</v>
+        <v>88</v>
       </c>
       <c r="E1157" t="n">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="F1157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1157" t="n">
         <v>1</v>
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>6250000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="E1158" t="n">
-        <v>172</v>
+        <v>675</v>
       </c>
       <c r="F1158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1158" t="n">
         <v>5</v>
       </c>
       <c r="H1158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>7200000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E1159" t="n">
-        <v>196</v>
+        <v>534</v>
       </c>
       <c r="F1159" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G1159" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H1159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1160">
@@ -32900,23 +32900,23 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>2600000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>88</v>
+        <v>928</v>
       </c>
       <c r="E1160" t="n">
-        <v>55</v>
+        <v>378</v>
       </c>
       <c r="F1160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1160" t="n">
         <v>1</v>
@@ -32928,26 +32928,26 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>65000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>1000</v>
+        <v>112</v>
       </c>
       <c r="E1161" t="n">
-        <v>675</v>
+        <v>70</v>
       </c>
       <c r="F1161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1162">
@@ -32956,26 +32956,26 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>23000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>375</v>
+        <v>1350</v>
       </c>
       <c r="E1162" t="n">
-        <v>534</v>
+        <v>863</v>
       </c>
       <c r="F1162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1162" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,23 +32984,23 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>15500000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>928</v>
+        <v>280</v>
       </c>
       <c r="E1163" t="n">
-        <v>378</v>
+        <v>120</v>
       </c>
       <c r="F1163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1163" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1163" t="n">
         <v>1</v>
@@ -33012,17 +33012,17 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>2830000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E1164" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F1164" t="n">
         <v>2</v>
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>38000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="E1165" t="n">
-        <v>863</v>
+        <v>1050</v>
       </c>
       <c r="F1165" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1165" t="n">
         <v>6</v>
-      </c>
-      <c r="G1165" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1165" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,26 +33068,26 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>8800000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="E1166" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="F1166" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1166" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1167">
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>2600000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="E1167" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F1167" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>68000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E1168" t="n">
-        <v>1050</v>
+        <v>304</v>
       </c>
       <c r="F1168" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1168" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1168" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,17 +33152,17 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>22000000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="E1169" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="F1169" t="n">
         <v>3</v>
@@ -33171,7 +33171,7 @@
         <v>3</v>
       </c>
       <c r="H1169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1170">
@@ -33180,23 +33180,23 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>4800000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="E1170" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F1170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1170" t="n">
         <v>2</v>
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>13500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E1171" t="n">
-        <v>304</v>
+        <v>1554</v>
       </c>
       <c r="F1171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1171" t="n">
         <v>5</v>
       </c>
       <c r="H1171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,26 +33236,26 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>14500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E1172" t="n">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="F1172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,26 +33264,26 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>New House Full Furnished Kemang Selatan</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>8500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>262</v>
+        <v>760</v>
       </c>
       <c r="E1173" t="n">
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="F1173" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1173" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>52500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1174" t="n">
-        <v>1554</v>
+        <v>160</v>
       </c>
       <c r="F1174" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1174" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,17 +33320,17 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>6900000000</v>
+        <v>2950000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1175" t="n">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="F1175" t="n">
         <v>4</v>
@@ -33339,7 +33339,7 @@
         <v>4</v>
       </c>
       <c r="H1175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>New House Full Furnished Kemang Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>38000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>760</v>
+        <v>500</v>
       </c>
       <c r="E1176" t="n">
-        <v>518</v>
+        <v>351</v>
       </c>
       <c r="F1176" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1176" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H1176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
+          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>7800000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E1177" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="F1177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Brand New House Modern Design With Pool Cilandak</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>48000000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>810</v>
+        <v>428</v>
       </c>
       <c r="E1178" t="n">
-        <v>370</v>
+        <v>204</v>
       </c>
       <c r="F1178" t="n">
         <v>4</v>
       </c>
       <c r="G1178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1178" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
+          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>2950000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>200</v>
+        <v>588</v>
       </c>
       <c r="E1179" t="n">
-        <v>172</v>
+        <v>866</v>
       </c>
       <c r="F1179" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,26 +33460,26 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>34500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="E1180" t="n">
-        <v>351</v>
+        <v>105</v>
       </c>
       <c r="F1180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1181">
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
+          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>2500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="E1181" t="n">
-        <v>50</v>
+        <v>650</v>
       </c>
       <c r="F1181" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1181" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1181" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Brand New House Modern Design With Pool Cilandak</t>
+          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>9800000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>428</v>
+        <v>1115</v>
       </c>
       <c r="E1182" t="n">
-        <v>204</v>
+        <v>759</v>
       </c>
       <c r="F1182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1182" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
+          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>37000000000</v>
+        <v>4550000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>588</v>
+        <v>100</v>
       </c>
       <c r="E1183" t="n">
-        <v>866</v>
+        <v>197</v>
       </c>
       <c r="F1183" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1183" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>2400000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="E1184" t="n">
-        <v>105</v>
+        <v>344</v>
       </c>
       <c r="F1184" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G1184" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H1184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,26 +33600,26 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
+          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>45000000000</v>
+        <v>31200000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E1185" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F1185" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G1185" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1186">
@@ -33628,23 +33628,23 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
+          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>60000000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>1115</v>
+        <v>198</v>
       </c>
       <c r="E1186" t="n">
-        <v>759</v>
+        <v>105</v>
       </c>
       <c r="F1186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1186" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1186" t="n">
         <v>2</v>
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>4550000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="E1187" t="n">
-        <v>197</v>
+        <v>469</v>
       </c>
       <c r="F1187" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1187" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>8000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="E1188" t="n">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="F1188" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G1188" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H1188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>31200000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="E1189" t="n">
-        <v>1200</v>
+        <v>272</v>
       </c>
       <c r="F1189" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G1189" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,23 +33740,23 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>3850000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>198</v>
+        <v>400</v>
       </c>
       <c r="E1190" t="n">
-        <v>105</v>
+        <v>543</v>
       </c>
       <c r="F1190" t="n">
         <v>5</v>
       </c>
       <c r="G1190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1190" t="n">
         <v>2</v>
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>27000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>301</v>
+        <v>500</v>
       </c>
       <c r="E1191" t="n">
-        <v>469</v>
+        <v>1028</v>
       </c>
       <c r="F1191" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1191" t="n">
         <v>4</v>
       </c>
       <c r="H1191" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,17 +33796,17 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>16000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>616</v>
+        <v>250</v>
       </c>
       <c r="E1192" t="n">
-        <v>383</v>
+        <v>304</v>
       </c>
       <c r="F1192" t="n">
         <v>4</v>
@@ -33815,7 +33815,7 @@
         <v>3</v>
       </c>
       <c r="H1192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>5500000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1193" t="n">
         <v>350</v>
       </c>
       <c r="E1193" t="n">
-        <v>272</v>
+        <v>793</v>
       </c>
       <c r="F1193" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1193" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1193" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,23 +33852,23 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>21000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>400</v>
+        <v>559</v>
       </c>
       <c r="E1194" t="n">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="F1194" t="n">
         <v>5</v>
       </c>
       <c r="G1194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1194" t="n">
         <v>2</v>
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>18500000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="E1195" t="n">
-        <v>1028</v>
+        <v>1000</v>
       </c>
       <c r="F1195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1195" t="n">
         <v>4</v>
       </c>
       <c r="H1195" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>5550000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="E1196" t="n">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="F1196" t="n">
         <v>4</v>
       </c>
       <c r="G1196" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
+          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>15300000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>350</v>
+        <v>760</v>
       </c>
       <c r="E1197" t="n">
-        <v>793</v>
+        <v>517</v>
       </c>
       <c r="F1197" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1197" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>24000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>559</v>
+        <v>500</v>
       </c>
       <c r="E1198" t="n">
-        <v>572</v>
+        <v>340</v>
       </c>
       <c r="F1198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1198" t="n">
         <v>4</v>
       </c>
       <c r="H1198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>35000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>1100</v>
+        <v>318</v>
       </c>
       <c r="E1199" t="n">
-        <v>1000</v>
+        <v>497</v>
       </c>
       <c r="F1199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1199" t="n">
         <v>4</v>
       </c>
       <c r="H1199" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
+          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>11000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>310</v>
+        <v>650</v>
       </c>
       <c r="E1200" t="n">
-        <v>260</v>
+        <v>544</v>
       </c>
       <c r="F1200" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,26 +34048,26 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
+          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>38000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>760</v>
+        <v>250</v>
       </c>
       <c r="E1201" t="n">
-        <v>517</v>
+        <v>348</v>
       </c>
       <c r="F1201" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1201" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,23 +34076,23 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>13900000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="E1202" t="n">
-        <v>340</v>
+        <v>230</v>
       </c>
       <c r="F1202" t="n">
         <v>4</v>
       </c>
       <c r="G1202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1202" t="n">
         <v>1</v>
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>12500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="E1203" t="n">
-        <v>497</v>
+        <v>66</v>
       </c>
       <c r="F1203" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,23 +34132,23 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
+          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>12500000000</v>
+        <v>990000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>650</v>
+        <v>125</v>
       </c>
       <c r="E1204" t="n">
-        <v>544</v>
+        <v>72</v>
       </c>
       <c r="F1204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1204" t="n">
         <v>2</v>
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
+          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>12000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1205" t="n">
         <v>250</v>
       </c>
       <c r="E1205" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F1205" t="n">
         <v>4</v>
       </c>
       <c r="G1205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1205" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,26 +34188,26 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>9800000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="E1206" t="n">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="F1206" t="n">
         <v>4</v>
       </c>
       <c r="G1206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>3500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>147</v>
+        <v>340</v>
       </c>
       <c r="E1207" t="n">
-        <v>66</v>
+        <v>350</v>
       </c>
       <c r="F1207" t="n">
         <v>3</v>
       </c>
       <c r="G1207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,20 +34244,20 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>990000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>125</v>
+        <v>288</v>
       </c>
       <c r="E1208" t="n">
-        <v>72</v>
+        <v>598</v>
       </c>
       <c r="F1208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1208" t="n">
         <v>3</v>
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>10000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="E1209" t="n">
-        <v>347</v>
+        <v>260</v>
       </c>
       <c r="F1209" t="n">
         <v>4</v>
       </c>
       <c r="G1209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,17 +34300,17 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>1900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>150</v>
+        <v>431</v>
       </c>
       <c r="E1210" t="n">
-        <v>105</v>
+        <v>874</v>
       </c>
       <c r="F1210" t="n">
         <v>4</v>
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>15500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E1211" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="F1211" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,17 +34356,17 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>17000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="E1212" t="n">
-        <v>598</v>
+        <v>30</v>
       </c>
       <c r="F1212" t="n">
         <v>3</v>
@@ -34375,7 +34375,7 @@
         <v>3</v>
       </c>
       <c r="H1212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,23 +34384,23 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>11000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1213" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1213" t="n">
         <v>310</v>
       </c>
-      <c r="E1213" t="n">
-        <v>260</v>
-      </c>
       <c r="F1213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1213" t="n">
         <v>1</v>
@@ -34412,17 +34412,17 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1214" t="n">
         <v>15000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="E1214" t="n">
-        <v>874</v>
+        <v>515</v>
       </c>
       <c r="F1214" t="n">
         <v>4</v>
@@ -34431,7 +34431,7 @@
         <v>4</v>
       </c>
       <c r="H1214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>8500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>440</v>
+        <v>636</v>
       </c>
       <c r="E1215" t="n">
-        <v>200</v>
+        <v>938</v>
       </c>
       <c r="F1215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1215" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1215" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,23 +34468,23 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>2600000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="E1216" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F1216" t="n">
         <v>3</v>
       </c>
       <c r="G1216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1216" t="n">
         <v>1</v>
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>15000000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E1217" t="n">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="F1217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1217" t="n">
         <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,17 +34524,17 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="E1218" t="n">
-        <v>515</v>
+        <v>648</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
@@ -34543,7 +34543,7 @@
         <v>4</v>
       </c>
       <c r="H1218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>40000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="E1219" t="n">
-        <v>938</v>
+        <v>307</v>
       </c>
       <c r="F1219" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1219" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>6750000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E1220" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="F1220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1220" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>3700000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1221" t="n">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="F1221" t="n">
         <v>4</v>
       </c>
       <c r="G1221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>10000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="E1222" t="n">
-        <v>648</v>
+        <v>231</v>
       </c>
       <c r="F1222" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>15000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="E1223" t="n">
-        <v>307</v>
+        <v>104</v>
       </c>
       <c r="F1223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>2600000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E1224" t="n">
-        <v>113</v>
+        <v>582</v>
       </c>
       <c r="F1224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1224" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>6950000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E1225" t="n">
-        <v>322</v>
+        <v>209</v>
       </c>
       <c r="F1225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1225" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1225" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,23 +34748,23 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>4500000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E1226" t="n">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="F1226" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G1226" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1226" t="n">
         <v>1</v>
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>4900000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="E1227" t="n">
-        <v>104</v>
+        <v>909</v>
       </c>
       <c r="F1227" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1227" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1227" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>32000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="E1228" t="n">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="F1228" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1228" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1228" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>12900000000</v>
+        <v>10300000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>450</v>
+        <v>1</v>
       </c>
       <c r="E1229" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="F1229" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1229" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1229" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,23 +34860,23 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>4000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="E1230" t="n">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="F1230" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1230" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1230" t="n">
         <v>1</v>
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>16000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="E1231" t="n">
-        <v>909</v>
+        <v>563</v>
       </c>
       <c r="F1231" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G1231" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H1231" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>28000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>432</v>
+        <v>193</v>
       </c>
       <c r="E1232" t="n">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="F1232" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1232" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,23 +34944,23 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>10300000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E1233" t="n">
-        <v>186</v>
+        <v>543</v>
       </c>
       <c r="F1233" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1233" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1233" t="n">
         <v>12</v>
@@ -34972,23 +34972,23 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>1950000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="E1234" t="n">
-        <v>93</v>
+        <v>304</v>
       </c>
       <c r="F1234" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1234" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1234" t="n">
         <v>1</v>
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>55000000000</v>
+        <v>1050000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>400</v>
+        <v>64</v>
       </c>
       <c r="E1235" t="n">
-        <v>563</v>
+        <v>32</v>
       </c>
       <c r="F1235" t="n">
         <v>2</v>
       </c>
       <c r="G1235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1235" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>22500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>193</v>
+        <v>559</v>
       </c>
       <c r="E1236" t="n">
-        <v>283</v>
+        <v>572</v>
       </c>
       <c r="F1236" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1236" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1236" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>11000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1237" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="E1237" t="n">
-        <v>260</v>
+        <v>408</v>
       </c>
       <c r="F1237" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G1237" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1237" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>18500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>503</v>
+        <v>1000</v>
       </c>
       <c r="E1238" t="n">
-        <v>421</v>
+        <v>620</v>
       </c>
       <c r="F1238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1238" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>20500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1239" t="n">
-        <v>543</v>
+        <v>1925</v>
       </c>
       <c r="F1239" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G1239" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H1239" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>5550000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1240" t="n">
-        <v>304</v>
+        <v>407</v>
       </c>
       <c r="F1240" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G1240" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1240" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>1050000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>64</v>
+        <v>1600</v>
       </c>
       <c r="E1241" t="n">
-        <v>32</v>
+        <v>1050</v>
       </c>
       <c r="F1241" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="G1241" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="H1241" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,20 +35196,20 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>24000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>559</v>
+        <v>325</v>
       </c>
       <c r="E1242" t="n">
-        <v>572</v>
+        <v>348</v>
       </c>
       <c r="F1242" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G1242" t="n">
         <v>41</v>
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+          <t>American Classic House Dalam Town House Di Kemang</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>16899999999</v>
+        <v>8500000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="E1243" t="n">
-        <v>408</v>
+        <v>247</v>
       </c>
       <c r="F1243" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1243" t="n">
         <v>31</v>
       </c>
       <c r="H1243" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>45000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E1244" t="n">
-        <v>620</v>
+        <v>260</v>
       </c>
       <c r="F1244" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1244" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1244" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>42000000000</v>
+        <v>38900000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
       <c r="E1245" t="n">
-        <v>1925</v>
+        <v>932</v>
       </c>
       <c r="F1245" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G1245" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="H1245" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>10500000000</v>
+        <v>6350000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="E1246" t="n">
-        <v>407</v>
+        <v>200</v>
       </c>
       <c r="F1246" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1246" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1246" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>68000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="E1247" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
       <c r="F1247" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="G1247" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="H1247" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>7500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>325</v>
+        <v>800</v>
       </c>
       <c r="E1248" t="n">
-        <v>348</v>
+        <v>1335</v>
       </c>
       <c r="F1248" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G1248" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1248" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>American Classic House Dalam Town House Di Kemang</t>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>8500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>380</v>
+        <v>900</v>
       </c>
       <c r="E1249" t="n">
-        <v>247</v>
+        <v>1098</v>
       </c>
       <c r="F1249" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G1249" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H1249" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>7000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="E1250" t="n">
-        <v>260</v>
+        <v>936</v>
       </c>
       <c r="F1250" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1250" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1250" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>38900000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="E1251" t="n">
-        <v>932</v>
+        <v>123</v>
       </c>
       <c r="F1251" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1251" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1251" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>6350000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E1252" t="n">
-        <v>200</v>
+        <v>588</v>
       </c>
       <c r="F1252" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1252" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1252" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>13500000000</v>
+        <v>1250000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="E1253" t="n">
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="F1253" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1253" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1253" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>27000000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1254" t="n">
         <v>800</v>
       </c>
       <c r="E1254" t="n">
-        <v>1335</v>
+        <v>1980</v>
       </c>
       <c r="F1254" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="G1254" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H1254" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>20000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="E1255" t="n">
-        <v>1098</v>
+        <v>515</v>
       </c>
       <c r="F1255" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G1255" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H1255" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,17 +35588,17 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>57000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>1200</v>
+        <v>135</v>
       </c>
       <c r="E1256" t="n">
-        <v>936</v>
+        <v>30</v>
       </c>
       <c r="F1256" t="n">
         <v>3</v>
@@ -35607,7 +35607,7 @@
         <v>3</v>
       </c>
       <c r="H1256" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>2900000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E1257" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="F1257" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1257" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1257" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>11500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1258" t="n">
         <v>400</v>
       </c>
       <c r="E1258" t="n">
-        <v>588</v>
+        <v>267</v>
       </c>
       <c r="F1258" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1258" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1258" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>1250000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="E1259" t="n">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="F1259" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1259" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1259" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>7090000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="E1260" t="n">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="F1260" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1260" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>8500000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>262</v>
+        <v>800</v>
       </c>
       <c r="E1261" t="n">
-        <v>161</v>
+        <v>700</v>
       </c>
       <c r="F1261" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1261" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1261" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>135000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>800</v>
+        <v>1280</v>
       </c>
       <c r="E1262" t="n">
-        <v>1980</v>
+        <v>600</v>
       </c>
       <c r="F1262" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G1262" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H1262" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>13500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1263" t="n">
-        <v>515</v>
+        <v>703</v>
       </c>
       <c r="F1263" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G1263" t="n">
         <v>41</v>
       </c>
       <c r="H1263" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
+          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>2500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>135</v>
+        <v>850</v>
       </c>
       <c r="E1264" t="n">
-        <v>30</v>
+        <v>1925</v>
       </c>
       <c r="F1264" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1264" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1264" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>15500000000</v>
+        <v>3100000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="E1265" t="n">
-        <v>350</v>
+        <v>88</v>
       </c>
       <c r="F1265" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1265" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1265" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
+          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>9000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>300</v>
+        <v>72</v>
       </c>
       <c r="E1266" t="n">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="F1266" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1266" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H1266" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>2600000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>60</v>
+        <v>317</v>
       </c>
       <c r="E1267" t="n">
-        <v>60</v>
+        <v>419</v>
       </c>
       <c r="F1267" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1267" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
+          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>5550000000</v>
+        <v>2450000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1268" t="n">
-        <v>267</v>
+        <v>90</v>
       </c>
       <c r="F1268" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1268" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1268" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>8500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>440</v>
+        <v>285</v>
       </c>
       <c r="E1269" t="n">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="F1269" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1269" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1269" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,23 +35980,23 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>8500000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E1270" t="n">
-        <v>202</v>
+        <v>752</v>
       </c>
       <c r="F1270" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1270" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1270" t="n">
         <v>22</v>
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>2600000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E1271" t="n">
-        <v>60</v>
+        <v>1050</v>
       </c>
       <c r="F1271" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G1271" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1271" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>76000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1272" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="F1272" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1272" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1272" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
+          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>16000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>1280</v>
+        <v>150</v>
       </c>
       <c r="E1273" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F1273" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="G1273" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="H1273" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,23 +36092,23 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>8000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1274" t="n">
-        <v>165</v>
+        <v>370</v>
       </c>
       <c r="F1274" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1274" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1274" t="n">
         <v>24</v>
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>2830000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="E1275" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="F1275" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1275" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1275" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>2000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E1276" t="n">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="F1276" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1276" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1276" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>4800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>325</v>
+        <v>800</v>
       </c>
       <c r="E1277" t="n">
-        <v>340</v>
+        <v>1335</v>
       </c>
       <c r="F1277" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1277" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1277" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,14 +36204,14 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>2000000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E1278" t="n">
         <v>60</v>
@@ -36220,10 +36220,10 @@
         <v>3</v>
       </c>
       <c r="G1278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1278" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>32000000000</v>
+        <v>35800000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E1279" t="n">
-        <v>703</v>
+        <v>800</v>
       </c>
       <c r="F1279" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1279" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1279" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>4900000000</v>
+        <v>185000000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>360</v>
+        <v>800</v>
       </c>
       <c r="E1280" t="n">
-        <v>127</v>
+        <v>1358</v>
       </c>
       <c r="F1280" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1280" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="H1280" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>40000000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1281" t="n">
+        <v>900</v>
+      </c>
+      <c r="E1281" t="n">
         <v>850</v>
       </c>
-      <c r="E1281" t="n">
-        <v>1925</v>
-      </c>
       <c r="F1281" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1281" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H1281" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>3100000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E1282" t="n">
-        <v>88</v>
+        <v>300</v>
       </c>
       <c r="F1282" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1282" t="n">
         <v>2</v>
       </c>
       <c r="H1282" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>1500000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>72</v>
+        <v>700</v>
       </c>
       <c r="E1283" t="n">
-        <v>81</v>
+        <v>960</v>
       </c>
       <c r="F1283" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1283" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1283" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>18500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>317</v>
+        <v>1200</v>
       </c>
       <c r="E1284" t="n">
-        <v>419</v>
+        <v>584</v>
       </c>
       <c r="F1284" t="n">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="G1284" t="n">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="H1284" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>2450000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1285" t="n">
-        <v>90</v>
+        <v>1094</v>
       </c>
       <c r="F1285" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1285" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1285" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
+          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>7000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="E1286" t="n">
-        <v>177</v>
+        <v>1153</v>
       </c>
       <c r="F1286" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1286" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1286" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>13500000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="E1287" t="n">
-        <v>752</v>
+        <v>60</v>
       </c>
       <c r="F1287" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1287" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H1287" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>23000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>800</v>
+        <v>340</v>
       </c>
       <c r="E1288" t="n">
-        <v>1050</v>
+        <v>350</v>
       </c>
       <c r="F1288" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="G1288" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1288" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,23 +36512,23 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>17000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1289" t="n">
-        <v>1100</v>
+        <v>779</v>
       </c>
       <c r="F1289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1289" t="n">
         <v>1</v>
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>1900000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>150</v>
+        <v>262</v>
       </c>
       <c r="E1290" t="n">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="F1290" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1290" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1290" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>10000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>150</v>
+        <v>560</v>
       </c>
       <c r="E1291" t="n">
-        <v>370</v>
+        <v>248</v>
       </c>
       <c r="F1291" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G1291" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1291" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>23000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>1200</v>
+        <v>375</v>
       </c>
       <c r="E1292" t="n">
-        <v>1000</v>
+        <v>76</v>
       </c>
       <c r="F1292" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1292" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1292" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>4900000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>42</v>
+        <v>503</v>
       </c>
       <c r="E1293" t="n">
-        <v>174</v>
+        <v>421</v>
       </c>
       <c r="F1293" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1293" t="n">
         <v>4</v>
       </c>
       <c r="H1293" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>27000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1294" t="n">
-        <v>1335</v>
+        <v>60</v>
       </c>
       <c r="F1294" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1294" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1294" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,23 +36680,23 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>1420000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="E1295" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="F1295" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G1295" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1295" t="n">
         <v>1</v>
@@ -36708,26 +36708,26 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>35800000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="E1296" t="n">
-        <v>800</v>
+        <v>598</v>
       </c>
       <c r="F1296" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1296" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1296" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1297">
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>185000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1297" t="n">
-        <v>1358</v>
+        <v>165</v>
       </c>
       <c r="F1297" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1297" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1297" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>61000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="E1298" t="n">
-        <v>850</v>
+        <v>60</v>
       </c>
       <c r="F1298" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1298" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H1298" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,23 +36792,23 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>12800000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="E1299" t="n">
-        <v>300</v>
+        <v>530</v>
       </c>
       <c r="F1299" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1299" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1299" t="n">
         <v>11</v>
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>21000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="E1300" t="n">
-        <v>960</v>
+        <v>60</v>
       </c>
       <c r="F1300" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1300" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1300" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>40000000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>1200</v>
+        <v>98</v>
       </c>
       <c r="E1301" t="n">
-        <v>584</v>
+        <v>98</v>
       </c>
       <c r="F1301" t="n">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="G1301" t="n">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="H1301" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>49000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="E1302" t="n">
-        <v>1094</v>
+        <v>60</v>
       </c>
       <c r="F1302" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1302" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1302" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,26 +36904,782 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>15000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="E1303" t="n">
-        <v>1153</v>
+        <v>60</v>
       </c>
       <c r="F1303" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1303" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1303" t="n">
-        <v>26</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>390</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>307</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>330</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>5750000000</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>208</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>80</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>110</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>829000000</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>1420000000</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>53000000000</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>457</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>494</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>26000000000</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>1374</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>1493</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>1318</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>144</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>232</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>1319</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>340</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>2550000000</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>117</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>1322</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>16899999999</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Rumah Gandaria Dekat Gandaria City</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>10500000000</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>247</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>37000000000</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>1326</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>9900000000</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>367</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>437</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>330</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>1328</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>80</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>1329</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Rumah, di Pondok Indah, Bukit Golf</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>160000000000</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1330"/>
+  <dimension ref="A1:H1360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30912,26 +30912,26 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>1650000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1089" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="E1089" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="F1089" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1089" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1089" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1090">
@@ -30940,17 +30940,17 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
+          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>3900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1090" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="E1090" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="F1090" t="n">
         <v>4</v>
@@ -30959,7 +30959,7 @@
         <v>4</v>
       </c>
       <c r="H1090" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1091">
@@ -30968,23 +30968,23 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>1800000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1091" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E1091" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F1091" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1091" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1091" t="n">
         <v>2</v>
@@ -30996,23 +30996,23 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
+          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2400000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1092" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="E1092" t="n">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="F1092" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1092" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1092" t="n">
         <v>2</v>
@@ -31024,23 +31024,23 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
+          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>3850000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1093" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E1093" t="n">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="F1093" t="n">
         <v>5</v>
       </c>
       <c r="G1093" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1093" t="n">
         <v>2</v>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
+          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -31062,7 +31062,7 @@
         <v>180</v>
       </c>
       <c r="E1094" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1094" t="n">
         <v>5</v>
@@ -31080,20 +31080,20 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
+          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>3950000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1095" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E1095" t="n">
-        <v>162</v>
+        <v>446</v>
       </c>
       <c r="F1095" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1095" t="n">
         <v>3</v>
@@ -31108,26 +31108,26 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
+          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>3950000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1096" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1096" t="n">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="F1096" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1096" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1096" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1097">
@@ -31136,26 +31136,26 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
+          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>11500000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1097" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E1097" t="n">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="F1097" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1097" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1097" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1098">
@@ -31164,26 +31164,26 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
+          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>9500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1098" t="n">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="E1098" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
       <c r="F1098" t="n">
         <v>4</v>
       </c>
       <c r="G1098" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1098" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1099">
@@ -31192,26 +31192,26 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>35000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1099" t="n">
-        <v>650</v>
+        <v>1374</v>
       </c>
       <c r="E1099" t="n">
-        <v>406</v>
+        <v>1493</v>
       </c>
       <c r="F1099" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1099" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H1099" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1100">
@@ -31220,17 +31220,17 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
+          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>30000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1100" t="n">
-        <v>274</v>
+        <v>467</v>
       </c>
       <c r="E1100" t="n">
-        <v>448</v>
+        <v>899</v>
       </c>
       <c r="F1100" t="n">
         <v>4</v>
@@ -31239,7 +31239,7 @@
         <v>4</v>
       </c>
       <c r="H1100" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1101">
@@ -31248,26 +31248,26 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
+          <t>Rumah Mewah Baru di Jagakarsa</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>26000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1101" t="n">
-        <v>1374</v>
+        <v>520</v>
       </c>
       <c r="E1101" t="n">
-        <v>1493</v>
+        <v>720</v>
       </c>
       <c r="F1101" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G1101" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H1101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1102">
@@ -31276,26 +31276,26 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
+          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>18000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1102" t="n">
-        <v>467</v>
+        <v>150</v>
       </c>
       <c r="E1102" t="n">
-        <v>899</v>
+        <v>300</v>
       </c>
       <c r="F1102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1102" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1103">
@@ -31304,26 +31304,26 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Rumah Mewah Baru di Jagakarsa</t>
+          <t>Dijual Bawah Njop Kemang Rp 13.3juta/m2 Luas 2028m2 Bebas Banjir</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>12500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1103" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="E1103" t="n">
-        <v>720</v>
+        <v>2028</v>
       </c>
       <c r="F1103" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1104">
@@ -31332,26 +31332,26 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
+          <t>Baru Akses Jalan Utama Khafi 1 Siap Huni Tanah Luas Free Canopy Bata Merah</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>13000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1104" t="n">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="E1104" t="n">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="F1104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1105">
@@ -31360,26 +31360,26 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Dijual Bawah Njop Kemang Rp 13.3juta/m2 Luas 2028m2 Bebas Banjir</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>27000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1105" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="E1105" t="n">
-        <v>2028</v>
+        <v>250</v>
       </c>
       <c r="F1105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1106">
@@ -31388,23 +31388,23 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Baru Akses Jalan Utama Khafi 1 Siap Huni Tanah Luas Free Canopy Bata Merah</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>2500000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1106" t="n">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="E1106" t="n">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="F1106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1106" t="n">
         <v>2</v>
@@ -31416,23 +31416,23 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>8000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1107" t="n">
-        <v>430</v>
+        <v>850</v>
       </c>
       <c r="E1107" t="n">
-        <v>250</v>
+        <v>384</v>
       </c>
       <c r="F1107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1107" t="n">
         <v>3</v>
@@ -31444,23 +31444,23 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>5500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1108" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="E1108" t="n">
-        <v>318</v>
+        <v>108</v>
       </c>
       <c r="F1108" t="n">
         <v>5</v>
       </c>
       <c r="G1108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1108" t="n">
         <v>2</v>
@@ -31472,26 +31472,26 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>14000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1109" t="n">
-        <v>850</v>
+        <v>409</v>
       </c>
       <c r="E1109" t="n">
-        <v>384</v>
+        <v>520</v>
       </c>
       <c r="F1109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1109" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1110">
@@ -31500,17 +31500,17 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>4800000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1110" t="n">
-        <v>258</v>
+        <v>440</v>
       </c>
       <c r="E1110" t="n">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="F1110" t="n">
         <v>5</v>
@@ -31528,26 +31528,26 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>19000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1111" t="n">
-        <v>409</v>
+        <v>1000</v>
       </c>
       <c r="E1111" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F1111" t="n">
         <v>5</v>
       </c>
       <c r="G1111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1112">
@@ -31556,26 +31556,26 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
+          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>9000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1112" t="n">
-        <v>440</v>
+        <v>1600</v>
       </c>
       <c r="E1112" t="n">
-        <v>202</v>
+        <v>1050</v>
       </c>
       <c r="F1112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1112" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1113">
@@ -31584,26 +31584,26 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
+          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>45000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1113" t="n">
-        <v>1000</v>
+        <v>825</v>
       </c>
       <c r="E1113" t="n">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="F1113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1113" t="n">
         <v>5</v>
       </c>
       <c r="H1113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1114">
@@ -31612,26 +31612,26 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>68000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1114" t="n">
-        <v>1600</v>
+        <v>380</v>
       </c>
       <c r="E1114" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="F1114" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1114" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1114" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1115">
@@ -31640,17 +31640,17 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
+          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>32000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1115" t="n">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="E1115" t="n">
-        <v>768</v>
+        <v>1925</v>
       </c>
       <c r="F1115" t="n">
         <v>6</v>
@@ -31659,7 +31659,7 @@
         <v>5</v>
       </c>
       <c r="H1115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1116">
@@ -31668,26 +31668,26 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
+          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>14000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1116" t="n">
-        <v>380</v>
+        <v>1200</v>
       </c>
       <c r="E1116" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F1116" t="n">
         <v>6</v>
       </c>
       <c r="G1116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1117">
@@ -31696,26 +31696,26 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
+          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>42000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1117" t="n">
-        <v>850</v>
+        <v>240</v>
       </c>
       <c r="E1117" t="n">
-        <v>1925</v>
+        <v>310</v>
       </c>
       <c r="F1117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1117" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1118">
@@ -31724,26 +31724,26 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>45000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1118" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1118" t="n">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="F1118" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1118" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H1118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1119">
@@ -31752,23 +31752,23 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>15800000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1119" t="n">
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="E1119" t="n">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="F1119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1119" t="n">
         <v>1</v>
@@ -31780,17 +31780,17 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>17000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1120" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E1120" t="n">
-        <v>1070</v>
+        <v>1250</v>
       </c>
       <c r="F1120" t="n">
         <v>4</v>
@@ -31799,7 +31799,7 @@
         <v>3</v>
       </c>
       <c r="H1120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1121">
@@ -31808,26 +31808,26 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
+          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>9700000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1121" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="E1121" t="n">
-        <v>216</v>
+        <v>467</v>
       </c>
       <c r="F1121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1122">
@@ -31836,26 +31836,26 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>23000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1122" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="E1122" t="n">
-        <v>1250</v>
+        <v>620</v>
       </c>
       <c r="F1122" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G1122" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H1122" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1123">
@@ -31864,26 +31864,26 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
+          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>12000000000</v>
+        <v>60600000000</v>
       </c>
       <c r="D1123" t="n">
-        <v>580</v>
+        <v>1130</v>
       </c>
       <c r="E1123" t="n">
-        <v>467</v>
+        <v>4041</v>
       </c>
       <c r="F1123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1123" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1124">
@@ -31892,26 +31892,26 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>42000000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1124" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1124" t="n">
-        <v>620</v>
+        <v>534</v>
       </c>
       <c r="F1124" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G1124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H1124" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1125">
@@ -31920,26 +31920,26 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>60600000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1125" t="n">
-        <v>1130</v>
+        <v>600</v>
       </c>
       <c r="E1125" t="n">
-        <v>4041</v>
+        <v>550</v>
       </c>
       <c r="F1125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1125" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1126">
@@ -31948,26 +31948,26 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>40500000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1126" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="E1126" t="n">
-        <v>534</v>
+        <v>850</v>
       </c>
       <c r="F1126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1127">
@@ -31976,26 +31976,26 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>12000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1127" t="n">
-        <v>550</v>
+        <v>1235</v>
       </c>
       <c r="F1127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1128">
@@ -32004,26 +32004,26 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>61000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>900</v>
+        <v>195</v>
       </c>
       <c r="E1128" t="n">
-        <v>850</v>
+        <v>252</v>
       </c>
       <c r="F1128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,26 +32032,26 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
+          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>45000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1129" t="n">
-        <v>1235</v>
+        <v>379</v>
       </c>
       <c r="F1129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1130">
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
+          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>14000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="E1130" t="n">
-        <v>252</v>
+        <v>604</v>
       </c>
       <c r="F1130" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,17 +32088,17 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
+          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>21000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1131" t="n">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="F1131" t="n">
         <v>4</v>
@@ -32107,7 +32107,7 @@
         <v>3</v>
       </c>
       <c r="H1131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1132">
@@ -32116,23 +32116,23 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
+          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>40000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E1132" t="n">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="F1132" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1132" t="n">
         <v>4</v>
@@ -32144,26 +32144,26 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
+          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>15000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1133" t="n">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="F1133" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1133" t="n">
         <v>3</v>
       </c>
       <c r="H1133" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,26 +32172,26 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>13500000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1134" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="F1134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1135">
@@ -32200,26 +32200,26 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>27000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>301</v>
+        <v>850</v>
       </c>
       <c r="E1135" t="n">
-        <v>469</v>
+        <v>1925</v>
       </c>
       <c r="F1135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1135" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1135" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,26 +32228,26 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>21000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>600</v>
+        <v>882</v>
       </c>
       <c r="E1136" t="n">
-        <v>630</v>
+        <v>1845</v>
       </c>
       <c r="F1136" t="n">
         <v>5</v>
       </c>
       <c r="G1136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1137">
@@ -32256,26 +32256,26 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>42000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>850</v>
+        <v>250</v>
       </c>
       <c r="E1137" t="n">
-        <v>1925</v>
+        <v>140</v>
       </c>
       <c r="F1137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1137" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1138">
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>71900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="E1138" t="n">
-        <v>1845</v>
+        <v>1925</v>
       </c>
       <c r="F1138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1138" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>6500000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1139" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="F1139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,26 +32340,26 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>42000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1140" t="n">
-        <v>850</v>
+        <v>325</v>
       </c>
       <c r="E1140" t="n">
-        <v>1925</v>
+        <v>696</v>
       </c>
       <c r="F1140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1140" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1141">
@@ -32368,26 +32368,26 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>49000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>1100</v>
+        <v>880</v>
       </c>
       <c r="E1141" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="F1141" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1141" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1142">
@@ -32396,26 +32396,26 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>13000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1142" t="n">
-        <v>696</v>
+        <v>187</v>
       </c>
       <c r="F1142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,26 +32424,26 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>62000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1143" t="n">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="E1143" t="n">
-        <v>1000</v>
+        <v>692</v>
       </c>
       <c r="F1143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1143" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1143" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1144">
@@ -32452,23 +32452,23 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>4990000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1144" t="n">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="F1144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1144" t="n">
         <v>2</v>
@@ -32480,26 +32480,26 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>13800000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>407</v>
+        <v>1050</v>
       </c>
       <c r="E1145" t="n">
-        <v>692</v>
+        <v>627</v>
       </c>
       <c r="F1145" t="n">
         <v>5</v>
       </c>
       <c r="G1145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,26 +32508,26 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>13900000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E1146" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F1146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1147">
@@ -32536,26 +32536,26 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>44000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1147" t="n">
-        <v>1050</v>
+        <v>325</v>
       </c>
       <c r="E1147" t="n">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="F1147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1148">
@@ -32564,26 +32564,26 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>31900000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E1148" t="n">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="F1148" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1149">
@@ -32592,26 +32592,26 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>13000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1149" t="n">
-        <v>696</v>
+        <v>246</v>
       </c>
       <c r="F1149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1149" t="n">
         <v>3</v>
       </c>
       <c r="H1149" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,26 +32620,26 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>7090000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1150" t="n">
-        <v>76</v>
+        <v>510</v>
       </c>
       <c r="F1150" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1150" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1151">
@@ -32648,23 +32648,23 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>7500000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="E1151" t="n">
-        <v>246</v>
+        <v>32</v>
       </c>
       <c r="F1151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1151" t="n">
         <v>1</v>
@@ -32676,26 +32676,26 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>7300000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>600</v>
+        <v>232</v>
       </c>
       <c r="E1152" t="n">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="F1152" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1153">
@@ -32704,23 +32704,23 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>998000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="E1153" t="n">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="F1153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1153" t="n">
         <v>1</v>
@@ -32732,23 +32732,23 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>22000000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="E1154" t="n">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="F1154" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1154" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H1154" t="n">
         <v>1</v>
@@ -32760,23 +32760,23 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>6250000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="E1155" t="n">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="F1155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1155" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1155" t="n">
         <v>1</v>
@@ -32788,26 +32788,26 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>7200000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="E1156" t="n">
-        <v>196</v>
+        <v>675</v>
       </c>
       <c r="F1156" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G1156" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H1156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1157">
@@ -32816,26 +32816,26 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>2600000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>88</v>
+        <v>375</v>
       </c>
       <c r="E1157" t="n">
-        <v>55</v>
+        <v>534</v>
       </c>
       <c r="F1157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1158">
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>65000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="E1158" t="n">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="F1158" t="n">
         <v>4</v>
       </c>
       <c r="G1158" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>23000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="E1159" t="n">
-        <v>534</v>
+        <v>70</v>
       </c>
       <c r="F1159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1160">
@@ -32900,23 +32900,23 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>15500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>928</v>
+        <v>1350</v>
       </c>
       <c r="E1160" t="n">
-        <v>378</v>
+        <v>863</v>
       </c>
       <c r="F1160" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1160" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1160" t="n">
         <v>1</v>
@@ -32928,23 +32928,23 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>2830000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>112</v>
+        <v>280</v>
       </c>
       <c r="E1161" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F1161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1161" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1161" t="n">
         <v>1</v>
@@ -32956,23 +32956,23 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>38000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>1350</v>
+        <v>130</v>
       </c>
       <c r="E1162" t="n">
-        <v>863</v>
+        <v>117</v>
       </c>
       <c r="F1162" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1162" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1162" t="n">
         <v>1</v>
@@ -32984,26 +32984,26 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>8800000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>280</v>
+        <v>1600</v>
       </c>
       <c r="E1163" t="n">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="F1163" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1163" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1163" t="n">
         <v>6</v>
-      </c>
-      <c r="H1163" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="1164">
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>2600000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="E1164" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="F1164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>68000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="E1165" t="n">
-        <v>1050</v>
+        <v>150</v>
       </c>
       <c r="F1165" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1165" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1165" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,23 +33068,23 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>22000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>182</v>
+        <v>600</v>
       </c>
       <c r="E1166" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="F1166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1166" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1166" t="n">
         <v>2</v>
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>4800000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1167" t="n">
         <v>300</v>
       </c>
       <c r="E1167" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F1167" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1167" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,23 +33124,23 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>13500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>600</v>
+        <v>262</v>
       </c>
       <c r="E1168" t="n">
-        <v>304</v>
+        <v>161</v>
       </c>
       <c r="F1168" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1168" t="n">
         <v>2</v>
@@ -33152,23 +33152,23 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>14500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1169" t="n">
-        <v>240</v>
+        <v>1554</v>
       </c>
       <c r="F1169" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1169" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1169" t="n">
         <v>4</v>
@@ -33180,17 +33180,17 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>8500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="E1170" t="n">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="F1170" t="n">
         <v>4</v>
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>New House Full Furnished Kemang Selatan</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>52500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E1171" t="n">
-        <v>1554</v>
+        <v>518</v>
       </c>
       <c r="F1171" t="n">
         <v>7</v>
       </c>
       <c r="G1171" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H1171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,17 +33236,17 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>6900000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1172" t="n">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="F1172" t="n">
         <v>4</v>
@@ -33264,26 +33264,26 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>New House Full Furnished Kemang Selatan</t>
+          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>38000000000</v>
+        <v>2950000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>760</v>
+        <v>200</v>
       </c>
       <c r="E1173" t="n">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="F1173" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1173" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>7800000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1174" t="n">
-        <v>160</v>
+        <v>351</v>
       </c>
       <c r="F1174" t="n">
         <v>4</v>
       </c>
       <c r="G1174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,23 +33320,23 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
+          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>2950000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E1175" t="n">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="F1175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1175" t="n">
         <v>1</v>
@@ -33348,17 +33348,17 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Brand New House Modern Design With Pool Cilandak</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>34500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>500</v>
+        <v>428</v>
       </c>
       <c r="E1176" t="n">
-        <v>351</v>
+        <v>204</v>
       </c>
       <c r="F1176" t="n">
         <v>4</v>
@@ -33367,7 +33367,7 @@
         <v>3</v>
       </c>
       <c r="H1176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
+          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2500000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="E1177" t="n">
-        <v>50</v>
+        <v>866</v>
       </c>
       <c r="F1177" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Brand New House Modern Design With Pool Cilandak</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>9800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>428</v>
+        <v>140</v>
       </c>
       <c r="E1178" t="n">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="F1178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
+          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>37000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E1179" t="n">
-        <v>866</v>
+        <v>650</v>
       </c>
       <c r="F1179" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1179" t="n">
         <v>6</v>
-      </c>
-      <c r="G1179" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1179" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,23 +33460,23 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>2400000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>140</v>
+        <v>1115</v>
       </c>
       <c r="E1180" t="n">
-        <v>105</v>
+        <v>759</v>
       </c>
       <c r="F1180" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1180" t="n">
         <v>2</v>
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
+          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>45000000000</v>
+        <v>4550000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E1181" t="n">
-        <v>650</v>
+        <v>197</v>
       </c>
       <c r="F1181" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1181" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1181" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>60000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>1115</v>
+        <v>580</v>
       </c>
       <c r="E1182" t="n">
-        <v>759</v>
+        <v>344</v>
       </c>
       <c r="F1182" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H1182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
+          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>4550000000</v>
+        <v>31200000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E1183" t="n">
-        <v>197</v>
+        <v>1200</v>
       </c>
       <c r="F1183" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G1183" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1183" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>8000000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>580</v>
+        <v>198</v>
       </c>
       <c r="E1184" t="n">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="F1184" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G1184" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H1184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,26 +33600,26 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>31200000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>1000</v>
+        <v>301</v>
       </c>
       <c r="E1185" t="n">
-        <v>1200</v>
+        <v>469</v>
       </c>
       <c r="F1185" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G1185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1185" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1186">
@@ -33628,23 +33628,23 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
+          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>3850000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>198</v>
+        <v>616</v>
       </c>
       <c r="E1186" t="n">
-        <v>105</v>
+        <v>383</v>
       </c>
       <c r="F1186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1186" t="n">
         <v>2</v>
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>27000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="E1187" t="n">
-        <v>469</v>
+        <v>272</v>
       </c>
       <c r="F1187" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1187" t="n">
         <v>4</v>
       </c>
       <c r="H1187" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,23 +33684,23 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>16000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>616</v>
+        <v>400</v>
       </c>
       <c r="E1188" t="n">
-        <v>383</v>
+        <v>543</v>
       </c>
       <c r="F1188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1188" t="n">
         <v>2</v>
@@ -33712,20 +33712,20 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>5500000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1189" t="n">
-        <v>272</v>
+        <v>1028</v>
       </c>
       <c r="F1189" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1189" t="n">
         <v>4</v>
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>21000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1190" t="n">
-        <v>543</v>
+        <v>304</v>
       </c>
       <c r="F1190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1190" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
+          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>18500000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1191" t="n">
-        <v>1028</v>
+        <v>793</v>
       </c>
       <c r="F1191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1191" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>5550000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>250</v>
+        <v>559</v>
       </c>
       <c r="E1192" t="n">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="F1192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
+          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>15300000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1193" t="n">
-        <v>793</v>
+        <v>1000</v>
       </c>
       <c r="F1193" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,26 +33852,26 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>24000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>559</v>
+        <v>310</v>
       </c>
       <c r="E1194" t="n">
-        <v>572</v>
+        <v>260</v>
       </c>
       <c r="F1194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1195">
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
+          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>35000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>1100</v>
+        <v>760</v>
       </c>
       <c r="E1195" t="n">
-        <v>1000</v>
+        <v>517</v>
       </c>
       <c r="F1195" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1195" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1195" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
+          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>11000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="E1196" t="n">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="F1196" t="n">
         <v>4</v>
       </c>
       <c r="G1196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>38000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>760</v>
+        <v>318</v>
       </c>
       <c r="E1197" t="n">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="F1197" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1197" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
+          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>13900000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E1198" t="n">
-        <v>340</v>
+        <v>544</v>
       </c>
       <c r="F1198" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1198" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>12500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="E1199" t="n">
-        <v>497</v>
+        <v>348</v>
       </c>
       <c r="F1199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>12500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>650</v>
+        <v>260</v>
       </c>
       <c r="E1200" t="n">
-        <v>544</v>
+        <v>230</v>
       </c>
       <c r="F1200" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1200" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,26 +34048,26 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>12000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="E1201" t="n">
-        <v>348</v>
+        <v>66</v>
       </c>
       <c r="F1201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1201" t="n">
         <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,17 +34076,17 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>9800000000</v>
+        <v>990000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="E1202" t="n">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="F1202" t="n">
         <v>4</v>
@@ -34095,7 +34095,7 @@
         <v>3</v>
       </c>
       <c r="H1202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>3500000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E1203" t="n">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="F1203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,23 +34132,23 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
+          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>990000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E1204" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="F1204" t="n">
         <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1204" t="n">
         <v>2</v>
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>10000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="E1205" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F1205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1205" t="n">
         <v>4</v>
       </c>
       <c r="H1205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,23 +34188,23 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>1900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="E1206" t="n">
-        <v>105</v>
+        <v>598</v>
       </c>
       <c r="F1206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1206" t="n">
         <v>2</v>
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>15500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="E1207" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="F1207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,23 +34244,23 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>17000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>288</v>
+        <v>431</v>
       </c>
       <c r="E1208" t="n">
-        <v>598</v>
+        <v>874</v>
       </c>
       <c r="F1208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1208" t="n">
         <v>2</v>
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>11000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="E1209" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="F1209" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1209" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>15000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>431</v>
+        <v>135</v>
       </c>
       <c r="E1210" t="n">
-        <v>874</v>
+        <v>30</v>
       </c>
       <c r="F1210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>8500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="E1211" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="F1211" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,23 +34356,23 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>2600000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="E1212" t="n">
-        <v>30</v>
+        <v>515</v>
       </c>
       <c r="F1212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1212" t="n">
         <v>1</v>
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>15000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>240</v>
+        <v>636</v>
       </c>
       <c r="E1213" t="n">
-        <v>310</v>
+        <v>938</v>
       </c>
       <c r="F1213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1213" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,20 +34412,20 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>15000000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1214" t="n">
-        <v>515</v>
+        <v>160</v>
       </c>
       <c r="F1214" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1214" t="n">
         <v>4</v>
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>40000000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>636</v>
+        <v>250</v>
       </c>
       <c r="E1215" t="n">
-        <v>938</v>
+        <v>205</v>
       </c>
       <c r="F1215" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>6750000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="E1216" t="n">
-        <v>160</v>
+        <v>648</v>
       </c>
       <c r="F1216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1216" t="n">
         <v>4</v>
       </c>
       <c r="H1216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,17 +34496,17 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>3700000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E1217" t="n">
-        <v>205</v>
+        <v>307</v>
       </c>
       <c r="F1217" t="n">
         <v>4</v>
@@ -34524,23 +34524,23 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>10000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>355</v>
+        <v>100</v>
       </c>
       <c r="E1218" t="n">
-        <v>648</v>
+        <v>113</v>
       </c>
       <c r="F1218" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1218" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1218" t="n">
         <v>2</v>
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>15000000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="E1219" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="F1219" t="n">
         <v>4</v>
       </c>
       <c r="G1219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>2600000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E1220" t="n">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="F1220" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1220" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>6950000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="E1221" t="n">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="F1221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1221" t="n">
         <v>3</v>
       </c>
       <c r="H1221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1222" t="n">
-        <v>231</v>
+        <v>582</v>
       </c>
       <c r="F1222" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1222" t="n">
         <v>5</v>
       </c>
       <c r="H1222" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>4900000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="E1223" t="n">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="F1223" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1223" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1223" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>32000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>400</v>
+        <v>181</v>
       </c>
       <c r="E1224" t="n">
-        <v>582</v>
+        <v>182</v>
       </c>
       <c r="F1224" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1224" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1224" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>12900000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="E1225" t="n">
-        <v>209</v>
+        <v>909</v>
       </c>
       <c r="F1225" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1225" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H1225" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,17 +34748,17 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>4000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>181</v>
+        <v>432</v>
       </c>
       <c r="E1226" t="n">
-        <v>182</v>
+        <v>600</v>
       </c>
       <c r="F1226" t="n">
         <v>31</v>
@@ -34767,7 +34767,7 @@
         <v>31</v>
       </c>
       <c r="H1226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>16000000000</v>
+        <v>10300000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>320</v>
+        <v>1</v>
       </c>
       <c r="E1227" t="n">
-        <v>909</v>
+        <v>186</v>
       </c>
       <c r="F1227" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1227" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H1227" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>28000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>432</v>
+        <v>130</v>
       </c>
       <c r="E1228" t="n">
-        <v>600</v>
+        <v>93</v>
       </c>
       <c r="F1228" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1228" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>10300000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E1229" t="n">
-        <v>186</v>
+        <v>563</v>
       </c>
       <c r="F1229" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1229" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1229" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>1950000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="E1230" t="n">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="F1230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1230" t="n">
         <v>3</v>
       </c>
       <c r="H1230" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>55000000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1231" t="n">
         <v>400</v>
       </c>
       <c r="E1231" t="n">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="F1231" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1231" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1231" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>22500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="E1232" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="F1232" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1232" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1232" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>20500000000</v>
+        <v>1050000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>400</v>
+        <v>64</v>
       </c>
       <c r="E1233" t="n">
-        <v>543</v>
+        <v>32</v>
       </c>
       <c r="F1233" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1233" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1233" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>5550000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>250</v>
+        <v>559</v>
       </c>
       <c r="E1234" t="n">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="F1234" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1234" t="n">
         <v>41</v>
       </c>
-      <c r="G1234" t="n">
-        <v>31</v>
-      </c>
       <c r="H1234" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>1050000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1235" t="n">
-        <v>64</v>
+        <v>400</v>
       </c>
       <c r="E1235" t="n">
-        <v>32</v>
+        <v>408</v>
       </c>
       <c r="F1235" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1235" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1235" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>24000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>559</v>
+        <v>1000</v>
       </c>
       <c r="E1236" t="n">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="F1236" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1236" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1236" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>16899999999</v>
+        <v>42000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1237" t="n">
-        <v>408</v>
+        <v>1925</v>
       </c>
       <c r="F1237" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G1237" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H1237" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>45000000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E1238" t="n">
-        <v>620</v>
+        <v>407</v>
       </c>
       <c r="F1238" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G1238" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1238" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>42000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>850</v>
+        <v>1600</v>
       </c>
       <c r="E1239" t="n">
-        <v>1925</v>
+        <v>1050</v>
       </c>
       <c r="F1239" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G1239" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H1239" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,23 +35140,23 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>10500000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>600</v>
+        <v>325</v>
       </c>
       <c r="E1240" t="n">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="F1240" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G1240" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1240" t="n">
         <v>22</v>
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>American Classic House Dalam Town House Di Kemang</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>68000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>1600</v>
+        <v>380</v>
       </c>
       <c r="E1241" t="n">
-        <v>1050</v>
+        <v>247</v>
       </c>
       <c r="F1241" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="G1241" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="H1241" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>7500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="E1242" t="n">
-        <v>348</v>
+        <v>260</v>
       </c>
       <c r="F1242" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1242" t="n">
         <v>41</v>
       </c>
       <c r="H1242" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>American Classic House Dalam Town House Di Kemang</t>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>8500000000</v>
+        <v>38900000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>380</v>
+        <v>650</v>
       </c>
       <c r="E1243" t="n">
-        <v>247</v>
+        <v>932</v>
       </c>
       <c r="F1243" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1243" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1243" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>7000000000</v>
+        <v>6350000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1244" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="F1244" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1244" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1244" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>38900000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="E1245" t="n">
-        <v>932</v>
+        <v>500</v>
       </c>
       <c r="F1245" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1245" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H1245" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>6350000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="E1246" t="n">
-        <v>200</v>
+        <v>1335</v>
       </c>
       <c r="F1246" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1246" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1246" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>13500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E1247" t="n">
-        <v>500</v>
+        <v>1098</v>
       </c>
       <c r="F1247" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G1247" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H1247" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>27000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E1248" t="n">
-        <v>1335</v>
+        <v>936</v>
       </c>
       <c r="F1248" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1248" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1248" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>20000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="E1249" t="n">
-        <v>1098</v>
+        <v>123</v>
       </c>
       <c r="F1249" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1249" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H1249" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,23 +35420,23 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>57000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E1250" t="n">
-        <v>936</v>
+        <v>588</v>
       </c>
       <c r="F1250" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1250" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1250" t="n">
         <v>22</v>
@@ -35448,17 +35448,17 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>2900000000</v>
+        <v>1250000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="E1251" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="F1251" t="n">
         <v>2</v>
@@ -35467,7 +35467,7 @@
         <v>2</v>
       </c>
       <c r="H1251" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>11500000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1252" t="n">
-        <v>588</v>
+        <v>1980</v>
       </c>
       <c r="F1252" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G1252" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1252" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>1250000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="E1253" t="n">
-        <v>87</v>
+        <v>515</v>
       </c>
       <c r="F1253" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1253" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1253" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>135000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>800</v>
+        <v>135</v>
       </c>
       <c r="E1254" t="n">
-        <v>1980</v>
+        <v>30</v>
       </c>
       <c r="F1254" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1254" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>13500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1255" t="n">
-        <v>515</v>
+        <v>205</v>
       </c>
       <c r="F1255" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1255" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1255" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
+          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>2500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="E1256" t="n">
-        <v>30</v>
+        <v>267</v>
       </c>
       <c r="F1256" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1256" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1256" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>9000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="E1257" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F1257" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1257" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1257" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>5550000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="E1258" t="n">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="F1258" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G1258" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1258" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>8500000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="E1259" t="n">
-        <v>202</v>
+        <v>700</v>
       </c>
       <c r="F1259" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1259" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1259" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>8500000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>440</v>
+        <v>1280</v>
       </c>
       <c r="E1260" t="n">
-        <v>202</v>
+        <v>600</v>
       </c>
       <c r="F1260" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G1260" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H1260" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>76000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1261" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F1261" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G1261" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1261" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
+          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>16000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>1280</v>
+        <v>850</v>
       </c>
       <c r="E1262" t="n">
-        <v>600</v>
+        <v>1925</v>
       </c>
       <c r="F1262" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G1262" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="H1262" t="n">
-        <v>34</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>32000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="E1263" t="n">
-        <v>703</v>
+        <v>88</v>
       </c>
       <c r="F1263" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1263" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1263" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
+          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>40000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>850</v>
+        <v>72</v>
       </c>
       <c r="E1264" t="n">
-        <v>1925</v>
+        <v>81</v>
       </c>
       <c r="F1264" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1264" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1264" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>3100000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>130</v>
+        <v>317</v>
       </c>
       <c r="E1265" t="n">
-        <v>88</v>
+        <v>419</v>
       </c>
       <c r="F1265" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1265" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1265" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
+          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>1500000000</v>
+        <v>2450000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="E1266" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F1266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1266" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
+          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>18500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="E1267" t="n">
-        <v>419</v>
+        <v>177</v>
       </c>
       <c r="F1267" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1267" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1267" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>2450000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="E1268" t="n">
-        <v>90</v>
+        <v>752</v>
       </c>
       <c r="F1268" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1268" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1268" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>7000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>285</v>
+        <v>800</v>
       </c>
       <c r="E1269" t="n">
-        <v>177</v>
+        <v>1050</v>
       </c>
       <c r="F1269" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="G1269" t="n">
         <v>41</v>
       </c>
       <c r="H1269" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>13500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="E1270" t="n">
-        <v>752</v>
+        <v>1100</v>
       </c>
       <c r="F1270" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1270" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1270" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>23000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="E1271" t="n">
-        <v>1050</v>
+        <v>100</v>
       </c>
       <c r="F1271" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1271" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1271" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>17000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1272" t="n">
-        <v>1100</v>
+        <v>370</v>
       </c>
       <c r="F1272" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1272" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1272" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
+          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>1900000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1273" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F1273" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1273" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1273" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>10000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="E1274" t="n">
-        <v>370</v>
+        <v>174</v>
       </c>
       <c r="F1274" t="n">
         <v>5</v>
       </c>
       <c r="G1274" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1274" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>23000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E1275" t="n">
-        <v>1000</v>
+        <v>1335</v>
       </c>
       <c r="F1275" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1275" t="n">
         <v>6</v>
       </c>
       <c r="H1275" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
+          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>4900000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="E1276" t="n">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="F1276" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1276" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>27000000000</v>
+        <v>35800000000</v>
       </c>
       <c r="D1277" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1277" t="n">
         <v>800</v>
       </c>
-      <c r="E1277" t="n">
-        <v>1335</v>
-      </c>
       <c r="F1277" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1277" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1277" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
+          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>1420000000</v>
+        <v>185000000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>120</v>
+        <v>800</v>
       </c>
       <c r="E1278" t="n">
-        <v>60</v>
+        <v>1358</v>
       </c>
       <c r="F1278" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1278" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1278" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>35800000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E1279" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="F1279" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1279" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1279" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
+          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>185000000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="E1280" t="n">
-        <v>1358</v>
+        <v>300</v>
       </c>
       <c r="F1280" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1280" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>61000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E1281" t="n">
-        <v>850</v>
+        <v>960</v>
       </c>
       <c r="F1281" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1281" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1281" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>12800000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1282" t="n">
-        <v>300</v>
+        <v>584</v>
       </c>
       <c r="F1282" t="n">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="G1282" t="n">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="H1282" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>21000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="E1283" t="n">
-        <v>960</v>
+        <v>1094</v>
       </c>
       <c r="F1283" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1283" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1283" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
+          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>40000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E1284" t="n">
-        <v>584</v>
+        <v>1153</v>
       </c>
       <c r="F1284" t="n">
-        <v>171</v>
+        <v>5</v>
       </c>
       <c r="G1284" t="n">
-        <v>182</v>
+        <v>4</v>
       </c>
       <c r="H1284" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>49000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1285" t="n">
-        <v>1094</v>
+        <v>779</v>
       </c>
       <c r="F1285" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1285" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H1285" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>15000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>1000</v>
+        <v>262</v>
       </c>
       <c r="E1286" t="n">
-        <v>1153</v>
+        <v>161</v>
       </c>
       <c r="F1286" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1286" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1286" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>7090000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="E1287" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1287" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1287" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>15500000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>340</v>
+        <v>503</v>
       </c>
       <c r="E1288" t="n">
-        <v>350</v>
+        <v>421</v>
       </c>
       <c r="F1288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1288" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1288" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,20 +36512,20 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>9500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="E1289" t="n">
-        <v>779</v>
+        <v>260</v>
       </c>
       <c r="F1289" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G1289" t="n">
         <v>52</v>
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>8500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E1290" t="n">
-        <v>161</v>
+        <v>598</v>
       </c>
       <c r="F1290" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1290" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1290" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>22500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="E1291" t="n">
-        <v>248</v>
+        <v>530</v>
       </c>
       <c r="F1291" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G1291" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H1291" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>6900000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>375</v>
+        <v>98</v>
       </c>
       <c r="E1292" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F1292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1292" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>18500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>503</v>
+        <v>360</v>
       </c>
       <c r="E1293" t="n">
-        <v>421</v>
+        <v>127</v>
       </c>
       <c r="F1293" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1293" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1293" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>1900000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="E1294" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1294" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1294" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>11000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="E1295" t="n">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="F1295" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G1295" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1295" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,23 +36708,23 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>17000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="E1296" t="n">
-        <v>598</v>
+        <v>330</v>
       </c>
       <c r="F1296" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1296" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1296" t="n">
         <v>22</v>
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>8000000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="E1297" t="n">
-        <v>165</v>
+        <v>394</v>
       </c>
       <c r="F1297" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1297" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H1297" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>2600000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="E1298" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F1298" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1298" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,26 +36792,26 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>15000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="E1299" t="n">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="F1299" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1299" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1299" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1300">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>2000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E1300" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F1300" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1300" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1300" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>979000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E1301" t="n">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="F1301" t="n">
         <v>3</v>
       </c>
       <c r="G1301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1301" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,23 +36876,23 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>2830000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E1302" t="n">
         <v>60</v>
       </c>
       <c r="F1302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1302" t="n">
         <v>1</v>
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>2000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>85</v>
+        <v>810</v>
       </c>
       <c r="E1303" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="F1303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1303" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1303" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>4900000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="E1304" t="n">
-        <v>127</v>
+        <v>494</v>
       </c>
       <c r="F1304" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1304" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="H1304" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,26 +36960,26 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>6900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>375</v>
+        <v>850</v>
       </c>
       <c r="E1305" t="n">
-        <v>76</v>
+        <v>1925</v>
       </c>
       <c r="F1305" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="G1305" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1305" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>12900000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>390</v>
+        <v>1374</v>
       </c>
       <c r="E1306" t="n">
-        <v>307</v>
+        <v>1493</v>
       </c>
       <c r="F1306" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G1306" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H1306" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>10000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="E1307" t="n">
-        <v>330</v>
+        <v>180</v>
       </c>
       <c r="F1307" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1307" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>5750000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="E1308" t="n">
-        <v>394</v>
+        <v>232</v>
       </c>
       <c r="F1308" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1308" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,26 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>3000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="E1309" t="n">
-        <v>108</v>
+        <v>340</v>
       </c>
       <c r="F1309" t="n">
         <v>5</v>
       </c>
       <c r="G1309" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1309" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1310">
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>850000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1310" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="E1310" t="n">
-        <v>40</v>
+        <v>570</v>
       </c>
       <c r="F1310" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1310" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Rumah Gandaria Dekat Gandaria City</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>1900000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="E1311" t="n">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="F1311" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1311" t="n">
         <v>31</v>
       </c>
       <c r="H1311" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,26 +37156,26 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>829000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
       <c r="E1312" t="n">
-        <v>40</v>
+        <v>634</v>
       </c>
       <c r="F1312" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1312" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1312" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1313">
@@ -37184,26 +37184,26 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>1420000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>120</v>
+        <v>367</v>
       </c>
       <c r="E1313" t="n">
-        <v>60</v>
+        <v>437</v>
       </c>
       <c r="F1313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1313" t="n">
         <v>3</v>
       </c>
       <c r="H1313" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1314">
@@ -37212,26 +37212,26 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>48000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>810</v>
+        <v>569</v>
       </c>
       <c r="E1314" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="F1314" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1314" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1314" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,26 +37240,26 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>53000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="E1315" t="n">
-        <v>494</v>
+        <v>38</v>
       </c>
       <c r="F1315" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1315" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1316">
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>42000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>850</v>
+        <v>1450</v>
       </c>
       <c r="E1316" t="n">
-        <v>1925</v>
+        <v>1620</v>
       </c>
       <c r="F1316" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="G1316" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1316" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,26 +37296,26 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>26000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>1374</v>
+        <v>60</v>
       </c>
       <c r="E1317" t="n">
-        <v>1493</v>
+        <v>60</v>
       </c>
       <c r="F1317" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G1317" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H1317" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318">
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>1200000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="E1318" t="n">
-        <v>180</v>
+        <v>1038</v>
       </c>
       <c r="F1318" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1318" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H1318" t="n">
-        <v>11</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>1900000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E1319" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="F1319" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1319" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1319" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,26 +37380,26 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>4800000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="E1320" t="n">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="F1320" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1320" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1320" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1321">
@@ -37408,26 +37408,26 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>2550000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="E1321" t="n">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="F1321" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1321" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1322">
@@ -37436,17 +37436,17 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>1900000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E1322" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F1322" t="n">
         <v>3</v>
@@ -37455,7 +37455,7 @@
         <v>3</v>
       </c>
       <c r="H1322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>16899999999</v>
+        <v>135000000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1323" t="n">
-        <v>570</v>
+        <v>1980</v>
       </c>
       <c r="F1323" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G1323" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H1323" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Rumah Gandaria Dekat Gandaria City</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>10500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1324" t="n">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="F1324" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1324" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1324" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>13500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1325" t="n">
-        <v>515</v>
+        <v>200</v>
       </c>
       <c r="F1325" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1325" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1325" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>37000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>720</v>
+        <v>188</v>
       </c>
       <c r="E1326" t="n">
-        <v>634</v>
+        <v>200</v>
       </c>
       <c r="F1326" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1326" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1326" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>9900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>367</v>
+        <v>250</v>
       </c>
       <c r="E1327" t="n">
-        <v>437</v>
+        <v>165</v>
       </c>
       <c r="F1327" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1327" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1327" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,26 +37604,26 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>8000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>569</v>
+        <v>60</v>
       </c>
       <c r="E1328" t="n">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="F1328" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1328" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1329">
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>850000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E1329" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F1329" t="n">
         <v>3</v>
       </c>
       <c r="G1329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1329" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,26 +37660,866 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah, di Pondok Indah, Bukit Golf</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>160000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>1450</v>
+        <v>400</v>
       </c>
       <c r="E1330" t="n">
-        <v>1620</v>
+        <v>945</v>
       </c>
       <c r="F1330" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1330" t="n">
-        <v>1</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>50000000000</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>865</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>1331</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>9100000000</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>438</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>1333</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>1334</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>1335</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>248</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>262</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>161</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>341</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>1339</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah Lokasi Strategis SHM di Tebet Timur</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>2700000000</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>130</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>147</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Jarang Ada, Dijual Rumah Murah Sekali 2Lt Akses Mobil Tebet SHM</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>1350000000</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Angsuran Pasti Sampai Lunas : Dp 0, Free BPHTB, AJB, Bbn, By Ntrs</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>1343</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>550</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>450</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>1344</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Jual Cepat: Rumah Lama Murah Dibangka Kemang Jak Sel</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>340</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>489</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>1345</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Rumah Dilebak Bulus Hook Dekat MRT Lebak Bulus SHM</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>380</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>320</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>1346</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>6750000000</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Rumah Industrial Ada Pool Dalam Komplek Dilebak Bulus SHM</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>337</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>128</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>1348</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Rumah Baru Full Furnised Siap Huni di Permata Hijaj</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>7500000000</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>115</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>1349</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Rumah di Pondok Indah Jakarta Selatan Jalan Besar Lingkungan Asri SHM</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>16000000000</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah di Tebet Utara Jakarta Selatan Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>128</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Termurah</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>2700000000</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>143</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>1352</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Rumah Baru Siap Huni Deket MRT Lebak Bulus Dalam Cluster Dekat Tol</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>134</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>1353</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>129</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>1354</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>3800000000</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>149</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>1355</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>117</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>1356</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>2550000000</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>1358</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>5800000000</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>282</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>148</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>1359</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1385"/>
+  <dimension ref="A1:H1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31332,17 +31332,17 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>8000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1104" t="n">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="E1104" t="n">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="F1104" t="n">
         <v>5</v>
@@ -31351,7 +31351,7 @@
         <v>5</v>
       </c>
       <c r="H1104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1105">
@@ -31360,23 +31360,23 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>5500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1105" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="E1105" t="n">
-        <v>318</v>
+        <v>108</v>
       </c>
       <c r="F1105" t="n">
         <v>5</v>
       </c>
       <c r="G1105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1105" t="n">
         <v>2</v>
@@ -31388,26 +31388,26 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>14000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1106" t="n">
-        <v>850</v>
+        <v>409</v>
       </c>
       <c r="E1106" t="n">
-        <v>384</v>
+        <v>520</v>
       </c>
       <c r="F1106" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1107">
@@ -31416,17 +31416,17 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>4800000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1107" t="n">
-        <v>258</v>
+        <v>440</v>
       </c>
       <c r="E1107" t="n">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="F1107" t="n">
         <v>5</v>
@@ -31444,26 +31444,26 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Rumah Mewah Prime Location Area Permata Hijau Harga Menarik</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>19000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1108" t="n">
-        <v>409</v>
+        <v>1000</v>
       </c>
       <c r="E1108" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="F1108" t="n">
         <v>5</v>
       </c>
       <c r="G1108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1109">
@@ -31472,26 +31472,26 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Luxury House At West Jakarta Taman Palem Cengkareng</t>
+          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>9000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1109" t="n">
-        <v>440</v>
+        <v>1600</v>
       </c>
       <c r="E1109" t="n">
-        <v>202</v>
+        <v>1050</v>
       </c>
       <c r="F1109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1109" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1110">
@@ -31500,26 +31500,26 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic Di Jakarta Selatan</t>
+          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>45000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1110" t="n">
-        <v>1000</v>
+        <v>825</v>
       </c>
       <c r="E1110" t="n">
-        <v>620</v>
+        <v>768</v>
       </c>
       <c r="F1110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1110" t="n">
         <v>5</v>
       </c>
       <c r="H1110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1111">
@@ -31528,26 +31528,26 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Jual Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>68000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1111" t="n">
-        <v>1600</v>
+        <v>380</v>
       </c>
       <c r="E1111" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="F1111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1111" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1112">
@@ -31556,17 +31556,17 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
+          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>32000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1112" t="n">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="E1112" t="n">
-        <v>768</v>
+        <v>1925</v>
       </c>
       <c r="F1112" t="n">
         <v>6</v>
@@ -31575,7 +31575,7 @@
         <v>5</v>
       </c>
       <c r="H1112" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1113">
@@ -31584,26 +31584,26 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
+          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>14000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1113" t="n">
-        <v>380</v>
+        <v>1200</v>
       </c>
       <c r="E1113" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F1113" t="n">
         <v>6</v>
       </c>
       <c r="G1113" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1114">
@@ -31612,26 +31612,26 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Rumah Rasa Villa Luas 2000M 6 Kamar Cipete Dekat Pondok Indah</t>
+          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>42000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1114" t="n">
-        <v>850</v>
+        <v>240</v>
       </c>
       <c r="E1114" t="n">
-        <v>1925</v>
+        <v>310</v>
       </c>
       <c r="F1114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1115">
@@ -31640,26 +31640,26 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>45000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1115" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1115" t="n">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="F1115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1115" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H1115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1116">
@@ -31668,23 +31668,23 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>15800000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1116" t="n">
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="E1116" t="n">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="F1116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1116" t="n">
         <v>1</v>
@@ -31696,17 +31696,17 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>17000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1117" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E1117" t="n">
-        <v>1070</v>
+        <v>1250</v>
       </c>
       <c r="F1117" t="n">
         <v>4</v>
@@ -31715,7 +31715,7 @@
         <v>3</v>
       </c>
       <c r="H1117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1118">
@@ -31724,26 +31724,26 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Rumah Besar Tebet Utara, Jakarta Selatan.</t>
+          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>9700000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1118" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="E1118" t="n">
-        <v>216</v>
+        <v>467</v>
       </c>
       <c r="F1118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1119">
@@ -31752,26 +31752,26 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Kemang Masih Sangat Terawat dan Bangunan Masih Bagus</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>23000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1119" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="E1119" t="n">
-        <v>1250</v>
+        <v>620</v>
       </c>
       <c r="F1119" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G1119" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H1119" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1120">
@@ -31780,26 +31780,26 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Dijual Rumah Renovated Di Kemang, Dekat Kemang Dalam Lt 467m Hanya Rp 12 Milyar</t>
+          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>12000000000</v>
+        <v>60600000000</v>
       </c>
       <c r="D1120" t="n">
-        <v>580</v>
+        <v>1130</v>
       </c>
       <c r="E1120" t="n">
-        <v>467</v>
+        <v>4041</v>
       </c>
       <c r="F1120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1120" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1121">
@@ -31808,26 +31808,26 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>42000000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1121" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="E1121" t="n">
-        <v>620</v>
+        <v>534</v>
       </c>
       <c r="F1121" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G1121" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H1121" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1122">
@@ -31836,26 +31836,26 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Dijual Murah 15Jt/M2 di Kemang.pejaten Barat Kemang. Rumah Model Bali Luas 4041M2 Siap Huni Hanya Rp 15Juta/M</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>60600000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1122" t="n">
-        <v>1130</v>
+        <v>600</v>
       </c>
       <c r="E1122" t="n">
-        <v>4041</v>
+        <v>550</v>
       </c>
       <c r="F1122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1122" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1123">
@@ -31864,26 +31864,26 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>40500000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1123" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="E1123" t="n">
-        <v>534</v>
+        <v>850</v>
       </c>
       <c r="F1123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1124">
@@ -31892,26 +31892,26 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>12000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1124" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1124" t="n">
-        <v>550</v>
+        <v>1235</v>
       </c>
       <c r="F1124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1125">
@@ -31920,26 +31920,26 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>61000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1125" t="n">
-        <v>900</v>
+        <v>195</v>
       </c>
       <c r="E1125" t="n">
-        <v>850</v>
+        <v>252</v>
       </c>
       <c r="F1125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1126">
@@ -31948,26 +31948,26 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Dijual Cepat Mendekati NJOP Rumah di Pondok Indah (Dalam Portal) Luas 1235M2.hanya Rp.36.4jt/M</t>
+          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>45000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1126" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1126" t="n">
-        <v>1235</v>
+        <v>379</v>
       </c>
       <c r="F1126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1127">
@@ -31976,26 +31976,26 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Dijual Murah Area Senopati Rumah untuk Hunian / Kantor / Klinik / Usaha Luas 252M Jalan Lebar Rp 14 M</t>
+          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>14000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>195</v>
+        <v>800</v>
       </c>
       <c r="E1127" t="n">
-        <v>252</v>
+        <v>604</v>
       </c>
       <c r="F1127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1128">
@@ -32004,17 +32004,17 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Dijua Murah Rumah Depan Taman di Kebayoran Baru. Luas 379M Lokasi Bagus</t>
+          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>21000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1128" t="n">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="F1128" t="n">
         <v>4</v>
@@ -32023,7 +32023,7 @@
         <v>3</v>
       </c>
       <c r="H1128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,23 +32032,23 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lux di Mega Kuningan (Dalam Komplek) Luas.tanah 604M2 Rp 40 M Nego</t>
+          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>40000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E1129" t="n">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="F1129" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1129" t="n">
         <v>4</v>
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah di Kebayoran Baru. Lingkungan Seperti Komplek(Gated) . Jalan Lebar dan Tenang. Luas.293m Rp 15 M (Rp 51.1Jt/M Nego)</t>
+          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>15000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1130" t="n">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="F1130" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1130" t="n">
         <v>3</v>
       </c>
       <c r="H1130" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,26 +32088,26 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive Di Kawasan Elit Kemang Jaksel</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>13500000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1131" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="F1131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1132">
@@ -32116,26 +32116,26 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Area Pakubuwono Kebayoran Baru</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>27000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>301</v>
+        <v>850</v>
       </c>
       <c r="E1132" t="n">
-        <v>469</v>
+        <v>1925</v>
       </c>
       <c r="F1132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1132" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1132" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1133">
@@ -32144,26 +32144,26 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>21000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>600</v>
+        <v>882</v>
       </c>
       <c r="E1133" t="n">
-        <v>630</v>
+        <v>1845</v>
       </c>
       <c r="F1133" t="n">
         <v>5</v>
       </c>
       <c r="G1133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,26 +32172,26 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>42000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>850</v>
+        <v>250</v>
       </c>
       <c r="E1134" t="n">
-        <v>1925</v>
+        <v>140</v>
       </c>
       <c r="F1134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1134" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1135">
@@ -32200,26 +32200,26 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>71900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="E1135" t="n">
-        <v>1845</v>
+        <v>1925</v>
       </c>
       <c r="F1135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1135" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,26 +32228,26 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>6500000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1136" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="F1136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1137">
@@ -32256,26 +32256,26 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>42000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>850</v>
+        <v>325</v>
       </c>
       <c r="E1137" t="n">
-        <v>1925</v>
+        <v>696</v>
       </c>
       <c r="F1137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1137" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1138">
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>49000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>1100</v>
+        <v>880</v>
       </c>
       <c r="E1138" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="F1138" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1138" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Cantik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>13000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1139" t="n">
-        <v>696</v>
+        <v>187</v>
       </c>
       <c r="F1139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,26 +32340,26 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>62000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1140" t="n">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="E1140" t="n">
-        <v>1000</v>
+        <v>692</v>
       </c>
       <c r="F1140" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1140" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1140" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1141">
@@ -32368,23 +32368,23 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>4990000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1141" t="n">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="F1141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1141" t="n">
         <v>2</v>
@@ -32396,26 +32396,26 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>13800000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>407</v>
+        <v>1050</v>
       </c>
       <c r="E1142" t="n">
-        <v>692</v>
+        <v>627</v>
       </c>
       <c r="F1142" t="n">
         <v>5</v>
       </c>
       <c r="G1142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1142" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,26 +32424,26 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Lokasi Strategis Dekat Kemang dan Pejaten dan Mampang Prapatan Area Kalibata Mampang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>13900000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1143" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E1143" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F1143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1144">
@@ -32452,26 +32452,26 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>44000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>1050</v>
+        <v>325</v>
       </c>
       <c r="E1144" t="n">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="F1144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1145">
@@ -32480,26 +32480,26 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>31900000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E1145" t="n">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="F1145" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,26 +32508,26 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>13000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1146" t="n">
-        <v>696</v>
+        <v>246</v>
       </c>
       <c r="F1146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1146" t="n">
         <v>3</v>
       </c>
       <c r="H1146" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1147">
@@ -32536,26 +32536,26 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>7090000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1147" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1147" t="n">
-        <v>76</v>
+        <v>510</v>
       </c>
       <c r="F1147" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1147" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1148">
@@ -32564,23 +32564,23 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>7500000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="E1148" t="n">
-        <v>246</v>
+        <v>32</v>
       </c>
       <c r="F1148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1148" t="n">
         <v>1</v>
@@ -32592,26 +32592,26 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>7300000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>600</v>
+        <v>232</v>
       </c>
       <c r="E1149" t="n">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="F1149" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1149" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,23 +32620,23 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>998000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="E1150" t="n">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="F1150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1150" t="n">
         <v>1</v>
@@ -32648,23 +32648,23 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>22000000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="E1151" t="n">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="F1151" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1151" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H1151" t="n">
         <v>1</v>
@@ -32676,23 +32676,23 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>6250000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="E1152" t="n">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="F1152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1152" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1152" t="n">
         <v>1</v>
@@ -32704,26 +32704,26 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>7200000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="E1153" t="n">
-        <v>196</v>
+        <v>675</v>
       </c>
       <c r="F1153" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G1153" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H1153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1154">
@@ -32732,26 +32732,26 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>2600000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>88</v>
+        <v>375</v>
       </c>
       <c r="E1154" t="n">
-        <v>55</v>
+        <v>534</v>
       </c>
       <c r="F1154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1155">
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>65000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="E1155" t="n">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="F1155" t="n">
         <v>4</v>
       </c>
       <c r="G1155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,26 +32788,26 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>23000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="E1156" t="n">
-        <v>534</v>
+        <v>70</v>
       </c>
       <c r="F1156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1157">
@@ -32816,23 +32816,23 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>15500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>928</v>
+        <v>1350</v>
       </c>
       <c r="E1157" t="n">
-        <v>378</v>
+        <v>863</v>
       </c>
       <c r="F1157" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1157" t="n">
         <v>1</v>
@@ -32844,23 +32844,23 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>2830000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>112</v>
+        <v>280</v>
       </c>
       <c r="E1158" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F1158" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1158" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1158" t="n">
         <v>1</v>
@@ -32872,23 +32872,23 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>38000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>1350</v>
+        <v>130</v>
       </c>
       <c r="E1159" t="n">
-        <v>863</v>
+        <v>117</v>
       </c>
       <c r="F1159" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1159" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1159" t="n">
         <v>1</v>
@@ -32900,26 +32900,26 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>8800000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>280</v>
+        <v>1600</v>
       </c>
       <c r="E1160" t="n">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="F1160" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1160" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1160" t="n">
         <v>6</v>
-      </c>
-      <c r="H1160" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="1161">
@@ -32928,26 +32928,26 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>2600000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="E1161" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="F1161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1162">
@@ -32956,26 +32956,26 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>68000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="E1162" t="n">
-        <v>1050</v>
+        <v>150</v>
       </c>
       <c r="F1162" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1162" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1162" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,23 +32984,23 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>22000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>182</v>
+        <v>600</v>
       </c>
       <c r="E1163" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="F1163" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1163" t="n">
         <v>2</v>
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>4800000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1164" t="n">
         <v>300</v>
       </c>
       <c r="E1164" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F1164" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,23 +33040,23 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>13500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>600</v>
+        <v>262</v>
       </c>
       <c r="E1165" t="n">
-        <v>304</v>
+        <v>161</v>
       </c>
       <c r="F1165" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1165" t="n">
         <v>2</v>
@@ -33068,23 +33068,23 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>14500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1166" t="n">
-        <v>240</v>
+        <v>1554</v>
       </c>
       <c r="F1166" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1166" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1166" t="n">
         <v>4</v>
@@ -33096,17 +33096,17 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>8500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="E1167" t="n">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="F1167" t="n">
         <v>4</v>
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>New House Full Furnished Kemang Selatan</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>52500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E1168" t="n">
-        <v>1554</v>
+        <v>518</v>
       </c>
       <c r="F1168" t="n">
         <v>7</v>
       </c>
       <c r="G1168" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H1168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,17 +33152,17 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>6900000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1169" t="n">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="F1169" t="n">
         <v>4</v>
@@ -33180,26 +33180,26 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>New House Full Furnished Kemang Selatan</t>
+          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>38000000000</v>
+        <v>2950000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>760</v>
+        <v>200</v>
       </c>
       <c r="E1170" t="n">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="F1170" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1170" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1171">
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>7800000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1171" t="n">
-        <v>160</v>
+        <v>351</v>
       </c>
       <c r="F1171" t="n">
         <v>4</v>
       </c>
       <c r="G1171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,23 +33236,23 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
+          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2950000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E1172" t="n">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="F1172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1172" t="n">
         <v>1</v>
@@ -33264,17 +33264,17 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Brand New House Modern Design With Pool Cilandak</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>34500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>500</v>
+        <v>428</v>
       </c>
       <c r="E1173" t="n">
-        <v>351</v>
+        <v>204</v>
       </c>
       <c r="F1173" t="n">
         <v>4</v>
@@ -33283,7 +33283,7 @@
         <v>3</v>
       </c>
       <c r="H1173" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
+          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>2500000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="E1174" t="n">
-        <v>50</v>
+        <v>866</v>
       </c>
       <c r="F1174" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1174" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Brand New House Modern Design With Pool Cilandak</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>9800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>428</v>
+        <v>140</v>
       </c>
       <c r="E1175" t="n">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="F1175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
+          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>37000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E1176" t="n">
-        <v>866</v>
+        <v>650</v>
       </c>
       <c r="F1176" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1176" t="n">
         <v>6</v>
-      </c>
-      <c r="G1176" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1176" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,23 +33376,23 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2400000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>140</v>
+        <v>1115</v>
       </c>
       <c r="E1177" t="n">
-        <v>105</v>
+        <v>759</v>
       </c>
       <c r="F1177" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1177" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1177" t="n">
         <v>2</v>
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
+          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>45000000000</v>
+        <v>4550000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E1178" t="n">
-        <v>650</v>
+        <v>197</v>
       </c>
       <c r="F1178" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1178" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1178" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>60000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>1115</v>
+        <v>580</v>
       </c>
       <c r="E1179" t="n">
-        <v>759</v>
+        <v>344</v>
       </c>
       <c r="F1179" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G1179" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H1179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,26 +33460,26 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
+          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>4550000000</v>
+        <v>31200000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E1180" t="n">
-        <v>197</v>
+        <v>1200</v>
       </c>
       <c r="F1180" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G1180" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1180" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1181">
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>8000000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>580</v>
+        <v>198</v>
       </c>
       <c r="E1181" t="n">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="F1181" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G1181" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H1181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
+          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>31200000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>1000</v>
+        <v>616</v>
       </c>
       <c r="E1182" t="n">
-        <v>1200</v>
+        <v>383</v>
       </c>
       <c r="F1182" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G1182" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1182" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,23 +33544,23 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>3850000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>198</v>
+        <v>400</v>
       </c>
       <c r="E1183" t="n">
-        <v>105</v>
+        <v>543</v>
       </c>
       <c r="F1183" t="n">
         <v>5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1183" t="n">
         <v>2</v>
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>27000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>301</v>
+        <v>500</v>
       </c>
       <c r="E1184" t="n">
-        <v>469</v>
+        <v>1028</v>
       </c>
       <c r="F1184" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1184" t="n">
         <v>4</v>
       </c>
       <c r="H1184" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,17 +33600,17 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>16000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>616</v>
+        <v>250</v>
       </c>
       <c r="E1185" t="n">
-        <v>383</v>
+        <v>304</v>
       </c>
       <c r="F1185" t="n">
         <v>4</v>
@@ -33619,7 +33619,7 @@
         <v>3</v>
       </c>
       <c r="H1185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1186">
@@ -33628,26 +33628,26 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>21000000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1186" t="n">
-        <v>543</v>
+        <v>793</v>
       </c>
       <c r="F1186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1186" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1186" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1187">
@@ -33656,17 +33656,17 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>18500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>500</v>
+        <v>559</v>
       </c>
       <c r="E1187" t="n">
-        <v>1028</v>
+        <v>572</v>
       </c>
       <c r="F1187" t="n">
         <v>5</v>
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>5550000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1188" t="n">
-        <v>304</v>
+        <v>1000</v>
       </c>
       <c r="F1188" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1188" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
+          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>15300000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="E1189" t="n">
-        <v>793</v>
+        <v>260</v>
       </c>
       <c r="F1189" t="n">
         <v>4</v>
       </c>
       <c r="G1189" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1189" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>24000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>559</v>
+        <v>760</v>
       </c>
       <c r="E1190" t="n">
-        <v>572</v>
+        <v>517</v>
       </c>
       <c r="F1190" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1190" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
+          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>35000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E1191" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="F1191" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1191" t="n">
         <v>4</v>
       </c>
       <c r="H1191" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
+          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>11000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>310</v>
+        <v>650</v>
       </c>
       <c r="E1192" t="n">
-        <v>260</v>
+        <v>544</v>
       </c>
       <c r="F1192" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1192" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
+          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>38000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>760</v>
+        <v>250</v>
       </c>
       <c r="E1193" t="n">
-        <v>517</v>
+        <v>348</v>
       </c>
       <c r="F1193" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1193" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,26 +33852,26 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
+          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>13900000000</v>
+        <v>990000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="E1194" t="n">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="F1194" t="n">
         <v>4</v>
       </c>
       <c r="G1194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1195">
@@ -33880,23 +33880,23 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
+          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>12500000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="E1195" t="n">
-        <v>544</v>
+        <v>347</v>
       </c>
       <c r="F1195" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1195" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1195" t="n">
         <v>2</v>
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
+          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>12000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1196" t="n">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="F1196" t="n">
         <v>4</v>
       </c>
       <c r="G1196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,20 +33936,20 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>990000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>125</v>
+        <v>288</v>
       </c>
       <c r="E1197" t="n">
-        <v>72</v>
+        <v>598</v>
       </c>
       <c r="F1197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1197" t="n">
         <v>3</v>
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>10000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="E1198" t="n">
-        <v>347</v>
+        <v>260</v>
       </c>
       <c r="F1198" t="n">
         <v>4</v>
       </c>
       <c r="G1198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,17 +33992,17 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>1900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>150</v>
+        <v>431</v>
       </c>
       <c r="E1199" t="n">
-        <v>105</v>
+        <v>874</v>
       </c>
       <c r="F1199" t="n">
         <v>4</v>
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>15500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E1200" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="F1200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,17 +34048,17 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>17000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="E1201" t="n">
-        <v>598</v>
+        <v>30</v>
       </c>
       <c r="F1201" t="n">
         <v>3</v>
@@ -34067,7 +34067,7 @@
         <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,23 +34076,23 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>11000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1202" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1202" t="n">
         <v>310</v>
       </c>
-      <c r="E1202" t="n">
-        <v>260</v>
-      </c>
       <c r="F1202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1202" t="n">
         <v>1</v>
@@ -34104,17 +34104,17 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1203" t="n">
         <v>15000000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="E1203" t="n">
-        <v>874</v>
+        <v>515</v>
       </c>
       <c r="F1203" t="n">
         <v>4</v>
@@ -34123,7 +34123,7 @@
         <v>4</v>
       </c>
       <c r="H1203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>8500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>440</v>
+        <v>636</v>
       </c>
       <c r="E1204" t="n">
-        <v>200</v>
+        <v>938</v>
       </c>
       <c r="F1204" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1204" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1204" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,23 +34160,23 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>2600000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="E1205" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F1205" t="n">
         <v>3</v>
       </c>
       <c r="G1205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1205" t="n">
         <v>1</v>
@@ -34188,26 +34188,26 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>15000000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E1206" t="n">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="F1206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1206" t="n">
         <v>4</v>
       </c>
       <c r="H1206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,17 +34216,17 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="E1207" t="n">
-        <v>515</v>
+        <v>648</v>
       </c>
       <c r="F1207" t="n">
         <v>4</v>
@@ -34235,7 +34235,7 @@
         <v>4</v>
       </c>
       <c r="H1207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,26 +34244,26 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>40000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="E1208" t="n">
-        <v>938</v>
+        <v>307</v>
       </c>
       <c r="F1208" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1208" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>6750000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E1209" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="F1209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>3700000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1210" t="n">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="F1210" t="n">
         <v>4</v>
       </c>
       <c r="G1210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>10000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="E1211" t="n">
-        <v>648</v>
+        <v>231</v>
       </c>
       <c r="F1211" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>15000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="E1212" t="n">
-        <v>307</v>
+        <v>104</v>
       </c>
       <c r="F1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>2600000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E1213" t="n">
-        <v>113</v>
+        <v>582</v>
       </c>
       <c r="F1213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1213" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>6950000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E1214" t="n">
-        <v>322</v>
+        <v>209</v>
       </c>
       <c r="F1214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1214" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1214" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,23 +34440,23 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>4500000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E1215" t="n">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="F1215" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G1215" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1215" t="n">
         <v>1</v>
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>4900000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="E1216" t="n">
-        <v>104</v>
+        <v>909</v>
       </c>
       <c r="F1216" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1216" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1216" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>32000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="E1217" t="n">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="F1217" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1217" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1217" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>12900000000</v>
+        <v>10300000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>450</v>
+        <v>1</v>
       </c>
       <c r="E1218" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="F1218" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1218" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1218" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,23 +34552,23 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>4000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="E1219" t="n">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="F1219" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1219" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1219" t="n">
         <v>1</v>
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>16000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="E1220" t="n">
-        <v>909</v>
+        <v>563</v>
       </c>
       <c r="F1220" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G1220" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H1220" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>28000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>432</v>
+        <v>193</v>
       </c>
       <c r="E1221" t="n">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="F1221" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1221" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1221" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,23 +34636,23 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>10300000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E1222" t="n">
-        <v>186</v>
+        <v>543</v>
       </c>
       <c r="F1222" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1222" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1222" t="n">
         <v>12</v>
@@ -34664,23 +34664,23 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>1950000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="E1223" t="n">
-        <v>93</v>
+        <v>304</v>
       </c>
       <c r="F1223" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1223" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1223" t="n">
         <v>1</v>
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>55000000000</v>
+        <v>1050000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>400</v>
+        <v>64</v>
       </c>
       <c r="E1224" t="n">
-        <v>563</v>
+        <v>32</v>
       </c>
       <c r="F1224" t="n">
         <v>2</v>
       </c>
       <c r="G1224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1224" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>22500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>193</v>
+        <v>559</v>
       </c>
       <c r="E1225" t="n">
-        <v>283</v>
+        <v>572</v>
       </c>
       <c r="F1225" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1225" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1225" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,23 +34748,23 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>20500000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1226" t="n">
         <v>400</v>
       </c>
       <c r="E1226" t="n">
-        <v>543</v>
+        <v>408</v>
       </c>
       <c r="F1226" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1226" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1226" t="n">
         <v>12</v>
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>5550000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="E1227" t="n">
-        <v>304</v>
+        <v>620</v>
       </c>
       <c r="F1227" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1227" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1227" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>1050000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>64</v>
+        <v>850</v>
       </c>
       <c r="E1228" t="n">
-        <v>32</v>
+        <v>1925</v>
       </c>
       <c r="F1228" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G1228" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H1228" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,23 +34832,23 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>24000000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="E1229" t="n">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="F1229" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1229" t="n">
         <v>51</v>
-      </c>
-      <c r="G1229" t="n">
-        <v>41</v>
       </c>
       <c r="H1229" t="n">
         <v>22</v>
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>16899999999</v>
+        <v>68000000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="E1230" t="n">
-        <v>408</v>
+        <v>1050</v>
       </c>
       <c r="F1230" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="G1230" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H1230" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>45000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>1000</v>
+        <v>325</v>
       </c>
       <c r="E1231" t="n">
-        <v>620</v>
+        <v>348</v>
       </c>
       <c r="F1231" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1231" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1231" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>American Classic House Dalam Town House Di Kemang</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>42000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>850</v>
+        <v>380</v>
       </c>
       <c r="E1232" t="n">
-        <v>1925</v>
+        <v>247</v>
       </c>
       <c r="F1232" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G1232" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="H1232" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>10500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1233" t="n">
-        <v>407</v>
+        <v>260</v>
       </c>
       <c r="F1233" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G1233" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1233" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>68000000000</v>
+        <v>38900000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>1600</v>
+        <v>650</v>
       </c>
       <c r="E1234" t="n">
-        <v>1050</v>
+        <v>932</v>
       </c>
       <c r="F1234" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G1234" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="H1234" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>7500000000</v>
+        <v>6350000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="E1235" t="n">
-        <v>348</v>
+        <v>200</v>
       </c>
       <c r="F1235" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1235" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1235" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>American Classic House Dalam Town House Di Kemang</t>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>8500000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="E1236" t="n">
-        <v>247</v>
+        <v>500</v>
       </c>
       <c r="F1236" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G1236" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1236" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>7000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1237" t="n">
-        <v>260</v>
+        <v>1335</v>
       </c>
       <c r="F1237" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1237" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1237" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>38900000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="E1238" t="n">
-        <v>932</v>
+        <v>1098</v>
       </c>
       <c r="F1238" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="G1238" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H1238" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>6350000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1239" t="n">
-        <v>200</v>
+        <v>936</v>
       </c>
       <c r="F1239" t="n">
         <v>3</v>
       </c>
       <c r="G1239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1239" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>13500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1240" t="n">
         <v>200</v>
       </c>
       <c r="E1240" t="n">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="F1240" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1240" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1240" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>27000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1241" t="n">
-        <v>1335</v>
+        <v>588</v>
       </c>
       <c r="F1241" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G1241" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1241" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>20000000000</v>
+        <v>1250000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="E1242" t="n">
-        <v>1098</v>
+        <v>87</v>
       </c>
       <c r="F1242" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1242" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H1242" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>57000000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E1243" t="n">
-        <v>936</v>
+        <v>1980</v>
       </c>
       <c r="F1243" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="G1243" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1243" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>2900000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1244" t="n">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="F1244" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1244" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1244" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>11500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="E1245" t="n">
-        <v>588</v>
+        <v>30</v>
       </c>
       <c r="F1245" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1245" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1245" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>1250000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="E1246" t="n">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="F1246" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1246" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1246" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>135000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1247" t="n">
-        <v>1980</v>
+        <v>267</v>
       </c>
       <c r="F1247" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G1247" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H1247" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>13500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="E1248" t="n">
-        <v>515</v>
+        <v>202</v>
       </c>
       <c r="F1248" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1248" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1248" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>2500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>135</v>
+        <v>440</v>
       </c>
       <c r="E1249" t="n">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c r="F1249" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1249" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>9000000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1250" t="n">
-        <v>205</v>
+        <v>700</v>
       </c>
       <c r="F1250" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="G1250" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1250" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
+          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>5550000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>400</v>
+        <v>1280</v>
       </c>
       <c r="E1251" t="n">
-        <v>267</v>
+        <v>600</v>
       </c>
       <c r="F1251" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G1251" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="H1251" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>8500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="E1252" t="n">
-        <v>202</v>
+        <v>703</v>
       </c>
       <c r="F1252" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="G1252" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1252" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>8500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>440</v>
+        <v>850</v>
       </c>
       <c r="E1253" t="n">
-        <v>202</v>
+        <v>1925</v>
       </c>
       <c r="F1253" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1253" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1253" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>76000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="E1254" t="n">
-        <v>700</v>
+        <v>88</v>
       </c>
       <c r="F1254" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1254" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1254" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
+          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>16000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>1280</v>
+        <v>72</v>
       </c>
       <c r="E1255" t="n">
-        <v>600</v>
+        <v>81</v>
       </c>
       <c r="F1255" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="G1255" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H1255" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>500</v>
+        <v>317</v>
       </c>
       <c r="E1256" t="n">
-        <v>703</v>
+        <v>419</v>
       </c>
       <c r="F1256" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="G1256" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1256" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
+          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>40000000000</v>
+        <v>2450000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="E1257" t="n">
-        <v>1925</v>
+        <v>90</v>
       </c>
       <c r="F1257" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1257" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1257" t="n">
-        <v>210</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>3100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="E1258" t="n">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="F1258" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1258" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>1500000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="E1259" t="n">
-        <v>81</v>
+        <v>752</v>
       </c>
       <c r="F1259" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="G1259" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H1259" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>18500000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>317</v>
+        <v>800</v>
       </c>
       <c r="E1260" t="n">
-        <v>419</v>
+        <v>1050</v>
       </c>
       <c r="F1260" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="G1260" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1260" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,17 +35728,17 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>2450000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E1261" t="n">
-        <v>90</v>
+        <v>1100</v>
       </c>
       <c r="F1261" t="n">
         <v>4</v>
@@ -35747,7 +35747,7 @@
         <v>4</v>
       </c>
       <c r="H1261" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>7000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>285</v>
+        <v>150</v>
       </c>
       <c r="E1262" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="F1262" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1262" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1262" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>13500000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="E1263" t="n">
-        <v>752</v>
+        <v>370</v>
       </c>
       <c r="F1263" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1263" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1263" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
         </is>
       </c>
       <c r="C1264" t="n">
         <v>23000000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E1264" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="F1264" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="G1264" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1264" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>17000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>400</v>
+        <v>42</v>
       </c>
       <c r="E1265" t="n">
-        <v>1100</v>
+        <v>174</v>
       </c>
       <c r="F1265" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1265" t="n">
         <v>4</v>
       </c>
       <c r="H1265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>1900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="E1266" t="n">
-        <v>100</v>
+        <v>1335</v>
       </c>
       <c r="F1266" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1266" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1266" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>10000000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E1267" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1267" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1267" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
+          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>23000000000</v>
+        <v>35800000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E1268" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F1268" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1268" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1268" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
+          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>4900000000</v>
+        <v>185000000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="E1269" t="n">
-        <v>174</v>
+        <v>1358</v>
       </c>
       <c r="F1269" t="n">
         <v>5</v>
       </c>
       <c r="G1269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1269" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>27000000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E1270" t="n">
-        <v>1335</v>
+        <v>850</v>
       </c>
       <c r="F1270" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1270" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H1270" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
+          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>1420000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E1271" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="F1271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1271" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>35800000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E1272" t="n">
-        <v>800</v>
+        <v>960</v>
       </c>
       <c r="F1272" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1272" t="n">
         <v>4</v>
       </c>
       <c r="H1272" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>185000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E1273" t="n">
-        <v>1358</v>
+        <v>584</v>
       </c>
       <c r="F1273" t="n">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="G1273" t="n">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="H1273" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>61000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E1274" t="n">
-        <v>850</v>
+        <v>1094</v>
       </c>
       <c r="F1274" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1274" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H1274" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>12800000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="E1275" t="n">
-        <v>300</v>
+        <v>1153</v>
       </c>
       <c r="F1275" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1275" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1275" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>21000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="E1276" t="n">
-        <v>960</v>
+        <v>779</v>
       </c>
       <c r="F1276" t="n">
         <v>5</v>
       </c>
       <c r="G1276" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1276" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>40000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>1200</v>
+        <v>262</v>
       </c>
       <c r="E1277" t="n">
-        <v>584</v>
+        <v>161</v>
       </c>
       <c r="F1277" t="n">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="G1277" t="n">
-        <v>182</v>
+        <v>41</v>
       </c>
       <c r="H1277" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>49000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>1200</v>
+        <v>503</v>
       </c>
       <c r="E1278" t="n">
-        <v>1094</v>
+        <v>421</v>
       </c>
       <c r="F1278" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1278" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1278" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>15000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="E1279" t="n">
-        <v>1153</v>
+        <v>260</v>
       </c>
       <c r="F1279" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G1279" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1279" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>9500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="E1280" t="n">
-        <v>779</v>
+        <v>598</v>
       </c>
       <c r="F1280" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1280" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1280" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>8500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="E1281" t="n">
-        <v>161</v>
+        <v>530</v>
       </c>
       <c r="F1281" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1281" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1281" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>6900000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>375</v>
+        <v>98</v>
       </c>
       <c r="E1282" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F1282" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1282" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1282" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>18500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>503</v>
+        <v>360</v>
       </c>
       <c r="E1283" t="n">
-        <v>421</v>
+        <v>127</v>
       </c>
       <c r="F1283" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1283" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1283" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>11000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="E1284" t="n">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="F1284" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G1284" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1284" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,23 +36400,23 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>17000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="E1285" t="n">
-        <v>598</v>
+        <v>330</v>
       </c>
       <c r="F1285" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1285" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1285" t="n">
         <v>22</v>
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>15000000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>600</v>
+        <v>208</v>
       </c>
       <c r="E1286" t="n">
-        <v>530</v>
+        <v>394</v>
       </c>
       <c r="F1286" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G1286" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="H1286" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>979000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="E1287" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F1287" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1287" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1287" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>4900000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="E1288" t="n">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="F1288" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1288" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="H1288" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,26 +36512,26 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>6900000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>375</v>
+        <v>160</v>
       </c>
       <c r="E1289" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="F1289" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1289" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1289" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1290">
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>12900000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="E1290" t="n">
-        <v>307</v>
+        <v>40</v>
       </c>
       <c r="F1290" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1290" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1290" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>10000000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E1291" t="n">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="F1291" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1291" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>5750000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>208</v>
+        <v>810</v>
       </c>
       <c r="E1292" t="n">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="F1292" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1292" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1292" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>3000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>225</v>
+        <v>850</v>
       </c>
       <c r="E1293" t="n">
-        <v>108</v>
+        <v>1925</v>
       </c>
       <c r="F1293" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G1293" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1293" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>850000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>80</v>
+        <v>1374</v>
       </c>
       <c r="E1294" t="n">
-        <v>40</v>
+        <v>1493</v>
       </c>
       <c r="F1294" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G1294" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H1294" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>1900000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="E1295" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="F1295" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1295" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1295" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,17 +36708,17 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>829000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="E1296" t="n">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="F1296" t="n">
         <v>3</v>
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>1420000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="E1297" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="F1297" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1297" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>48000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1298" t="n">
-        <v>810</v>
+        <v>600</v>
       </c>
       <c r="E1298" t="n">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="F1298" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1298" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,26 +36792,26 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Gandaria Dekat Gandaria City</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>42000000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E1299" t="n">
-        <v>1925</v>
+        <v>247</v>
       </c>
       <c r="F1299" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G1299" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1299" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1300">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>26000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>1374</v>
+        <v>720</v>
       </c>
       <c r="E1300" t="n">
-        <v>1493</v>
+        <v>634</v>
       </c>
       <c r="F1300" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G1300" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="H1300" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>1200000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>110</v>
+        <v>367</v>
       </c>
       <c r="E1301" t="n">
-        <v>180</v>
+        <v>437</v>
       </c>
       <c r="F1301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1301" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>1900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>144</v>
+        <v>569</v>
       </c>
       <c r="E1302" t="n">
-        <v>232</v>
+        <v>330</v>
       </c>
       <c r="F1302" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1302" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>4800000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="E1303" t="n">
-        <v>340</v>
+        <v>38</v>
       </c>
       <c r="F1303" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1303" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Rumah, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>16899999999</v>
+        <v>160000000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>600</v>
+        <v>1450</v>
       </c>
       <c r="E1304" t="n">
-        <v>570</v>
+        <v>1620</v>
       </c>
       <c r="F1304" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1304" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H1304" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,23 +36960,23 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Rumah Gandaria Dekat Gandaria City</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>10500000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="E1305" t="n">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="F1305" t="n">
         <v>41</v>
       </c>
       <c r="G1305" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1305" t="n">
         <v>11</v>
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>37000000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>720</v>
+        <v>230</v>
       </c>
       <c r="E1306" t="n">
-        <v>634</v>
+        <v>200</v>
       </c>
       <c r="F1306" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1306" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1306" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>9900000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>367</v>
+        <v>800</v>
       </c>
       <c r="E1307" t="n">
-        <v>437</v>
+        <v>1980</v>
       </c>
       <c r="F1307" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="G1307" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H1307" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1308" t="n">
         <v>8000000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>569</v>
+        <v>300</v>
       </c>
       <c r="E1308" t="n">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="F1308" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1308" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,26 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>850000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="E1309" t="n">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="F1309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1309" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1310">
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Rumah, di Pondok Indah, Bukit Golf</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>160000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>1450</v>
+        <v>400</v>
       </c>
       <c r="E1310" t="n">
-        <v>1620</v>
+        <v>945</v>
       </c>
       <c r="F1310" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1310" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1310" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>3900000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="E1311" t="n">
-        <v>201</v>
+        <v>865</v>
       </c>
       <c r="F1311" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1311" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1311" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,23 +37156,23 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>6300000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>230</v>
+        <v>438</v>
       </c>
       <c r="E1312" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1312" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1312" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1312" t="n">
         <v>2</v>
@@ -37184,26 +37184,26 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>135000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1313" t="n">
-        <v>1980</v>
+        <v>515</v>
       </c>
       <c r="F1313" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G1313" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H1313" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1314">
@@ -37212,26 +37212,26 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>8000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>300</v>
+        <v>560</v>
       </c>
       <c r="E1314" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="F1314" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G1314" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1314" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,26 +37240,26 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>4700000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="E1315" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="F1315" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1315" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1315" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1316">
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>57000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="E1316" t="n">
-        <v>945</v>
+        <v>448</v>
       </c>
       <c r="F1316" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1316" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1316" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,26 +37296,26 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah Lokasi Strategis SHM di Tebet Timur</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>50000000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="E1317" t="n">
-        <v>865</v>
+        <v>147</v>
       </c>
       <c r="F1317" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1317" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1317" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318">
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>Jarang Ada, Dijual Rumah Murah Sekali 2Lt Akses Mobil Tebet SHM</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>9100000000</v>
+        <v>1350000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>438</v>
+        <v>110</v>
       </c>
       <c r="E1318" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="F1318" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1318" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Angsuran Pasti Sampai Lunas : Dp 0, Free BPHTB, AJB, Bbn, By Ntrs</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>13500000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="E1319" t="n">
-        <v>515</v>
+        <v>63</v>
       </c>
       <c r="F1319" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1319" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H1319" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,26 +37380,26 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Jual Cepat: Rumah Lama Murah Dibangka Kemang Jak Sel</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>22500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>560</v>
+        <v>340</v>
       </c>
       <c r="E1320" t="n">
-        <v>248</v>
+        <v>489</v>
       </c>
       <c r="F1320" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G1320" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1320" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1321">
@@ -37408,26 +37408,26 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Rumah Dilebak Bulus Hook Dekat MRT Lebak Bulus SHM</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>8500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>262</v>
+        <v>380</v>
       </c>
       <c r="E1321" t="n">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="F1321" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1321" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1321" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1322">
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>24000000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>341</v>
+        <v>200</v>
       </c>
       <c r="E1322" t="n">
-        <v>448</v>
+        <v>160</v>
       </c>
       <c r="F1322" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G1322" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1322" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Lokasi Strategis SHM di Tebet Timur</t>
+          <t>Rumah Industrial Ada Pool Dalam Komplek Dilebak Bulus SHM</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>2700000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="E1323" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F1323" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1323" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Jarang Ada, Dijual Rumah Murah Sekali 2Lt Akses Mobil Tebet SHM</t>
+          <t>Rumah Baru Full Furnised Siap Huni di Permata Hijaj</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>1350000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="E1324" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F1324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1324" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1324" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+          <t>Rumah di Pondok Indah Jakarta Selatan Jalan Besar Lingkungan Asri SHM</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>15000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1325" t="n">
-        <v>700</v>
+        <v>394</v>
       </c>
       <c r="F1325" t="n">
         <v>5</v>
       </c>
       <c r="G1325" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1325" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Angsuran Pasti Sampai Lunas : Dp 0, Free BPHTB, AJB, Bbn, By Ntrs</t>
+          <t>Dijual Cepat Rumah di Tebet Utara Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>750000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="E1326" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="F1326" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1326" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Jual Cepat: Rumah Lama Murah Dibangka Kemang Jak Sel</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Termurah</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>8000000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>340</v>
+        <v>143</v>
       </c>
       <c r="E1327" t="n">
-        <v>489</v>
+        <v>92</v>
       </c>
       <c r="F1327" t="n">
         <v>4</v>
       </c>
       <c r="G1327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1327" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,26 +37604,26 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Rumah Dilebak Bulus Hook Dekat MRT Lebak Bulus SHM</t>
+          <t>Rumah Baru Siap Huni Deket MRT Lebak Bulus Dalam Cluster Dekat Tol</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>6500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>380</v>
+        <v>134</v>
       </c>
       <c r="E1328" t="n">
-        <v>320</v>
+        <v>127</v>
       </c>
       <c r="F1328" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1328" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1328" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1329">
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>6750000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="E1329" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F1329" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1329" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1329" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,23 +37660,23 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah Industrial Ada Pool Dalam Komplek Dilebak Bulus SHM</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>5500000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>337</v>
+        <v>149</v>
       </c>
       <c r="E1330" t="n">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="F1330" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1330" t="n">
         <v>2</v>
@@ -37688,26 +37688,26 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Rumah Baru Full Furnised Siap Huni di Permata Hijaj</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>7500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>250</v>
+        <v>117</v>
       </c>
       <c r="E1331" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F1331" t="n">
         <v>3</v>
       </c>
       <c r="G1331" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1331" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1332">
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Jakarta Selatan Jalan Besar Lingkungan Asri SHM</t>
+          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>16000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E1332" t="n">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="F1332" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1332" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1332" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Tebet Utara Jakarta Selatan Siap Huni</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>4000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>128</v>
+        <v>282</v>
       </c>
       <c r="E1333" t="n">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="F1333" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1333" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1333" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,23 +37772,23 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Termurah</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>2700000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E1334" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F1334" t="n">
         <v>4</v>
       </c>
       <c r="G1334" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1334" t="n">
         <v>2</v>
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni Deket MRT Lebak Bulus Dalam Cluster Dekat Tol</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>2000000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>134</v>
+        <v>325</v>
       </c>
       <c r="E1335" t="n">
-        <v>127</v>
+        <v>696</v>
       </c>
       <c r="F1335" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1335" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1335" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>1700000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>129</v>
+        <v>340</v>
       </c>
       <c r="E1336" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F1336" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1336" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>3800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="E1337" t="n">
-        <v>90</v>
+        <v>261</v>
       </c>
       <c r="F1337" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1337" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1337" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>1900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>117</v>
+        <v>510</v>
       </c>
       <c r="E1338" t="n">
-        <v>70</v>
+        <v>423</v>
       </c>
       <c r="F1338" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1338" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1338" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>2550000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="E1339" t="n">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="F1339" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G1339" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1339" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>5800000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="E1340" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F1340" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1340" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1340" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>1800000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="E1341" t="n">
-        <v>94</v>
+        <v>1000</v>
       </c>
       <c r="F1341" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1341" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1341" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>7090000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>60</v>
+        <v>550</v>
       </c>
       <c r="E1342" t="n">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="F1342" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1342" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1342" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>11800000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="E1343" t="n">
-        <v>696</v>
+        <v>261</v>
       </c>
       <c r="F1343" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1343" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H1343" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>15500000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>340</v>
+        <v>457</v>
       </c>
       <c r="E1344" t="n">
-        <v>350</v>
+        <v>494</v>
       </c>
       <c r="F1344" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1344" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1344" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>2500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>135</v>
+        <v>810</v>
       </c>
       <c r="E1345" t="n">
-        <v>30</v>
+        <v>370</v>
       </c>
       <c r="F1345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1345" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>9800000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>500</v>
+        <v>584</v>
       </c>
       <c r="E1346" t="n">
-        <v>261</v>
+        <v>682</v>
       </c>
       <c r="F1346" t="n">
         <v>4</v>
       </c>
       <c r="G1346" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1346" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>11500000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>510</v>
+        <v>250</v>
       </c>
       <c r="E1347" t="n">
-        <v>423</v>
+        <v>241</v>
       </c>
       <c r="F1347" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1347" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1347" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>27000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>301</v>
+        <v>1000</v>
       </c>
       <c r="E1348" t="n">
-        <v>466</v>
+        <v>1038</v>
       </c>
       <c r="F1348" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1348" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H1348" t="n">
-        <v>29</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,23 +38192,23 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>2600000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E1349" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="F1349" t="n">
         <v>2</v>
       </c>
       <c r="G1349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1349" t="n">
         <v>1</v>
@@ -38220,23 +38220,23 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>8000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>250</v>
+        <v>564</v>
       </c>
       <c r="E1350" t="n">
-        <v>165</v>
+        <v>726</v>
       </c>
       <c r="F1350" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G1350" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1350" t="n">
         <v>24</v>
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>2000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="E1351" t="n">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="F1351" t="n">
         <v>3</v>
       </c>
       <c r="G1351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1351" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,26 +38276,26 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>27500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E1352" t="n">
-        <v>1000</v>
+        <v>197</v>
       </c>
       <c r="F1352" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1352" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1352" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1353">
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>2830000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E1353" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F1353" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1353" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>2000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="E1354" t="n">
-        <v>60</v>
+        <v>570</v>
       </c>
       <c r="F1354" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1354" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1354" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>25000000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="E1355" t="n">
-        <v>450</v>
+        <v>230</v>
       </c>
       <c r="F1355" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1355" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1355" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>9500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1356" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F1356" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1356" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H1356" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>1900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E1357" t="n">
         <v>60</v>
       </c>
       <c r="F1357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1357" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>53000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>457</v>
+        <v>125</v>
       </c>
       <c r="E1358" t="n">
-        <v>494</v>
+        <v>93</v>
       </c>
       <c r="F1358" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1358" t="n">
         <v>4</v>
       </c>
       <c r="H1358" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>48000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>810</v>
+        <v>60</v>
       </c>
       <c r="E1359" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1359" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1359" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>28000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>584</v>
+        <v>1000</v>
       </c>
       <c r="E1360" t="n">
-        <v>682</v>
+        <v>1038</v>
       </c>
       <c r="F1360" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1360" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,26 +38528,26 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>9200000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="E1361" t="n">
-        <v>241</v>
+        <v>350</v>
       </c>
       <c r="F1361" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1361" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1361" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1362">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>90000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>1000</v>
+        <v>135</v>
       </c>
       <c r="E1362" t="n">
-        <v>1038</v>
+        <v>30</v>
       </c>
       <c r="F1362" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1362" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H1362" t="n">
-        <v>412</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,23 +38584,23 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>858000000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>40</v>
+        <v>395</v>
       </c>
       <c r="E1363" t="n">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="F1363" t="n">
         <v>2</v>
       </c>
       <c r="G1363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1363" t="n">
         <v>1</v>
@@ -38612,26 +38612,26 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>48000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>564</v>
+        <v>375</v>
       </c>
       <c r="E1364" t="n">
-        <v>726</v>
+        <v>76</v>
       </c>
       <c r="F1364" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1364" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H1364" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1365">
@@ -38640,26 +38640,26 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>16500000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1365" t="n">
-        <v>284</v>
+        <v>600</v>
       </c>
       <c r="F1365" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1365" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1365" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1366">
@@ -38668,26 +38668,26 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>3500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E1366" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="F1366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1367">
@@ -38696,26 +38696,26 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>5500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E1367" t="n">
-        <v>270</v>
+        <v>175</v>
       </c>
       <c r="F1367" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1367" t="n">
         <v>2</v>
       </c>
       <c r="H1367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1368">
@@ -38724,26 +38724,26 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>12500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="E1368" t="n">
-        <v>497</v>
+        <v>165</v>
       </c>
       <c r="F1368" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1368" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1369">
@@ -38752,26 +38752,26 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>9000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="E1369" t="n">
-        <v>414</v>
+        <v>60</v>
       </c>
       <c r="F1369" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1369" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1369" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1370">
@@ -38780,26 +38780,26 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>25000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="E1370" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="F1370" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1370" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1370" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1371">
@@ -38808,17 +38808,17 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>11000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="E1371" t="n">
-        <v>498</v>
+        <v>60</v>
       </c>
       <c r="F1371" t="n">
         <v>3</v>
@@ -38827,7 +38827,7 @@
         <v>2</v>
       </c>
       <c r="H1371" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1372">
@@ -38836,26 +38836,26 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E1372" t="n">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="F1372" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1372" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1372" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1373">
@@ -38864,26 +38864,26 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>4800000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="E1373" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F1373" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1373" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1374">
@@ -38892,26 +38892,26 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>11500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1374" t="n">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="F1374" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1374" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1374" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1375">
@@ -38920,26 +38920,26 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>9800000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>260</v>
+        <v>720</v>
       </c>
       <c r="E1375" t="n">
-        <v>230</v>
+        <v>634</v>
       </c>
       <c r="F1375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1375" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1375" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1376">
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>3500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>147</v>
+        <v>400</v>
       </c>
       <c r="E1376" t="n">
-        <v>66</v>
+        <v>750</v>
       </c>
       <c r="F1376" t="n">
         <v>3</v>
       </c>
       <c r="G1376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,26 +38976,26 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>6950000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E1377" t="n">
-        <v>339</v>
+        <v>498</v>
       </c>
       <c r="F1377" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1377" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1377" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1378">
@@ -39004,26 +39004,26 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>28700000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>250</v>
+        <v>124</v>
       </c>
       <c r="E1378" t="n">
-        <v>479</v>
+        <v>124</v>
       </c>
       <c r="F1378" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1378" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1378" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1379">
@@ -39032,26 +39032,26 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>6900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1379" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F1379" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1379" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1379" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1380">
@@ -39060,26 +39060,26 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>17000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>616</v>
+        <v>318</v>
       </c>
       <c r="E1380" t="n">
-        <v>383</v>
+        <v>497</v>
       </c>
       <c r="F1380" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1380" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1380" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1381">
@@ -39088,17 +39088,17 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>16899999999</v>
+        <v>9000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="E1381" t="n">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="F1381" t="n">
         <v>4</v>
@@ -39107,7 +39107,7 @@
         <v>4</v>
       </c>
       <c r="H1381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1382">
@@ -39116,26 +39116,26 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>5500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>350</v>
+        <v>1200</v>
       </c>
       <c r="E1382" t="n">
-        <v>272</v>
+        <v>1000</v>
       </c>
       <c r="F1382" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1382" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1382" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1383">
@@ -39144,26 +39144,26 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>2000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="E1383" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F1383" t="n">
         <v>3</v>
       </c>
       <c r="G1383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1383" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1384">
@@ -39172,26 +39172,26 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>1650000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="E1384" t="n">
-        <v>65</v>
+        <v>339</v>
       </c>
       <c r="F1384" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1384" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1385">
@@ -39200,26 +39200,530 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>1900000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E1385" t="n">
-        <v>93</v>
+        <v>479</v>
       </c>
       <c r="F1385" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1385" t="n">
         <v>4</v>
       </c>
       <c r="H1385" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>16899999999</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>616</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>383</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>16500000000</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>1391</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>52000000000</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>564</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>726</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>1392</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>1393</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>1127</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>5900000000</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>301</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>1396</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>22900000000</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>315</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>430</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>1398</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>258</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>1399</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>206</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>384</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>19800000000</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>960</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1403"/>
+  <dimension ref="A1:H1435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32956,23 +32956,23 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>4800000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1162" t="n">
-        <v>150</v>
+        <v>304</v>
       </c>
       <c r="F1162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1162" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1162" t="n">
         <v>2</v>
@@ -32984,26 +32984,26 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>13500000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E1163" t="n">
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="F1163" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1164">
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>14500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="E1164" t="n">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="F1164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>8500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>262</v>
+        <v>500</v>
       </c>
       <c r="E1165" t="n">
-        <v>161</v>
+        <v>1554</v>
       </c>
       <c r="F1165" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,26 +33068,26 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>52500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E1166" t="n">
-        <v>1554</v>
+        <v>76</v>
       </c>
       <c r="F1166" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1167">
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>New House Full Furnished Kemang Selatan</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>6900000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>375</v>
+        <v>760</v>
       </c>
       <c r="E1167" t="n">
-        <v>76</v>
+        <v>518</v>
       </c>
       <c r="F1167" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1167" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>New House Full Furnished Kemang Selatan</t>
+          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>38000000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>760</v>
+        <v>200</v>
       </c>
       <c r="E1168" t="n">
-        <v>518</v>
+        <v>160</v>
       </c>
       <c r="F1168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1168" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,17 +33152,17 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Daerah Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>7800000000</v>
+        <v>2950000000</v>
       </c>
       <c r="D1169" t="n">
         <v>200</v>
       </c>
       <c r="E1169" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F1169" t="n">
         <v>4</v>
@@ -33171,7 +33171,7 @@
         <v>4</v>
       </c>
       <c r="H1169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1170">
@@ -33180,23 +33180,23 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Strategis Akses 1Mobil Lokasi Tebet Timur</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>2950000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1170" t="n">
-        <v>172</v>
+        <v>351</v>
       </c>
       <c r="F1170" t="n">
         <v>4</v>
       </c>
       <c r="G1170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1170" t="n">
         <v>1</v>
@@ -33208,20 +33208,20 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>34500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="E1171" t="n">
-        <v>351</v>
+        <v>50</v>
       </c>
       <c r="F1171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1171" t="n">
         <v>3</v>
@@ -33236,26 +33236,26 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Jual rumah pondok labu cilandak, 5 Menit RSUP Fatmawati</t>
+          <t>Brand New House Modern Design With Pool Cilandak</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>120</v>
+        <v>428</v>
       </c>
       <c r="E1172" t="n">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="F1172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1172" t="n">
         <v>3</v>
       </c>
       <c r="H1172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,26 +33264,26 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Brand New House Modern Design With Pool Cilandak</t>
+          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>9800000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>428</v>
+        <v>588</v>
       </c>
       <c r="E1173" t="n">
-        <v>204</v>
+        <v>866</v>
       </c>
       <c r="F1173" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1173" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,23 +33292,23 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Pondok Indah Mendekat NJOP</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>37000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>588</v>
+        <v>140</v>
       </c>
       <c r="E1174" t="n">
-        <v>866</v>
+        <v>105</v>
       </c>
       <c r="F1174" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1174" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1174" t="n">
         <v>2</v>
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>2400000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="E1175" t="n">
-        <v>105</v>
+        <v>650</v>
       </c>
       <c r="F1175" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1175" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1175" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Murah dan Mewah di Taman Bukit Hijau Pondo Indah</t>
+          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>45000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>600</v>
+        <v>1115</v>
       </c>
       <c r="E1176" t="n">
-        <v>650</v>
+        <v>759</v>
       </c>
       <c r="F1176" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1176" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Rumah Tropical Modern Dekat Dengan Area Golf Pondok Indah</t>
+          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>60000000000</v>
+        <v>4550000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>1115</v>
+        <v>100</v>
       </c>
       <c r="E1177" t="n">
-        <v>759</v>
+        <v>197</v>
       </c>
       <c r="F1177" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1177" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,23 +33404,23 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Rumah Lama Hitung Tanah di Lokasi Bagus dan Tenang</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>4550000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="E1178" t="n">
-        <v>197</v>
+        <v>344</v>
       </c>
       <c r="F1178" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G1178" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H1178" t="n">
         <v>1</v>
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>8000000000</v>
+        <v>31200000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="E1179" t="n">
-        <v>344</v>
+        <v>1200</v>
       </c>
       <c r="F1179" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1179" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H1179" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,26 +33460,26 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Dijual Lahan Berikut Rumah dan Ruko Didalamnya</t>
+          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>31200000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>1000</v>
+        <v>198</v>
       </c>
       <c r="E1180" t="n">
-        <v>1200</v>
+        <v>105</v>
       </c>
       <c r="F1180" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G1180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1181">
@@ -33488,23 +33488,23 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Rumah Djual Dalam Cluster Dekat Cilandak Trakindo</t>
+          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>3850000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>198</v>
+        <v>616</v>
       </c>
       <c r="E1181" t="n">
-        <v>105</v>
+        <v>383</v>
       </c>
       <c r="F1181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1181" t="n">
         <v>2</v>
@@ -33516,23 +33516,23 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hook Di Pinang Perak Pondok Indah Shm Lokasi Bagus</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>16000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>616</v>
+        <v>400</v>
       </c>
       <c r="E1182" t="n">
-        <v>383</v>
+        <v>543</v>
       </c>
       <c r="F1182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1182" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1182" t="n">
         <v>2</v>
@@ -33544,23 +33544,23 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>21000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1183" t="n">
-        <v>543</v>
+        <v>1028</v>
       </c>
       <c r="F1183" t="n">
         <v>5</v>
       </c>
       <c r="G1183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1183" t="n">
         <v>2</v>
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Rumah Tropical Rasa Resort Bali di Pejaten Kemang Jakarta Selatan</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>18500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1184" t="n">
-        <v>1028</v>
+        <v>304</v>
       </c>
       <c r="F1184" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,17 +33600,17 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>5550000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1185" t="n">
-        <v>304</v>
+        <v>793</v>
       </c>
       <c r="F1185" t="n">
         <v>4</v>
@@ -33619,7 +33619,7 @@
         <v>3</v>
       </c>
       <c r="H1185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1186">
@@ -33628,26 +33628,26 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Posisi Hoek di Cipete Kemang Jakarta Selatan SHM</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>15300000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>350</v>
+        <v>559</v>
       </c>
       <c r="E1186" t="n">
-        <v>793</v>
+        <v>572</v>
       </c>
       <c r="F1186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1186" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1187">
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>24000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>559</v>
+        <v>1100</v>
       </c>
       <c r="E1187" t="n">
-        <v>572</v>
+        <v>1000</v>
       </c>
       <c r="F1187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1187" t="n">
         <v>4</v>
       </c>
       <c r="H1187" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai Bagus di Kemang Jaya Halaman Luas Siap Huni</t>
+          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>35000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>1100</v>
+        <v>310</v>
       </c>
       <c r="E1188" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="F1188" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1188" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,23 +33712,23 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Siap Huni, Sudah Renov Walking Distance To Mall</t>
+          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>11000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>310</v>
+        <v>760</v>
       </c>
       <c r="E1189" t="n">
-        <v>260</v>
+        <v>517</v>
       </c>
       <c r="F1189" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1189" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1189" t="n">
         <v>3</v>
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Baru American Classic di Kemang Bangunan Megah Mewah SHM</t>
+          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>38000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>760</v>
+        <v>500</v>
       </c>
       <c r="E1190" t="n">
-        <v>517</v>
+        <v>340</v>
       </c>
       <c r="F1190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai di Kemang Jakarta Selatan SHM Lokasi Bagus</t>
+          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>13900000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E1191" t="n">
-        <v>340</v>
+        <v>544</v>
       </c>
       <c r="F1191" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1191" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Jual Cepat Kemang Timur Harga Murah Bisa Nego</t>
+          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>12500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="E1192" t="n">
-        <v>544</v>
+        <v>348</v>
       </c>
       <c r="F1192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1192" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1192" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,17 +33824,17 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Rumah Cocok Untuk Usaha Di Tebet Selangkah Ke Mt Haryono Shm</t>
+          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>12000000000</v>
+        <v>990000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="E1193" t="n">
-        <v>348</v>
+        <v>72</v>
       </c>
       <c r="F1193" t="n">
         <v>4</v>
@@ -33843,7 +33843,7 @@
         <v>3</v>
       </c>
       <c r="H1193" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,23 +33852,23 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah Furnished 4 Kamar Tidur Di Selatan Jakarta Akses Dekat Tol</t>
+          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>990000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E1194" t="n">
-        <v>72</v>
+        <v>347</v>
       </c>
       <c r="F1194" t="n">
         <v>4</v>
       </c>
       <c r="G1194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1194" t="n">
         <v>2</v>
@@ -33880,17 +33880,17 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah 7Residence Duren Tiga Belakang Total Buah</t>
+          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>10000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1195" t="n">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="F1195" t="n">
         <v>4</v>
@@ -33908,23 +33908,23 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah, 2 Lantai, SHM, Dekat Akses KRL 4+1 Kt</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>1900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="E1196" t="n">
-        <v>105</v>
+        <v>598</v>
       </c>
       <c r="F1196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1196" t="n">
         <v>2</v>
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>17000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="E1197" t="n">
-        <v>598</v>
+        <v>260</v>
       </c>
       <c r="F1197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1197" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>11000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>310</v>
+        <v>431</v>
       </c>
       <c r="E1198" t="n">
-        <v>260</v>
+        <v>874</v>
       </c>
       <c r="F1198" t="n">
         <v>4</v>
       </c>
       <c r="G1198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,23 +33992,23 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Exclusive Pine View Residence - Hot Listing Dijual Cepat!</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>15000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E1199" t="n">
-        <v>874</v>
+        <v>200</v>
       </c>
       <c r="F1199" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1199" t="n">
         <v>2</v>
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>8500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>440</v>
+        <v>135</v>
       </c>
       <c r="E1200" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="F1200" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1200" t="n">
         <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,23 +34048,23 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari Mrt Fatmawati</t>
+          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>2600000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="E1201" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="F1201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1201" t="n">
         <v>1</v>
@@ -34076,20 +34076,20 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Murah ,Jual Cepat Rumah Asri Depan Taman Area Kebayoran Baru</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1202" t="n">
         <v>15000000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="E1202" t="n">
-        <v>310</v>
+        <v>515</v>
       </c>
       <c r="F1202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1202" t="n">
         <v>4</v>
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>15000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="E1203" t="n">
-        <v>515</v>
+        <v>938</v>
       </c>
       <c r="F1203" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1203" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat di Pondok Indah Harga Bagus Hoek , Strategis</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>40000000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>636</v>
+        <v>200</v>
       </c>
       <c r="E1204" t="n">
-        <v>938</v>
+        <v>160</v>
       </c>
       <c r="F1204" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1204" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>6750000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1205" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="F1205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1205" t="n">
         <v>4</v>
       </c>
       <c r="H1205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,17 +34188,17 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Rumah di Villa Cinere Mas SHM Asri Siap Huni Jarang Ada</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>3700000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>250</v>
+        <v>355</v>
       </c>
       <c r="E1206" t="n">
-        <v>205</v>
+        <v>648</v>
       </c>
       <c r="F1206" t="n">
         <v>4</v>
@@ -34207,7 +34207,7 @@
         <v>4</v>
       </c>
       <c r="H1206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,17 +34216,17 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E1207" t="n">
-        <v>648</v>
+        <v>307</v>
       </c>
       <c r="F1207" t="n">
         <v>4</v>
@@ -34235,7 +34235,7 @@
         <v>4</v>
       </c>
       <c r="H1207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,26 +34244,26 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>15000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="E1208" t="n">
-        <v>307</v>
+        <v>113</v>
       </c>
       <c r="F1208" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1208" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,23 +34272,23 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Lestari Dekat Stasiun MRT Lebak Bulus Jaksel</t>
+          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>2600000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E1209" t="n">
-        <v>113</v>
+        <v>322</v>
       </c>
       <c r="F1209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1209" t="n">
         <v>2</v>
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Cepat Hunian Nyaman Dalam Cluster Private Jagakarsa | Lokasi Favorit Jaksel</t>
+          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>6950000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1210" t="n">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="F1210" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,23 +34328,23 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni bisa Utk Rumah Kos. Dpn Taman Akses 2 Mobil</t>
+          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>4500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E1211" t="n">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="F1211" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1211" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1211" t="n">
         <v>1</v>
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Tebet Barat, Rumah Bangunan 2025 Akses Jalan 2 Mobil</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>4900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E1212" t="n">
-        <v>104</v>
+        <v>582</v>
       </c>
       <c r="F1212" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1212" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1212" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>32000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E1213" t="n">
-        <v>582</v>
+        <v>209</v>
       </c>
       <c r="F1213" t="n">
         <v>5</v>
       </c>
       <c r="G1213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1213" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>12900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>450</v>
+        <v>181</v>
       </c>
       <c r="E1214" t="n">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="F1214" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1214" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1214" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Cantik Terawat Pejaten Barat. Strategis Dekat ke Mampang Kuningan dan Tol Tb Simatupang .</t>
+          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>4000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>181</v>
+        <v>320</v>
       </c>
       <c r="E1215" t="n">
-        <v>182</v>
+        <v>909</v>
       </c>
       <c r="F1215" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G1215" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1215" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Murah!!! Rumah Cantik Pejaten di Tengah Kota.harga#Njop#Hiddengem /Privasi Area #Pejatenbarat_pasar.minggu .Sangat.dekat#Pasarminggu.#Warumgbuncit#Pancoran#Tbsimatupang#Kuningan #Harhaterjungpayung Dari 26M Menjadi 16M #Njop.rumah Cantik #Pejatenbarat #Nj</t>
+          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>16000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>320</v>
+        <v>432</v>
       </c>
       <c r="E1216" t="n">
-        <v>909</v>
+        <v>600</v>
       </c>
       <c r="F1216" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1216" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H1216" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,17 +34496,17 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Permata Hijau, Lingkungan Sangat Tenang dan Strategis.</t>
+          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>28000000000</v>
+        <v>10300000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>432</v>
+        <v>1</v>
       </c>
       <c r="E1217" t="n">
-        <v>600</v>
+        <v>186</v>
       </c>
       <c r="F1217" t="n">
         <v>31</v>
@@ -34515,7 +34515,7 @@
         <v>31</v>
       </c>
       <c r="H1217" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Termurah Dijual Rumah Tua Hitung Harga Tanah di Lokasi Premium Pakubuwono Jln. Kerinci, Kebayoran Baru</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>10300000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="E1218" t="n">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="F1218" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1218" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1218" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>1950000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="E1219" t="n">
-        <v>93</v>
+        <v>563</v>
       </c>
       <c r="F1219" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1219" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Dijual, Kebayoran Baru, Strategis di Area Komersil, Rumah Ex Klinik Kecantikan</t>
+          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>55000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>400</v>
+        <v>193</v>
       </c>
       <c r="E1220" t="n">
-        <v>563</v>
+        <v>283</v>
       </c>
       <c r="F1220" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1220" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Rumah di Widya Chandra , Scbd, Kebayoran Baru</t>
+          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>22500000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>193</v>
+        <v>400</v>
       </c>
       <c r="E1221" t="n">
-        <v>283</v>
+        <v>543</v>
       </c>
       <c r="F1221" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1221" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1221" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Ceiling Tinggi, Dilengkapi Kolam Renang, Lay Out Bagus</t>
+          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>20500000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1222" t="n">
-        <v>543</v>
+        <v>304</v>
       </c>
       <c r="F1222" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1222" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1222" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,23 +34664,23 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Rumah Jakarta Selatan Siap Huni Minim Renovasi</t>
+          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>5550000000</v>
+        <v>1050000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="E1223" t="n">
-        <v>304</v>
+        <v>32</v>
       </c>
       <c r="F1223" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1223" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1223" t="n">
         <v>1</v>
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Baru Berhadiah Umroh Mulai Rp 1Milyar-An Dalam Cluster Fatmawati</t>
+          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>1050000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>64</v>
+        <v>559</v>
       </c>
       <c r="E1224" t="n">
-        <v>32</v>
+        <v>572</v>
       </c>
       <c r="F1224" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1224" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1224" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Rumah Kokoh, Lingkungan Tenang, Siap Huni, Sirkulasi Udara Bagus</t>
+          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>24000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1225" t="n">
-        <v>559</v>
+        <v>400</v>
       </c>
       <c r="E1225" t="n">
-        <v>572</v>
+        <v>408</v>
       </c>
       <c r="F1225" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1225" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1225" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Terawat, Jalan Lebar</t>
+          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>16899999999</v>
+        <v>45000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1226" t="n">
-        <v>408</v>
+        <v>620</v>
       </c>
       <c r="F1226" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1226" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1226" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Pondok Indah - For Sale Rumah Modern Classic di Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>45000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="E1227" t="n">
-        <v>620</v>
+        <v>1925</v>
       </c>
       <c r="F1227" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G1227" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="H1227" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Lokasi Strategis Dekat Cipete</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>42000000000</v>
+        <v>10500000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1228" t="n">
-        <v>1925</v>
+        <v>407</v>
       </c>
       <c r="F1228" t="n">
         <v>62</v>
       </c>
       <c r="G1228" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H1228" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Strategis Dekat Cipete</t>
+          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>10500000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="E1229" t="n">
-        <v>407</v>
+        <v>1050</v>
       </c>
       <c r="F1229" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G1229" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H1229" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>For Sale Rumah Bagus SHM di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>68000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>1600</v>
+        <v>325</v>
       </c>
       <c r="E1230" t="n">
-        <v>1050</v>
+        <v>348</v>
       </c>
       <c r="F1230" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1230" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="H1230" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Town House di Fatmawati Raya Rumah</t>
+          <t>American Classic House Dalam Town House Di Kemang</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>7500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="E1231" t="n">
-        <v>348</v>
+        <v>247</v>
       </c>
       <c r="F1231" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1231" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1231" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>American Classic House Dalam Town House Di Kemang</t>
+          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>8500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="E1232" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="F1232" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1232" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1232" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Minimalis Tropical House di Kemang Jakarta Selatan</t>
+          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>7000000000</v>
+        <v>38900000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="E1233" t="n">
-        <v>260</v>
+        <v>932</v>
       </c>
       <c r="F1233" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1233" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1233" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Rumah Bagus Lokasi Strategis dan Area Bagus</t>
+          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>38900000000</v>
+        <v>6350000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>650</v>
+        <v>150</v>
       </c>
       <c r="E1234" t="n">
-        <v>932</v>
+        <v>200</v>
       </c>
       <c r="F1234" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G1234" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1234" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Harga di Bawah N J O P Dekat Niaga Nijau Raya Pondok Indah</t>
+          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>6350000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E1235" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1235" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1235" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Best Deal!! Radio Dalam Kebayoran Baru Dibawah NJOP</t>
+          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>13500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1236" t="n">
-        <v>500</v>
+        <v>1335</v>
       </c>
       <c r="F1236" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1236" t="n">
         <v>6</v>
       </c>
-      <c r="G1236" t="n">
-        <v>5</v>
-      </c>
       <c r="H1236" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Vibes Villa Ampera Kemang</t>
+          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>27000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E1237" t="n">
-        <v>1335</v>
+        <v>1098</v>
       </c>
       <c r="F1237" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G1237" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H1237" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah NJOP Gedung Ex Kantor di Pasar Minggu Jakarta Selatan</t>
+          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>20000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E1238" t="n">
-        <v>1098</v>
+        <v>936</v>
       </c>
       <c r="F1238" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1238" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H1238" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dibawah NJOP, Rumah Kantor di Sisingamangaraja Keb Baru Jakarta Selatan</t>
+          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>57000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E1239" t="n">
-        <v>936</v>
+        <v>123</v>
       </c>
       <c r="F1239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1239" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Jual Rumah Tebet Dalam Siap Huni Akses Jalan 1 Mobil</t>
+          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>2900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1240" t="n">
-        <v>123</v>
+        <v>588</v>
       </c>
       <c r="F1240" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1240" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1240" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Cluster di Cipete Dekat ke MRT Cipete Raya</t>
+          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>11500000000</v>
+        <v>1250000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="E1241" t="n">
-        <v>588</v>
+        <v>87</v>
       </c>
       <c r="F1241" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G1241" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1241" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Pejaten Timur Poltangan Strategis</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>1250000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="E1242" t="n">
-        <v>87</v>
+        <v>1980</v>
       </c>
       <c r="F1242" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="G1242" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H1242" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>135000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1243" t="n">
-        <v>1980</v>
+        <v>515</v>
       </c>
       <c r="F1243" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G1243" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H1243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Rumah Brand New di Pondok Labu, 400 Meter ke Jalan Raya Fatmawati, Cocok untuk Keluarga Besar</t>
+          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>13500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="E1244" t="n">
-        <v>515</v>
+        <v>30</v>
       </c>
       <c r="F1244" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1244" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Murah Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati</t>
+          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>2500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="E1245" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="F1245" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1245" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1245" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Rumah Lama Area Senopati Dekat Scbd Bebas Banjir Kebayoran Baru</t>
+          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>9000000000</v>
+        <v>5550000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1246" t="n">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="F1246" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1246" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1246" t="n">
         <v>21</v>
-      </c>
-      <c r="H1246" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Rumah Lama 2Lt Dekat Citos Dekat MRT Dn Gerbang Tol di Cilandak</t>
+          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>5550000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="E1247" t="n">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="F1247" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G1247" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1247" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Tinggal Bawa Koper! Rumah Mewah 3.5 Lt Desain European Style</t>
+          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Jual Cepat! Rumah 10X20 Eroupean Style Palem Lestari Jakarta Barat</t>
+          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>8500000000</v>
+        <v>76000000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="E1249" t="n">
-        <v>202</v>
+        <v>700</v>
       </c>
       <c r="F1249" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1249" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Brand New House 700M2 Kawasan Elit Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>76000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>800</v>
+        <v>1280</v>
       </c>
       <c r="E1250" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F1250" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="G1250" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="H1250" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Luas 600 di Jalan Adiyaksa Lebak Bulus,Dkt MRT</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>16000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>1280</v>
+        <v>500</v>
       </c>
       <c r="E1251" t="n">
-        <v>600</v>
+        <v>703</v>
       </c>
       <c r="F1251" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1251" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H1251" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>32000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1252" t="n">
-        <v>703</v>
+        <v>1925</v>
       </c>
       <c r="F1252" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G1252" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1252" t="n">
-        <v>25</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Tropical Modern Resort di Cilandak Kawasan Premium Dekat MRT</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>40000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>850</v>
+        <v>130</v>
       </c>
       <c r="E1253" t="n">
-        <v>1925</v>
+        <v>88</v>
       </c>
       <c r="F1253" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1253" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1253" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,23 +35532,23 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>3100000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="E1254" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F1254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1254" t="n">
         <v>1</v>
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Tebet 1 M-An Dekat Jalan Mobil, Dekat Eco Park</t>
+          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>1500000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="E1255" t="n">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="F1255" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1255" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1255" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Kebayoran Baru Cantik dan Asri</t>
+          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>18500000000</v>
+        <v>2450000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>317</v>
+        <v>150</v>
       </c>
       <c r="E1256" t="n">
-        <v>419</v>
+        <v>90</v>
       </c>
       <c r="F1256" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1256" t="n">
         <v>4</v>
       </c>
       <c r="H1256" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Jalan 2 Mobil</t>
+          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>2450000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>150</v>
+        <v>285</v>
       </c>
       <c r="E1257" t="n">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="F1257" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1257" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1257" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Townhouse Mewah 3 Lantai Siap Huni di Kemang Jakarta Selatan</t>
+          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>7000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="E1258" t="n">
-        <v>177</v>
+        <v>752</v>
       </c>
       <c r="F1258" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1258" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1258" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah Terawat Lingkungan Prime Area Ampera Dekat Tol Jorr Tb Simatupang</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>13500000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>230</v>
+        <v>800</v>
       </c>
       <c r="E1259" t="n">
-        <v>752</v>
+        <v>1050</v>
       </c>
       <c r="F1259" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G1259" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1259" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>23000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1260" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="F1260" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1260" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1260" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,17 +35728,17 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>17000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1261" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="F1261" t="n">
         <v>4</v>
@@ -35747,7 +35747,7 @@
         <v>4</v>
       </c>
       <c r="H1261" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>1900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1262" t="n">
         <v>150</v>
       </c>
       <c r="E1262" t="n">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="F1262" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1262" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1262" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah di Setiabudi Minangkabau Sepi Tenang</t>
+          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>10000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1263" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="F1263" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1263" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1263" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Best Deal!! Rumah Furnished Asem Baris Tebet</t>
+          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>23000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>1200</v>
+        <v>42</v>
       </c>
       <c r="E1264" t="n">
-        <v>1000</v>
+        <v>174</v>
       </c>
       <c r="F1264" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1264" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1264" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Townhouse Mewah Furnished di Cipinang</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>4900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="E1265" t="n">
-        <v>174</v>
+        <v>1335</v>
       </c>
       <c r="F1265" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1265" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1265" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>27000000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="E1266" t="n">
-        <v>1335</v>
+        <v>60</v>
       </c>
       <c r="F1266" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1266" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1266" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Wajib Visit!! Rumah Tanpa DP Dekat Aeon Mall</t>
+          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>1420000000</v>
+        <v>35800000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1267" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="F1267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1267" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Dijual Murah Dibawah Pasar Jl. Brawijaya 795M Hanya Rp 45Jt/M Nego</t>
+          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>35800000000</v>
+        <v>185000000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1268" t="n">
-        <v>800</v>
+        <v>1358</v>
       </c>
       <c r="F1268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1268" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik di Jakarta di Area Jl. Sriwijaya - Kelurahan Selong Luas 1358M2 Harga Rp 185 M</t>
+          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>185000000000</v>
+        <v>61000000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E1269" t="n">
-        <v>1358</v>
+        <v>850</v>
       </c>
       <c r="F1269" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1269" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H1269" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Jl. Wijaya Kebayoran Baru Jalan Lebar, Strategis. Lt 850M2 Rp 63 M Nego</t>
+          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>61000000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="E1270" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="F1270" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1270" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1270" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300M Hanya 13 M . Jalan Lebar dan Tenang, Dalam Portal</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>12800000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E1271" t="n">
-        <v>300</v>
+        <v>960</v>
       </c>
       <c r="F1271" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1271" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1271" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>21000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="E1272" t="n">
-        <v>960</v>
+        <v>584</v>
       </c>
       <c r="F1272" t="n">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="G1272" t="n">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="H1272" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>40000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1273" t="n">
         <v>1200</v>
       </c>
       <c r="E1273" t="n">
-        <v>584</v>
+        <v>1094</v>
       </c>
       <c r="F1273" t="n">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="G1273" t="n">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="H1273" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual Rp 48 Milyar</t>
+          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>49000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E1274" t="n">
-        <v>1094</v>
+        <v>1153</v>
       </c>
       <c r="F1274" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1274" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1274" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Dijual Murah Hanya Rp 13Jt/M Rumah Lama di Kemang - Cipete, Luas 1153M Harga Rp 15 M</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>15000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="E1275" t="n">
-        <v>1153</v>
+        <v>779</v>
       </c>
       <c r="F1275" t="n">
         <v>5</v>
       </c>
       <c r="G1275" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1275" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>9500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E1276" t="n">
-        <v>779</v>
+        <v>161</v>
       </c>
       <c r="F1276" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1276" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>8500000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>262</v>
+        <v>503</v>
       </c>
       <c r="E1277" t="n">
-        <v>161</v>
+        <v>421</v>
       </c>
       <c r="F1277" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1277" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1277" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>18500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>503</v>
+        <v>310</v>
       </c>
       <c r="E1278" t="n">
-        <v>421</v>
+        <v>260</v>
       </c>
       <c r="F1278" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1278" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1278" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>11000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="E1279" t="n">
-        <v>260</v>
+        <v>598</v>
       </c>
       <c r="F1279" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G1279" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1279" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>17000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>288</v>
+        <v>600</v>
       </c>
       <c r="E1280" t="n">
-        <v>598</v>
+        <v>530</v>
       </c>
       <c r="F1280" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1280" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1280" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,23 +36288,23 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>15000000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>600</v>
+        <v>98</v>
       </c>
       <c r="E1281" t="n">
-        <v>530</v>
+        <v>98</v>
       </c>
       <c r="F1281" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1281" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1281" t="n">
         <v>11</v>
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>979000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>98</v>
+        <v>360</v>
       </c>
       <c r="E1282" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F1282" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1282" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="H1282" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>4900000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E1283" t="n">
-        <v>127</v>
+        <v>307</v>
       </c>
       <c r="F1283" t="n">
         <v>41</v>
       </c>
       <c r="G1283" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="H1283" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,17 +36372,17 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>12900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="E1284" t="n">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="F1284" t="n">
         <v>41</v>
@@ -36391,7 +36391,7 @@
         <v>41</v>
       </c>
       <c r="H1284" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,23 +36400,23 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>10000000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="E1285" t="n">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="F1285" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1285" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1285" t="n">
         <v>22</v>
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>5750000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E1286" t="n">
-        <v>394</v>
+        <v>108</v>
       </c>
       <c r="F1286" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1286" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="H1286" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,23 +36456,23 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>3000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="E1287" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="F1287" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1287" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1287" t="n">
         <v>2</v>
@@ -36484,23 +36484,23 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>850000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="E1288" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F1288" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1288" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1288" t="n">
         <v>2</v>
@@ -36512,26 +36512,26 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>1900000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="E1289" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F1289" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1289" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1290">
@@ -36540,17 +36540,17 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>829000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1290" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F1290" t="n">
         <v>3</v>
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>1420000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>120</v>
+        <v>810</v>
       </c>
       <c r="E1291" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="F1291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>48000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="E1292" t="n">
-        <v>370</v>
+        <v>1925</v>
       </c>
       <c r="F1292" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="G1292" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1292" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>42000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>850</v>
+        <v>1374</v>
       </c>
       <c r="E1293" t="n">
-        <v>1925</v>
+        <v>1493</v>
       </c>
       <c r="F1293" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G1293" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1293" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>26000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>1374</v>
+        <v>110</v>
       </c>
       <c r="E1294" t="n">
-        <v>1493</v>
+        <v>180</v>
       </c>
       <c r="F1294" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G1294" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H1294" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>1200000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="E1295" t="n">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="F1295" t="n">
         <v>3</v>
       </c>
       <c r="G1295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1295" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,26 +36708,26 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>1900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>144</v>
+        <v>325</v>
       </c>
       <c r="E1296" t="n">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="F1296" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1296" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1297">
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>4800000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1297" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1297" t="n">
-        <v>340</v>
+        <v>570</v>
       </c>
       <c r="F1297" t="n">
         <v>5</v>
       </c>
       <c r="G1297" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1297" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Rumah Gandaria Dekat Gandaria City</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>16899999999</v>
+        <v>10500000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E1298" t="n">
-        <v>570</v>
+        <v>247</v>
       </c>
       <c r="F1298" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1298" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1298" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,26 +36792,26 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Rumah Gandaria Dekat Gandaria City</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>10500000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="E1299" t="n">
-        <v>247</v>
+        <v>634</v>
       </c>
       <c r="F1299" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1299" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1299" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1300">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>37000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>720</v>
+        <v>367</v>
       </c>
       <c r="E1300" t="n">
-        <v>634</v>
+        <v>437</v>
       </c>
       <c r="F1300" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1300" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Rumah Dijual Di Lebak Bulus Lokasi Strategis Nego Sampai Deal.</t>
+          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>9900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>367</v>
+        <v>569</v>
       </c>
       <c r="E1301" t="n">
-        <v>437</v>
+        <v>330</v>
       </c>
       <c r="F1301" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1301" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1301" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Hunian Private Kawasan Prime Kebayoran Lama, Jakarta Selatan</t>
+          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>8000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>569</v>
+        <v>80</v>
       </c>
       <c r="E1302" t="n">
-        <v>330</v>
+        <v>38</v>
       </c>
       <c r="F1302" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1302" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,23 +36904,23 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>800Jutaan Jaksel,Rumah Mewah Minimalis Jalan Raya Utama Siap Huni Jagakarsa</t>
+          <t>Rumah, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>850000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>80</v>
+        <v>1450</v>
       </c>
       <c r="E1303" t="n">
-        <v>38</v>
+        <v>1620</v>
       </c>
       <c r="F1303" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1303" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H1303" t="n">
         <v>1</v>
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Rumah, di Pondok Indah, Bukit Golf</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>160000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>1450</v>
+        <v>160</v>
       </c>
       <c r="E1304" t="n">
-        <v>1620</v>
+        <v>201</v>
       </c>
       <c r="F1304" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="G1304" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="H1304" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,17 +36960,17 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>3900000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="E1305" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F1305" t="n">
         <v>41</v>
@@ -36979,7 +36979,7 @@
         <v>41</v>
       </c>
       <c r="H1305" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>6300000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>230</v>
+        <v>800</v>
       </c>
       <c r="E1306" t="n">
-        <v>200</v>
+        <v>1980</v>
       </c>
       <c r="F1306" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G1306" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H1306" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>135000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1307" t="n">
-        <v>1980</v>
+        <v>200</v>
       </c>
       <c r="F1307" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="G1307" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>8000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>300</v>
+        <v>188</v>
       </c>
       <c r="E1308" t="n">
         <v>200</v>
       </c>
       <c r="F1308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1308" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1308" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,26 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>4700000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="E1309" t="n">
-        <v>200</v>
+        <v>945</v>
       </c>
       <c r="F1309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1309" t="n">
         <v>4</v>
       </c>
       <c r="H1309" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1310">
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>57000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1310" t="n">
-        <v>945</v>
+        <v>865</v>
       </c>
       <c r="F1310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1310" t="n">
         <v>4</v>
       </c>
       <c r="H1310" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>50000000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>500</v>
+        <v>438</v>
       </c>
       <c r="E1311" t="n">
-        <v>865</v>
+        <v>250</v>
       </c>
       <c r="F1311" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1311" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1311" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,26 +37156,26 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>9100000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="E1312" t="n">
-        <v>250</v>
+        <v>515</v>
       </c>
       <c r="F1312" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1312" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1313">
@@ -37184,26 +37184,26 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>13500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="E1313" t="n">
-        <v>515</v>
+        <v>248</v>
       </c>
       <c r="F1313" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G1313" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1313" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1314">
@@ -37212,26 +37212,26 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>22500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>560</v>
+        <v>262</v>
       </c>
       <c r="E1314" t="n">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="F1314" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G1314" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1314" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,26 +37240,26 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>8500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="E1315" t="n">
-        <v>161</v>
+        <v>448</v>
       </c>
       <c r="F1315" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G1315" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1315" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1316">
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Rumah Hitung Tanah Lokasi Strategis SHM di Tebet Timur</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>24000000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>341</v>
+        <v>130</v>
       </c>
       <c r="E1316" t="n">
-        <v>448</v>
+        <v>147</v>
       </c>
       <c r="F1316" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G1316" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H1316" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,23 +37296,23 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Lokasi Strategis SHM di Tebet Timur</t>
+          <t>Jarang Ada, Dijual Rumah Murah Sekali 2Lt Akses Mobil Tebet SHM</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>2700000000</v>
+        <v>1350000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E1317" t="n">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="F1317" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1317" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1317" t="n">
         <v>1</v>
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Jarang Ada, Dijual Rumah Murah Sekali 2Lt Akses Mobil Tebet SHM</t>
+          <t>Angsuran Pasti Sampai Lunas : Dp 0, Free BPHTB, AJB, Bbn, By Ntrs</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>1350000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="E1318" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F1318" t="n">
         <v>2</v>
       </c>
       <c r="G1318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Angsuran Pasti Sampai Lunas : Dp 0, Free BPHTB, AJB, Bbn, By Ntrs</t>
+          <t>Jual Cepat: Rumah Lama Murah Dibangka Kemang Jak Sel</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>750000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>36</v>
+        <v>340</v>
       </c>
       <c r="E1319" t="n">
-        <v>63</v>
+        <v>489</v>
       </c>
       <c r="F1319" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1319" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,20 +37380,20 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Jual Cepat: Rumah Lama Murah Dibangka Kemang Jak Sel</t>
+          <t>Rumah Dilebak Bulus Hook Dekat MRT Lebak Bulus SHM</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>8000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="E1320" t="n">
-        <v>489</v>
+        <v>320</v>
       </c>
       <c r="F1320" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1320" t="n">
         <v>3</v>
@@ -37408,26 +37408,26 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Rumah Dilebak Bulus Hook Dekat MRT Lebak Bulus SHM</t>
+          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>6500000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="E1321" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F1321" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1321" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1321" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1322">
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Terawat 5Menit ke Pim 2 SHM</t>
+          <t>Rumah Industrial Ada Pool Dalam Komplek Dilebak Bulus SHM</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>6750000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>200</v>
+        <v>337</v>
       </c>
       <c r="E1322" t="n">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="F1322" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1322" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1322" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Rumah Industrial Ada Pool Dalam Komplek Dilebak Bulus SHM</t>
+          <t>Rumah Baru Full Furnised Siap Huni di Permata Hijaj</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>5500000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>337</v>
+        <v>250</v>
       </c>
       <c r="E1323" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F1323" t="n">
         <v>3</v>
       </c>
       <c r="G1323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1323" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Rumah Baru Full Furnised Siap Huni di Permata Hijaj</t>
+          <t>Rumah di Pondok Indah Jakarta Selatan Jalan Besar Lingkungan Asri SHM</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>7500000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1324" t="n">
-        <v>115</v>
+        <v>394</v>
       </c>
       <c r="F1324" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1324" t="n">
         <v>4</v>
       </c>
       <c r="H1324" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Rumah di Pondok Indah Jakarta Selatan Jalan Besar Lingkungan Asri SHM</t>
+          <t>Dijual Cepat Rumah di Tebet Utara Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>16000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E1325" t="n">
-        <v>394</v>
+        <v>90</v>
       </c>
       <c r="F1325" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1325" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1325" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Tebet Utara Jakarta Selatan Siap Huni</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Termurah</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>4000000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="E1326" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F1326" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1326" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,17 +37576,17 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Termurah</t>
+          <t>Rumah Baru Siap Huni Deket MRT Lebak Bulus Dalam Cluster Dekat Tol</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>2700000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E1327" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="F1327" t="n">
         <v>4</v>
@@ -37604,23 +37604,23 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni Deket MRT Lebak Bulus Dalam Cluster Dekat Tol</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>2000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E1328" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="F1328" t="n">
         <v>4</v>
       </c>
       <c r="G1328" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1328" t="n">
         <v>2</v>
@@ -37632,23 +37632,23 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>1700000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E1329" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F1329" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1329" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1329" t="n">
         <v>2</v>
@@ -37660,23 +37660,23 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>3800000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="E1330" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F1330" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1330" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1330" t="n">
         <v>2</v>
@@ -37688,23 +37688,23 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Tanah Luas Akses Strategis Termurah</t>
+          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>1900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E1331" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F1331" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1331" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1331" t="n">
         <v>2</v>
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Modern Classic di Lebak Bulus 5 Menit MRT Lebakbulus Paling Murah</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>2550000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="E1332" t="n">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="F1332" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1332" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1332" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>5800000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="E1333" t="n">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="F1333" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1333" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1333" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>1800000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="E1334" t="n">
-        <v>94</v>
+        <v>696</v>
       </c>
       <c r="F1334" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
       </c>
       <c r="H1334" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>11800000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="E1335" t="n">
-        <v>696</v>
+        <v>350</v>
       </c>
       <c r="F1335" t="n">
         <v>3</v>
       </c>
       <c r="G1335" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1335" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>15500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="E1336" t="n">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="F1336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1336" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1336" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>9800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>500</v>
+        <v>301</v>
       </c>
       <c r="E1337" t="n">
-        <v>261</v>
+        <v>466</v>
       </c>
       <c r="F1337" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G1337" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1337" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>11500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>510</v>
+        <v>250</v>
       </c>
       <c r="E1338" t="n">
-        <v>423</v>
+        <v>165</v>
       </c>
       <c r="F1338" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1338" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1338" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>27000000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>301</v>
+        <v>1200</v>
       </c>
       <c r="E1339" t="n">
-        <v>466</v>
+        <v>1000</v>
       </c>
       <c r="F1339" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1339" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1339" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>8000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="E1340" t="n">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="F1340" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1340" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1340" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>27500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E1341" t="n">
-        <v>1000</v>
+        <v>261</v>
       </c>
       <c r="F1341" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="G1341" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1341" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>25000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>550</v>
+        <v>457</v>
       </c>
       <c r="E1342" t="n">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="F1342" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1342" t="n">
         <v>4</v>
       </c>
       <c r="H1342" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>9500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>300</v>
+        <v>810</v>
       </c>
       <c r="E1343" t="n">
-        <v>261</v>
+        <v>370</v>
       </c>
       <c r="F1343" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1343" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1343" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>53000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="E1344" t="n">
-        <v>494</v>
+        <v>682</v>
       </c>
       <c r="F1344" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1344" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>48000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>810</v>
+        <v>250</v>
       </c>
       <c r="E1345" t="n">
-        <v>370</v>
+        <v>241</v>
       </c>
       <c r="F1345" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1345" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1345" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>28000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>584</v>
+        <v>1000</v>
       </c>
       <c r="E1346" t="n">
-        <v>682</v>
+        <v>1038</v>
       </c>
       <c r="F1346" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1346" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1346" t="n">
-        <v>12</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>9200000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="E1347" t="n">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="F1347" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1347" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1347" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>90000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>1000</v>
+        <v>564</v>
       </c>
       <c r="E1348" t="n">
-        <v>1038</v>
+        <v>726</v>
       </c>
       <c r="F1348" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="G1348" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H1348" t="n">
-        <v>412</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,26 +38192,26 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>858000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="E1349" t="n">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="F1349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1349" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1350">
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>48000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="E1350" t="n">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="F1350" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1350" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1350" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>16500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="E1351" t="n">
-        <v>284</v>
+        <v>122</v>
       </c>
       <c r="F1351" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1351" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1351" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,26 +38276,26 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>6900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1352" t="n">
         <v>300</v>
       </c>
       <c r="E1352" t="n">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="F1352" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1353">
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>4800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="E1353" t="n">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="F1353" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1353" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1353" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>11500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1354" t="n">
-        <v>570</v>
+        <v>260</v>
       </c>
       <c r="F1354" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1354" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>9800000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="E1355" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
       <c r="F1355" t="n">
         <v>4</v>
       </c>
       <c r="G1355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1355" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>6900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1356" t="n">
-        <v>260</v>
+        <v>1038</v>
       </c>
       <c r="F1356" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1356" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H1356" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>2000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>85</v>
+        <v>340</v>
       </c>
       <c r="E1357" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="F1357" t="n">
         <v>3</v>
       </c>
       <c r="G1357" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1357" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>1900000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E1358" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F1358" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1358" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,17 +38472,17 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>7090000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>60</v>
+        <v>395</v>
       </c>
       <c r="E1359" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F1359" t="n">
         <v>2</v>
@@ -38500,23 +38500,23 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>90000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E1360" t="n">
-        <v>1038</v>
+        <v>600</v>
       </c>
       <c r="F1360" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1360" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1360" t="n">
         <v>1</v>
@@ -38528,23 +38528,23 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>15500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="E1361" t="n">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="F1361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1361" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1361" t="n">
         <v>1</v>
@@ -38556,23 +38556,23 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>2500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>135</v>
+        <v>360</v>
       </c>
       <c r="E1362" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="F1362" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1362" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1362" t="n">
         <v>1</v>
@@ -38584,23 +38584,23 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>6700000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>395</v>
+        <v>720</v>
       </c>
       <c r="E1363" t="n">
-        <v>172</v>
+        <v>634</v>
       </c>
       <c r="F1363" t="n">
         <v>2</v>
       </c>
       <c r="G1363" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1363" t="n">
         <v>1</v>
@@ -38612,20 +38612,20 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>6900000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="E1364" t="n">
-        <v>76</v>
+        <v>750</v>
       </c>
       <c r="F1364" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1364" t="n">
         <v>4</v>
@@ -38640,23 +38640,23 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>46000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1365" t="n">
-        <v>600</v>
+        <v>498</v>
       </c>
       <c r="F1365" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1365" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1365" t="n">
         <v>1</v>
@@ -38668,23 +38668,23 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>6400000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="E1366" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="F1366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1366" t="n">
         <v>1</v>
@@ -38696,20 +38696,20 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>2400000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E1367" t="n">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="F1367" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1367" t="n">
         <v>2</v>
@@ -38724,23 +38724,23 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>8000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="E1368" t="n">
-        <v>165</v>
+        <v>497</v>
       </c>
       <c r="F1368" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1368" t="n">
         <v>1</v>
@@ -38752,23 +38752,23 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>2000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="E1369" t="n">
-        <v>60</v>
+        <v>414</v>
       </c>
       <c r="F1369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1369" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1369" t="n">
         <v>1</v>
@@ -38780,23 +38780,23 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>1900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="E1370" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="F1370" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1370" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1370" t="n">
         <v>1</v>
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>2000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="E1371" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F1371" t="n">
         <v>3</v>
       </c>
       <c r="G1371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>4900000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="E1372" t="n">
-        <v>127</v>
+        <v>339</v>
       </c>
       <c r="F1372" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1372" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,20 +38864,20 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>6900000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1373" t="n">
-        <v>76</v>
+        <v>479</v>
       </c>
       <c r="F1373" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1373" t="n">
         <v>4</v>
@@ -38892,23 +38892,23 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>2600000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1374" t="n">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="E1374" t="n">
-        <v>60</v>
+        <v>425</v>
       </c>
       <c r="F1374" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1374" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -38920,23 +38920,23 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>37000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1375" t="n">
-        <v>634</v>
+        <v>272</v>
       </c>
       <c r="F1375" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1375" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1375" t="n">
         <v>1</v>
@@ -38948,20 +38948,20 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>18000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="E1376" t="n">
-        <v>750</v>
+        <v>469</v>
       </c>
       <c r="F1376" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1376" t="n">
         <v>4</v>
@@ -38976,23 +38976,23 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>11000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>350</v>
+        <v>616</v>
       </c>
       <c r="E1377" t="n">
-        <v>498</v>
+        <v>383</v>
       </c>
       <c r="F1377" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1377" t="n">
         <v>1</v>
@@ -39004,23 +39004,23 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>3500000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E1378" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="F1378" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1378" t="n">
         <v>1</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>5500000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E1379" t="n">
-        <v>270</v>
+        <v>525</v>
       </c>
       <c r="F1379" t="n">
         <v>5</v>
       </c>
       <c r="G1379" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>12500000000</v>
+        <v>52000000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>318</v>
+        <v>564</v>
       </c>
       <c r="E1380" t="n">
-        <v>497</v>
+        <v>726</v>
       </c>
       <c r="F1380" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>9000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="E1381" t="n">
-        <v>414</v>
+        <v>700</v>
       </c>
       <c r="F1381" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1381" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>25000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="E1382" t="n">
-        <v>1000</v>
+        <v>1127</v>
       </c>
       <c r="F1382" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1382" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>3500000000</v>
+        <v>5900000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="E1383" t="n">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c r="F1383" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,23 +39172,23 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>6950000000</v>
+        <v>22900000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="E1384" t="n">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="F1384" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1384" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1384" t="n">
         <v>1</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>28700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1385" t="n">
+        <v>430</v>
+      </c>
+      <c r="E1385" t="n">
         <v>250</v>
       </c>
-      <c r="E1385" t="n">
-        <v>479</v>
-      </c>
       <c r="F1385" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1385" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,20 +39228,20 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>16899999999</v>
+        <v>4800000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="E1386" t="n">
-        <v>425</v>
+        <v>108</v>
       </c>
       <c r="F1386" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1386" t="n">
         <v>4</v>
@@ -39256,23 +39256,23 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>5500000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E1387" t="n">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="F1387" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1387" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1387" t="n">
         <v>1</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>27000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>301</v>
+        <v>850</v>
       </c>
       <c r="E1388" t="n">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="F1388" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1388" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,23 +39312,23 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>17000000000</v>
+        <v>19800000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>616</v>
+        <v>1200</v>
       </c>
       <c r="E1389" t="n">
-        <v>383</v>
+        <v>960</v>
       </c>
       <c r="F1389" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1389" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>2830000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E1390" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F1390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1390" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,23 +39368,23 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>16500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="E1391" t="n">
-        <v>525</v>
+        <v>60</v>
       </c>
       <c r="F1391" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1391" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>52000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>564</v>
+        <v>220</v>
       </c>
       <c r="E1392" t="n">
-        <v>726</v>
+        <v>98</v>
       </c>
       <c r="F1392" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1392" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,23 +39424,23 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>15000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E1393" t="n">
-        <v>700</v>
+        <v>76</v>
       </c>
       <c r="F1393" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1393" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1393" t="n">
         <v>1</v>
@@ -39452,20 +39452,20 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>42000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>850</v>
+        <v>301</v>
       </c>
       <c r="E1394" t="n">
-        <v>1925</v>
+        <v>466</v>
       </c>
       <c r="F1394" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -39480,23 +39480,23 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>20000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="E1395" t="n">
-        <v>1127</v>
+        <v>423</v>
       </c>
       <c r="F1395" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1395" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1395" t="n">
         <v>1</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>5900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1396" t="n">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="F1396" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1396" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>22900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="E1397" t="n">
-        <v>300</v>
+        <v>147</v>
       </c>
       <c r="F1397" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1397" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,23 +39564,23 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>8000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>430</v>
+        <v>60</v>
       </c>
       <c r="E1398" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F1398" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1398" t="n">
         <v>1</v>
@@ -39592,20 +39592,20 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>4800000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E1399" t="n">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="F1399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1399" t="n">
         <v>4</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>7100000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="E1400" t="n">
-        <v>206</v>
+        <v>60</v>
       </c>
       <c r="F1400" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1400" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>14000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E1401" t="n">
-        <v>384</v>
+        <v>261</v>
       </c>
       <c r="F1401" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>19800000000</v>
+        <v>18700000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E1402" t="n">
-        <v>960</v>
+        <v>410</v>
       </c>
       <c r="F1402" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1402" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,25 +39704,921 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>1650000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1403" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1404" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>160000000000</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>259</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1407" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>341</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>180</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1409" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>381</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>341</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>1412</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>235</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1414" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>1415</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>823</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>7900000000</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>234</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>248</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Rumah Murah Siap Huni di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Di Jual Rumah 3 Lantai Strategis Dekat Mall Casabalnca Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>1160000000</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>69</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 3 Lantai Ada Rooftop Kondisi Baru di Dalam Cluster Strategis</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>127</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cantik Semi Klasik di Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>26000000000</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1425" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1427" t="n">
         <v>150</v>
       </c>
-      <c r="E1403" t="n">
-        <v>65</v>
-      </c>
-      <c r="F1403" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1403" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1403" t="n">
+      <c r="F1427" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Luxurious Modern Classic House Bukit Hijau, Fully Furnished By Lifetime Design. Private Pool. Posisi Hook, Depan Taman</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>45000000000</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Prime Area Rumah Hoek Kerinci Raya Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1429" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>1429</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>127</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Hunian Mewah di Kawasan Paling Prestisius Jakarta Selatan. Lingkungan Tenang dan Asri</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>29500000000</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>630</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>750</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Hot Price Rumah Dekat MRT dan Urban Forest di Cipete, Jaksel</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>625</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1433" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>1433</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Dekat Pakubuwono Senayan Lokasi Strategis di Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>For Sale Rumah di Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>410</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1435" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1483"/>
+  <dimension ref="A1:H1510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>11800000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="E1323" t="n">
-        <v>696</v>
+        <v>350</v>
       </c>
       <c r="F1323" t="n">
         <v>3</v>
       </c>
       <c r="G1323" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1323" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>15500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="E1324" t="n">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="F1324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1324" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1324" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>9800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>500</v>
+        <v>301</v>
       </c>
       <c r="E1325" t="n">
-        <v>261</v>
+        <v>466</v>
       </c>
       <c r="F1325" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G1325" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1325" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>27000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="E1326" t="n">
-        <v>466</v>
+        <v>165</v>
       </c>
       <c r="F1326" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G1326" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1326" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>8000000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="E1327" t="n">
-        <v>165</v>
+        <v>1000</v>
       </c>
       <c r="F1327" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G1327" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H1327" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,26 +37604,26 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>27500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="E1328" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="F1328" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1328" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1328" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1329">
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>25000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="E1329" t="n">
-        <v>450</v>
+        <v>261</v>
       </c>
       <c r="F1329" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1329" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1329" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,26 +37660,26 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>9500000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="E1330" t="n">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="F1330" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1330" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1331">
@@ -37688,26 +37688,26 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>53000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="E1331" t="n">
-        <v>494</v>
+        <v>682</v>
       </c>
       <c r="F1331" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1331" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1331" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1332">
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>48000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>810</v>
+        <v>250</v>
       </c>
       <c r="E1332" t="n">
-        <v>370</v>
+        <v>241</v>
       </c>
       <c r="F1332" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1332" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1332" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>28000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>584</v>
+        <v>1000</v>
       </c>
       <c r="E1333" t="n">
-        <v>682</v>
+        <v>1038</v>
       </c>
       <c r="F1333" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1333" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1333" t="n">
-        <v>12</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>9200000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="E1334" t="n">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="F1334" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1334" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1334" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>90000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>1000</v>
+        <v>564</v>
       </c>
       <c r="E1335" t="n">
-        <v>1038</v>
+        <v>726</v>
       </c>
       <c r="F1335" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="G1335" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H1335" t="n">
-        <v>412</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>858000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="E1336" t="n">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="F1336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1336" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>48000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="E1337" t="n">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="F1337" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1337" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1337" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>16500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="E1338" t="n">
-        <v>284</v>
+        <v>122</v>
       </c>
       <c r="F1338" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1338" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1338" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>6900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1339" t="n">
         <v>300</v>
       </c>
       <c r="E1339" t="n">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="F1339" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1339" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>4800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="E1340" t="n">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="F1340" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1340" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1340" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>11500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1341" t="n">
-        <v>570</v>
+        <v>260</v>
       </c>
       <c r="F1341" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1341" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1341" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>9800000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="E1342" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
       <c r="F1342" t="n">
         <v>4</v>
       </c>
       <c r="G1342" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1342" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Siap Huni Ada Kolam Renang SHM</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>6900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1343" t="n">
-        <v>260</v>
+        <v>1038</v>
       </c>
       <c r="F1343" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1343" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H1343" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Siaphuni 3 Lantai Free Biaya2 Pondok Cabe Deket Tol Cinere Jaksel</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>1900000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="E1344" t="n">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="F1344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
       </c>
       <c r="H1344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,23 +38080,23 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>90000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>1000</v>
+        <v>135</v>
       </c>
       <c r="E1345" t="n">
-        <v>1038</v>
+        <v>30</v>
       </c>
       <c r="F1345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1345" t="n">
         <v>1</v>
@@ -38108,23 +38108,23 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>15500000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="E1346" t="n">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="F1346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1346" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1346" t="n">
         <v>1</v>
@@ -38136,23 +38136,23 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>2500000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>135</v>
+        <v>800</v>
       </c>
       <c r="E1347" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="F1347" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1347" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1347" t="n">
         <v>1</v>
@@ -38164,23 +38164,23 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>6700000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>395</v>
+        <v>175</v>
       </c>
       <c r="E1348" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F1348" t="n">
         <v>2</v>
       </c>
       <c r="G1348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1348" t="n">
         <v>1</v>
@@ -38192,23 +38192,23 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>46000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="E1349" t="n">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="F1349" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1349" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1349" t="n">
         <v>1</v>
@@ -38220,23 +38220,23 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>2400000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="E1350" t="n">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="F1350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1350" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1350" t="n">
         <v>1</v>
@@ -38248,23 +38248,23 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>37000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1351" t="n">
-        <v>634</v>
+        <v>498</v>
       </c>
       <c r="F1351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1351" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1351" t="n">
         <v>1</v>
@@ -38276,23 +38276,23 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>18000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>400</v>
+        <v>124</v>
       </c>
       <c r="E1352" t="n">
-        <v>750</v>
+        <v>124</v>
       </c>
       <c r="F1352" t="n">
         <v>3</v>
       </c>
       <c r="G1352" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1352" t="n">
         <v>1</v>
@@ -38304,20 +38304,20 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>11000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E1353" t="n">
-        <v>498</v>
+        <v>270</v>
       </c>
       <c r="F1353" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -38332,23 +38332,23 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>3500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="E1354" t="n">
-        <v>124</v>
+        <v>497</v>
       </c>
       <c r="F1354" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1354" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1354" t="n">
         <v>1</v>
@@ -38360,23 +38360,23 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E1355" t="n">
-        <v>270</v>
+        <v>414</v>
       </c>
       <c r="F1355" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1355" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1355" t="n">
         <v>1</v>
@@ -38388,23 +38388,23 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>12500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>318</v>
+        <v>1200</v>
       </c>
       <c r="E1356" t="n">
-        <v>497</v>
+        <v>1000</v>
       </c>
       <c r="F1356" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1356" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1356" t="n">
         <v>1</v>
@@ -38416,23 +38416,23 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>9000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="E1357" t="n">
-        <v>414</v>
+        <v>66</v>
       </c>
       <c r="F1357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1357" t="n">
         <v>1</v>
@@ -38444,20 +38444,20 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>25000000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="E1358" t="n">
-        <v>1000</v>
+        <v>339</v>
       </c>
       <c r="F1358" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1358" t="n">
         <v>6</v>
@@ -38472,23 +38472,23 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>3500000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E1359" t="n">
-        <v>66</v>
+        <v>479</v>
       </c>
       <c r="F1359" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1359" t="n">
         <v>1</v>
@@ -38500,23 +38500,23 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>6950000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1360" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="E1360" t="n">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="F1360" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1360" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1360" t="n">
         <v>1</v>
@@ -38528,17 +38528,17 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>28700000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1361" t="n">
-        <v>479</v>
+        <v>272</v>
       </c>
       <c r="F1361" t="n">
         <v>7</v>
@@ -38556,20 +38556,20 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>16899999999</v>
+        <v>27000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>450</v>
+        <v>301</v>
       </c>
       <c r="E1362" t="n">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="F1362" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -38584,23 +38584,23 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>5500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>350</v>
+        <v>616</v>
       </c>
       <c r="E1363" t="n">
-        <v>272</v>
+        <v>383</v>
       </c>
       <c r="F1363" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1363" t="n">
         <v>1</v>
@@ -38612,20 +38612,20 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>27000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="E1364" t="n">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="F1364" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1364" t="n">
         <v>4</v>
@@ -38640,20 +38640,20 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>17000000000</v>
+        <v>52000000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>616</v>
+        <v>564</v>
       </c>
       <c r="E1365" t="n">
-        <v>383</v>
+        <v>726</v>
       </c>
       <c r="F1365" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1365" t="n">
         <v>3</v>
@@ -38668,23 +38668,23 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>16500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1366" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="F1366" t="n">
         <v>5</v>
       </c>
       <c r="G1366" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1366" t="n">
         <v>1</v>
@@ -38696,23 +38696,23 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>52000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>564</v>
+        <v>450</v>
       </c>
       <c r="E1367" t="n">
-        <v>726</v>
+        <v>1127</v>
       </c>
       <c r="F1367" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1367" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1367" t="n">
         <v>1</v>
@@ -38724,23 +38724,23 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>15000000000</v>
+        <v>5900000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1368" t="n">
-        <v>700</v>
+        <v>301</v>
       </c>
       <c r="F1368" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1368" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1368" t="n">
         <v>1</v>
@@ -38752,23 +38752,23 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
+          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>20000000000</v>
+        <v>22900000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>450</v>
+        <v>315</v>
       </c>
       <c r="E1369" t="n">
-        <v>1127</v>
+        <v>300</v>
       </c>
       <c r="F1369" t="n">
         <v>5</v>
       </c>
       <c r="G1369" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1369" t="n">
         <v>1</v>
@@ -38780,23 +38780,23 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>5900000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>200</v>
+        <v>850</v>
       </c>
       <c r="E1370" t="n">
-        <v>301</v>
+        <v>384</v>
       </c>
       <c r="F1370" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1370" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1370" t="n">
         <v>1</v>
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
+          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>22900000000</v>
+        <v>19800000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>315</v>
+        <v>1200</v>
       </c>
       <c r="E1371" t="n">
-        <v>300</v>
+        <v>960</v>
       </c>
       <c r="F1371" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1371" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>14000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>850</v>
+        <v>220</v>
       </c>
       <c r="E1372" t="n">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="F1372" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1372" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,23 +38864,23 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>19800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>1200</v>
+        <v>301</v>
       </c>
       <c r="E1373" t="n">
-        <v>960</v>
+        <v>466</v>
       </c>
       <c r="F1373" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1373" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1373" t="n">
         <v>1</v>
@@ -38892,20 +38892,20 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>2900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="E1374" t="n">
-        <v>98</v>
+        <v>423</v>
       </c>
       <c r="F1374" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1374" t="n">
         <v>6</v>
@@ -38920,23 +38920,23 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>27000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E1375" t="n">
-        <v>466</v>
+        <v>261</v>
       </c>
       <c r="F1375" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1375" t="n">
         <v>1</v>
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>11500000000</v>
+        <v>18700000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E1376" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="F1376" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1376" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,23 +38976,23 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>9500000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>300</v>
+        <v>1450</v>
       </c>
       <c r="E1377" t="n">
-        <v>261</v>
+        <v>1620</v>
       </c>
       <c r="F1377" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1377" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H1377" t="n">
         <v>1</v>
@@ -39004,23 +39004,23 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>18700000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>500</v>
+        <v>341</v>
       </c>
       <c r="E1378" t="n">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="F1378" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1378" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1378" t="n">
         <v>1</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>160000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>1450</v>
+        <v>180</v>
       </c>
       <c r="E1379" t="n">
-        <v>1620</v>
+        <v>230</v>
       </c>
       <c r="F1379" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1379" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>24000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>341</v>
+        <v>800</v>
       </c>
       <c r="E1380" t="n">
-        <v>448</v>
+        <v>1335</v>
       </c>
       <c r="F1380" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1380" t="n">
         <v>6</v>
-      </c>
-      <c r="G1380" t="n">
-        <v>1</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,20 +39088,20 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>2900000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>180</v>
+        <v>381</v>
       </c>
       <c r="E1381" t="n">
-        <v>230</v>
+        <v>448</v>
       </c>
       <c r="F1381" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1381" t="n">
         <v>3</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>27000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>800</v>
+        <v>341</v>
       </c>
       <c r="E1382" t="n">
-        <v>1335</v>
+        <v>448</v>
       </c>
       <c r="F1382" t="n">
         <v>7</v>
       </c>
       <c r="G1382" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>24000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>381</v>
+        <v>850</v>
       </c>
       <c r="E1383" t="n">
-        <v>448</v>
+        <v>1925</v>
       </c>
       <c r="F1383" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,20 +39172,20 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>24000000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E1384" t="n">
-        <v>448</v>
+        <v>235</v>
       </c>
       <c r="F1384" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1384" t="n">
         <v>3</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>42000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E1385" t="n">
-        <v>1925</v>
+        <v>200</v>
       </c>
       <c r="F1385" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1385" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,23 +39228,23 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>7100000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1386" t="n">
-        <v>235</v>
+        <v>823</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1386" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1386" t="n">
         <v>1</v>
@@ -39256,23 +39256,23 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>5200000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="E1387" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="F1387" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1387" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1387" t="n">
         <v>1</v>
@@ -39284,20 +39284,20 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Rumah Murah Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>12000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1388" t="n">
-        <v>823</v>
+        <v>120</v>
       </c>
       <c r="F1388" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1388" t="n">
         <v>5</v>
@@ -39312,23 +39312,23 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>7900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="E1389" t="n">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="F1389" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1389" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni di Pondok Indah</t>
+          <t>Di Jual Rumah 3 Lantai Strategis Dekat Mall Casabalnca Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>6000000000</v>
+        <v>1160000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="E1390" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F1390" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1390" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,14 +39368,14 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+          <t>For Sale Rumah 3 Lantai Ada Rooftop Kondisi Baru di Dalam Cluster Strategis</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>2000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E1391" t="n">
         <v>60</v>
@@ -39384,7 +39384,7 @@
         <v>3</v>
       </c>
       <c r="G1391" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Di Jual Rumah 3 Lantai Strategis Dekat Mall Casabalnca Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Semi Klasik di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>1160000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>69</v>
+        <v>500</v>
       </c>
       <c r="E1392" t="n">
-        <v>24</v>
+        <v>366</v>
       </c>
       <c r="F1392" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1392" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,23 +39424,23 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>For Sale Rumah 3 Lantai Ada Rooftop Kondisi Baru di Dalam Cluster Strategis</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>3000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>127</v>
+        <v>300</v>
       </c>
       <c r="E1393" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F1393" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1393" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1393" t="n">
         <v>1</v>
@@ -39452,23 +39452,23 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Semi Klasik di Kebayoran Baru</t>
+          <t>Luxurious Modern Classic House Bukit Hijau, Fully Furnished By Lifetime Design. Private Pool. Posisi Hook, Depan Taman</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>26000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E1394" t="n">
-        <v>366</v>
+        <v>650</v>
       </c>
       <c r="F1394" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1394" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1394" t="n">
         <v>1</v>
@@ -39480,17 +39480,17 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Prime Area Rumah Hoek Kerinci Raya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>4800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1395" t="n">
-        <v>150</v>
+        <v>469</v>
       </c>
       <c r="F1395" t="n">
         <v>5</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Luxurious Modern Classic House Bukit Hijau, Fully Furnished By Lifetime Design. Private Pool. Posisi Hook, Depan Taman</t>
+          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>45000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="E1396" t="n">
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="F1396" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1396" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Prime Area Rumah Hoek Kerinci Raya Kebayoran Baru Jakarta Selatan</t>
+          <t>Hunian Mewah di Kawasan Paling Prestisius Jakarta Selatan. Lingkungan Tenang dan Asri</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>27000000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>301</v>
+        <v>630</v>
       </c>
       <c r="E1397" t="n">
-        <v>469</v>
+        <v>750</v>
       </c>
       <c r="F1397" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1397" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,20 +39564,20 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
+          <t>Hot Price Rumah Dekat MRT dan Urban Forest di Cipete, Jaksel</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>3000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="E1398" t="n">
-        <v>60</v>
+        <v>625</v>
       </c>
       <c r="F1398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
         <v>3</v>
@@ -39592,23 +39592,23 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Hunian Mewah di Kawasan Paling Prestisius Jakarta Selatan. Lingkungan Tenang dan Asri</t>
+          <t>Dekat Pakubuwono Senayan Lokasi Strategis di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>29500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>630</v>
+        <v>301</v>
       </c>
       <c r="E1399" t="n">
-        <v>750</v>
+        <v>469</v>
       </c>
       <c r="F1399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1399" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1399" t="n">
         <v>1</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Hot Price Rumah Dekat MRT dan Urban Forest di Cipete, Jaksel</t>
+          <t>For Sale Rumah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>12500000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="E1400" t="n">
-        <v>625</v>
+        <v>410</v>
       </c>
       <c r="F1400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1400" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Dekat Pakubuwono Senayan Lokasi Strategis di Kebayoran Baru</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>27000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>301</v>
+        <v>60</v>
       </c>
       <c r="E1401" t="n">
-        <v>469</v>
+        <v>60</v>
       </c>
       <c r="F1401" t="n">
         <v>2</v>
       </c>
       <c r="G1401" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>For Sale Rumah di Jakarta Selatan</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>19000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>140</v>
+        <v>467</v>
       </c>
       <c r="E1402" t="n">
-        <v>410</v>
+        <v>899</v>
       </c>
       <c r="F1402" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,23 +39704,23 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Sutera Rasuna by Alam Sutera</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>1400000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1403" t="n">
-        <v>60</v>
+        <v>1554</v>
       </c>
       <c r="F1403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1403" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1403" t="n">
         <v>1</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>16000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1404" t="n">
-        <v>467</v>
+        <v>250</v>
       </c>
       <c r="E1404" t="n">
-        <v>899</v>
+        <v>165</v>
       </c>
       <c r="F1404" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,23 +39760,23 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>52500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="E1405" t="n">
-        <v>1554</v>
+        <v>344</v>
       </c>
       <c r="F1405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1405" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1405" t="n">
         <v>1</v>
@@ -39788,20 +39788,20 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>8500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1406" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="F1406" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>8000000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1407" t="n">
-        <v>165</v>
+        <v>700</v>
       </c>
       <c r="F1407" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1407" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>22500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1408" t="n">
         <v>500</v>
       </c>
       <c r="E1408" t="n">
-        <v>366</v>
+        <v>259</v>
       </c>
       <c r="F1408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>2000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="E1409" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F1409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>2000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>85</v>
+        <v>720</v>
       </c>
       <c r="E1410" t="n">
-        <v>60</v>
+        <v>634</v>
       </c>
       <c r="F1410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1410" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,20 +39928,20 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>8000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>580</v>
+        <v>125</v>
       </c>
       <c r="E1411" t="n">
-        <v>344</v>
+        <v>184</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1411" t="n">
         <v>1</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>4800000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>325</v>
+        <v>56</v>
       </c>
       <c r="E1412" t="n">
-        <v>340</v>
+        <v>29</v>
       </c>
       <c r="F1412" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1412" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>14800000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="E1413" t="n">
-        <v>700</v>
+        <v>82</v>
       </c>
       <c r="F1413" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1413" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,23 +40012,23 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>11000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1414" t="n">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="F1414" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>6250000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="E1415" t="n">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="F1415" t="n">
         <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>32000000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>720</v>
+        <v>150</v>
       </c>
       <c r="E1416" t="n">
-        <v>634</v>
+        <v>65</v>
       </c>
       <c r="F1416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1416" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>5400000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E1417" t="n">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="F1417" t="n">
         <v>1</v>
       </c>
       <c r="G1417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,23 +40124,23 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>1170000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c r="E1418" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="F1418" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1418" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1418" t="n">
         <v>1</v>
@@ -40152,23 +40152,23 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>4390000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="E1419" t="n">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="F1419" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1419" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1419" t="n">
         <v>1</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>27000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="E1420" t="n">
-        <v>335</v>
+        <v>169</v>
       </c>
       <c r="F1420" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1420" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah 4 Lantai di Jagakarsa Jakarta Selatan Selangkah Tol Andara Satu Cluster Sama Artis Raffi Ahmad</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>7900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>417</v>
+        <v>258</v>
       </c>
       <c r="E1421" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="F1421" t="n">
         <v>1</v>
       </c>
       <c r="G1421" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>1650000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="E1422" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="F1422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,23 +40264,23 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Scandinavian di Cilandak, Desain Ala Apartement</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>2000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="E1423" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1423" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1423" t="n">
         <v>1</v>
@@ -40292,17 +40292,17 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>3000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>225</v>
+        <v>430</v>
       </c>
       <c r="E1424" t="n">
-        <v>108</v>
+        <v>250</v>
       </c>
       <c r="F1424" t="n">
         <v>5</v>
@@ -40320,23 +40320,23 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>5800000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="E1425" t="n">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="F1425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1425" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1425" t="n">
         <v>1</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>Hunian 3,5 Lantai Konsep Scandinavian Ala Apartement di Cilandak.</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>4000000000</v>
+        <v>1470000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="E1426" t="n">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="F1426" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1426" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,20 +40376,20 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai di Jagakarsa Jakarta Selatan Selangkah Tol Andara Satu Cluster Sama Artis Raffi Ahmad</t>
+          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>4800000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="E1427" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F1427" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>3900000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1428" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1428" t="n">
         <v>206</v>
       </c>
-      <c r="E1428" t="n">
-        <v>170</v>
-      </c>
       <c r="F1428" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1428" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Scandinavian di Cilandak, Desain Ala Apartement</t>
+          <t>Rumah Sultan Pinggir Jalan Raya Utama Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>1000000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>64</v>
+        <v>400</v>
       </c>
       <c r="E1429" t="n">
-        <v>40</v>
+        <v>515</v>
       </c>
       <c r="F1429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>8000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="E1430" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F1430" t="n">
         <v>5</v>
       </c>
       <c r="G1430" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,23 +40488,23 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>1800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E1431" t="n">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="F1431" t="n">
         <v>4</v>
       </c>
       <c r="G1431" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1431" t="n">
         <v>1</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Hunian 3,5 Lantai Konsep Scandinavian Ala Apartement di Cilandak.</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>1470000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="E1432" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="F1432" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1432" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>3850000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1433" t="n">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="F1433" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1433" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>7100000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1434" t="n">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="F1434" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,20 +40600,20 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah Sultan Pinggir Jalan Raya Utama Cilandak, Jakarta Selatan</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>14500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1435" t="n">
-        <v>515</v>
+        <v>155</v>
       </c>
       <c r="F1435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>22500000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="E1436" t="n">
-        <v>248</v>
+        <v>404</v>
       </c>
       <c r="F1436" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1436" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>2400000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1437" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="E1437" t="n">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="F1437" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1437" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>4800000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="E1438" t="n">
-        <v>108</v>
+        <v>696</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1438" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,23 +40712,23 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>6900000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>375</v>
+        <v>850</v>
       </c>
       <c r="E1439" t="n">
-        <v>76</v>
+        <v>1925</v>
       </c>
       <c r="F1439" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1439" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1439" t="n">
         <v>1</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>22500000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="E1440" t="n">
-        <v>335</v>
+        <v>261</v>
       </c>
       <c r="F1440" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1440" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>5800000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1441" t="n">
-        <v>305</v>
+        <v>703</v>
       </c>
       <c r="F1441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1441" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,20 +40796,20 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>2900000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E1442" t="n">
-        <v>155</v>
+        <v>1035</v>
       </c>
       <c r="F1442" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1442" t="n">
         <v>4</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>10000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>360</v>
+        <v>881</v>
       </c>
       <c r="E1443" t="n">
-        <v>307</v>
+        <v>1066</v>
       </c>
       <c r="F1443" t="n">
         <v>4</v>
       </c>
       <c r="G1443" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>6900000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>375</v>
+        <v>614</v>
       </c>
       <c r="E1444" t="n">
-        <v>76</v>
+        <v>921</v>
       </c>
       <c r="F1444" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1444" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>21000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>410</v>
+        <v>720</v>
       </c>
       <c r="E1445" t="n">
-        <v>404</v>
+        <v>634</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1445" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>7900000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="E1446" t="n">
-        <v>60</v>
+        <v>257</v>
       </c>
       <c r="F1446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>5500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>240</v>
+        <v>1100</v>
       </c>
       <c r="E1447" t="n">
-        <v>147</v>
+        <v>730</v>
       </c>
       <c r="F1447" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1447" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>4099999999</v>
+        <v>4420000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1448" t="n">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="F1448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,17 +40992,17 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>6900000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1449" t="n">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="F1449" t="n">
         <v>4</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>2600000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="E1450" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="F1450" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>4900000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E1451" t="n">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="F1451" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1451" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>12000000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E1452" t="n">
-        <v>696</v>
+        <v>228</v>
       </c>
       <c r="F1452" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,23 +41104,23 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>41000000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>850</v>
+        <v>198</v>
       </c>
       <c r="E1453" t="n">
-        <v>1925</v>
+        <v>105</v>
       </c>
       <c r="F1453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1453" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1453" t="n">
         <v>1</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>2830000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="E1454" t="n">
-        <v>60</v>
+        <v>674</v>
       </c>
       <c r="F1454" t="n">
         <v>2</v>
       </c>
       <c r="G1454" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>4500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="E1455" t="n">
-        <v>261</v>
+        <v>123</v>
       </c>
       <c r="F1455" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1455" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>32000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>500</v>
+        <v>171</v>
       </c>
       <c r="E1456" t="n">
-        <v>703</v>
+        <v>181</v>
       </c>
       <c r="F1456" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1456" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1456" t="n">
         <v>1</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>18500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="E1457" t="n">
-        <v>1035</v>
+        <v>461</v>
       </c>
       <c r="F1457" t="n">
         <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>6400000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1458" t="n">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="F1458" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1458" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>62000000000</v>
+        <v>3040000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>881</v>
+        <v>215</v>
       </c>
       <c r="E1459" t="n">
-        <v>1066</v>
+        <v>151</v>
       </c>
       <c r="F1459" t="n">
         <v>4</v>
       </c>
       <c r="G1459" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>20000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>614</v>
+        <v>881</v>
       </c>
       <c r="E1460" t="n">
-        <v>921</v>
+        <v>1066</v>
       </c>
       <c r="F1460" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1460" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>32000000000</v>
+        <v>4980000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>720</v>
+        <v>200</v>
       </c>
       <c r="E1461" t="n">
-        <v>634</v>
+        <v>400</v>
       </c>
       <c r="F1461" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1461" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,23 +41356,23 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>9700000000</v>
+        <v>4980000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E1462" t="n">
-        <v>257</v>
+        <v>400</v>
       </c>
       <c r="F1462" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>45000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>1100</v>
+        <v>144</v>
       </c>
       <c r="E1463" t="n">
-        <v>730</v>
+        <v>232</v>
       </c>
       <c r="F1463" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1463" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>4420000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="E1464" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F1464" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>15300000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="E1465" t="n">
-        <v>597</v>
+        <v>98</v>
       </c>
       <c r="F1465" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1465" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>6860000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1466" t="n">
-        <v>500</v>
+        <v>76</v>
       </c>
       <c r="F1466" t="n">
         <v>4</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>7800000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="E1467" t="n">
-        <v>248</v>
+        <v>822</v>
       </c>
       <c r="F1467" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1467" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>4150000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="E1468" t="n">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="F1468" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1468" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,23 +41552,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>3320000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>198</v>
+        <v>395</v>
       </c>
       <c r="E1469" t="n">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="F1469" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1469" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1469" t="n">
         <v>1</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>1900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="E1470" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="F1470" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1470" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>21500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1471" t="n">
-        <v>674</v>
+        <v>76</v>
       </c>
       <c r="F1471" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1471" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>2550000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E1472" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="F1472" t="n">
         <v>5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,23 +41664,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>2550000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>171</v>
+        <v>650</v>
       </c>
       <c r="E1473" t="n">
-        <v>181</v>
+        <v>544</v>
       </c>
       <c r="F1473" t="n">
         <v>3</v>
       </c>
       <c r="G1473" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1473" t="n">
         <v>1</v>
@@ -41692,17 +41692,17 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>15000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>1300</v>
+        <v>60</v>
       </c>
       <c r="E1474" t="n">
-        <v>461</v>
+        <v>60</v>
       </c>
       <c r="F1474" t="n">
         <v>2</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>6500000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1475" t="n">
         <v>250</v>
       </c>
       <c r="E1475" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="F1475" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1475" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,20 +41748,20 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>3040000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>215</v>
+        <v>325</v>
       </c>
       <c r="E1476" t="n">
-        <v>151</v>
+        <v>696</v>
       </c>
       <c r="F1476" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1476" t="n">
         <v>3</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>62000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>881</v>
+        <v>450</v>
       </c>
       <c r="E1477" t="n">
-        <v>1066</v>
+        <v>942</v>
       </c>
       <c r="F1477" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1477" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>4980000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1478" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>4980000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E1479" t="n">
-        <v>400</v>
+        <v>864</v>
       </c>
       <c r="F1479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,20 +41860,20 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>1900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="E1480" t="n">
-        <v>232</v>
+        <v>600</v>
       </c>
       <c r="F1480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1480" t="n">
         <v>3</v>
@@ -41888,20 +41888,20 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>1200000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="E1481" t="n">
-        <v>180</v>
+        <v>1300</v>
       </c>
       <c r="F1481" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1481" t="n">
         <v>2</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>979000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E1482" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="F1482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,25 +41944,781 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1483" t="n">
+        <v>275000000000</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>1585</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>1483</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>52</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>1484</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>366</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>1486</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>154</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>11300000000</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>535</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>1488</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>158</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>159</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>1490</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
         <v>6900000000</v>
       </c>
-      <c r="D1483" t="n">
+      <c r="D1492" t="n">
         <v>375</v>
       </c>
-      <c r="E1483" t="n">
+      <c r="E1492" t="n">
         <v>76</v>
       </c>
-      <c r="F1483" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1483" t="n">
-        <v>4</v>
-      </c>
-      <c r="H1483" t="n">
+      <c r="F1492" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>307</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>7300000000</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>501</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>147</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>216</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Terawat Dalam Komplek di Tebet</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>13900000000</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Termurah Rumah Hitung Tanah di Tebet Akses Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>5800000000</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>253</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Ada Kolam Renang Akses Mudah</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>179</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Rumah Luas, Strategis Dekat Pintu Tol Dijual Murah</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>2550000000</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>380</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>311</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Private Offering - Pondok Indah, 644 M² Land Parcel</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>23500000000</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>442</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>644</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Rumah Tua Masih Layak Huni Terletak di Segitiga Emas Jakarta Selatan bisa Dibangun 4 Lantai . bisa Komersil. Cocok.buat Kost2n . Lapangan Olah Raga. Lokasi Sgt Strategis Dekat Pusat Perkantoran SHM</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>31000000000</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>750</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1510" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1571"/>
+  <dimension ref="A1:H1600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38052,20 +38052,20 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>12500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>318</v>
+        <v>240</v>
       </c>
       <c r="E1344" t="n">
-        <v>497</v>
+        <v>414</v>
       </c>
       <c r="F1344" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
@@ -38080,23 +38080,23 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>9000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="E1345" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="F1345" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1345" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1345" t="n">
         <v>1</v>
@@ -38108,23 +38108,23 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>25000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>1200</v>
+        <v>147</v>
       </c>
       <c r="E1346" t="n">
-        <v>1000</v>
+        <v>66</v>
       </c>
       <c r="F1346" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1346" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1346" t="n">
         <v>1</v>
@@ -38136,23 +38136,23 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>3500000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="E1347" t="n">
-        <v>66</v>
+        <v>339</v>
       </c>
       <c r="F1347" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1347" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1347" t="n">
         <v>1</v>
@@ -38164,23 +38164,23 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>6950000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="E1348" t="n">
-        <v>339</v>
+        <v>479</v>
       </c>
       <c r="F1348" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1348" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1348" t="n">
         <v>1</v>
@@ -38192,20 +38192,20 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>28700000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1349" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E1349" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="F1349" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1349" t="n">
         <v>4</v>
@@ -38220,20 +38220,20 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>16899999999</v>
+        <v>5500000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E1350" t="n">
-        <v>425</v>
+        <v>272</v>
       </c>
       <c r="F1350" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1350" t="n">
         <v>4</v>
@@ -38248,20 +38248,20 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>5500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="E1351" t="n">
-        <v>272</v>
+        <v>469</v>
       </c>
       <c r="F1351" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1351" t="n">
         <v>4</v>
@@ -38276,23 +38276,23 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>27000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>301</v>
+        <v>616</v>
       </c>
       <c r="E1352" t="n">
-        <v>469</v>
+        <v>383</v>
       </c>
       <c r="F1352" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1352" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1352" t="n">
         <v>1</v>
@@ -38304,23 +38304,23 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>17000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>616</v>
+        <v>400</v>
       </c>
       <c r="E1353" t="n">
-        <v>383</v>
+        <v>525</v>
       </c>
       <c r="F1353" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1353" t="n">
         <v>1</v>
@@ -38332,23 +38332,23 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>16500000000</v>
+        <v>52000000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>400</v>
+        <v>564</v>
       </c>
       <c r="E1354" t="n">
-        <v>525</v>
+        <v>726</v>
       </c>
       <c r="F1354" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1354" t="n">
         <v>1</v>
@@ -38360,23 +38360,23 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>52000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>564</v>
+        <v>500</v>
       </c>
       <c r="E1355" t="n">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="F1355" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1355" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1355" t="n">
         <v>1</v>
@@ -38388,23 +38388,23 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Tanjung Barat Siap Huni Furnished Harga Terbaik</t>
+          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>15000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E1356" t="n">
-        <v>700</v>
+        <v>1127</v>
       </c>
       <c r="F1356" t="n">
         <v>5</v>
       </c>
       <c r="G1356" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1356" t="n">
         <v>1</v>
@@ -38416,20 +38416,20 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Rumah Dan Paviliun Siap Huni Di Jalan Bangka Jakarta Selatan</t>
+          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>20000000000</v>
+        <v>5900000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="E1357" t="n">
-        <v>1127</v>
+        <v>301</v>
       </c>
       <c r="F1357" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1357" t="n">
         <v>4</v>
@@ -38444,23 +38444,23 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Rumah Dijual di Cilandak, Belakang Citos</t>
+          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>5900000000</v>
+        <v>22900000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>200</v>
+        <v>315</v>
       </c>
       <c r="E1358" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F1358" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1358" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1358" t="n">
         <v>1</v>
@@ -38472,23 +38472,23 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Rumah Mewah 2 Lantai, Lokasi Strategis di Kuningan Jakarta Selatan</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>22900000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>315</v>
+        <v>850</v>
       </c>
       <c r="E1359" t="n">
-        <v>300</v>
+        <v>384</v>
       </c>
       <c r="F1359" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1359" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1359" t="n">
         <v>1</v>
@@ -38500,20 +38500,20 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>14000000000</v>
+        <v>19800000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="E1360" t="n">
-        <v>384</v>
+        <v>960</v>
       </c>
       <c r="F1360" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1360" t="n">
         <v>8</v>
@@ -38528,23 +38528,23 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah Murah Free Koskosan di Dkt Tol Veteran Jaksel</t>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>19800000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>1200</v>
+        <v>220</v>
       </c>
       <c r="E1361" t="n">
-        <v>960</v>
+        <v>98</v>
       </c>
       <c r="F1361" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1361" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1361" t="n">
         <v>1</v>
@@ -38556,23 +38556,23 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>2900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="E1362" t="n">
-        <v>98</v>
+        <v>466</v>
       </c>
       <c r="F1362" t="n">
         <v>5</v>
       </c>
       <c r="G1362" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1362" t="n">
         <v>1</v>
@@ -38584,23 +38584,23 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>27000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>301</v>
+        <v>510</v>
       </c>
       <c r="E1363" t="n">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="F1363" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1363" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1363" t="n">
         <v>1</v>
@@ -38612,23 +38612,23 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>11500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="E1364" t="n">
-        <v>423</v>
+        <v>261</v>
       </c>
       <c r="F1364" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1364" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1364" t="n">
         <v>1</v>
@@ -38640,23 +38640,23 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>9500000000</v>
+        <v>18700000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1365" t="n">
-        <v>261</v>
+        <v>410</v>
       </c>
       <c r="F1365" t="n">
         <v>1</v>
       </c>
       <c r="G1365" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1365" t="n">
         <v>1</v>
@@ -38668,23 +38668,23 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>18700000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>500</v>
+        <v>1450</v>
       </c>
       <c r="E1366" t="n">
-        <v>410</v>
+        <v>1620</v>
       </c>
       <c r="F1366" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1366" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1366" t="n">
         <v>1</v>
@@ -38696,23 +38696,23 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>160000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>1450</v>
+        <v>341</v>
       </c>
       <c r="E1367" t="n">
-        <v>1620</v>
+        <v>448</v>
       </c>
       <c r="F1367" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1367" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H1367" t="n">
         <v>1</v>
@@ -38724,23 +38724,23 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>24000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>341</v>
+        <v>180</v>
       </c>
       <c r="E1368" t="n">
-        <v>448</v>
+        <v>230</v>
       </c>
       <c r="F1368" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1368" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1368" t="n">
         <v>1</v>
@@ -38752,23 +38752,23 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>2900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>180</v>
+        <v>800</v>
       </c>
       <c r="E1369" t="n">
-        <v>230</v>
+        <v>1335</v>
       </c>
       <c r="F1369" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1369" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1369" t="n">
         <v>1</v>
@@ -38780,23 +38780,23 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>27000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>800</v>
+        <v>381</v>
       </c>
       <c r="E1370" t="n">
-        <v>1335</v>
+        <v>448</v>
       </c>
       <c r="F1370" t="n">
         <v>7</v>
       </c>
       <c r="G1370" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1370" t="n">
         <v>1</v>
@@ -38808,14 +38808,14 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
         </is>
       </c>
       <c r="C1371" t="n">
         <v>24000000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="E1371" t="n">
         <v>448</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>24000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>341</v>
+        <v>850</v>
       </c>
       <c r="E1372" t="n">
-        <v>448</v>
+        <v>1925</v>
       </c>
       <c r="F1372" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,23 +38864,23 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>42000000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E1373" t="n">
-        <v>1925</v>
+        <v>235</v>
       </c>
       <c r="F1373" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1373" t="n">
         <v>1</v>
@@ -38892,23 +38892,23 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>7100000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1374" t="n">
         <v>350</v>
       </c>
       <c r="E1374" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="F1374" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1374" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -38920,20 +38920,20 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>5200000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1375" t="n">
-        <v>200</v>
+        <v>823</v>
       </c>
       <c r="F1375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1375" t="n">
         <v>5</v>
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>12000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="E1376" t="n">
-        <v>823</v>
+        <v>234</v>
       </c>
       <c r="F1376" t="n">
         <v>1</v>
       </c>
       <c r="G1376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,23 +38976,23 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+          <t>Rumah Murah Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>7900000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E1377" t="n">
-        <v>234</v>
+        <v>120</v>
       </c>
       <c r="F1377" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1377" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1377" t="n">
         <v>1</v>
@@ -39004,23 +39004,23 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni di Pondok Indah</t>
+          <t>Di Jual Rumah 3 Lantai Strategis Dekat Mall Casabalnca Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>6000000000</v>
+        <v>1160000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="E1378" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F1378" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1378" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1378" t="n">
         <v>1</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Di Jual Rumah 3 Lantai Strategis Dekat Mall Casabalnca Jakarta Selatan</t>
+          <t>For Sale Rumah 3 Lantai Ada Rooftop Kondisi Baru di Dalam Cluster Strategis</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>1160000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="E1379" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F1379" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1379" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>For Sale Rumah 3 Lantai Ada Rooftop Kondisi Baru di Dalam Cluster Strategis</t>
+          <t>Dijual Rumah Cantik Semi Klasik di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>3000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>127</v>
+        <v>500</v>
       </c>
       <c r="E1380" t="n">
-        <v>60</v>
+        <v>366</v>
       </c>
       <c r="F1380" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1380" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Semi Klasik di Kebayoran Baru</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>26000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1381" t="n">
-        <v>366</v>
+        <v>150</v>
       </c>
       <c r="F1381" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1381" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Luxurious Modern Classic House Bukit Hijau, Fully Furnished By Lifetime Design. Private Pool. Posisi Hook, Depan Taman</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>4800000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E1382" t="n">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="F1382" t="n">
         <v>5</v>
       </c>
       <c r="G1382" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Luxurious Modern Classic House Bukit Hijau, Fully Furnished By Lifetime Design. Private Pool. Posisi Hook, Depan Taman</t>
+          <t>Prime Area Rumah Hoek Kerinci Raya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>45000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>650</v>
+        <v>301</v>
       </c>
       <c r="E1383" t="n">
-        <v>650</v>
+        <v>469</v>
       </c>
       <c r="F1383" t="n">
         <v>5</v>
       </c>
       <c r="G1383" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,23 +39172,23 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Prime Area Rumah Hoek Kerinci Raya Kebayoran Baru Jakarta Selatan</t>
+          <t>Hunian Mewah di Kawasan Paling Prestisius Jakarta Selatan. Lingkungan Tenang dan Asri</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>27000000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>301</v>
+        <v>630</v>
       </c>
       <c r="E1384" t="n">
-        <v>469</v>
+        <v>750</v>
       </c>
       <c r="F1384" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1384" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1384" t="n">
         <v>1</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Hunian Mewah di Kawasan Paling Prestisius Jakarta Selatan. Lingkungan Tenang dan Asri</t>
+          <t>Hot Price Rumah Dekat MRT dan Urban Forest di Cipete, Jaksel</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>29500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>630</v>
+        <v>250</v>
       </c>
       <c r="E1385" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="F1385" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1385" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,23 +39228,23 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Hot Price Rumah Dekat MRT dan Urban Forest di Cipete, Jaksel</t>
+          <t>Dekat Pakubuwono Senayan Lokasi Strategis di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>12500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="E1386" t="n">
-        <v>625</v>
+        <v>469</v>
       </c>
       <c r="F1386" t="n">
         <v>2</v>
       </c>
       <c r="G1386" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1386" t="n">
         <v>1</v>
@@ -39256,23 +39256,23 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Dekat Pakubuwono Senayan Lokasi Strategis di Kebayoran Baru</t>
+          <t>For Sale Rumah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>27000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>301</v>
+        <v>140</v>
       </c>
       <c r="E1387" t="n">
-        <v>469</v>
+        <v>410</v>
       </c>
       <c r="F1387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1387" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1387" t="n">
         <v>1</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>For Sale Rumah di Jakarta Selatan</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>19000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E1388" t="n">
-        <v>410</v>
+        <v>60</v>
       </c>
       <c r="F1388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,23 +39312,23 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Sutera Rasuna by Alam Sutera</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>1400000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>60</v>
+        <v>467</v>
       </c>
       <c r="E1389" t="n">
-        <v>60</v>
+        <v>899</v>
       </c>
       <c r="F1389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1389" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>16000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="E1390" t="n">
-        <v>899</v>
+        <v>1554</v>
       </c>
       <c r="F1390" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1390" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,23 +39368,23 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>52500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1391" t="n">
-        <v>1554</v>
+        <v>165</v>
       </c>
       <c r="F1391" t="n">
         <v>1</v>
       </c>
       <c r="G1391" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1392" t="n">
         <v>8000000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="E1392" t="n">
-        <v>165</v>
+        <v>344</v>
       </c>
       <c r="F1392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1392" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,23 +39424,23 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>8000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>580</v>
+        <v>325</v>
       </c>
       <c r="E1393" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F1393" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1393" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1393" t="n">
         <v>1</v>
@@ -39452,20 +39452,20 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>4800000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="E1394" t="n">
-        <v>340</v>
+        <v>259</v>
       </c>
       <c r="F1394" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1394" t="n">
         <v>4</v>
@@ -39480,23 +39480,23 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>11000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1395" t="n">
-        <v>259</v>
+        <v>122</v>
       </c>
       <c r="F1395" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1395" t="n">
         <v>1</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>6250000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="E1396" t="n">
-        <v>122</v>
+        <v>634</v>
       </c>
       <c r="F1396" t="n">
         <v>1</v>
       </c>
       <c r="G1396" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>32000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>720</v>
+        <v>125</v>
       </c>
       <c r="E1397" t="n">
-        <v>634</v>
+        <v>184</v>
       </c>
       <c r="F1397" t="n">
         <v>1</v>
       </c>
       <c r="G1397" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,23 +39564,23 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>5400000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="E1398" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1398" t="n">
         <v>1</v>
@@ -39592,23 +39592,23 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>1170000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="E1399" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F1399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1399" t="n">
         <v>1</v>
@@ -39620,20 +39620,20 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>4390000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E1400" t="n">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="F1400" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1400" t="n">
         <v>3</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>27000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="E1401" t="n">
-        <v>335</v>
+        <v>180</v>
       </c>
       <c r="F1401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>7900000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>417</v>
+        <v>150</v>
       </c>
       <c r="E1402" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="F1402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1402" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,20 +39704,20 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>1650000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E1403" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F1403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1403" t="n">
         <v>3</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>2000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1404" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1404" t="n">
         <v>108</v>
       </c>
-      <c r="E1404" t="n">
-        <v>80</v>
-      </c>
       <c r="F1404" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1404" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,17 +39760,17 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>3000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="E1405" t="n">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="F1405" t="n">
         <v>5</v>
@@ -39788,17 +39788,17 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>5800000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="E1406" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F1406" t="n">
         <v>5</v>
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>Rumah 4 Lantai di Jagakarsa Jakarta Selatan Selangkah Tol Andara Satu Cluster Sama Artis Raffi Ahmad</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>4000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>340</v>
+        <v>258</v>
       </c>
       <c r="E1407" t="n">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="F1407" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1407" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,20 +39844,20 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai di Jagakarsa Jakarta Selatan Selangkah Tol Andara Satu Cluster Sama Artis Raffi Ahmad</t>
+          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>4800000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="E1408" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="F1408" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1408" t="n">
         <v>4</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Private Lift Di Senopati Boulevard Selatan Jakarta</t>
+          <t>Rumah 2 Lantai Scandinavian di Cilandak, Desain Ala Apartement</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>3900000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>206</v>
+        <v>64</v>
       </c>
       <c r="E1409" t="n">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="F1409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Scandinavian di Cilandak, Desain Ala Apartement</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>1000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>64</v>
+        <v>430</v>
       </c>
       <c r="E1410" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="F1410" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1410" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>8000000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>430</v>
+        <v>120</v>
       </c>
       <c r="E1411" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
       <c r="F1411" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1411" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,17 +39956,17 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Hunian 3,5 Lantai Konsep Scandinavian Ala Apartement di Cilandak.</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>1800000000</v>
+        <v>1470000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E1412" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="F1412" t="n">
         <v>4</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Hunian 3,5 Lantai Konsep Scandinavian Ala Apartement di Cilandak.</t>
+          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>1470000000</v>
+        <v>3850000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="E1413" t="n">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="F1413" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,23 +40012,23 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Rumah 4 Lantai Private Pool di Jagakarsa Jakarta Selatan Cluster</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>3850000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1414" t="n">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="F1414" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1414" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah Sultan Pinggir Jalan Raya Utama Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>7100000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1415" t="n">
         <v>400</v>
       </c>
       <c r="E1415" t="n">
-        <v>206</v>
+        <v>515</v>
       </c>
       <c r="F1415" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Rumah Sultan Pinggir Jalan Raya Utama Cilandak, Jakarta Selatan</t>
+          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>14500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1416" t="n">
-        <v>515</v>
+        <v>248</v>
       </c>
       <c r="F1416" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1416" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
+          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>22500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>500</v>
+        <v>148</v>
       </c>
       <c r="E1417" t="n">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="F1417" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1417" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,20 +40124,20 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Rumah Baru Siap Huni di Dekat Tol Andara Jagakarsa Jakarta Selatan</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>2400000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="E1418" t="n">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="F1418" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1418" t="n">
         <v>4</v>
@@ -40152,23 +40152,23 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>4800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>258</v>
+        <v>600</v>
       </c>
       <c r="E1419" t="n">
-        <v>108</v>
+        <v>335</v>
       </c>
       <c r="F1419" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G1419" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1419" t="n">
         <v>1</v>
@@ -40180,20 +40180,20 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>22500000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1420" t="n">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="F1420" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1420" t="n">
         <v>3</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>5800000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E1421" t="n">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="F1421" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1421" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>2900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="E1422" t="n">
-        <v>155</v>
+        <v>404</v>
       </c>
       <c r="F1422" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1422" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,23 +40264,23 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>21000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1423" t="n">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="E1423" t="n">
-        <v>404</v>
+        <v>244</v>
       </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1423" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1423" t="n">
         <v>1</v>
@@ -40292,23 +40292,23 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>4099999999</v>
+        <v>12000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="E1424" t="n">
-        <v>244</v>
+        <v>696</v>
       </c>
       <c r="F1424" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1424" t="n">
         <v>1</v>
@@ -40320,23 +40320,23 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>12000000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>325</v>
+        <v>850</v>
       </c>
       <c r="E1425" t="n">
-        <v>696</v>
+        <v>1925</v>
       </c>
       <c r="F1425" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1425" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1425" t="n">
         <v>1</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>41000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>850</v>
+        <v>360</v>
       </c>
       <c r="E1426" t="n">
-        <v>1925</v>
+        <v>261</v>
       </c>
       <c r="F1426" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1426" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,20 +40376,20 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="E1427" t="n">
-        <v>261</v>
+        <v>703</v>
       </c>
       <c r="F1427" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -40404,17 +40404,17 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E1428" t="n">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F1428" t="n">
         <v>2</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>18500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1429" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F1429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1429" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>62000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>881</v>
+        <v>614</v>
       </c>
       <c r="E1430" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="F1430" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1430" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,23 +40488,23 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>614</v>
+        <v>720</v>
       </c>
       <c r="E1431" t="n">
-        <v>921</v>
+        <v>634</v>
       </c>
       <c r="F1431" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1431" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1431" t="n">
         <v>1</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1432" t="n">
-        <v>634</v>
+        <v>257</v>
       </c>
       <c r="F1432" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1432" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>9700000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1433" t="n">
-        <v>257</v>
+        <v>730</v>
       </c>
       <c r="F1433" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1433" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>45000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1434" t="n">
-        <v>730</v>
+        <v>176</v>
       </c>
       <c r="F1434" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>4420000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1435" t="n">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="F1435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1435" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>15300000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1436" t="n">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F1436" t="n">
         <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>6860000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1437" t="n">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="F1437" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1437" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>7800000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E1438" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F1438" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1438" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,23 +40712,23 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>4150000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="E1439" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F1439" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1439" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1439" t="n">
         <v>1</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>3320000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>198</v>
+        <v>600</v>
       </c>
       <c r="E1440" t="n">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="F1440" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1440" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>21500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1441" t="n">
-        <v>674</v>
+        <v>123</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1441" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,20 +40796,20 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1442" t="n">
         <v>2550000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E1442" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F1442" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1442" t="n">
         <v>2</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>2550000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="E1443" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="F1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1443" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="E1444" t="n">
-        <v>461</v>
+        <v>179</v>
       </c>
       <c r="F1444" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1444" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>6500000000</v>
+        <v>3040000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="E1445" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F1445" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1445" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,20 +40908,20 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
+          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>3040000000</v>
+        <v>4980000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E1446" t="n">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="F1446" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1446" t="n">
         <v>3</v>
@@ -40936,7 +40936,7 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
+          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
         </is>
       </c>
       <c r="C1447" t="n">
@@ -40964,17 +40964,17 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
+          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>4980000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="E1448" t="n">
-        <v>400</v>
+        <v>232</v>
       </c>
       <c r="F1448" t="n">
         <v>3</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
+          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>1900000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E1449" t="n">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="F1449" t="n">
         <v>3</v>
       </c>
       <c r="G1449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,17 +41020,17 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>1200000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E1450" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="F1450" t="n">
         <v>3</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>979000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>98</v>
+        <v>609</v>
       </c>
       <c r="E1451" t="n">
-        <v>98</v>
+        <v>822</v>
       </c>
       <c r="F1451" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1451" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>29500000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>609</v>
+        <v>90</v>
       </c>
       <c r="E1452" t="n">
-        <v>822</v>
+        <v>91</v>
       </c>
       <c r="F1452" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1452" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,23 +41104,23 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>2300000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="E1453" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="F1453" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1453" t="n">
         <v>1</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>6400000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>395</v>
+        <v>810</v>
       </c>
       <c r="E1454" t="n">
-        <v>172</v>
+        <v>370</v>
       </c>
       <c r="F1454" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,20 +41160,20 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>48000000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>810</v>
+        <v>200</v>
       </c>
       <c r="E1455" t="n">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="F1455" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1455" t="n">
         <v>4</v>
@@ -41188,20 +41188,20 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>2350000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="E1456" t="n">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="F1456" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>28000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="E1457" t="n">
-        <v>544</v>
+        <v>60</v>
       </c>
       <c r="F1457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>7900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1458" t="n">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="F1458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1458" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,20 +41272,20 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>4500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1459" t="n">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="F1459" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1459" t="n">
         <v>3</v>
@@ -41300,20 +41300,20 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>11800000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="E1460" t="n">
-        <v>696</v>
+        <v>942</v>
       </c>
       <c r="F1460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>25000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="E1461" t="n">
-        <v>942</v>
+        <v>60</v>
       </c>
       <c r="F1461" t="n">
         <v>2</v>
       </c>
       <c r="G1461" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,23 +41356,23 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>2600000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="E1462" t="n">
-        <v>60</v>
+        <v>864</v>
       </c>
       <c r="F1462" t="n">
         <v>2</v>
       </c>
       <c r="G1462" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>17700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1463" t="n">
-        <v>864</v>
+        <v>600</v>
       </c>
       <c r="F1463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1463" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>8000000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1464" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F1464" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>70000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1465" t="n">
-        <v>1300</v>
+        <v>60</v>
       </c>
       <c r="F1465" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>2830000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>60</v>
+        <v>1300</v>
       </c>
       <c r="E1466" t="n">
-        <v>60</v>
+        <v>1585</v>
       </c>
       <c r="F1466" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1466" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>275000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>1300</v>
+        <v>52</v>
       </c>
       <c r="E1467" t="n">
-        <v>1585</v>
+        <v>27</v>
       </c>
       <c r="F1467" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1467" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>1100000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>52</v>
+        <v>366</v>
       </c>
       <c r="E1468" t="n">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="F1468" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1468" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,23 +41552,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>22500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>366</v>
+        <v>60</v>
       </c>
       <c r="E1469" t="n">
-        <v>366</v>
+        <v>60</v>
       </c>
       <c r="F1469" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1469" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1469" t="n">
         <v>1</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>6400000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1470" t="n">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="F1470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,17 +41608,17 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>6800000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E1471" t="n">
-        <v>154</v>
+        <v>535</v>
       </c>
       <c r="F1471" t="n">
         <v>1</v>
@@ -41636,17 +41636,17 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>11300000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>600</v>
+        <v>158</v>
       </c>
       <c r="E1472" t="n">
-        <v>535</v>
+        <v>63</v>
       </c>
       <c r="F1472" t="n">
         <v>1</v>
@@ -41664,14 +41664,14 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>2100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E1473" t="n">
         <v>63</v>
@@ -41692,20 +41692,20 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E1474" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F1474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1474" t="n">
         <v>3</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>7800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1475" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1475" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>10000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E1476" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="F1476" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1476" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,17 +41776,17 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>6000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="E1477" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F1477" t="n">
         <v>5</v>
@@ -41804,20 +41804,20 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>7300000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>501</v>
+        <v>240</v>
       </c>
       <c r="E1478" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F1478" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1478" t="n">
         <v>3</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>5000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="E1479" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="F1479" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>1700000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1480" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F1480" t="n">
         <v>2</v>
       </c>
       <c r="G1480" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,23 +41888,23 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>8500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1481" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1481" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1481" t="n">
         <v>1</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>2000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1482" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F1482" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,23 +41944,23 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>10000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="E1483" t="n">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="F1483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1483" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1483" t="n">
         <v>1</v>
@@ -41972,20 +41972,20 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Termurah Rumah Hitung Tanah di Tebet Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>2000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="E1484" t="n">
-        <v>60</v>
+        <v>253</v>
       </c>
       <c r="F1484" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1484" t="n">
         <v>2</v>
@@ -42000,23 +42000,23 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Termurah Rumah Hitung Tanah di Tebet Akses Jalan Lebar</t>
+          <t>Rumah Siap Huni Ada Kolam Renang Akses Mudah</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>5800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1485" t="n">
-        <v>253</v>
+        <v>179</v>
       </c>
       <c r="F1485" t="n">
         <v>5</v>
       </c>
       <c r="G1485" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1485" t="n">
         <v>1</v>
@@ -42028,23 +42028,23 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Ada Kolam Renang Akses Mudah</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>6500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E1486" t="n">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="F1486" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1486" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1486" t="n">
         <v>1</v>
@@ -42056,23 +42056,23 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Rumah Luas, Strategis Dekat Pintu Tol Dijual Murah</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>4900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E1487" t="n">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="F1487" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1487" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1487" t="n">
         <v>1</v>
@@ -42084,23 +42084,23 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Luas, Strategis Dekat Pintu Tol Dijual Murah</t>
+          <t>Private Offering - Pondok Indah, 644 M² Land Parcel</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>2550000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="E1488" t="n">
-        <v>311</v>
+        <v>644</v>
       </c>
       <c r="F1488" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1488" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1488" t="n">
         <v>1</v>
@@ -42112,23 +42112,23 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Private Offering - Pondok Indah, 644 M² Land Parcel</t>
+          <t>Rumah Tua Masih Layak Huni Terletak di Segitiga Emas Jakarta Selatan bisa Dibangun 4 Lantai . bisa Komersil. Cocok.buat Kost2n . Lapangan Olah Raga. Lokasi Sgt Strategis Dekat Pusat Perkantoran SHM</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>23500000000</v>
+        <v>31000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E1489" t="n">
-        <v>644</v>
+        <v>750</v>
       </c>
       <c r="F1489" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1489" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1489" t="n">
         <v>1</v>
@@ -42140,26 +42140,26 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Rumah Tua Masih Layak Huni Terletak di Segitiga Emas Jakarta Selatan bisa Dibangun 4 Lantai . bisa Komersil. Cocok.buat Kost2n . Lapangan Olah Raga. Lokasi Sgt Strategis Dekat Pusat Perkantoran SHM</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>31000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E1490" t="n">
-        <v>750</v>
+        <v>242</v>
       </c>
       <c r="F1490" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1490" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1491">
@@ -42168,26 +42168,26 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1491" t="n">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="F1491" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1491" t="n">
         <v>4</v>
       </c>
       <c r="H1491" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1492">
@@ -42196,26 +42196,26 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>6900000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="E1492" t="n">
-        <v>76</v>
+        <v>1554</v>
       </c>
       <c r="F1492" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="G1492" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1492" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1493">
@@ -42224,26 +42224,26 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>52500000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>500</v>
+        <v>610</v>
       </c>
       <c r="E1493" t="n">
-        <v>1554</v>
+        <v>822</v>
       </c>
       <c r="F1493" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G1493" t="n">
         <v>52</v>
       </c>
       <c r="H1493" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1494">
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>28500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="E1494" t="n">
-        <v>822</v>
+        <v>634</v>
       </c>
       <c r="F1494" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G1494" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1494" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>32000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>720</v>
+        <v>450</v>
       </c>
       <c r="E1495" t="n">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="F1495" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1495" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1495" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>20000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1496" t="n">
-        <v>612</v>
+        <v>1925</v>
       </c>
       <c r="F1496" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1496" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H1496" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>49000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="E1497" t="n">
-        <v>1925</v>
+        <v>2500</v>
       </c>
       <c r="F1497" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G1497" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1497" t="n">
-        <v>210</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>35000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E1498" t="n">
-        <v>2500</v>
+        <v>76</v>
       </c>
       <c r="F1498" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1498" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1498" t="n">
-        <v>412</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>6900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>375</v>
+        <v>245</v>
       </c>
       <c r="E1499" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1499" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1499" t="n">
         <v>4</v>
       </c>
       <c r="H1499" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>17000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="E1500" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="F1500" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1500" t="n">
         <v>4</v>
       </c>
       <c r="H1500" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1501" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1501" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1501" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1501" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,26 +42476,26 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>4900000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="E1502" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="F1502" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G1502" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="H1502" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1503">
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rc Veteran Bintaro Jaksel Rumah Mewah Dekat Pintu Tol Siap Huni</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>6400000000</v>
+        <v>8700000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>395</v>
+        <v>600</v>
       </c>
       <c r="E1503" t="n">
-        <v>172</v>
+        <v>482</v>
       </c>
       <c r="F1503" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G1503" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="H1503" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Rc Veteran Bintaro Jaksel Rumah Mewah Dekat Pintu Tol Siap Huni</t>
+          <t>Jarang Ada Harga Dibawah Pasar Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>8700000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="E1504" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F1504" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G1504" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="H1504" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Jarang Ada Harga Dibawah Pasar Lokasi Strategis</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>12000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>680</v>
+        <v>80</v>
       </c>
       <c r="E1505" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="F1505" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1505" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H1505" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>1750000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="E1506" t="n">
-        <v>120</v>
+        <v>494</v>
       </c>
       <c r="F1506" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1506" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1506" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Siap Huni Dalam Cluster Dekat Tol Andara</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>53000000000</v>
+        <v>2049999999</v>
       </c>
       <c r="D1507" t="n">
-        <v>457</v>
+        <v>180</v>
       </c>
       <c r="E1507" t="n">
-        <v>494</v>
+        <v>95</v>
       </c>
       <c r="F1507" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1507" t="n">
         <v>4</v>
       </c>
       <c r="H1507" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Cluster Dekat Tol Andara</t>
+          <t>Rumah Nyaman 1,5 Lantai Pejaten Timur Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>2049999999</v>
+        <v>5000000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1508" t="n">
-        <v>95</v>
+        <v>572</v>
       </c>
       <c r="F1508" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1508" t="n">
         <v>4</v>
       </c>
       <c r="H1508" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Rumah Nyaman 1,5 Lantai Pejaten Timur Pasar Minggu Jakarta Selatan</t>
+          <t>Rumah Mewah Jalan Lebar Siap Huni</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>5000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1509" t="n">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="F1509" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1509" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1509" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Rumah Mewah Jalan Lebar Siap Huni</t>
+          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>13000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="E1510" t="n">
-        <v>335</v>
+        <v>60</v>
       </c>
       <c r="F1510" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1510" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1510" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+          <t>Rumah Cluster On Progres Lt.50 Idr 989Jt Lt.54 Idr 1,038M Lt,60 Idr 1,111M Lt,70 Idr 1,233M</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>2000000000</v>
+        <v>989000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E1511" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F1511" t="n">
         <v>3</v>
       </c>
       <c r="G1511" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1511" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,23 +42756,23 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Rumah Cluster On Progres Lt.50 Idr 989Jt Lt.54 Idr 1,038M Lt,60 Idr 1,111M Lt,70 Idr 1,233M</t>
+          <t>Dijual Rumah di Kertanegara Kebayoran Baru Lokasi Premium</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>989000000</v>
+        <v>220000000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="E1512" t="n">
-        <v>50</v>
+        <v>1644</v>
       </c>
       <c r="F1512" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1512" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H1512" t="n">
         <v>1</v>
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Kertanegara Kebayoran Baru Lokasi Premium</t>
+          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>220000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>630</v>
+        <v>127</v>
       </c>
       <c r="E1513" t="n">
-        <v>1644</v>
+        <v>60</v>
       </c>
       <c r="F1513" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1513" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="H1513" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,26 +42812,26 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>3000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>127</v>
+        <v>375</v>
       </c>
       <c r="E1514" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1515">
@@ -42840,26 +42840,26 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
+          <t>Rumah Hitung Tanah Saja 765 Meter Area Kyai Maja</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>6900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>375</v>
+        <v>765</v>
       </c>
       <c r="E1515" t="n">
-        <v>76</v>
+        <v>765</v>
       </c>
       <c r="F1515" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1515" t="n">
         <v>4</v>
       </c>
       <c r="H1515" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Saja 765 Meter Area Kyai Maja</t>
+          <t>Rumah Mewah Dalam Komplek Jepang One Gate System</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>25000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>765</v>
+        <v>300</v>
       </c>
       <c r="E1516" t="n">
-        <v>765</v>
+        <v>394</v>
       </c>
       <c r="F1516" t="n">
         <v>7</v>
       </c>
       <c r="G1516" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1516" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Komplek Jepang One Gate System</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>13900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1517" t="n">
-        <v>394</v>
+        <v>263</v>
       </c>
       <c r="F1517" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1517" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1517" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,23 +42924,23 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah Bagus Baru 2 Lantai Dijual Kondisi Bagus Kawasan Dekat Sekolah</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>5500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="E1518" t="n">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="F1518" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1518" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1518" t="n">
         <v>11</v>
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Rumah Bagus Baru 2 Lantai Dijual Kondisi Bagus Kawasan Dekat Sekolah</t>
+          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>2000000000</v>
+        <v>31500000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E1519" t="n">
-        <v>60</v>
+        <v>2620</v>
       </c>
       <c r="F1519" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1519" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1519" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1520">
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>31500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>400</v>
+        <v>760</v>
       </c>
       <c r="E1520" t="n">
-        <v>2620</v>
+        <v>517</v>
       </c>
       <c r="F1520" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G1520" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H1520" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>38000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>760</v>
+        <v>375</v>
       </c>
       <c r="E1521" t="n">
-        <v>517</v>
+        <v>76</v>
       </c>
       <c r="F1521" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1521" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1521" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>6900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="E1522" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F1522" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1522" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1522" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>2000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="E1523" t="n">
-        <v>60</v>
+        <v>2360</v>
       </c>
       <c r="F1523" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="G1523" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1523" t="n">
-        <v>11</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Rumah Murah Sekali Dekat MRT dan Citos di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>48000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E1524" t="n">
-        <v>2360</v>
+        <v>488</v>
       </c>
       <c r="F1524" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G1524" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H1524" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,26 +43120,26 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Rumah Murah Sekali Dekat MRT dan Citos di Cilandak Jakarta Selatan</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>7500000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="E1525" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="F1525" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1525" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H1525" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1526">
@@ -43148,26 +43148,26 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>80000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1526" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="E1526" t="n">
-        <v>1050</v>
+        <v>425</v>
       </c>
       <c r="F1526" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G1526" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H1526" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1527">
@@ -43176,26 +43176,26 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>15500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1527" t="n">
-        <v>340</v>
+        <v>850</v>
       </c>
       <c r="E1527" t="n">
-        <v>350</v>
+        <v>1800</v>
       </c>
       <c r="F1527" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1527" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H1527" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1528">
@@ -43204,26 +43204,26 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>1200000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>65</v>
+        <v>609</v>
       </c>
       <c r="E1528" t="n">
-        <v>106</v>
+        <v>822</v>
       </c>
       <c r="F1528" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1528" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1528" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1529">
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>2500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="E1529" t="n">
-        <v>30</v>
+        <v>580</v>
       </c>
       <c r="F1529" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1529" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1529" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,26 +43260,26 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>25000000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="E1530" t="n">
-        <v>425</v>
+        <v>257</v>
       </c>
       <c r="F1530" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G1530" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1530" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>40000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>850</v>
+        <v>250</v>
       </c>
       <c r="E1531" t="n">
-        <v>1800</v>
+        <v>388</v>
       </c>
       <c r="F1531" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1531" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1531" t="n">
-        <v>220</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>30000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>609</v>
+        <v>350</v>
       </c>
       <c r="E1532" t="n">
-        <v>822</v>
+        <v>237</v>
       </c>
       <c r="F1532" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1532" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1532" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>7900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>375</v>
+        <v>145</v>
       </c>
       <c r="E1533" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1533" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1533" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>12500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1534" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="F1534" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1534" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1534" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>9600000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="E1535" t="n">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="F1535" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G1535" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1535" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>3500000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1536" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="E1536" t="n">
-        <v>388</v>
+        <v>130</v>
       </c>
       <c r="F1536" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1536" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1536" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>13500000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>374</v>
+        <v>800</v>
       </c>
       <c r="E1537" t="n">
-        <v>181</v>
+        <v>1050</v>
       </c>
       <c r="F1537" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="G1537" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1537" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>1700000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1538" t="n">
-        <v>237</v>
+        <v>667</v>
       </c>
       <c r="F1538" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1538" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1538" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>2550000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1539" t="n">
-        <v>145</v>
+        <v>500</v>
       </c>
       <c r="E1539" t="n">
-        <v>75</v>
+        <v>703</v>
       </c>
       <c r="F1539" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G1539" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1539" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>2000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E1540" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F1540" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1540" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1540" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,26 +43568,26 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>2600000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>88</v>
+        <v>400</v>
       </c>
       <c r="E1541" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="F1541" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1541" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1541" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1542">
@@ -43596,23 +43596,23 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>2100000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E1542" t="n">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F1542" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1542" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1542" t="n">
         <v>2</v>
@@ -43624,23 +43624,23 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>4700000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="E1543" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F1543" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1543" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H1543" t="n">
         <v>1</v>
@@ -43652,26 +43652,26 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>23000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1544" t="n">
-        <v>1050</v>
+        <v>400</v>
       </c>
       <c r="F1544" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="G1544" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1544" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1545">
@@ -43680,26 +43680,26 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Eksklusif! Hunian Elit di Jl Wijaya, Melawai, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>2830000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>112</v>
+        <v>1000</v>
       </c>
       <c r="E1545" t="n">
-        <v>70</v>
+        <v>504</v>
       </c>
       <c r="F1545" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1545" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1545" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,23 +43708,23 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>890000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E1546" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="F1546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1546" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1546" t="n">
         <v>1</v>
@@ -43736,26 +43736,26 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>For Sale Rumah Pondok Indah Backyard</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>48000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="E1547" t="n">
-        <v>667</v>
+        <v>2835</v>
       </c>
       <c r="F1547" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G1547" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="H1547" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1548">
@@ -43764,26 +43764,26 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Rumah Mewah Bangka Kemang Private Cluster 6 KT Tetangga Pejabat</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>22500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1548" t="n">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="F1548" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G1548" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1548" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1549">
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Rumah Jl Benda Kemang 1000 M2 Jarang Ada Bagus</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>8500000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>250</v>
+        <v>1400</v>
       </c>
       <c r="E1549" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F1549" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G1549" t="n">
         <v>41</v>
       </c>
       <c r="H1549" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,26 +43820,26 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>8000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E1550" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F1550" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1550" t="n">
         <v>31</v>
       </c>
       <c r="H1550" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1551">
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Baru Lokasi Strategis Dekat Simatupang di Cilandak Jakarta</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>32000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1551" t="n">
-        <v>703</v>
+        <v>100</v>
       </c>
       <c r="F1551" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G1551" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1551" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>4500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E1552" t="n">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="F1552" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G1552" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Rumah Mewah Terawat Dalam Komplek di Tebet</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>6800000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1553" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1553" t="n">
-        <v>240</v>
+        <v>394</v>
       </c>
       <c r="F1553" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1553" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1553" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>Rumah Cluster Semifurnish Harga Dekat NJOP di Area Strategis Jagakarsa Mahr434</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>3500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="E1554" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F1554" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1554" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,26 +43960,26 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Termurah! Rumah Fully Furnished Dalam Cluster Dekat MRT</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>2900000000</v>
+        <v>2180000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E1555" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F1555" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1555" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1555" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1556">
@@ -43988,23 +43988,23 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>14800000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>500</v>
+        <v>318</v>
       </c>
       <c r="E1556" t="n">
-        <v>700</v>
+        <v>497</v>
       </c>
       <c r="F1556" t="n">
         <v>5</v>
       </c>
       <c r="G1556" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1556" t="n">
         <v>22</v>
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>6400000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>308</v>
+        <v>120</v>
       </c>
       <c r="E1557" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="F1557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,26 +44044,26 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>15700000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="E1558" t="n">
-        <v>400</v>
+        <v>317</v>
       </c>
       <c r="F1558" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1558" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1558" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1559">
@@ -44072,26 +44072,26 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Eksklusif! Hunian Elit di Jl Wijaya, Melawai, Kebayoran Baru, Jakarta Selatan</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>68000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>1000</v>
+        <v>185</v>
       </c>
       <c r="E1559" t="n">
-        <v>504</v>
+        <v>300</v>
       </c>
       <c r="F1559" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G1559" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1559" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1560">
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>1950000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="E1560" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F1560" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1560" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1560" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>1700000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>92</v>
+        <v>775</v>
       </c>
       <c r="E1561" t="n">
-        <v>90</v>
+        <v>925</v>
       </c>
       <c r="F1561" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1561" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1561" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,26 +44156,26 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>For Sale Rumah Pondok Indah Backyard</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>170000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>1400</v>
+        <v>320</v>
       </c>
       <c r="E1562" t="n">
-        <v>2835</v>
+        <v>664</v>
       </c>
       <c r="F1562" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G1562" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H1562" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,26 +44184,26 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Rumah Mewah Bangka Kemang Private Cluster 6 KT Tetangga Pejabat</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>12500000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1563" t="n">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="F1563" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="G1563" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1563" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1564">
@@ -44212,26 +44212,26 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Rumah Jl Benda Kemang 1000 M2 Jarang Ada Bagus</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>28000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="E1564" t="n">
-        <v>1000</v>
+        <v>301</v>
       </c>
       <c r="F1564" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G1564" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1564" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1565">
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>3900000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="E1565" t="n">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="F1565" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1565" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1565" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Rumah Baru Lokasi Strategis Dekat Simatupang di Cilandak Jakarta</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>3900000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E1566" t="n">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="F1566" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1566" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1566" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Luxe Court Permata Hijau Signature</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>1700000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="E1567" t="n">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="F1567" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G1567" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1567" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>62000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>881</v>
+        <v>340</v>
       </c>
       <c r="E1568" t="n">
-        <v>1066</v>
+        <v>350</v>
       </c>
       <c r="F1568" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1568" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H1568" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat Dalam Komplek di Tebet</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>13900000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>300</v>
+        <v>135</v>
       </c>
       <c r="E1569" t="n">
-        <v>394</v>
+        <v>30</v>
       </c>
       <c r="F1569" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1569" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1569" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Rumah Cluster Semifurnish Harga Dekat NJOP di Area Strategis Jagakarsa Mahr434</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>2000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="E1570" t="n">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="F1570" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1570" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1570" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,838 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Fully Furnished Dalam Cluster Dekat MRT</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>2180000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1571" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1571" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>346</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1572" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>457</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1573" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>452</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1574" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>880</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1575" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>17500000000</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>470</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>412</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1576" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>1576</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>627</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1577" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>7500000000</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>404</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>49000000000</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>540</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>584</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1585" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1586" t="n">
         <v>70</v>
       </c>
-      <c r="E1571" t="n">
-        <v>70</v>
-      </c>
-      <c r="F1571" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1571" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1571" t="n">
-        <v>2</v>
+      <c r="F1586" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1586" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Rumah 3 Lantai Bagus Lokasi Strategis di Kalibata Jaksel</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>119</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>1587</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1588" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Termurah - Turun Harga Rumah Lebak Bulus - Strategis Jalan Raya</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>13600000000</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1590" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1590" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>4950000000</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>370</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>91</v>
+      </c>
+      <c r="H1591" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>14800000000</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1592" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>69</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1593" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Rumah Dijual Baru Bebas Banjir Modern Dilengkapi Ai Fasum Lengkap</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1594" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>1594</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Dharmawangsa - Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>85000000000</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1595" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Rumah Konsep Compound 3 Unit - Cipete Selatan - LT 1.295 M² - SHM</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>1295</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1596" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1597" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>JUAL RUMAH HOMEY DALAM KOMPLEKS EKSKLUSIF DI LEBAK BULUS DEKAT MRT FATMAWATI</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>5750000000</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>207</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1598" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1598" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>1598</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Luas dan Nyaman di Pejaten Indah Ii , Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>349</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1599" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1599" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Rumah Harga Menarik di Kuningan Area - Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>15500000000</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>407</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>391</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1600" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1623"/>
+  <dimension ref="A1:H1655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40152,23 +40152,23 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>2900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="E1419" t="n">
-        <v>155</v>
+        <v>404</v>
       </c>
       <c r="F1419" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1419" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1419" t="n">
         <v>1</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>21000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1420" t="n">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="E1420" t="n">
-        <v>404</v>
+        <v>244</v>
       </c>
       <c r="F1420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1420" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>4099999999</v>
+        <v>12000000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="E1421" t="n">
-        <v>244</v>
+        <v>696</v>
       </c>
       <c r="F1421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>12000000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>325</v>
+        <v>850</v>
       </c>
       <c r="E1422" t="n">
-        <v>696</v>
+        <v>1925</v>
       </c>
       <c r="F1422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1422" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,23 +40264,23 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>41000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>850</v>
+        <v>360</v>
       </c>
       <c r="E1423" t="n">
-        <v>1925</v>
+        <v>261</v>
       </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1423" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1423" t="n">
         <v>1</v>
@@ -40292,20 +40292,20 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="E1424" t="n">
-        <v>261</v>
+        <v>703</v>
       </c>
       <c r="F1424" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1424" t="n">
         <v>4</v>
@@ -40320,17 +40320,17 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E1425" t="n">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F1425" t="n">
         <v>2</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>18500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1426" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F1426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1426" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,23 +40376,23 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>62000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>881</v>
+        <v>614</v>
       </c>
       <c r="E1427" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="F1427" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1427" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1427" t="n">
         <v>1</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>614</v>
+        <v>720</v>
       </c>
       <c r="E1428" t="n">
-        <v>921</v>
+        <v>634</v>
       </c>
       <c r="F1428" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1428" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1429" t="n">
-        <v>634</v>
+        <v>257</v>
       </c>
       <c r="F1429" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1429" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>9700000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1430" t="n">
-        <v>257</v>
+        <v>730</v>
       </c>
       <c r="F1430" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1430" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,23 +40488,23 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>45000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1431" t="n">
-        <v>730</v>
+        <v>176</v>
       </c>
       <c r="F1431" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1431" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1431" t="n">
         <v>1</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>4420000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1432" t="n">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="F1432" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1432" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>15300000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1433" t="n">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F1433" t="n">
         <v>4</v>
       </c>
       <c r="G1433" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>6860000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1434" t="n">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="F1434" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1434" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>7800000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E1435" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F1435" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1435" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>4150000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="E1436" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F1436" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>3320000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>198</v>
+        <v>600</v>
       </c>
       <c r="E1437" t="n">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="F1437" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1437" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>21500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1438" t="n">
-        <v>674</v>
+        <v>123</v>
       </c>
       <c r="F1438" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1438" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,20 +40712,20 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1439" t="n">
         <v>2550000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E1439" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F1439" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1439" t="n">
         <v>2</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>2550000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="E1440" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="F1440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="E1441" t="n">
-        <v>461</v>
+        <v>179</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1441" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,23 +40796,23 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>6500000000</v>
+        <v>3040000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="E1442" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F1442" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1442" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1442" t="n">
         <v>1</v>
@@ -40824,20 +40824,20 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah LT 151 SHM Hadap Utara 10 Menit ke Aeon Mall Tanjung Barat J-17334</t>
+          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>3040000000</v>
+        <v>4980000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E1443" t="n">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="F1443" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1443" t="n">
         <v>3</v>
@@ -40852,7 +40852,7 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Rumah Luas 1 LT Dekat Cilandak 10 Menit ke Gerbang Tol Dibantu KPR J45797</t>
+          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
         </is>
       </c>
       <c r="C1444" t="n">
@@ -40880,17 +40880,17 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Luas Terawat 15 Menit ke Rsu Andhika Siap KPR Hadap Timur J45797</t>
+          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>4980000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="E1445" t="n">
-        <v>400</v>
+        <v>232</v>
       </c>
       <c r="F1445" t="n">
         <v>3</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Hitung Tanah Dibawah NJOP Lebak Bulus</t>
+          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>1900000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E1446" t="n">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="F1446" t="n">
         <v>3</v>
       </c>
       <c r="G1446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,17 +40936,17 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah Dikomplek Ciputat Legoso</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>1200000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E1447" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="F1447" t="n">
         <v>3</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>979000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>98</v>
+        <v>609</v>
       </c>
       <c r="E1448" t="n">
-        <v>98</v>
+        <v>822</v>
       </c>
       <c r="F1448" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1448" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>29500000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>609</v>
+        <v>90</v>
       </c>
       <c r="E1449" t="n">
-        <v>822</v>
+        <v>91</v>
       </c>
       <c r="F1449" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1449" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>2300000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="E1450" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="F1450" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>6400000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>395</v>
+        <v>810</v>
       </c>
       <c r="E1451" t="n">
-        <v>172</v>
+        <v>370</v>
       </c>
       <c r="F1451" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1451" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,20 +41076,20 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>48000000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>810</v>
+        <v>200</v>
       </c>
       <c r="E1452" t="n">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="F1452" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1452" t="n">
         <v>4</v>
@@ -41104,20 +41104,20 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>2350000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="E1453" t="n">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="F1453" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1453" t="n">
         <v>4</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>28000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="E1454" t="n">
-        <v>544</v>
+        <v>60</v>
       </c>
       <c r="F1454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1454" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>7900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1455" t="n">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="F1455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1455" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,20 +41188,20 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>4500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1456" t="n">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="F1456" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1456" t="n">
         <v>3</v>
@@ -41216,20 +41216,20 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>11800000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="E1457" t="n">
-        <v>696</v>
+        <v>942</v>
       </c>
       <c r="F1457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1457" t="n">
         <v>3</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>25000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="E1458" t="n">
-        <v>942</v>
+        <v>60</v>
       </c>
       <c r="F1458" t="n">
         <v>2</v>
       </c>
       <c r="G1458" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>2600000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="E1459" t="n">
-        <v>60</v>
+        <v>864</v>
       </c>
       <c r="F1459" t="n">
         <v>2</v>
       </c>
       <c r="G1459" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>17700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1460" t="n">
-        <v>864</v>
+        <v>600</v>
       </c>
       <c r="F1460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>8000000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1461" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F1461" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,23 +41356,23 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>70000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1462" t="n">
-        <v>1300</v>
+        <v>60</v>
       </c>
       <c r="F1462" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>2830000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>60</v>
+        <v>1300</v>
       </c>
       <c r="E1463" t="n">
-        <v>60</v>
+        <v>1585</v>
       </c>
       <c r="F1463" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1463" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>275000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>1300</v>
+        <v>52</v>
       </c>
       <c r="E1464" t="n">
-        <v>1585</v>
+        <v>27</v>
       </c>
       <c r="F1464" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1464" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>1100000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>52</v>
+        <v>366</v>
       </c>
       <c r="E1465" t="n">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="F1465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>22500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>366</v>
+        <v>60</v>
       </c>
       <c r="E1466" t="n">
-        <v>366</v>
+        <v>60</v>
       </c>
       <c r="F1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>6400000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1467" t="n">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="F1467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1467" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,17 +41524,17 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>6800000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E1468" t="n">
-        <v>154</v>
+        <v>535</v>
       </c>
       <c r="F1468" t="n">
         <v>1</v>
@@ -41552,17 +41552,17 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>11300000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>600</v>
+        <v>158</v>
       </c>
       <c r="E1469" t="n">
-        <v>535</v>
+        <v>63</v>
       </c>
       <c r="F1469" t="n">
         <v>1</v>
@@ -41580,14 +41580,14 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>2100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E1470" t="n">
         <v>63</v>
@@ -41608,20 +41608,20 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E1471" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F1471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>7800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1472" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F1472" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1472" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,23 +41664,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>10000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E1473" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="F1473" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1473" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1473" t="n">
         <v>1</v>
@@ -41692,17 +41692,17 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>6000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="E1474" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F1474" t="n">
         <v>5</v>
@@ -41720,20 +41720,20 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>7300000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>501</v>
+        <v>240</v>
       </c>
       <c r="E1475" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F1475" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>5000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="E1476" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="F1476" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>1700000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1477" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F1477" t="n">
         <v>2</v>
       </c>
       <c r="G1477" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>8500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1478" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1478" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>2000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1479" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F1479" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>10000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="E1480" t="n">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="F1480" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,20 +41888,20 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Termurah Rumah Hitung Tanah di Tebet Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>2000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="E1481" t="n">
-        <v>60</v>
+        <v>253</v>
       </c>
       <c r="F1481" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1481" t="n">
         <v>2</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Termurah Rumah Hitung Tanah di Tebet Akses Jalan Lebar</t>
+          <t>Rumah Siap Huni Ada Kolam Renang Akses Mudah</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>5800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1482" t="n">
-        <v>253</v>
+        <v>179</v>
       </c>
       <c r="F1482" t="n">
         <v>5</v>
       </c>
       <c r="G1482" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,23 +41944,23 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Ada Kolam Renang Akses Mudah</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>6500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E1483" t="n">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="F1483" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1483" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1483" t="n">
         <v>1</v>
@@ -41972,23 +41972,23 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Rumah Luas, Strategis Dekat Pintu Tol Dijual Murah</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>4900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E1484" t="n">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="F1484" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1484" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1484" t="n">
         <v>1</v>
@@ -42000,23 +42000,23 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Luas, Strategis Dekat Pintu Tol Dijual Murah</t>
+          <t>Private Offering - Pondok Indah, 644 M² Land Parcel</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>2550000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="E1485" t="n">
-        <v>311</v>
+        <v>644</v>
       </c>
       <c r="F1485" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1485" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1485" t="n">
         <v>1</v>
@@ -42028,23 +42028,23 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Private Offering - Pondok Indah, 644 M² Land Parcel</t>
+          <t>Rumah Tua Masih Layak Huni Terletak di Segitiga Emas Jakarta Selatan bisa Dibangun 4 Lantai . bisa Komersil. Cocok.buat Kost2n . Lapangan Olah Raga. Lokasi Sgt Strategis Dekat Pusat Perkantoran SHM</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>23500000000</v>
+        <v>31000000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E1486" t="n">
-        <v>644</v>
+        <v>750</v>
       </c>
       <c r="F1486" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1486" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1486" t="n">
         <v>1</v>
@@ -42056,26 +42056,26 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Tua Masih Layak Huni Terletak di Segitiga Emas Jakarta Selatan bisa Dibangun 4 Lantai . bisa Komersil. Cocok.buat Kost2n . Lapangan Olah Raga. Lokasi Sgt Strategis Dekat Pusat Perkantoran SHM</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>31000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E1487" t="n">
-        <v>750</v>
+        <v>242</v>
       </c>
       <c r="F1487" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1487" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1488">
@@ -42084,26 +42084,26 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1488" t="n">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="F1488" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1488" t="n">
         <v>4</v>
       </c>
       <c r="H1488" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1489">
@@ -42112,26 +42112,26 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>6900000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="E1489" t="n">
-        <v>76</v>
+        <v>1554</v>
       </c>
       <c r="F1489" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="G1489" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1489" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1490">
@@ -42140,26 +42140,26 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>52500000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>500</v>
+        <v>610</v>
       </c>
       <c r="E1490" t="n">
-        <v>1554</v>
+        <v>822</v>
       </c>
       <c r="F1490" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G1490" t="n">
         <v>52</v>
       </c>
       <c r="H1490" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1491">
@@ -42168,23 +42168,23 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>28500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>610</v>
+        <v>450</v>
       </c>
       <c r="E1491" t="n">
-        <v>822</v>
+        <v>612</v>
       </c>
       <c r="F1491" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1491" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1491" t="n">
         <v>22</v>
@@ -42196,26 +42196,26 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>20000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1492" t="n">
-        <v>612</v>
+        <v>1925</v>
       </c>
       <c r="F1492" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1492" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H1492" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1493">
@@ -42224,26 +42224,26 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>49000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="E1493" t="n">
-        <v>1925</v>
+        <v>2500</v>
       </c>
       <c r="F1493" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G1493" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1493" t="n">
-        <v>210</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1494">
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>35000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E1494" t="n">
-        <v>2500</v>
+        <v>76</v>
       </c>
       <c r="F1494" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1494" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1494" t="n">
-        <v>412</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>6900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>375</v>
+        <v>245</v>
       </c>
       <c r="E1495" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1495" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
       </c>
       <c r="H1495" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>17000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="E1496" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1496" t="n">
         <v>4</v>
       </c>
       <c r="H1496" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1497" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1497" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1497" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1497" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>4900000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="E1498" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="F1498" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G1498" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="H1498" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rc Veteran Bintaro Jaksel Rumah Mewah Dekat Pintu Tol Siap Huni</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>6400000000</v>
+        <v>8700000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>395</v>
+        <v>600</v>
       </c>
       <c r="E1499" t="n">
-        <v>172</v>
+        <v>482</v>
       </c>
       <c r="F1499" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G1499" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="H1499" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Rc Veteran Bintaro Jaksel Rumah Mewah Dekat Pintu Tol Siap Huni</t>
+          <t>Jarang Ada Harga Dibawah Pasar Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>8700000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="E1500" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F1500" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G1500" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="H1500" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Jarang Ada Harga Dibawah Pasar Lokasi Strategis</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>12000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>680</v>
+        <v>80</v>
       </c>
       <c r="E1501" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="F1501" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1501" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H1501" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,26 +42476,26 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>1750000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="E1502" t="n">
-        <v>120</v>
+        <v>494</v>
       </c>
       <c r="F1502" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1502" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1502" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1503">
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Siap Huni Dalam Cluster Dekat Tol Andara</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>53000000000</v>
+        <v>2049999999</v>
       </c>
       <c r="D1503" t="n">
-        <v>457</v>
+        <v>180</v>
       </c>
       <c r="E1503" t="n">
-        <v>494</v>
+        <v>95</v>
       </c>
       <c r="F1503" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1503" t="n">
         <v>4</v>
       </c>
       <c r="H1503" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Cluster Dekat Tol Andara</t>
+          <t>Rumah Nyaman 1,5 Lantai Pejaten Timur Pasar Minggu Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>2049999999</v>
+        <v>5000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1504" t="n">
-        <v>95</v>
+        <v>572</v>
       </c>
       <c r="F1504" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1504" t="n">
         <v>4</v>
       </c>
       <c r="H1504" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Rumah Nyaman 1,5 Lantai Pejaten Timur Pasar Minggu Jakarta Selatan</t>
+          <t>Rumah Mewah Jalan Lebar Siap Huni</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>5000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1505" t="n">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="F1505" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1505" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1505" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Rumah Mewah Jalan Lebar Siap Huni</t>
+          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>13000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="E1506" t="n">
-        <v>335</v>
+        <v>60</v>
       </c>
       <c r="F1506" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1506" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1506" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Rumah Murah Hanya 2 M di Jakarta Jarang Ada Kondisi Baru Desain Modern</t>
+          <t>Rumah Cluster On Progres Lt.50 Idr 989Jt Lt.54 Idr 1,038M Lt,60 Idr 1,111M Lt,70 Idr 1,233M</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>2000000000</v>
+        <v>989000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E1507" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F1507" t="n">
         <v>3</v>
       </c>
       <c r="G1507" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1507" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,23 +42644,23 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Rumah Cluster On Progres Lt.50 Idr 989Jt Lt.54 Idr 1,038M Lt,60 Idr 1,111M Lt,70 Idr 1,233M</t>
+          <t>Dijual Rumah di Kertanegara Kebayoran Baru Lokasi Premium</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>989000000</v>
+        <v>220000000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="E1508" t="n">
-        <v>50</v>
+        <v>1644</v>
       </c>
       <c r="F1508" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1508" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H1508" t="n">
         <v>1</v>
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Kertanegara Kebayoran Baru Lokasi Premium</t>
+          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>220000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>630</v>
+        <v>127</v>
       </c>
       <c r="E1509" t="n">
-        <v>1644</v>
+        <v>60</v>
       </c>
       <c r="F1509" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1509" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="H1509" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Ada Rooftop Kondisi Baru Dijual di Cijantung, Dekat Transum</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>3000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>127</v>
+        <v>375</v>
       </c>
       <c r="E1510" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1510" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1510" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1510" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel Dekat SCBD 4 Lantai Jarang Ada</t>
+          <t>Rumah Hitung Tanah Saja 765 Meter Area Kyai Maja</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>6900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>375</v>
+        <v>765</v>
       </c>
       <c r="E1511" t="n">
-        <v>76</v>
+        <v>765</v>
       </c>
       <c r="F1511" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1511" t="n">
         <v>4</v>
       </c>
       <c r="H1511" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Saja 765 Meter Area Kyai Maja</t>
+          <t>Rumah Mewah Dalam Komplek Jepang One Gate System</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>25000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>765</v>
+        <v>300</v>
       </c>
       <c r="E1512" t="n">
-        <v>765</v>
+        <v>394</v>
       </c>
       <c r="F1512" t="n">
         <v>7</v>
       </c>
       <c r="G1512" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1512" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dalam Komplek Jepang One Gate System</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>13900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1513" t="n">
-        <v>394</v>
+        <v>263</v>
       </c>
       <c r="F1513" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1513" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1513" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,23 +42812,23 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah Bagus Baru 2 Lantai Dijual Kondisi Bagus Kawasan Dekat Sekolah</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>5500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="E1514" t="n">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="F1514" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1514" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1514" t="n">
         <v>11</v>
@@ -42840,26 +42840,26 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Rumah Bagus Baru 2 Lantai Dijual Kondisi Bagus Kawasan Dekat Sekolah</t>
+          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>2000000000</v>
+        <v>31500000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E1515" t="n">
-        <v>60</v>
+        <v>2620</v>
       </c>
       <c r="F1515" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1515" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1515" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>31500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E1516" t="n">
-        <v>2620</v>
+        <v>76</v>
       </c>
       <c r="F1516" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1516" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1516" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>38000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>760</v>
+        <v>85</v>
       </c>
       <c r="E1517" t="n">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="F1517" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1517" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1517" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai</t>
+          <t>Rumah Murah Sekali Dekat MRT dan Citos di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>6900000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1518" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="F1518" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1518" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1518" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>2000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E1519" t="n">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="F1519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1519" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1520">
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>48000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E1520" t="n">
-        <v>2360</v>
+        <v>425</v>
       </c>
       <c r="F1520" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G1520" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H1520" t="n">
-        <v>220</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Rumah Murah Sekali Dekat MRT dan Citos di Cilandak Jakarta Selatan</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>7500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>200</v>
+        <v>850</v>
       </c>
       <c r="E1521" t="n">
-        <v>488</v>
+        <v>1800</v>
       </c>
       <c r="F1521" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G1521" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H1521" t="n">
-        <v>12</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>1200000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>65</v>
+        <v>609</v>
       </c>
       <c r="E1522" t="n">
-        <v>106</v>
+        <v>822</v>
       </c>
       <c r="F1522" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1522" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1522" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>25000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="E1523" t="n">
-        <v>425</v>
+        <v>580</v>
       </c>
       <c r="F1523" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G1523" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H1523" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>40000000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E1524" t="n">
-        <v>1800</v>
+        <v>257</v>
       </c>
       <c r="F1524" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G1524" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H1524" t="n">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,23 +43120,23 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>30000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>609</v>
+        <v>250</v>
       </c>
       <c r="E1525" t="n">
-        <v>822</v>
+        <v>388</v>
       </c>
       <c r="F1525" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1525" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1525" t="n">
         <v>22</v>
@@ -43148,26 +43148,26 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>12500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1526" t="n">
-        <v>400</v>
+        <v>145</v>
       </c>
       <c r="E1526" t="n">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="F1526" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G1526" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H1526" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1527">
@@ -43176,26 +43176,26 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>9600000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1527" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E1527" t="n">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="F1527" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G1527" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1527" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1528">
@@ -43204,26 +43204,26 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>3500000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="E1528" t="n">
-        <v>388</v>
+        <v>130</v>
       </c>
       <c r="F1528" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1528" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1528" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1529">
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>2550000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>145</v>
+        <v>800</v>
       </c>
       <c r="E1529" t="n">
-        <v>75</v>
+        <v>1050</v>
       </c>
       <c r="F1529" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="G1529" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1529" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,26 +43260,26 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>2000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="E1530" t="n">
-        <v>200</v>
+        <v>667</v>
       </c>
       <c r="F1530" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G1530" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1530" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>4700000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>275</v>
+        <v>500</v>
       </c>
       <c r="E1531" t="n">
-        <v>130</v>
+        <v>703</v>
       </c>
       <c r="F1531" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G1531" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H1531" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>23000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1532" t="n">
-        <v>1050</v>
+        <v>196</v>
       </c>
       <c r="F1532" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="G1532" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1532" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>48000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1533" t="n">
-        <v>667</v>
+        <v>240</v>
       </c>
       <c r="F1533" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1533" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1533" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>32000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1534" t="n">
-        <v>703</v>
+        <v>135</v>
       </c>
       <c r="F1534" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G1534" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1534" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>4500000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1535" t="n">
-        <v>196</v>
+        <v>400</v>
       </c>
       <c r="F1535" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G1535" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1535" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Eksklusif! Hunian Elit di Jl Wijaya, Melawai, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>6800000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1536" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1536" t="n">
-        <v>240</v>
+        <v>504</v>
       </c>
       <c r="F1536" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1536" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1536" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>For Sale Rumah Pondok Indah Backyard</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>3500000000</v>
+        <v>170000000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="E1537" t="n">
-        <v>135</v>
+        <v>2835</v>
       </c>
       <c r="F1537" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1537" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="H1537" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Mewah Bangka Kemang Private Cluster 6 KT Tetangga Pejabat</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>15700000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1538" t="n">
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="F1538" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="G1538" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1538" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Eksklusif! Hunian Elit di Jl Wijaya, Melawai, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Rumah Jl Benda Kemang 1000 M2 Jarang Ada Bagus</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>68000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1539" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1539" t="n">
         <v>1000</v>
       </c>
-      <c r="E1539" t="n">
-        <v>504</v>
-      </c>
       <c r="F1539" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1539" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1539" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>For Sale Rumah Pondok Indah Backyard</t>
+          <t>Rumah Baru Lokasi Strategis Dekat Simatupang di Cilandak Jakarta</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>170000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="E1540" t="n">
-        <v>2835</v>
+        <v>100</v>
       </c>
       <c r="F1540" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G1540" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="H1540" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,23 +43568,23 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Rumah Mewah Bangka Kemang Private Cluster 6 KT Tetangga Pejabat</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>12500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="E1541" t="n">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="F1541" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="G1541" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1541" t="n">
         <v>2</v>
@@ -43596,26 +43596,26 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Rumah Jl Benda Kemang 1000 M2 Jarang Ada Bagus</t>
+          <t>Rumah Mewah Terawat Dalam Komplek di Tebet</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>28000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="E1542" t="n">
-        <v>1000</v>
+        <v>394</v>
       </c>
       <c r="F1542" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1542" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1542" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1543">
@@ -43624,26 +43624,26 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Rumah Baru Lokasi Strategis Dekat Simatupang di Cilandak Jakarta</t>
+          <t>Rumah Cluster Semifurnish Harga Dekat NJOP di Area Strategis Jagakarsa Mahr434</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>3900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="E1543" t="n">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="F1543" t="n">
         <v>31</v>
       </c>
       <c r="G1543" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1543" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1544">
@@ -43652,23 +43652,23 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Termurah! Rumah Fully Furnished Dalam Cluster Dekat MRT</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>1700000000</v>
+        <v>2180000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E1544" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F1544" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G1544" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1544" t="n">
         <v>2</v>
@@ -43680,26 +43680,26 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat Dalam Komplek di Tebet</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>13900000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E1545" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="F1545" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1545" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1545" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,26 +43708,26 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Rumah Cluster Semifurnish Harga Dekat NJOP di Area Strategis Jagakarsa Mahr434</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>2000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E1546" t="n">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="F1546" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1546" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1547">
@@ -43736,26 +43736,26 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Fully Furnished Dalam Cluster Dekat MRT</t>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>2180000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="E1547" t="n">
-        <v>70</v>
+        <v>317</v>
       </c>
       <c r="F1547" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1547" t="n">
         <v>3</v>
       </c>
       <c r="H1547" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1548">
@@ -43764,23 +43764,23 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>12500000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>318</v>
+        <v>185</v>
       </c>
       <c r="E1548" t="n">
-        <v>497</v>
+        <v>300</v>
       </c>
       <c r="F1548" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G1548" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1548" t="n">
         <v>22</v>
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>1400000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1549" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F1549" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1549" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1549" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,26 +43820,26 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>9200000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>440</v>
+        <v>775</v>
       </c>
       <c r="E1550" t="n">
-        <v>317</v>
+        <v>925</v>
       </c>
       <c r="F1550" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1550" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1550" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1551">
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>16500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="E1551" t="n">
-        <v>300</v>
+        <v>664</v>
       </c>
       <c r="F1551" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G1551" t="n">
         <v>41</v>
       </c>
       <c r="H1551" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Dijual Rumah Area Jakarta Selatan</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>25000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1552" t="n">
-        <v>800</v>
+        <v>301</v>
       </c>
       <c r="F1552" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="G1552" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1552" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>120000000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1553" t="n">
-        <v>775</v>
+        <v>56</v>
       </c>
       <c r="E1553" t="n">
-        <v>925</v>
+        <v>29</v>
       </c>
       <c r="F1553" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G1553" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1553" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>9500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E1554" t="n">
-        <v>664</v>
+        <v>208</v>
       </c>
       <c r="F1554" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1554" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1554" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,26 +43960,26 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>6000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1555" t="n">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="F1555" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G1555" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1555" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1556">
@@ -43988,26 +43988,26 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>890000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>56</v>
+        <v>457</v>
       </c>
       <c r="E1556" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="F1556" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1556" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1556" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1557">
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>9000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>300</v>
+        <v>452</v>
       </c>
       <c r="E1557" t="n">
-        <v>208</v>
+        <v>1165</v>
       </c>
       <c r="F1557" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1557" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1557" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,26 +44044,26 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>32000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>400</v>
+        <v>880</v>
       </c>
       <c r="E1558" t="n">
-        <v>346</v>
+        <v>1000</v>
       </c>
       <c r="F1558" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1558" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1558" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1559">
@@ -44072,26 +44072,26 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>55000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>457</v>
+        <v>1050</v>
       </c>
       <c r="E1559" t="n">
-        <v>500</v>
+        <v>627</v>
       </c>
       <c r="F1559" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1559" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1559" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1560">
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>55000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>452</v>
+        <v>250</v>
       </c>
       <c r="E1560" t="n">
-        <v>1165</v>
+        <v>404</v>
       </c>
       <c r="F1560" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1560" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1560" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>62000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>880</v>
+        <v>1100</v>
       </c>
       <c r="E1561" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="F1561" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1561" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1561" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,23 +44156,23 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>40000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="E1562" t="n">
-        <v>627</v>
+        <v>1230</v>
       </c>
       <c r="F1562" t="n">
         <v>5</v>
       </c>
       <c r="G1562" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1562" t="n">
         <v>5</v>
@@ -44184,23 +44184,23 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>7500000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1563" t="n">
-        <v>404</v>
+        <v>584</v>
       </c>
       <c r="F1563" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1563" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1563" t="n">
         <v>4</v>
@@ -44212,26 +44212,26 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Rumah 3 Lantai Bagus Lokasi Strategis di Kalibata Jaksel</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>49000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1564" t="n">
-        <v>540</v>
+        <v>119</v>
       </c>
       <c r="F1564" t="n">
         <v>5</v>
       </c>
       <c r="G1564" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1564" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1565">
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>32000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>650</v>
+        <v>90</v>
       </c>
       <c r="E1565" t="n">
-        <v>1230</v>
+        <v>91</v>
       </c>
       <c r="F1565" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1565" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1565" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Termurah - Turun Harga Rumah Lebak Bulus - Strategis Jalan Raya</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>19000000000</v>
+        <v>13600000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1566" t="n">
-        <v>584</v>
+        <v>700</v>
       </c>
       <c r="F1566" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1566" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1566" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Bagus Lokasi Strategis di Kalibata Jaksel</t>
+          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>3100000000</v>
+        <v>4950000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="E1567" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F1567" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1567" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="H1567" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>2900000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E1568" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
       <c r="F1568" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1568" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1568" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,23 +44352,23 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Termurah - Turun Harga Rumah Lebak Bulus - Strategis Jalan Raya</t>
+          <t>Rumah Dijual Baru Bebas Banjir Modern Dilengkapi Ai Fasum Lengkap</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>13600000000</v>
+        <v>600000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E1569" t="n">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="F1569" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1569" t="n">
         <v>1</v>
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
+          <t>Dijual Rumah Mewah Dharmawangsa - Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>4950000000</v>
+        <v>85000000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>370</v>
+        <v>1500</v>
       </c>
       <c r="E1570" t="n">
-        <v>120</v>
+        <v>634</v>
       </c>
       <c r="F1570" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1570" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="H1570" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rumah Konsep Compound 3 Unit - Cipete Selatan - LT 1.295 M² - SHM</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>14800000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E1571" t="n">
-        <v>700</v>
+        <v>1295</v>
       </c>
       <c r="F1571" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1571" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1571" t="n">
-        <v>22</v>
+        <v>410</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Rumah Dijual Baru Bebas Banjir Modern Dilengkapi Ai Fasum Lengkap</t>
+          <t>JUAL RUMAH HOMEY DALAM KOMPLEKS EKSKLUSIF DI LEBAK BULUS DEKAT MRT FATMAWATI</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>600000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1572" t="n">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="F1572" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G1572" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1572" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Dharmawangsa - Jakarta Selatan</t>
+          <t>Dijual Rumah Luas dan Nyaman di Pejaten Indah Ii , Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>85000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>1500</v>
+        <v>450</v>
       </c>
       <c r="E1573" t="n">
-        <v>634</v>
+        <v>349</v>
       </c>
       <c r="F1573" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1573" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1573" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Rumah Konsep Compound 3 Unit - Cipete Selatan - LT 1.295 M² - SHM</t>
+          <t>Rumah Harga Menarik di Kuningan Area - Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>30000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>1000</v>
+        <v>407</v>
       </c>
       <c r="E1574" t="n">
-        <v>1295</v>
+        <v>391</v>
       </c>
       <c r="F1574" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G1574" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1574" t="n">
-        <v>410</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,26 +44520,26 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>JUAL RUMAH HOMEY DALAM KOMPLEKS EKSKLUSIF DI LEBAK BULUS DEKAT MRT FATMAWATI</t>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>5750000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="E1575" t="n">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="F1575" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G1575" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1575" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1576">
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Dijual Rumah Luas dan Nyaman di Pejaten Indah Ii , Jakarta Selatan</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>6500000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="E1576" t="n">
-        <v>349</v>
+        <v>1050</v>
       </c>
       <c r="F1576" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1576" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1576" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,26 +44576,26 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Rumah Harga Menarik di Kuningan Area - Jakarta Selatan</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>15500000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1577" t="n">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="E1577" t="n">
-        <v>391</v>
+        <v>899</v>
       </c>
       <c r="F1577" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1577" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1577" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1578">
@@ -44604,26 +44604,26 @@
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>1100000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1578" t="n">
-        <v>69</v>
+        <v>340</v>
       </c>
       <c r="E1578" t="n">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="F1578" t="n">
         <v>3</v>
       </c>
       <c r="G1578" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1578" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1579">
@@ -44632,26 +44632,26 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>80000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1579" t="n">
-        <v>600</v>
+        <v>135</v>
       </c>
       <c r="E1579" t="n">
-        <v>1050</v>
+        <v>30</v>
       </c>
       <c r="F1579" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1579" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H1579" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1580">
@@ -44660,26 +44660,26 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>16000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1580" t="n">
-        <v>467</v>
+        <v>90</v>
       </c>
       <c r="E1580" t="n">
-        <v>899</v>
+        <v>80</v>
       </c>
       <c r="F1580" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1580" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1580" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1581">
@@ -44688,26 +44688,26 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>15500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1581" t="n">
-        <v>340</v>
+        <v>2700</v>
       </c>
       <c r="E1581" t="n">
-        <v>350</v>
+        <v>2382</v>
       </c>
       <c r="F1581" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G1581" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H1581" t="n">
-        <v>3</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1582">
@@ -44716,17 +44716,17 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>2500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1582" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E1582" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F1582" t="n">
         <v>3</v>
@@ -44744,23 +44744,23 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
+          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>1950000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1583" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E1583" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F1583" t="n">
         <v>3</v>
       </c>
       <c r="G1583" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1583" t="n">
         <v>1</v>
@@ -44772,26 +44772,26 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
+          <t>Dijual Rumah bisa Buatusaha</t>
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>90000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1584" t="n">
-        <v>2700</v>
+        <v>610</v>
       </c>
       <c r="E1584" t="n">
-        <v>2382</v>
+        <v>310</v>
       </c>
       <c r="F1584" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="G1584" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="H1584" t="n">
-        <v>510</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1585">
@@ -44800,26 +44800,26 @@
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>7900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1585" t="n">
-        <v>375</v>
+        <v>720</v>
       </c>
       <c r="E1585" t="n">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c r="F1585" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G1585" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1585" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1586">
@@ -44828,26 +44828,26 @@
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>8500000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1586" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1586" t="n">
-        <v>200</v>
+        <v>570</v>
       </c>
       <c r="F1586" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1586" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1586" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1587">
@@ -44856,26 +44856,26 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>22500000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1587" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="E1587" t="n">
-        <v>366</v>
+        <v>120</v>
       </c>
       <c r="F1587" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1587" t="n">
         <v>3</v>
       </c>
       <c r="H1587" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1588">
@@ -44884,26 +44884,26 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>8000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1588" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1588" t="n">
-        <v>165</v>
+        <v>1020</v>
       </c>
       <c r="F1588" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1588" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1588" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1589">
@@ -44912,26 +44912,26 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>13500000000</v>
+        <v>281000000000</v>
       </c>
       <c r="D1589" t="n">
-        <v>374</v>
+        <v>2000</v>
       </c>
       <c r="E1589" t="n">
-        <v>181</v>
+        <v>6250</v>
       </c>
       <c r="F1589" t="n">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="G1589" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="H1589" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1590">
@@ -44940,26 +44940,26 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
+          <t>Rumah Besar di Jl. Wijaya.</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>1400000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1590" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1590" t="n">
-        <v>60</v>
+        <v>579</v>
       </c>
       <c r="F1590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1591">
@@ -44968,26 +44968,26 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
+          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>1200000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1591" t="n">
-        <v>95</v>
+        <v>750</v>
       </c>
       <c r="E1591" t="n">
-        <v>95</v>
+        <v>607</v>
       </c>
       <c r="F1591" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1591" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H1591" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1592">
@@ -44996,26 +44996,26 @@
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Dijual Rumah bisa Buatusaha</t>
+          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>30000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1592" t="n">
-        <v>610</v>
+        <v>800</v>
       </c>
       <c r="E1592" t="n">
-        <v>310</v>
+        <v>475</v>
       </c>
       <c r="F1592" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="G1592" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H1592" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1593">
@@ -45024,26 +45024,26 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>2600000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1593" t="n">
-        <v>88</v>
+        <v>600</v>
       </c>
       <c r="E1593" t="n">
-        <v>55</v>
+        <v>637</v>
       </c>
       <c r="F1593" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1593" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1593" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1594">
@@ -45052,26 +45052,26 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>10000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1594" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1594" t="n">
-        <v>208</v>
+        <v>530</v>
       </c>
       <c r="F1594" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1594" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1594" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1595">
@@ -45080,26 +45080,26 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>32000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1595" t="n">
-        <v>720</v>
+        <v>450</v>
       </c>
       <c r="E1595" t="n">
-        <v>634</v>
+        <v>931</v>
       </c>
       <c r="F1595" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1595" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1595" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1596">
@@ -45108,26 +45108,26 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>16899999999</v>
+        <v>25000000000</v>
       </c>
       <c r="D1596" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E1596" t="n">
-        <v>570</v>
+        <v>676</v>
       </c>
       <c r="F1596" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1596" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1596" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1597">
@@ -45136,26 +45136,26 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>2830000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1597" t="n">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="E1597" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="F1597" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1597" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1597" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1598">
@@ -45164,26 +45164,26 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
+          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>4099999999</v>
+        <v>15000000000</v>
       </c>
       <c r="D1598" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="E1598" t="n">
-        <v>120</v>
+        <v>704</v>
       </c>
       <c r="F1598" t="n">
         <v>4</v>
       </c>
       <c r="G1598" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1598" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1599">
@@ -45192,20 +45192,20 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
+          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>21000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1599" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E1599" t="n">
-        <v>1020</v>
+        <v>60</v>
       </c>
       <c r="F1599" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1599" t="n">
         <v>2</v>
@@ -45220,26 +45220,26 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>281000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1600" t="n">
-        <v>2000</v>
+        <v>140</v>
       </c>
       <c r="E1600" t="n">
-        <v>6250</v>
+        <v>93</v>
       </c>
       <c r="F1600" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="G1600" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="H1600" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1601">
@@ -45248,26 +45248,26 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Rumah Besar di Jl. Wijaya.</t>
+          <t>Tanah Luas Dibawah NJOP Pejaten Barat Cuan</t>
         </is>
       </c>
       <c r="C1601" t="n">
-        <v>40000000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1601" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="E1601" t="n">
-        <v>579</v>
+        <v>297</v>
       </c>
       <c r="F1601" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1601" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1601" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1602">
@@ -45276,26 +45276,26 @@
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1602" t="n">
-        <v>28000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1602" t="n">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="E1602" t="n">
-        <v>607</v>
+        <v>237</v>
       </c>
       <c r="F1602" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1602" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="H1602" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1603">
@@ -45304,26 +45304,26 @@
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1603" t="n">
-        <v>11500000000</v>
+        <v>21300000000</v>
       </c>
       <c r="D1603" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1603" t="n">
-        <v>475</v>
+        <v>630</v>
       </c>
       <c r="F1603" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G1603" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="H1603" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1604">
@@ -45332,26 +45332,26 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
+          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1604" t="n">
-        <v>28500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1604" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1604" t="n">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="F1604" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1604" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1604" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1605">
@@ -45360,26 +45360,26 @@
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Rumah For Salebisa Buat Kost Kost atau Tempat Tinggal atau Kantor Lokasi Strategis Dekat Setiabudi dan Kuningan Area Gatot Subroto Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1605" t="n">
-        <v>62000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1605" t="n">
-        <v>881</v>
+        <v>600</v>
       </c>
       <c r="E1605" t="n">
-        <v>1066</v>
+        <v>560</v>
       </c>
       <c r="F1605" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1605" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1605" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1606">
@@ -45388,26 +45388,26 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
+          <t>For Salerumah Modern Dalam Townhouse Lokasi Dekat Sekolah Internasional dan Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1606" t="n">
-        <v>30000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1606" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E1606" t="n">
-        <v>530</v>
+        <v>412</v>
       </c>
       <c r="F1606" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1606" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1606" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1607">
@@ -45416,26 +45416,26 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>12000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1607" t="n">
-        <v>450</v>
+        <v>1600</v>
       </c>
       <c r="E1607" t="n">
-        <v>931</v>
+        <v>1800</v>
       </c>
       <c r="F1607" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1607" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1607" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1608">
@@ -45444,26 +45444,26 @@
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
+          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>25000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1608" t="n">
-        <v>560</v>
+        <v>325</v>
       </c>
       <c r="E1608" t="n">
-        <v>676</v>
+        <v>931</v>
       </c>
       <c r="F1608" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1608" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1608" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1609">
@@ -45472,26 +45472,26 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1609" t="n">
-        <v>6400000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1609" t="n">
-        <v>308</v>
+        <v>470</v>
       </c>
       <c r="E1609" t="n">
-        <v>160</v>
+        <v>412</v>
       </c>
       <c r="F1609" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1609" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1609" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1610">
@@ -45500,26 +45500,26 @@
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
         </is>
       </c>
       <c r="C1610" t="n">
-        <v>3900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1610" t="n">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="E1610" t="n">
-        <v>141</v>
+        <v>235</v>
       </c>
       <c r="F1610" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G1610" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1610" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1611">
@@ -45528,26 +45528,26 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>15000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1611" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="E1611" t="n">
-        <v>704</v>
+        <v>650</v>
       </c>
       <c r="F1611" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1611" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="H1611" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1612">
@@ -45556,26 +45556,26 @@
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
+          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>1100000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1612" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="E1612" t="n">
-        <v>60</v>
+        <v>660</v>
       </c>
       <c r="F1612" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1612" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1612" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1613">
@@ -45584,26 +45584,26 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>1700000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1613" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E1613" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="F1613" t="n">
         <v>3</v>
       </c>
       <c r="G1613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1614">
@@ -45612,26 +45612,26 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>2100000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1614" t="n">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="E1614" t="n">
-        <v>93</v>
+        <v>2138</v>
       </c>
       <c r="F1614" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1614" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H1614" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1615">
@@ -45640,26 +45640,26 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Tanah Luas Dibawah NJOP Pejaten Barat Cuan</t>
+          <t>Rumah Siap Huni Tebet Barat</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>1800000000</v>
+        <v>2800000000</v>
       </c>
       <c r="D1615" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E1615" t="n">
-        <v>297</v>
+        <v>122</v>
       </c>
       <c r="F1615" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G1615" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1615" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1616">
@@ -45668,26 +45668,26 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>1700000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1616" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1616" t="n">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="F1616" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1616" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1616" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1617">
@@ -45696,26 +45696,26 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>21300000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1617" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1617" t="n">
-        <v>630</v>
+        <v>76</v>
       </c>
       <c r="F1617" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1617" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1617" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1618">
@@ -45724,17 +45724,17 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1618" t="n">
-        <v>17000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1618" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E1618" t="n">
-        <v>620</v>
+        <v>366</v>
       </c>
       <c r="F1618" t="n">
         <v>3</v>
@@ -45743,7 +45743,7 @@
         <v>3</v>
       </c>
       <c r="H1618" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1619">
@@ -45752,26 +45752,26 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Rumah For Salebisa Buat Kost Kost atau Tempat Tinggal atau Kantor Lokasi Strategis Dekat Setiabudi dan Kuningan Area Gatot Subroto Jakarta Selatan</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>28000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1619" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1619" t="n">
-        <v>560</v>
+        <v>165</v>
       </c>
       <c r="F1619" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1619" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1619" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1620">
@@ -45780,26 +45780,26 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>For Salerumah Modern Dalam Townhouse Lokasi Dekat Sekolah Internasional dan Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
         </is>
       </c>
       <c r="C1620" t="n">
-        <v>16000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1620" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="E1620" t="n">
-        <v>412</v>
+        <v>74</v>
       </c>
       <c r="F1620" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1620" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1620" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1621">
@@ -45808,26 +45808,26 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1621" t="n">
-        <v>55000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1621" t="n">
-        <v>1600</v>
+        <v>308</v>
       </c>
       <c r="E1621" t="n">
-        <v>1800</v>
+        <v>160</v>
       </c>
       <c r="F1621" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1621" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1621" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1622">
@@ -45836,26 +45836,26 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>22000000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1622" t="n">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="E1622" t="n">
-        <v>931</v>
+        <v>515</v>
       </c>
       <c r="F1622" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1622" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1622" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1623">
@@ -45864,26 +45864,922 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>17500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1623" t="n">
-        <v>470</v>
+        <v>200</v>
       </c>
       <c r="E1623" t="n">
-        <v>412</v>
+        <v>155</v>
       </c>
       <c r="F1623" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1623" t="n">
         <v>4</v>
       </c>
       <c r="H1623" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>7900000000</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>262</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>161</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1624" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1624" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1625" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>114</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1626" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1626" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1627" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1627" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>17700000000</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1628" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1628" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1629" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1629" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>270</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1630" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1630" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1631" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1631" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>2360</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1632" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1632" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>23600000000</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1633" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1633" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1634" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1634" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>26000000000</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1635" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1635" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>443</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>655</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1636" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1636" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1637" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1637" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>76</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1638" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1638" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>72000000000</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>1267</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1639" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1639" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>256</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>256</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1640" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1640" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1641" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1641" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>160000000000</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>9635</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>9635</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1642" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1642" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1643" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1643" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1644" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1644" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1645" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>750</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>610</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1646" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1646" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>370</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1647" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1647" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>2700000000</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1648" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1648" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Rumah di Grinting Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>198</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1649" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1649" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>550</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1650" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1650" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1651" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1651" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>216</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1652" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1652" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1653" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1653" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1654" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1654" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>175000000000</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>9635</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1655" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1655" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1415"/>
+  <dimension ref="A1:H1458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33320,23 +33320,23 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>7090000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1175" t="n">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="F1175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1175" t="n">
         <v>1</v>
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>7500000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1176" t="n">
-        <v>246</v>
+        <v>510</v>
       </c>
       <c r="F1176" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1176" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>7300000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>600</v>
+        <v>64</v>
       </c>
       <c r="E1177" t="n">
-        <v>510</v>
+        <v>32</v>
       </c>
       <c r="F1177" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1177" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,20 +33404,20 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>998000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>64</v>
+        <v>232</v>
       </c>
       <c r="E1178" t="n">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="F1178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1178" t="n">
         <v>2</v>
@@ -33432,23 +33432,23 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>22000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="E1179" t="n">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="F1179" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1179" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1179" t="n">
         <v>1</v>
@@ -33460,23 +33460,23 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>6250000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="E1180" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F1180" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G1180" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H1180" t="n">
         <v>1</v>
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>7200000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="E1181" t="n">
-        <v>196</v>
+        <v>675</v>
       </c>
       <c r="F1181" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G1181" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H1181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>2600000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>88</v>
+        <v>375</v>
       </c>
       <c r="E1182" t="n">
-        <v>55</v>
+        <v>534</v>
       </c>
       <c r="F1182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>65000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="E1183" t="n">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="F1183" t="n">
         <v>4</v>
       </c>
       <c r="G1183" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>23000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="E1184" t="n">
-        <v>534</v>
+        <v>70</v>
       </c>
       <c r="F1184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,23 +33600,23 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>15500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>928</v>
+        <v>1350</v>
       </c>
       <c r="E1185" t="n">
-        <v>378</v>
+        <v>863</v>
       </c>
       <c r="F1185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1185" t="n">
         <v>1</v>
@@ -33628,26 +33628,26 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>2830000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>112</v>
+        <v>355</v>
       </c>
       <c r="E1186" t="n">
-        <v>70</v>
+        <v>648</v>
       </c>
       <c r="F1186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1187">
@@ -33656,20 +33656,20 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>38000000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>1350</v>
+        <v>280</v>
       </c>
       <c r="E1187" t="n">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="F1187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1187" t="n">
         <v>6</v>
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>10000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="E1188" t="n">
-        <v>648</v>
+        <v>117</v>
       </c>
       <c r="F1188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1188" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>8800000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="E1189" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F1189" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1189" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>2600000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>130</v>
+        <v>1600</v>
       </c>
       <c r="E1190" t="n">
-        <v>117</v>
+        <v>1050</v>
       </c>
       <c r="F1190" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1190" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1190" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>9000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="E1191" t="n">
-        <v>200</v>
+        <v>351</v>
       </c>
       <c r="F1191" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1191" t="n">
         <v>3</v>
       </c>
       <c r="H1191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>68000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>1600</v>
+        <v>182</v>
       </c>
       <c r="E1192" t="n">
-        <v>1050</v>
+        <v>290</v>
       </c>
       <c r="F1192" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1192" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1192" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>34500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="E1193" t="n">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="F1193" t="n">
         <v>4</v>
       </c>
       <c r="G1193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,17 +33852,17 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>22000000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="E1194" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="F1194" t="n">
         <v>3</v>
@@ -33871,7 +33871,7 @@
         <v>3</v>
       </c>
       <c r="H1194" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1195">
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>15000000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>360</v>
+        <v>190</v>
       </c>
       <c r="E1195" t="n">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="F1195" t="n">
         <v>4</v>
       </c>
       <c r="G1195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>14500000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="E1196" t="n">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="F1196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1196" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,17 +33936,17 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>1850000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>190</v>
+        <v>475</v>
       </c>
       <c r="E1197" t="n">
-        <v>73</v>
+        <v>475</v>
       </c>
       <c r="F1197" t="n">
         <v>4</v>
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>3300000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>130</v>
+        <v>3475</v>
       </c>
       <c r="E1198" t="n">
-        <v>88</v>
+        <v>3475</v>
       </c>
       <c r="F1198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,17 +33992,17 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>3350000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="E1199" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="F1199" t="n">
         <v>4</v>
@@ -34011,7 +34011,7 @@
         <v>3</v>
       </c>
       <c r="H1199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>45000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="E1200" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="F1200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1200" t="n">
         <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,20 +34048,20 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>42500000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="E1201" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="F1201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1201" t="n">
         <v>3</v>
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>7900000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="E1202" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="F1202" t="n">
         <v>4</v>
       </c>
       <c r="G1202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,23 +34104,23 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>13100000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="E1203" t="n">
-        <v>819</v>
+        <v>400</v>
       </c>
       <c r="F1203" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1203" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1203" t="n">
         <v>2</v>
@@ -34132,23 +34132,23 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>7000000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1204" t="n">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="F1204" t="n">
         <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1204" t="n">
         <v>3</v>
@@ -34160,23 +34160,23 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>28000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="E1205" t="n">
-        <v>400</v>
+        <v>307</v>
       </c>
       <c r="F1205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1205" t="n">
         <v>2</v>
@@ -34188,17 +34188,17 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>15200000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1206" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F1206" t="n">
         <v>4</v>
@@ -34207,7 +34207,7 @@
         <v>5</v>
       </c>
       <c r="H1206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,17 +34216,17 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>15000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="E1207" t="n">
-        <v>307</v>
+        <v>200</v>
       </c>
       <c r="F1207" t="n">
         <v>4</v>
@@ -34244,23 +34244,23 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>10100000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="E1208" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
       </c>
       <c r="G1208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1208" t="n">
         <v>2</v>
@@ -34272,23 +34272,23 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>9500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>436</v>
+        <v>700</v>
       </c>
       <c r="E1209" t="n">
-        <v>200</v>
+        <v>1150</v>
       </c>
       <c r="F1209" t="n">
         <v>4</v>
       </c>
       <c r="G1209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1209" t="n">
         <v>2</v>
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>8500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="E1210" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="F1210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,23 +34328,23 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>55000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="E1211" t="n">
-        <v>1150</v>
+        <v>209</v>
       </c>
       <c r="F1211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1211" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1211" t="n">
         <v>2</v>
@@ -34356,23 +34356,23 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>6500000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E1212" t="n">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="F1212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1212" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1212" t="n">
         <v>1</v>
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>12900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="E1213" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F1213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1213" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>6760000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1214" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="F1214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1214" t="n">
         <v>4</v>
       </c>
       <c r="H1214" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>9500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E1215" t="n">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="F1215" t="n">
         <v>4</v>
       </c>
       <c r="G1215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>55000000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E1216" t="n">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="F1216" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1216" t="n">
         <v>4</v>
       </c>
       <c r="H1216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>4900000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E1217" t="n">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="F1217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1217" t="n">
         <v>3</v>
       </c>
       <c r="H1217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,23 +34524,23 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>34900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1218" t="n">
-        <v>538</v>
+        <v>630</v>
       </c>
       <c r="F1218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1218" t="n">
         <v>5</v>
@@ -34552,17 +34552,17 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>10900000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E1219" t="n">
-        <v>276</v>
+        <v>140</v>
       </c>
       <c r="F1219" t="n">
         <v>3</v>
@@ -34571,7 +34571,7 @@
         <v>3</v>
       </c>
       <c r="H1219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>21000000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1220" t="n">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="F1220" t="n">
         <v>5</v>
       </c>
       <c r="G1220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>6500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1221" t="n">
-        <v>140</v>
+        <v>1026</v>
       </c>
       <c r="F1221" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1221" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1221" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,17 +34636,17 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>31900000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>400</v>
+        <v>882</v>
       </c>
       <c r="E1222" t="n">
-        <v>350</v>
+        <v>1845</v>
       </c>
       <c r="F1222" t="n">
         <v>5</v>
@@ -34655,7 +34655,7 @@
         <v>4</v>
       </c>
       <c r="H1222" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>90000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E1223" t="n">
-        <v>1026</v>
+        <v>540</v>
       </c>
       <c r="F1223" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1223" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1223" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,17 +34692,17 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>71900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>882</v>
+        <v>470</v>
       </c>
       <c r="E1224" t="n">
-        <v>1845</v>
+        <v>412</v>
       </c>
       <c r="F1224" t="n">
         <v>5</v>
@@ -34711,7 +34711,7 @@
         <v>4</v>
       </c>
       <c r="H1224" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,23 +34720,23 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>49000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1225" t="n">
-        <v>540</v>
+        <v>404</v>
       </c>
       <c r="F1225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1225" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1225" t="n">
         <v>5</v>
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>17000000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>470</v>
+        <v>850</v>
       </c>
       <c r="E1226" t="n">
-        <v>412</v>
+        <v>1060</v>
       </c>
       <c r="F1226" t="n">
         <v>5</v>
       </c>
       <c r="G1226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>7890000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1227" t="n">
-        <v>404</v>
+        <v>1084</v>
       </c>
       <c r="F1227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1227" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1227" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,17 +34804,17 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>29900000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>850</v>
+        <v>1050</v>
       </c>
       <c r="E1228" t="n">
-        <v>1060</v>
+        <v>627</v>
       </c>
       <c r="F1228" t="n">
         <v>5</v>
@@ -34823,7 +34823,7 @@
         <v>5</v>
       </c>
       <c r="H1228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>39800000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1229" t="n">
-        <v>1084</v>
+        <v>696</v>
       </c>
       <c r="F1229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1229" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>44000000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>1050</v>
+        <v>250</v>
       </c>
       <c r="E1230" t="n">
-        <v>627</v>
+        <v>187</v>
       </c>
       <c r="F1230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1230" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>12900000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="E1231" t="n">
-        <v>696</v>
+        <v>208</v>
       </c>
       <c r="F1231" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1231" t="n">
         <v>3</v>
       </c>
       <c r="H1231" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>4690000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="E1232" t="n">
-        <v>187</v>
+        <v>854</v>
       </c>
       <c r="F1232" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1232" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,23 +34944,23 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>8990000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1233" t="n">
-        <v>208</v>
+        <v>500</v>
       </c>
       <c r="F1233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1233" t="n">
         <v>3</v>
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>22000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>650</v>
+        <v>880</v>
       </c>
       <c r="E1234" t="n">
-        <v>854</v>
+        <v>1000</v>
       </c>
       <c r="F1234" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1234" t="n">
         <v>6</v>
       </c>
-      <c r="G1234" t="n">
-        <v>5</v>
-      </c>
       <c r="H1234" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>14700000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="E1235" t="n">
-        <v>500</v>
+        <v>692</v>
       </c>
       <c r="F1235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>62000000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>880</v>
+        <v>452</v>
       </c>
       <c r="E1236" t="n">
-        <v>1000</v>
+        <v>1165</v>
       </c>
       <c r="F1236" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1236" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>13800000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>407</v>
+        <v>300</v>
       </c>
       <c r="E1237" t="n">
-        <v>692</v>
+        <v>404</v>
       </c>
       <c r="F1237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>53500000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>452</v>
+        <v>200</v>
       </c>
       <c r="E1238" t="n">
-        <v>1165</v>
+        <v>120</v>
       </c>
       <c r="F1238" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G1238" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1238" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>7800000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1239" t="n">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="F1239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1239" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1239" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>7200000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1240" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="F1240" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1240" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1240" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>24900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1241" t="n">
-        <v>331</v>
+        <v>1000</v>
       </c>
       <c r="F1241" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1241" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1241" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>55000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1242" t="n">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="F1242" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1242" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H1242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>15000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="E1243" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="F1243" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1243" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H1243" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>38000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1244" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="F1244" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1244" t="n">
         <v>52</v>
       </c>
-      <c r="G1244" t="n">
-        <v>51</v>
-      </c>
       <c r="H1244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>1600</v>
+        <v>250</v>
       </c>
       <c r="E1245" t="n">
-        <v>1800</v>
+        <v>140</v>
       </c>
       <c r="F1245" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1245" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H1245" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>21500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="E1246" t="n">
-        <v>630</v>
+        <v>517</v>
       </c>
       <c r="F1246" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1246" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H1246" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>6500000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1247" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="F1247" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1247" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1247" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>38000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>760</v>
+        <v>1600</v>
       </c>
       <c r="E1248" t="n">
-        <v>517</v>
+        <v>1800</v>
       </c>
       <c r="F1248" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1248" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1248" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>31900000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1249" t="n">
-        <v>350</v>
+        <v>538</v>
       </c>
       <c r="F1249" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G1249" t="n">
         <v>41</v>
       </c>
       <c r="H1249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,23 +35420,23 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>55000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>1600</v>
+        <v>882</v>
       </c>
       <c r="E1250" t="n">
-        <v>1800</v>
+        <v>1845</v>
       </c>
       <c r="F1250" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1250" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H1250" t="n">
         <v>6</v>
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>34900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1251" t="n">
-        <v>538</v>
+        <v>1925</v>
       </c>
       <c r="F1251" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="G1251" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1251" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>71900000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>882</v>
+        <v>400</v>
       </c>
       <c r="E1252" t="n">
-        <v>1845</v>
+        <v>700</v>
       </c>
       <c r="F1252" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1252" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1252" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>42000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="E1253" t="n">
-        <v>1925</v>
+        <v>540</v>
       </c>
       <c r="F1253" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1253" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1253" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>14000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1254" t="n">
-        <v>700</v>
+        <v>1925</v>
       </c>
       <c r="F1254" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1254" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1254" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>49000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1255" t="n">
-        <v>540</v>
+        <v>276</v>
       </c>
       <c r="F1255" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1255" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1255" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>42000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>850</v>
+        <v>325</v>
       </c>
       <c r="E1256" t="n">
-        <v>1925</v>
+        <v>696</v>
       </c>
       <c r="F1256" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1256" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1256" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>10900000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>300</v>
+        <v>149</v>
       </c>
       <c r="E1257" t="n">
-        <v>276</v>
+        <v>90</v>
       </c>
       <c r="F1257" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1257" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>12900000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="E1258" t="n">
-        <v>696</v>
+        <v>159</v>
       </c>
       <c r="F1258" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1258" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1258" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,23 +35672,23 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>3800000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="E1259" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F1259" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1259" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1259" t="n">
         <v>2</v>
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
+          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>4200000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="E1260" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="F1260" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1260" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1260" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
+          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>1400000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="E1261" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="F1261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>2100000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="E1262" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F1262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,23 +35784,23 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
+          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>4200000000</v>
+        <v>4650000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E1263" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F1263" t="n">
         <v>4</v>
       </c>
       <c r="G1263" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1263" t="n">
         <v>1</v>
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>1800000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1264" t="n">
-        <v>94</v>
+        <v>322</v>
       </c>
       <c r="F1264" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>4650000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>110</v>
+        <v>850</v>
       </c>
       <c r="E1265" t="n">
-        <v>118</v>
+        <v>384</v>
       </c>
       <c r="F1265" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1265" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1265" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>7300000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1266" t="n">
         <v>400</v>
       </c>
       <c r="E1266" t="n">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="F1266" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1266" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1266" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>14000000000</v>
+        <v>1440000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>850</v>
+        <v>85</v>
       </c>
       <c r="E1267" t="n">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="F1267" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1267" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1267" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>7100000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="E1268" t="n">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="F1268" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1268" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1268" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,20 +35952,20 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
+          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>1440000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E1269" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F1269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1269" t="n">
         <v>2</v>
@@ -35980,20 +35980,20 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
+          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>2600000000</v>
+        <v>2770000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E1270" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="F1270" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1270" t="n">
         <v>3</v>
@@ -36008,23 +36008,23 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
+          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>2600000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="E1271" t="n">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="F1271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1271" t="n">
         <v>1</v>
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
+          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>2770000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>143</v>
+        <v>850</v>
       </c>
       <c r="E1272" t="n">
-        <v>143</v>
+        <v>1925</v>
       </c>
       <c r="F1272" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1272" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1272" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,26 +36064,26 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
+          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>2550000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1273" t="n">
-        <v>258</v>
+        <v>549</v>
       </c>
       <c r="F1273" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1273" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H1273" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1274">
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>40000000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="E1274" t="n">
-        <v>1925</v>
+        <v>525</v>
       </c>
       <c r="F1274" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1274" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1274" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
+          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>11000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E1275" t="n">
-        <v>549</v>
+        <v>101</v>
       </c>
       <c r="F1275" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G1275" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1275" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>23500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1276" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="F1276" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1276" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1276" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,23 +36176,23 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>2400000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="E1277" t="n">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="F1277" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1277" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1277" t="n">
         <v>2</v>
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>7800000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1278" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="F1278" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1278" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H1278" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>8500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="E1279" t="n">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="F1279" t="n">
         <v>41</v>
       </c>
       <c r="G1279" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1279" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
+          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>11500000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="E1280" t="n">
-        <v>317</v>
+        <v>182</v>
       </c>
       <c r="F1280" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1280" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1280" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,17 +36288,17 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>22500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="E1281" t="n">
-        <v>366</v>
+        <v>189</v>
       </c>
       <c r="F1281" t="n">
         <v>41</v>
@@ -36307,7 +36307,7 @@
         <v>31</v>
       </c>
       <c r="H1281" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
+          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>4700000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>152</v>
+        <v>450</v>
       </c>
       <c r="E1282" t="n">
-        <v>182</v>
+        <v>403</v>
       </c>
       <c r="F1282" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1282" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1282" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
+          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>4800000000</v>
+        <v>4600000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="E1283" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F1283" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1283" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1283" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
+          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>14000000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>450</v>
+        <v>155</v>
       </c>
       <c r="E1284" t="n">
-        <v>403</v>
+        <v>155</v>
       </c>
       <c r="F1284" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1284" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1284" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
+          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>4600000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E1285" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F1285" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G1285" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="H1285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>6100000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="E1286" t="n">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="F1286" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1286" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H1286" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>3000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="E1287" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F1287" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="G1287" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="H1287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>4800000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>258</v>
+        <v>500</v>
       </c>
       <c r="E1288" t="n">
-        <v>108</v>
+        <v>1554</v>
       </c>
       <c r="F1288" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G1288" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H1288" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,23 +36512,23 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>1700000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>129</v>
+        <v>450</v>
       </c>
       <c r="E1289" t="n">
-        <v>100</v>
+        <v>404</v>
       </c>
       <c r="F1289" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G1289" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1289" t="n">
         <v>2</v>
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>52500000000</v>
+        <v>110000000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E1290" t="n">
-        <v>1554</v>
+        <v>805</v>
       </c>
       <c r="F1290" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G1290" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H1290" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
+          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>17000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="E1291" t="n">
-        <v>404</v>
+        <v>201</v>
       </c>
       <c r="F1291" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1291" t="n">
         <v>11</v>
-      </c>
-      <c r="G1291" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1291" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
+          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>110000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>1000</v>
+        <v>275</v>
       </c>
       <c r="E1292" t="n">
-        <v>805</v>
+        <v>135</v>
       </c>
       <c r="F1292" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="G1292" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H1292" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,17 +36624,17 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>5400000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E1293" t="n">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="F1293" t="n">
         <v>5</v>
@@ -36643,7 +36643,7 @@
         <v>3</v>
       </c>
       <c r="H1293" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
+          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>4990000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>275</v>
+        <v>1200</v>
       </c>
       <c r="E1294" t="n">
-        <v>135</v>
+        <v>1000</v>
       </c>
       <c r="F1294" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1294" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1294" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,23 +36680,23 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Dijual Rumah Akses 2 Mobil</t>
+          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>4200000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E1295" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F1295" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1295" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H1295" t="n">
         <v>2</v>
@@ -36708,26 +36708,26 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
+          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>25000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E1296" t="n">
-        <v>1000</v>
+        <v>607</v>
       </c>
       <c r="F1296" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G1296" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="H1296" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1297">
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
+          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>5200000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>201</v>
+        <v>375</v>
       </c>
       <c r="E1297" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="F1297" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1297" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H1297" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
+          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>32000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>1000</v>
+        <v>141</v>
       </c>
       <c r="E1298" t="n">
-        <v>607</v>
+        <v>119</v>
       </c>
       <c r="F1298" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G1298" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="H1298" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,7 +36792,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1299" t="n">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
+          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>4000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>141</v>
+        <v>500</v>
       </c>
       <c r="E1300" t="n">
-        <v>119</v>
+        <v>1018</v>
       </c>
       <c r="F1300" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="G1300" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H1300" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
+          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>6900000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1301" t="n">
-        <v>76</v>
+        <v>850</v>
       </c>
       <c r="F1301" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1301" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1301" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>20000000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E1302" t="n">
-        <v>1018</v>
+        <v>1980</v>
       </c>
       <c r="F1302" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="G1302" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="H1302" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>65000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="E1303" t="n">
-        <v>850</v>
+        <v>779</v>
       </c>
       <c r="F1303" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1303" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H1303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>135000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>800</v>
+        <v>262</v>
       </c>
       <c r="E1304" t="n">
-        <v>1980</v>
+        <v>161</v>
       </c>
       <c r="F1304" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G1304" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H1304" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,26 +36960,26 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>9500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="E1305" t="n">
-        <v>779</v>
+        <v>598</v>
       </c>
       <c r="F1305" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1305" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1305" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>8500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="E1306" t="n">
-        <v>161</v>
+        <v>530</v>
       </c>
       <c r="F1306" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1306" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1306" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>17000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>288</v>
+        <v>360</v>
       </c>
       <c r="E1307" t="n">
-        <v>598</v>
+        <v>127</v>
       </c>
       <c r="F1307" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1307" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H1307" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>15000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="E1308" t="n">
-        <v>530</v>
+        <v>307</v>
       </c>
       <c r="F1308" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1308" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1308" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,26 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>4900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="E1309" t="n">
-        <v>127</v>
+        <v>330</v>
       </c>
       <c r="F1309" t="n">
         <v>41</v>
       </c>
       <c r="G1309" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="H1309" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1310">
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>12900000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>390</v>
+        <v>208</v>
       </c>
       <c r="E1310" t="n">
-        <v>307</v>
+        <v>394</v>
       </c>
       <c r="F1310" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1310" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1310" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>10000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E1311" t="n">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="F1311" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1311" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1311" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,26 +37156,26 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>5750000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="E1312" t="n">
-        <v>394</v>
+        <v>40</v>
       </c>
       <c r="F1312" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1312" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="H1312" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1313">
@@ -37184,23 +37184,23 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>3000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="E1313" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F1313" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1313" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1313" t="n">
         <v>2</v>
@@ -37212,14 +37212,14 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>850000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E1314" t="n">
         <v>40</v>
@@ -37228,10 +37228,10 @@
         <v>3</v>
       </c>
       <c r="G1314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,26 +37240,26 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>1900000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E1315" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F1315" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1315" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1316">
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>829000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="E1316" t="n">
-        <v>40</v>
+        <v>370</v>
       </c>
       <c r="F1316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,26 +37296,26 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>1420000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>120</v>
+        <v>850</v>
       </c>
       <c r="E1317" t="n">
-        <v>60</v>
+        <v>1925</v>
       </c>
       <c r="F1317" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G1317" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1317" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1318">
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>48000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>810</v>
+        <v>1374</v>
       </c>
       <c r="E1318" t="n">
-        <v>370</v>
+        <v>1493</v>
       </c>
       <c r="F1318" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1318" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1318" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>42000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="E1319" t="n">
-        <v>1925</v>
+        <v>632</v>
       </c>
       <c r="F1319" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="G1319" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1319" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,26 +37380,26 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>26000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>1374</v>
+        <v>400</v>
       </c>
       <c r="E1320" t="n">
-        <v>1493</v>
+        <v>582</v>
       </c>
       <c r="F1320" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1320" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H1320" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1321">
@@ -37408,23 +37408,23 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>16000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E1321" t="n">
-        <v>632</v>
+        <v>209</v>
       </c>
       <c r="F1321" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G1321" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H1321" t="n">
         <v>22</v>
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>400</v>
+        <v>503</v>
       </c>
       <c r="E1322" t="n">
-        <v>582</v>
+        <v>421</v>
       </c>
       <c r="F1322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1322" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>12900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="E1323" t="n">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="F1323" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G1323" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="H1323" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,23 +37492,23 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>18500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>503</v>
+        <v>600</v>
       </c>
       <c r="E1324" t="n">
-        <v>421</v>
+        <v>793</v>
       </c>
       <c r="F1324" t="n">
         <v>4</v>
       </c>
       <c r="G1324" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1324" t="n">
         <v>22</v>
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>11000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="E1325" t="n">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="F1325" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G1325" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H1325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,23 +37548,23 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>45000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="E1326" t="n">
-        <v>793</v>
+        <v>417</v>
       </c>
       <c r="F1326" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1326" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1326" t="n">
         <v>22</v>
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Jl. Kemang Dalam</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>11500000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1327" t="n">
-        <v>304</v>
+        <v>898</v>
       </c>
       <c r="F1327" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1327" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1327" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,26 +37604,26 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
+          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>9000000000</v>
+        <v>2250000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>350</v>
+        <v>125</v>
       </c>
       <c r="E1328" t="n">
-        <v>417</v>
+        <v>130</v>
       </c>
       <c r="F1328" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1328" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1328" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1329">
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Jl. Kemang Dalam</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>26000000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>450</v>
+        <v>98</v>
       </c>
       <c r="E1329" t="n">
-        <v>898</v>
+        <v>98</v>
       </c>
       <c r="F1329" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1329" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1329" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,23 +37660,23 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>2250000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E1330" t="n">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="F1330" t="n">
         <v>3</v>
       </c>
       <c r="G1330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1330" t="n">
         <v>1</v>
@@ -37688,17 +37688,17 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>979000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E1331" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="F1331" t="n">
         <v>3</v>
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>1900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="E1332" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="F1332" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>1200000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="E1333" t="n">
-        <v>180</v>
+        <v>1335</v>
       </c>
       <c r="F1333" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1333" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1333" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>4800000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="E1334" t="n">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F1334" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1334" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1334" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>27000000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>800</v>
+        <v>230</v>
       </c>
       <c r="E1335" t="n">
-        <v>1335</v>
+        <v>200</v>
       </c>
       <c r="F1335" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1335" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1335" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>3900000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="E1336" t="n">
-        <v>201</v>
+        <v>1980</v>
       </c>
       <c r="F1336" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G1336" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H1336" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,23 +37856,23 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>6300000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="E1337" t="n">
         <v>200</v>
       </c>
       <c r="F1337" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1337" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1337" t="n">
         <v>2</v>
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>135000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>800</v>
+        <v>188</v>
       </c>
       <c r="E1338" t="n">
-        <v>1980</v>
+        <v>200</v>
       </c>
       <c r="F1338" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="G1338" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H1338" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>8000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1339" t="n">
-        <v>200</v>
+        <v>945</v>
       </c>
       <c r="F1339" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1339" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1339" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>4700000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>188</v>
+        <v>438</v>
       </c>
       <c r="E1340" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1340" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1340" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1340" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>57000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1341" t="n">
         <v>400</v>
       </c>
       <c r="E1341" t="n">
-        <v>945</v>
+        <v>515</v>
       </c>
       <c r="F1341" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1341" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1341" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>9100000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>438</v>
+        <v>225</v>
       </c>
       <c r="E1342" t="n">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="F1342" t="n">
         <v>51</v>
       </c>
       <c r="G1342" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H1342" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>13500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="E1343" t="n">
-        <v>515</v>
+        <v>248</v>
       </c>
       <c r="F1343" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G1343" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1343" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>16000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E1344" t="n">
-        <v>312</v>
+        <v>161</v>
       </c>
       <c r="F1344" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1344" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H1344" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>22500000000</v>
+        <v>599000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>560</v>
+        <v>140</v>
       </c>
       <c r="E1345" t="n">
-        <v>248</v>
+        <v>100</v>
       </c>
       <c r="F1345" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G1345" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1345" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>8500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="E1346" t="n">
-        <v>161</v>
+        <v>448</v>
       </c>
       <c r="F1346" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G1346" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1346" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,23 +38136,23 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
+          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>599000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="E1347" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="F1347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1347" t="n">
         <v>1</v>
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>24000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="E1348" t="n">
-        <v>448</v>
+        <v>865</v>
       </c>
       <c r="F1348" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1348" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1348" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,26 +38192,26 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>750000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="E1349" t="n">
-        <v>72</v>
+        <v>1038</v>
       </c>
       <c r="F1349" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1349" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H1349" t="n">
-        <v>1</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1350">
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>50000000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1350" t="n">
-        <v>865</v>
+        <v>696</v>
       </c>
       <c r="F1350" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1350" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1350" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>90000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="E1351" t="n">
-        <v>1038</v>
+        <v>350</v>
       </c>
       <c r="F1351" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1351" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H1351" t="n">
-        <v>412</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,23 +38276,23 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>11800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="E1352" t="n">
-        <v>696</v>
+        <v>261</v>
       </c>
       <c r="F1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1352" t="n">
         <v>24</v>
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>15500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="E1353" t="n">
-        <v>350</v>
+        <v>466</v>
       </c>
       <c r="F1353" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1353" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H1353" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>9800000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="E1354" t="n">
-        <v>261</v>
+        <v>423</v>
       </c>
       <c r="F1354" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1354" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>27000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="E1355" t="n">
-        <v>466</v>
+        <v>165</v>
       </c>
       <c r="F1355" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G1355" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1355" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>11500000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>510</v>
+        <v>1200</v>
       </c>
       <c r="E1356" t="n">
-        <v>423</v>
+        <v>1000</v>
       </c>
       <c r="F1356" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
       </c>
       <c r="H1356" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>8000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="E1357" t="n">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="F1357" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1357" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1357" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>27500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E1358" t="n">
-        <v>1000</v>
+        <v>261</v>
       </c>
       <c r="F1358" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="G1358" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1358" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>25000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>550</v>
+        <v>457</v>
       </c>
       <c r="E1359" t="n">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="F1359" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1359" t="n">
         <v>4</v>
       </c>
       <c r="H1359" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>9500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>300</v>
+        <v>810</v>
       </c>
       <c r="E1360" t="n">
-        <v>261</v>
+        <v>370</v>
       </c>
       <c r="F1360" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1360" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1360" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,26 +38528,26 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>53000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="E1361" t="n">
-        <v>494</v>
+        <v>682</v>
       </c>
       <c r="F1361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1361" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1362">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>48000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>810</v>
+        <v>250</v>
       </c>
       <c r="E1362" t="n">
-        <v>370</v>
+        <v>241</v>
       </c>
       <c r="F1362" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1362" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1362" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,26 +38584,26 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>28000000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>584</v>
+        <v>40</v>
       </c>
       <c r="E1363" t="n">
-        <v>682</v>
+        <v>21</v>
       </c>
       <c r="F1363" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1363" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1364">
@@ -38612,26 +38612,26 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>9200000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>250</v>
+        <v>564</v>
       </c>
       <c r="E1364" t="n">
-        <v>241</v>
+        <v>726</v>
       </c>
       <c r="F1364" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G1364" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H1364" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1365">
@@ -38640,26 +38640,26 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>858000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="E1365" t="n">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="F1365" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1365" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1366">
@@ -38668,26 +38668,26 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>48000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>564</v>
+        <v>180</v>
       </c>
       <c r="E1366" t="n">
-        <v>726</v>
+        <v>122</v>
       </c>
       <c r="F1366" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G1366" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H1366" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1367">
@@ -38696,26 +38696,26 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>6900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1367" t="n">
         <v>300</v>
       </c>
       <c r="E1367" t="n">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="F1367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1367" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1367" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1368">
@@ -38724,26 +38724,26 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>4800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="E1368" t="n">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="F1368" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1368" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1369">
@@ -38752,26 +38752,26 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>11500000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1369" t="n">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="F1369" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1369" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1369" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1370">
@@ -38780,26 +38780,26 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>9800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>260</v>
+        <v>560</v>
       </c>
       <c r="E1370" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F1370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1370" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1371">
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>7090000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="E1371" t="n">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="F1371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1371" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>22500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="E1372" t="n">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="F1372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1372" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,20 +38864,20 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>8500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="E1373" t="n">
-        <v>161</v>
+        <v>1100</v>
       </c>
       <c r="F1373" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1373" t="n">
         <v>4</v>
@@ -38892,23 +38892,23 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>2000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="E1374" t="n">
-        <v>60</v>
+        <v>667</v>
       </c>
       <c r="F1374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1374" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -38920,20 +38920,20 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>17000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="E1375" t="n">
-        <v>1100</v>
+        <v>469</v>
       </c>
       <c r="F1375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>48000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1376" t="n">
-        <v>667</v>
+        <v>60</v>
       </c>
       <c r="F1376" t="n">
         <v>2</v>
       </c>
       <c r="G1376" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,23 +38976,23 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>27000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>301</v>
+        <v>1050</v>
       </c>
       <c r="E1377" t="n">
-        <v>469</v>
+        <v>627</v>
       </c>
       <c r="F1377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1377" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1377" t="n">
         <v>1</v>
@@ -39004,23 +39004,23 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>6400000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="E1378" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1378" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1378" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1378" t="n">
         <v>1</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>45000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>1050</v>
+        <v>250</v>
       </c>
       <c r="E1379" t="n">
-        <v>627</v>
+        <v>284</v>
       </c>
       <c r="F1379" t="n">
         <v>3</v>
       </c>
       <c r="G1379" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>6900000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>375</v>
+        <v>60</v>
       </c>
       <c r="E1380" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F1380" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1380" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>16500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1381" t="n">
-        <v>284</v>
+        <v>60</v>
       </c>
       <c r="F1381" t="n">
         <v>3</v>
       </c>
       <c r="G1381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>2600000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>60</v>
+        <v>1104</v>
       </c>
       <c r="E1382" t="n">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="F1382" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1383" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1383" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,23 +39172,23 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>11500000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>1104</v>
+        <v>60</v>
       </c>
       <c r="E1384" t="n">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="F1384" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1384" t="n">
         <v>1</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>6900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>375</v>
+        <v>1000</v>
       </c>
       <c r="E1385" t="n">
-        <v>76</v>
+        <v>1038</v>
       </c>
       <c r="F1385" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1385" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,23 +39228,23 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>2830000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="E1386" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1386" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1386" t="n">
         <v>1</v>
@@ -39256,23 +39256,23 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>90000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>1000</v>
+        <v>135</v>
       </c>
       <c r="E1387" t="n">
-        <v>1038</v>
+        <v>30</v>
       </c>
       <c r="F1387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1387" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1387" t="n">
         <v>1</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>15500000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="E1388" t="n">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="F1388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1388" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,23 +39312,23 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>2500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>135</v>
+        <v>375</v>
       </c>
       <c r="E1389" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F1389" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1389" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>6700000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>395</v>
+        <v>800</v>
       </c>
       <c r="E1390" t="n">
-        <v>172</v>
+        <v>600</v>
       </c>
       <c r="F1390" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1390" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,23 +39368,23 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>6900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>375</v>
+        <v>175</v>
       </c>
       <c r="E1391" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="F1391" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1391" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>46000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1392" t="n">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="F1392" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,20 +39424,20 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>2400000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="E1393" t="n">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="F1393" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1393" t="n">
         <v>2</v>
@@ -39452,23 +39452,23 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>8000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1394" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="F1394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1394" t="n">
         <v>1</v>
@@ -39480,23 +39480,23 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>2000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>85</v>
+        <v>360</v>
       </c>
       <c r="E1395" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="F1395" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1395" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1395" t="n">
         <v>1</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1396" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>4900000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="E1397" t="n">
-        <v>127</v>
+        <v>634</v>
       </c>
       <c r="F1397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1397" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,20 +39564,20 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>6900000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="E1398" t="n">
-        <v>76</v>
+        <v>750</v>
       </c>
       <c r="F1398" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -39592,23 +39592,23 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>37000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1399" t="n">
-        <v>634</v>
+        <v>498</v>
       </c>
       <c r="F1399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1399" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1399" t="n">
         <v>1</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>18000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="E1400" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="F1400" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1400" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,17 +39648,17 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>11000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>350</v>
+        <v>124</v>
       </c>
       <c r="E1401" t="n">
-        <v>498</v>
+        <v>124</v>
       </c>
       <c r="F1401" t="n">
         <v>3</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>1900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E1402" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="F1402" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,23 +39704,23 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>3500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="E1403" t="n">
-        <v>124</v>
+        <v>497</v>
       </c>
       <c r="F1403" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1403" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1403" t="n">
         <v>1</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1404" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E1404" t="n">
-        <v>270</v>
+        <v>414</v>
       </c>
       <c r="F1404" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,23 +39760,23 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>12500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>318</v>
+        <v>1200</v>
       </c>
       <c r="E1405" t="n">
-        <v>497</v>
+        <v>1000</v>
       </c>
       <c r="F1405" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1405" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1405" t="n">
         <v>1</v>
@@ -39788,23 +39788,23 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>9000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="E1406" t="n">
-        <v>414</v>
+        <v>66</v>
       </c>
       <c r="F1406" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1406" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1406" t="n">
         <v>1</v>
@@ -39816,20 +39816,20 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>25000000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="E1407" t="n">
-        <v>1000</v>
+        <v>339</v>
       </c>
       <c r="F1407" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1407" t="n">
         <v>6</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>3500000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E1408" t="n">
-        <v>66</v>
+        <v>479</v>
       </c>
       <c r="F1408" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>6950000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1409" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="E1409" t="n">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="F1409" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1409" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,17 +39900,17 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>28700000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1410" t="n">
-        <v>479</v>
+        <v>272</v>
       </c>
       <c r="F1410" t="n">
         <v>7</v>
@@ -39928,20 +39928,20 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>16899999999</v>
+        <v>27000000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>450</v>
+        <v>301</v>
       </c>
       <c r="E1411" t="n">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="F1411" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>5500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>350</v>
+        <v>616</v>
       </c>
       <c r="E1412" t="n">
-        <v>272</v>
+        <v>383</v>
       </c>
       <c r="F1412" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1412" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,20 +39984,20 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>27000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="E1413" t="n">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="F1413" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1413" t="n">
         <v>4</v>
@@ -40012,26 +40012,26 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah 2 Lantai di Kemang Bagus Ada Kolam Renang SHM Tidak Banjir</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>17000000000</v>
+        <v>11900000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>616</v>
+        <v>650</v>
       </c>
       <c r="E1414" t="n">
-        <v>383</v>
+        <v>544</v>
       </c>
       <c r="F1414" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1414" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1414" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1415">
@@ -40040,26 +40040,1230 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Rumah Bawah NJOP di Ciganjur Jagakarsa Dekat Tol Brigif SHM</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>16500000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1415" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1415" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>1415</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Dijual Di Jakarta Di Pakubuwono</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>88000000000</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Kemang Jakarta</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>33000000000</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>530</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>850</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>235</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>97000000000</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Nivara Resort Townhouse at Wijaya</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>7900000000</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>35000000000</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>255</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>1584</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>3300000000</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>219</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>159</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1424" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>308</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1425" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1426" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Rumah Area Senopati, Lokasi Bagus</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>15700000000</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>365</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>334</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1427" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1429" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>1429</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>832</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1430" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>85000000000</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1431" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>864</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1432" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1433" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>1433</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>261</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1435" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>44</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1436" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1437" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1439" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>53000000000</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1440" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1441" t="n">
         <v>400</v>
       </c>
-      <c r="E1415" t="n">
-        <v>525</v>
-      </c>
-      <c r="F1415" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1415" t="n">
-        <v>4</v>
-      </c>
-      <c r="H1415" t="n">
-        <v>1</v>
+      <c r="E1441" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1441" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>2360</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1442" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1443" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1444" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1445" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1446" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1447" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1448" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="n">
+        <v>1448</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>23500000000</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>442</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>644</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1449" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="n">
+        <v>1449</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>36000000000</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1450" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>340</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>290</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1451" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>674</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>63</v>
+      </c>
+      <c r="H1452" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1453" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>25800000000</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>1374</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>1493</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1454" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>4700000000</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>70</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>123</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1455" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>580</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1456" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>260</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1458"/>
+  <dimension ref="A1:H1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40180,26 +40180,26 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>97000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>800</v>
+        <v>255</v>
       </c>
       <c r="E1420" t="n">
-        <v>650</v>
+        <v>1584</v>
       </c>
       <c r="F1420" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="G1420" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="H1420" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1421">
@@ -40208,26 +40208,26 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>7900000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>375</v>
+        <v>219</v>
       </c>
       <c r="E1421" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="F1421" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1422">
@@ -40236,26 +40236,26 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
+          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>35000000000</v>
+        <v>3200000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="E1422" t="n">
-        <v>1584</v>
+        <v>159</v>
       </c>
       <c r="F1422" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1422" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1422" t="n">
-        <v>212</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1423">
@@ -40264,26 +40264,26 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
+          <t>Rumah Area Senopati, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>3300000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>219</v>
+        <v>365</v>
       </c>
       <c r="E1423" t="n">
-        <v>200</v>
+        <v>334</v>
       </c>
       <c r="F1423" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1423" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1423" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1424">
@@ -40292,26 +40292,26 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
+          <t>Luxe Court Permata Hijau Signature</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>3200000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>150</v>
+        <v>374</v>
       </c>
       <c r="E1424" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="F1424" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1424" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1425">
@@ -40320,26 +40320,26 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>6400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>308</v>
+        <v>700</v>
       </c>
       <c r="E1425" t="n">
-        <v>160</v>
+        <v>832</v>
       </c>
       <c r="F1425" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1425" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1426">
@@ -40348,17 +40348,17 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>2900000000</v>
+        <v>85000000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="E1426" t="n">
-        <v>155</v>
+        <v>634</v>
       </c>
       <c r="F1426" t="n">
         <v>4</v>
@@ -40367,7 +40367,7 @@
         <v>4</v>
       </c>
       <c r="H1426" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1427">
@@ -40376,26 +40376,26 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati, Lokasi Bagus</t>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>15700000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>365</v>
+        <v>700</v>
       </c>
       <c r="E1427" t="n">
-        <v>334</v>
+        <v>864</v>
       </c>
       <c r="F1427" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1427" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1427" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1428">
@@ -40404,26 +40404,26 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>32000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>1200</v>
+        <v>261</v>
       </c>
       <c r="E1428" t="n">
-        <v>2138</v>
+        <v>240</v>
       </c>
       <c r="F1428" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1428" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H1428" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1429">
@@ -40432,26 +40432,26 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>13500000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="E1429" t="n">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="F1429" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1429" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1429" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1430">
@@ -40460,26 +40460,26 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>14000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1430" t="n">
-        <v>832</v>
+        <v>1066</v>
       </c>
       <c r="F1430" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G1430" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="H1430" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1431">
@@ -40488,26 +40488,26 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>85000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E1431" t="n">
-        <v>634</v>
+        <v>1018</v>
       </c>
       <c r="F1431" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G1431" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1431" t="n">
-        <v>44</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1432">
@@ -40516,26 +40516,26 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>17200000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E1432" t="n">
-        <v>864</v>
+        <v>2360</v>
       </c>
       <c r="F1432" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="G1432" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1432" t="n">
-        <v>26</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1433">
@@ -40544,26 +40544,26 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>1900000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E1433" t="n">
-        <v>74</v>
+        <v>5500</v>
       </c>
       <c r="F1433" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1433" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H1433" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1434">
@@ -40572,26 +40572,26 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>22500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>500</v>
+        <v>88</v>
       </c>
       <c r="E1434" t="n">
-        <v>366</v>
+        <v>55</v>
       </c>
       <c r="F1434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1434" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1435">
@@ -40600,26 +40600,26 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>9000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>261</v>
+        <v>100</v>
       </c>
       <c r="E1435" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F1435" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1435" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1435" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1436">
@@ -40628,26 +40628,26 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>850000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E1436" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F1436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1436" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1437">
@@ -40656,26 +40656,26 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
+          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>5500000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="E1437" t="n">
-        <v>230</v>
+        <v>644</v>
       </c>
       <c r="F1437" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1437" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1437" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1438">
@@ -40684,26 +40684,26 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>62000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>881</v>
+        <v>450</v>
       </c>
       <c r="E1438" t="n">
-        <v>1066</v>
+        <v>500</v>
       </c>
       <c r="F1438" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G1438" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="H1438" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1439">
@@ -40712,26 +40712,26 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>38000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>760</v>
+        <v>340</v>
       </c>
       <c r="E1439" t="n">
-        <v>517</v>
+        <v>290</v>
       </c>
       <c r="F1439" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G1439" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1439" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1440">
@@ -40740,26 +40740,26 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>53000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E1440" t="n">
-        <v>1018</v>
+        <v>674</v>
       </c>
       <c r="F1440" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G1440" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H1440" t="n">
-        <v>213</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1441">
@@ -40768,26 +40768,26 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>12800000000</v>
+        <v>25800000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>400</v>
+        <v>1374</v>
       </c>
       <c r="E1441" t="n">
-        <v>515</v>
+        <v>1493</v>
       </c>
       <c r="F1441" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1441" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H1441" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1442">
@@ -40796,26 +40796,26 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>48000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="E1442" t="n">
-        <v>2360</v>
+        <v>123</v>
       </c>
       <c r="F1442" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="G1442" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1442" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1443">
@@ -40824,26 +40824,26 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>55000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E1443" t="n">
-        <v>5500</v>
+        <v>580</v>
       </c>
       <c r="F1443" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G1443" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1443" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1444">
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>2600000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E1444" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F1444" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1444" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,26 +40880,26 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>62000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>881</v>
+        <v>400</v>
       </c>
       <c r="E1445" t="n">
-        <v>1066</v>
+        <v>260</v>
       </c>
       <c r="F1445" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1445" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H1445" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1446">
@@ -40908,26 +40908,26 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>32000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>720</v>
+        <v>90</v>
       </c>
       <c r="E1446" t="n">
-        <v>634</v>
+        <v>71</v>
       </c>
       <c r="F1446" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1446" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1446" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1447">
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>5200000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E1447" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="F1447" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1447" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1447" t="n">
         <v>2</v>
@@ -40964,26 +40964,26 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>2830000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>112</v>
+        <v>685</v>
       </c>
       <c r="E1448" t="n">
-        <v>70</v>
+        <v>685</v>
       </c>
       <c r="F1448" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1448" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1449">
@@ -40992,26 +40992,26 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
+          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>23500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>442</v>
+        <v>300</v>
       </c>
       <c r="E1449" t="n">
-        <v>644</v>
+        <v>293</v>
       </c>
       <c r="F1449" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1449" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1449" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1450">
@@ -41020,26 +41020,26 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
+          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>36000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>450</v>
+        <v>765</v>
       </c>
       <c r="E1450" t="n">
-        <v>500</v>
+        <v>765</v>
       </c>
       <c r="F1450" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G1450" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H1450" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1451">
@@ -41048,26 +41048,26 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>9000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="E1451" t="n">
-        <v>290</v>
+        <v>497</v>
       </c>
       <c r="F1451" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G1451" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1451" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1452">
@@ -41076,26 +41076,26 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>20000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>560</v>
+        <v>417</v>
       </c>
       <c r="E1452" t="n">
-        <v>674</v>
+        <v>417</v>
       </c>
       <c r="F1452" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1452" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="H1452" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1453">
@@ -41104,26 +41104,26 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>1900000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="E1453" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1453" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1454">
@@ -41132,26 +41132,26 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>25800000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>1374</v>
+        <v>200</v>
       </c>
       <c r="E1454" t="n">
-        <v>1493</v>
+        <v>155</v>
       </c>
       <c r="F1454" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G1454" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H1454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1455">
@@ -41160,26 +41160,26 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>4700000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="E1455" t="n">
-        <v>123</v>
+        <v>650</v>
       </c>
       <c r="F1455" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1455" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H1455" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1456">
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
+          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>11500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>400</v>
+        <v>630</v>
       </c>
       <c r="E1456" t="n">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="F1456" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G1456" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1456" t="n">
         <v>26</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>2500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="E1457" t="n">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="F1457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,26 +41244,1006 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>6500000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1458" t="n">
+        <v>44</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>1458</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>1461</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>1462</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>9500000000</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>257</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>209000000000</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>1841</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>89</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>South Grove</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>7600000000</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>177</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>518</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1467" t="n">
         <v>400</v>
       </c>
-      <c r="E1458" t="n">
-        <v>260</v>
-      </c>
-      <c r="F1458" t="n">
+      <c r="E1467" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>520</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>750</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>83</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Rumah Kartika Utama Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>516</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>607</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>320</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>21500000000</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>780</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>936</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>53</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>182</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>201</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>280</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>157</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="n">
+        <v>1476</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>1 Park Homes</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>380</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>17700000000</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1478" t="n">
         <v>41</v>
       </c>
-      <c r="G1458" t="n">
+    </row>
+    <row r="1479">
+      <c r="A1479" t="n">
+        <v>1478</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1479" t="n">
         <v>11</v>
       </c>
-      <c r="H1458" t="n">
+    </row>
+    <row r="1480">
+      <c r="A1480" t="n">
+        <v>1479</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="n">
+        <v>1480</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>12 Merle Bintaro</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>3950000000</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>158</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="n">
+        <v>1481</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>550</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="n">
+        <v>1482</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>9700000000</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>245</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>647</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>1483</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>4280000000</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>262</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1484" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>1484</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Puri Rinda Residence</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>1960000000</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>188</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>19500000000</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>580</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>673</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>1486</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>1488</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Aparthouse Crystal</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>950000000</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>1490</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>120000000000</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1493"/>
+  <dimension ref="A1:H1525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40460,26 +40460,26 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>62000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>881</v>
+        <v>1</v>
       </c>
       <c r="E1430" t="n">
-        <v>1066</v>
+        <v>5500</v>
       </c>
       <c r="F1430" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="G1430" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="H1430" t="n">
-        <v>68</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1431">
@@ -40488,26 +40488,26 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>53000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>600</v>
+        <v>88</v>
       </c>
       <c r="E1431" t="n">
-        <v>1018</v>
+        <v>55</v>
       </c>
       <c r="F1431" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G1431" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1431" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1432">
@@ -40516,26 +40516,26 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>48000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E1432" t="n">
-        <v>2360</v>
+        <v>120</v>
       </c>
       <c r="F1432" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G1432" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H1432" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1433">
@@ -40544,26 +40544,26 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>55000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="E1433" t="n">
-        <v>5500</v>
+        <v>70</v>
       </c>
       <c r="F1433" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1433" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1433" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1434">
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>2600000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="E1434" t="n">
-        <v>55</v>
+        <v>644</v>
       </c>
       <c r="F1434" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1434" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,26 +40600,26 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>5200000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="E1435" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="F1435" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1435" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H1435" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1436">
@@ -40628,26 +40628,26 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>2830000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>112</v>
+        <v>340</v>
       </c>
       <c r="E1436" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="F1436" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G1436" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1436" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1437">
@@ -40656,26 +40656,26 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>23500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>442</v>
+        <v>560</v>
       </c>
       <c r="E1437" t="n">
-        <v>644</v>
+        <v>674</v>
       </c>
       <c r="F1437" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1437" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="H1437" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1438">
@@ -40684,26 +40684,26 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
+          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>36000000000</v>
+        <v>25800000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>450</v>
+        <v>1374</v>
       </c>
       <c r="E1438" t="n">
-        <v>500</v>
+        <v>1493</v>
       </c>
       <c r="F1438" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="G1438" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="H1438" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1439">
@@ -40712,26 +40712,26 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>9000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>340</v>
+        <v>70</v>
       </c>
       <c r="E1439" t="n">
-        <v>290</v>
+        <v>123</v>
       </c>
       <c r="F1439" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G1439" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1439" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1440">
@@ -40740,26 +40740,26 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>20000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>560</v>
+        <v>400</v>
       </c>
       <c r="E1440" t="n">
-        <v>674</v>
+        <v>580</v>
       </c>
       <c r="F1440" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1440" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="H1440" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1441">
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>25800000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>1374</v>
+        <v>110</v>
       </c>
       <c r="E1441" t="n">
-        <v>1493</v>
+        <v>68</v>
       </c>
       <c r="F1441" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G1441" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,26 +40796,26 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>4700000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="E1442" t="n">
-        <v>123</v>
+        <v>260</v>
       </c>
       <c r="F1442" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1442" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H1442" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1443">
@@ -40824,26 +40824,26 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>11500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="E1443" t="n">
-        <v>580</v>
+        <v>71</v>
       </c>
       <c r="F1443" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1443" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1444">
@@ -40852,26 +40852,26 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>2500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E1444" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F1444" t="n">
         <v>3</v>
       </c>
       <c r="G1444" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1445">
@@ -40880,26 +40880,26 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>6500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>400</v>
+        <v>685</v>
       </c>
       <c r="E1445" t="n">
-        <v>260</v>
+        <v>685</v>
       </c>
       <c r="F1445" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G1445" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1445" t="n">
         <v>11</v>
-      </c>
-      <c r="H1445" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="1446">
@@ -40908,26 +40908,26 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
+          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>1500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="E1446" t="n">
-        <v>71</v>
+        <v>293</v>
       </c>
       <c r="F1446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1446" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1447">
@@ -40936,26 +40936,26 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>1400000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="E1447" t="n">
-        <v>65</v>
+        <v>497</v>
       </c>
       <c r="F1447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1447" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1447" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1448">
@@ -40964,26 +40964,26 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>11000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>685</v>
+        <v>200</v>
       </c>
       <c r="E1448" t="n">
-        <v>685</v>
+        <v>155</v>
       </c>
       <c r="F1448" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1448" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1448" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1449">
@@ -40992,26 +40992,26 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
+          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>4900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>300</v>
+        <v>630</v>
       </c>
       <c r="E1449" t="n">
-        <v>293</v>
+        <v>750</v>
       </c>
       <c r="F1449" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G1449" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1449" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1450">
@@ -41020,26 +41020,26 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>21000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>765</v>
+        <v>308</v>
       </c>
       <c r="E1450" t="n">
-        <v>765</v>
+        <v>160</v>
       </c>
       <c r="F1450" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1450" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1451">
@@ -41048,26 +41048,26 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>12000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>500</v>
+        <v>92</v>
       </c>
       <c r="E1451" t="n">
-        <v>497</v>
+        <v>90</v>
       </c>
       <c r="F1451" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1451" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1451" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1452">
@@ -41076,26 +41076,26 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>23000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>417</v>
+        <v>500</v>
       </c>
       <c r="E1452" t="n">
-        <v>417</v>
+        <v>366</v>
       </c>
       <c r="F1452" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1452" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1452" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1453">
@@ -41104,26 +41104,26 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>7900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E1453" t="n">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="F1453" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G1453" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1453" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1454">
@@ -41132,26 +41132,26 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>2900000000</v>
+        <v>209000000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>200</v>
+        <v>1841</v>
       </c>
       <c r="E1454" t="n">
-        <v>155</v>
+        <v>4189</v>
       </c>
       <c r="F1454" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="G1454" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="H1454" t="n">
-        <v>2</v>
+        <v>910</v>
       </c>
     </row>
     <row r="1455">
@@ -41160,26 +41160,26 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>South Grove</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>97000000000</v>
+        <v>7600000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E1455" t="n">
-        <v>650</v>
+        <v>177</v>
       </c>
       <c r="F1455" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1455" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1455" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1456">
@@ -41188,26 +41188,26 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>25000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="E1456" t="n">
-        <v>750</v>
+        <v>518</v>
       </c>
       <c r="F1456" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G1456" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1456" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1457">
@@ -41216,26 +41216,26 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>6400000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>308</v>
+        <v>520</v>
       </c>
       <c r="E1457" t="n">
-        <v>160</v>
+        <v>750</v>
       </c>
       <c r="F1457" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="G1457" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H1457" t="n">
-        <v>1</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1458">
@@ -41244,26 +41244,26 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Rumah Kartika Utama Pondok Indah</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>850000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>44</v>
+        <v>516</v>
       </c>
       <c r="E1458" t="n">
+        <v>607</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1458" t="n">
         <v>24</v>
-      </c>
-      <c r="F1458" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1458" t="n">
-        <v>2</v>
-      </c>
-      <c r="H1458" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="1459">
@@ -41272,26 +41272,26 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>32000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="E1459" t="n">
-        <v>2138</v>
+        <v>320</v>
       </c>
       <c r="F1459" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1459" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H1459" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1460">
@@ -41300,26 +41300,26 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>1900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="E1460" t="n">
-        <v>74</v>
+        <v>634</v>
       </c>
       <c r="F1460" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1460" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="H1460" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1461">
@@ -41328,26 +41328,26 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>1700000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>92</v>
+        <v>780</v>
       </c>
       <c r="E1461" t="n">
-        <v>90</v>
+        <v>936</v>
       </c>
       <c r="F1461" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1461" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="H1461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1462">
@@ -41356,26 +41356,26 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>22500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E1462" t="n">
-        <v>366</v>
+        <v>182</v>
       </c>
       <c r="F1462" t="n">
         <v>3</v>
       </c>
       <c r="G1462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1462" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1463">
@@ -41384,26 +41384,26 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
+          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>9500000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>350</v>
+        <v>225</v>
       </c>
       <c r="E1463" t="n">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="F1463" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G1463" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H1463" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1464">
@@ -41412,26 +41412,26 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
+          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>209000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>1841</v>
+        <v>280</v>
       </c>
       <c r="E1464" t="n">
-        <v>4189</v>
+        <v>157</v>
       </c>
       <c r="F1464" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="G1464" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="H1464" t="n">
-        <v>910</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1465">
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>South Grove</t>
+          <t>1 Park Homes</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>7600000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="E1465" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F1465" t="n">
         <v>4</v>
       </c>
       <c r="G1465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,26 +41468,26 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>24000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>360</v>
+        <v>760</v>
       </c>
       <c r="E1466" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F1466" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1466" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1466" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1467">
@@ -41496,17 +41496,17 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>12 Merle Bintaro</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>12800000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="E1467" t="n">
-        <v>515</v>
+        <v>158</v>
       </c>
       <c r="F1467" t="n">
         <v>4</v>
@@ -41515,7 +41515,7 @@
         <v>4</v>
       </c>
       <c r="H1467" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1468">
@@ -41524,26 +41524,26 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>12500000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="E1468" t="n">
-        <v>750</v>
+        <v>1094</v>
       </c>
       <c r="F1468" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="G1468" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1468" t="n">
-        <v>310</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1469">
@@ -41552,26 +41552,26 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah Kartika Utama Pondok Indah</t>
+          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>28000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>516</v>
+        <v>245</v>
       </c>
       <c r="E1469" t="n">
-        <v>607</v>
+        <v>647</v>
       </c>
       <c r="F1469" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1469" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1469" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1470">
@@ -41580,26 +41580,26 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
+          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>11500000000</v>
+        <v>4280000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E1470" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="F1470" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1470" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1471">
@@ -41608,26 +41608,26 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Puri Rinda Residence</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>62000000000</v>
+        <v>1960000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>881</v>
+        <v>188</v>
       </c>
       <c r="E1471" t="n">
-        <v>1066</v>
+        <v>105</v>
       </c>
       <c r="F1471" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1471" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1471" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1472">
@@ -41636,26 +41636,26 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>32000000000</v>
+        <v>19500000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>720</v>
+        <v>580</v>
       </c>
       <c r="E1472" t="n">
-        <v>634</v>
+        <v>673</v>
       </c>
       <c r="F1472" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1472" t="n">
         <v>42</v>
-      </c>
-      <c r="G1472" t="n">
-        <v>51</v>
-      </c>
-      <c r="H1472" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="1473">
@@ -41664,26 +41664,26 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>21500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>780</v>
+        <v>1200</v>
       </c>
       <c r="E1473" t="n">
-        <v>936</v>
+        <v>2138</v>
       </c>
       <c r="F1473" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1473" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="H1473" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1474">
@@ -41692,26 +41692,26 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
+          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>2900000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E1474" t="n">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F1474" t="n">
         <v>3</v>
       </c>
       <c r="G1474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1474" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1475">
@@ -41720,26 +41720,26 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
+          <t>Aparthouse Crystal</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>5200000000</v>
+        <v>950000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="E1475" t="n">
-        <v>201</v>
+        <v>10</v>
       </c>
       <c r="F1475" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1475" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H1475" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1476">
@@ -41748,26 +41748,26 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
+          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>3900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>280</v>
+        <v>800</v>
       </c>
       <c r="E1476" t="n">
-        <v>157</v>
+        <v>1335</v>
       </c>
       <c r="F1476" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1476" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1476" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1477">
@@ -41776,26 +41776,26 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>1 Park Homes</t>
+          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>20000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>380</v>
+        <v>800</v>
       </c>
       <c r="E1477" t="n">
-        <v>200</v>
+        <v>1335</v>
       </c>
       <c r="F1477" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1477" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1477" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1478">
@@ -41804,26 +41804,26 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>17700000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="E1478" t="n">
-        <v>360</v>
+        <v>1025</v>
       </c>
       <c r="F1478" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1478" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="H1478" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1479">
@@ -41832,26 +41832,26 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>1900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="E1479" t="n">
-        <v>74</v>
+        <v>2138</v>
       </c>
       <c r="F1479" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1479" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1479" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1480">
@@ -41860,26 +41860,26 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>38000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>760</v>
+        <v>140</v>
       </c>
       <c r="E1480" t="n">
-        <v>517</v>
+        <v>93</v>
       </c>
       <c r="F1480" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1480" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1480" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1481">
@@ -41888,26 +41888,26 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>12 Merle Bintaro</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>3950000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>140</v>
+        <v>800</v>
       </c>
       <c r="E1481" t="n">
-        <v>158</v>
+        <v>650</v>
       </c>
       <c r="F1481" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1481" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1481" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1482">
@@ -41916,26 +41916,26 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>Kemang Siap Huni Best Price</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>19000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="E1482" t="n">
-        <v>1094</v>
+        <v>425</v>
       </c>
       <c r="F1482" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G1482" t="n">
         <v>41</v>
       </c>
       <c r="H1482" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1483">
@@ -41944,26 +41944,26 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
+          <t>Kemang Jakarta Selatan Harga Dibawah Pasaran</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>9700000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>245</v>
+        <v>460</v>
       </c>
       <c r="E1483" t="n">
-        <v>647</v>
+        <v>1075</v>
       </c>
       <c r="F1483" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="G1483" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="H1483" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1484">
@@ -41972,26 +41972,26 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
+          <t>Rumah, Pondok Indah 3 Lantai 7 Milyar</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>4280000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="E1484" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="F1484" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G1484" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H1484" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1485">
@@ -42000,26 +42000,26 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Puri Rinda Residence</t>
+          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>1960000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="E1485" t="n">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="F1485" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1485" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1485" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1486">
@@ -42028,26 +42028,26 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>19500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>580</v>
+        <v>1200</v>
       </c>
       <c r="E1486" t="n">
-        <v>673</v>
+        <v>2138</v>
       </c>
       <c r="F1486" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1486" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H1486" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1487">
@@ -42056,26 +42056,26 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>32000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>1200</v>
+        <v>375</v>
       </c>
       <c r="E1487" t="n">
-        <v>2138</v>
+        <v>76</v>
       </c>
       <c r="F1487" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1487" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1487" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1488">
@@ -42084,26 +42084,26 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>1400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E1488" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F1488" t="n">
         <v>3</v>
       </c>
       <c r="G1488" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1488" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1489">
@@ -42112,26 +42112,26 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Aparthouse Crystal</t>
+          <t>Rumah Siap Huni Ada Private Pool di Cilandak Dekat Citos</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>950000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="E1489" t="n">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="F1489" t="n">
         <v>2</v>
       </c>
       <c r="G1489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1489" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1490">
@@ -42140,26 +42140,26 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>27000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="E1490" t="n">
-        <v>1335</v>
+        <v>91</v>
       </c>
       <c r="F1490" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1490" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H1490" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1491">
@@ -42168,26 +42168,26 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
+          <t>Edenhaus Simatupang</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>27000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>800</v>
+        <v>222</v>
       </c>
       <c r="E1491" t="n">
-        <v>1335</v>
+        <v>240</v>
       </c>
       <c r="F1491" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1491" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1491" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1492">
@@ -42196,26 +42196,26 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>120000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>2100</v>
+        <v>44</v>
       </c>
       <c r="E1492" t="n">
-        <v>1025</v>
+        <v>24</v>
       </c>
       <c r="F1492" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1492" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1492" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1493">
@@ -42224,26 +42224,922 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
         </is>
       </c>
       <c r="C1493" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>370</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>91</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Dijual Rumah 716m2 Di Badan Jalan Permata Hijau Raya</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>716</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Asri Gaya American Country Nyaman dan Strategis Diandara, Cilandak</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>660</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Rumah Baru Fully Furnished SHM di Area Senopati Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>338</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai Dalam Town House Harga Dibawah di Bawah NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>17700000000</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Area Favorit Tenang Jalan Lebar Dalam Portal</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Area Tenang Depan Taman Jalan Lebar Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>238</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Spesifikasi Premium Lokasi Eksklusif di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>26900000000</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>430</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Siap Huni di Jagakarsa Akses Lebar Dekat Tol</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Fully-Furnished Bernuansa Resort di Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
         <v>32000000000</v>
       </c>
-      <c r="D1493" t="n">
+      <c r="D1507" t="n">
         <v>1200</v>
       </c>
-      <c r="E1493" t="n">
+      <c r="E1507" t="n">
         <v>2138</v>
       </c>
-      <c r="F1493" t="n">
-        <v>12</v>
-      </c>
-      <c r="G1493" t="n">
+      <c r="F1507" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Rumah Jl. Ciniru Kebayoran Baru Jaksel</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>36000000000</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>450</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Ruma Rempoa</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>2290000000</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>787</v>
+      </c>
+      <c r="F1511" t="n">
         <v>6</v>
       </c>
-      <c r="H1493" t="n">
-        <v>24</v>
+      <c r="G1511" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Brand New American Classic Style Dijagakarsa</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>M Living at Puri Pesanggrahan</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>182</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>111</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>39000000000</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>403</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>53000000000</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>21000000000</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>765</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>765</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Precium Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>220</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>334</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>23000000000</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>417</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>417</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>16000000000</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>695</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>220</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>168</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>67 Kebagusan</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>1470000000</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>74</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>2360</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>9980000000</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>785</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>353</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>18000000000</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>480</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>412</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1525"/>
+  <dimension ref="A1:H1559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40292,26 +40292,26 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>13500000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>374</v>
+        <v>700</v>
       </c>
       <c r="E1424" t="n">
-        <v>181</v>
+        <v>832</v>
       </c>
       <c r="F1424" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1424" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1424" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1425">
@@ -40320,26 +40320,26 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
+          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>14000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>700</v>
+        <v>261</v>
       </c>
       <c r="E1425" t="n">
-        <v>832</v>
+        <v>240</v>
       </c>
       <c r="F1425" t="n">
         <v>5</v>
       </c>
       <c r="G1425" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1425" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1426">
@@ -40348,26 +40348,26 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>85000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>1500</v>
+        <v>360</v>
       </c>
       <c r="E1426" t="n">
-        <v>634</v>
+        <v>230</v>
       </c>
       <c r="F1426" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1426" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1426" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1427">
@@ -40376,26 +40376,26 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>17200000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>700</v>
+        <v>1</v>
       </c>
       <c r="E1427" t="n">
-        <v>864</v>
+        <v>5500</v>
       </c>
       <c r="F1427" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1427" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1427" t="n">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1428">
@@ -40404,26 +40404,26 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>9000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>261</v>
+        <v>88</v>
       </c>
       <c r="E1428" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="F1428" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1428" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1428" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1429">
@@ -40432,26 +40432,26 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>5500000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="E1429" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="F1429" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1429" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1429" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1430">
@@ -40460,26 +40460,26 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>55000000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>1</v>
+        <v>442</v>
       </c>
       <c r="E1430" t="n">
-        <v>5500</v>
+        <v>644</v>
       </c>
       <c r="F1430" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G1430" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1430" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1431">
@@ -40488,26 +40488,26 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>2600000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>88</v>
+        <v>450</v>
       </c>
       <c r="E1431" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="F1431" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1431" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="H1431" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1432">
@@ -40516,26 +40516,26 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>5200000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="E1432" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="F1432" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1432" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H1432" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1433">
@@ -40544,26 +40544,26 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>2830000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>112</v>
+        <v>560</v>
       </c>
       <c r="E1433" t="n">
-        <v>70</v>
+        <v>674</v>
       </c>
       <c r="F1433" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1433" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="H1433" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1434">
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
+          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>23500000000</v>
+        <v>25800000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>442</v>
+        <v>1374</v>
       </c>
       <c r="E1434" t="n">
-        <v>644</v>
+        <v>1493</v>
       </c>
       <c r="F1434" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1434" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,26 +40600,26 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
+          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>36000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="E1435" t="n">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="F1435" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1435" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="H1435" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1436">
@@ -40628,26 +40628,26 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>9000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="E1436" t="n">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="F1436" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G1436" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1436" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1437">
@@ -40656,26 +40656,26 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>20000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>560</v>
+        <v>110</v>
       </c>
       <c r="E1437" t="n">
-        <v>674</v>
+        <v>68</v>
       </c>
       <c r="F1437" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G1437" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="H1437" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1438">
@@ -40684,26 +40684,26 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>25800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>1374</v>
+        <v>400</v>
       </c>
       <c r="E1438" t="n">
-        <v>1493</v>
+        <v>260</v>
       </c>
       <c r="F1438" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G1438" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H1438" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1439">
@@ -40712,20 +40712,20 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>4700000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E1439" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="F1439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1439" t="n">
         <v>2</v>
@@ -40740,26 +40740,26 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>11500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="E1440" t="n">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="F1440" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1440" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1441">
@@ -40768,26 +40768,26 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>2500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>110</v>
+        <v>685</v>
       </c>
       <c r="E1441" t="n">
-        <v>68</v>
+        <v>685</v>
       </c>
       <c r="F1441" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1441" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1442">
@@ -40796,26 +40796,26 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>6500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E1442" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="F1442" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1442" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1442" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1443">
@@ -40824,26 +40824,26 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
+          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>1500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E1443" t="n">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="F1443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1443" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1443" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1444">
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>1400000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E1444" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F1444" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1444" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1444" t="n">
         <v>2</v>
@@ -40880,26 +40880,26 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
+          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>11000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>685</v>
+        <v>630</v>
       </c>
       <c r="E1445" t="n">
-        <v>685</v>
+        <v>750</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G1445" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1445" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1446">
@@ -40908,20 +40908,20 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>4900000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1446" t="n">
-        <v>293</v>
+        <v>366</v>
       </c>
       <c r="F1446" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1446" t="n">
         <v>3</v>
@@ -40936,26 +40936,26 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
+          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>12000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1447" t="n">
-        <v>497</v>
+        <v>257</v>
       </c>
       <c r="F1447" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1447" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1447" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1448">
@@ -40964,26 +40964,26 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>2900000000</v>
+        <v>209000000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>200</v>
+        <v>1841</v>
       </c>
       <c r="E1448" t="n">
-        <v>155</v>
+        <v>4189</v>
       </c>
       <c r="F1448" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="G1448" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="H1448" t="n">
-        <v>2</v>
+        <v>910</v>
       </c>
     </row>
     <row r="1449">
@@ -40992,26 +40992,26 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
+          <t>South Grove</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>25000000000</v>
+        <v>7600000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>630</v>
+        <v>325</v>
       </c>
       <c r="E1449" t="n">
-        <v>750</v>
+        <v>177</v>
       </c>
       <c r="F1449" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G1449" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1449" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1450">
@@ -41020,26 +41020,26 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>6400000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E1450" t="n">
-        <v>160</v>
+        <v>518</v>
       </c>
       <c r="F1450" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1450" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1450" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1451">
@@ -41048,26 +41048,26 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>1700000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>92</v>
+        <v>520</v>
       </c>
       <c r="E1451" t="n">
-        <v>90</v>
+        <v>750</v>
       </c>
       <c r="F1451" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="G1451" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1451" t="n">
-        <v>1</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1452">
@@ -41076,26 +41076,26 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>22500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1452" t="n">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="F1452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1452" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1453">
@@ -41104,26 +41104,26 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>9500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>350</v>
+        <v>720</v>
       </c>
       <c r="E1453" t="n">
-        <v>257</v>
+        <v>634</v>
       </c>
       <c r="F1453" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1453" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1453" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1454">
@@ -41132,26 +41132,26 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
+          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>209000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>1841</v>
+        <v>780</v>
       </c>
       <c r="E1454" t="n">
-        <v>4189</v>
+        <v>936</v>
       </c>
       <c r="F1454" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G1454" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H1454" t="n">
-        <v>910</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1455">
@@ -41160,26 +41160,26 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>South Grove</t>
+          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>7600000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="E1455" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F1455" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1455" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1456">
@@ -41188,26 +41188,26 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>24000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>360</v>
+        <v>225</v>
       </c>
       <c r="E1456" t="n">
-        <v>518</v>
+        <v>201</v>
       </c>
       <c r="F1456" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1456" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1456" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1457">
@@ -41216,26 +41216,26 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
+          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>12500000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>520</v>
+        <v>280</v>
       </c>
       <c r="E1457" t="n">
-        <v>750</v>
+        <v>157</v>
       </c>
       <c r="F1457" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="G1457" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1457" t="n">
-        <v>310</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1458">
@@ -41244,26 +41244,26 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Rumah Kartika Utama Pondok Indah</t>
+          <t>1 Park Homes</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>28000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>516</v>
+        <v>380</v>
       </c>
       <c r="E1458" t="n">
-        <v>607</v>
+        <v>200</v>
       </c>
       <c r="F1458" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1458" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1458" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1459">
@@ -41272,26 +41272,26 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
+          <t>12 Merle Bintaro</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>11500000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="E1459" t="n">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="F1459" t="n">
         <v>4</v>
       </c>
       <c r="G1459" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1459" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1460">
@@ -41300,26 +41300,26 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>32000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>720</v>
+        <v>550</v>
       </c>
       <c r="E1460" t="n">
-        <v>634</v>
+        <v>1094</v>
       </c>
       <c r="F1460" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G1460" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1460" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1461">
@@ -41328,26 +41328,26 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
+          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>21500000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>780</v>
+        <v>245</v>
       </c>
       <c r="E1461" t="n">
-        <v>936</v>
+        <v>647</v>
       </c>
       <c r="F1461" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1461" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="H1461" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1462">
@@ -41356,26 +41356,26 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
+          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>2900000000</v>
+        <v>4280000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>100</v>
+        <v>262</v>
       </c>
       <c r="E1462" t="n">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="F1462" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1462" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1462" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1463">
@@ -41384,26 +41384,26 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
+          <t>Puri Rinda Residence</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>5200000000</v>
+        <v>1960000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="E1463" t="n">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="F1463" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G1463" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H1463" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1464">
@@ -41412,26 +41412,26 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
+          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>3900000000</v>
+        <v>19500000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>280</v>
+        <v>580</v>
       </c>
       <c r="E1464" t="n">
-        <v>157</v>
+        <v>673</v>
       </c>
       <c r="F1464" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1464" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1464" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1465">
@@ -41440,26 +41440,26 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>1 Park Homes</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>380</v>
+        <v>1200</v>
       </c>
       <c r="E1465" t="n">
-        <v>200</v>
+        <v>2138</v>
       </c>
       <c r="F1465" t="n">
         <v>4</v>
       </c>
       <c r="G1465" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1465" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1466">
@@ -41468,26 +41468,26 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>38000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>760</v>
+        <v>120</v>
       </c>
       <c r="E1466" t="n">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="F1466" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1466" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1466" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1467">
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>12 Merle Bintaro</t>
+          <t>Aparthouse Crystal</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>3950000000</v>
+        <v>950000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="E1467" t="n">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="F1467" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1467" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,26 +41524,26 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>19000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
       <c r="E1468" t="n">
-        <v>1094</v>
+        <v>1335</v>
       </c>
       <c r="F1468" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1468" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1468" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1469">
@@ -41552,26 +41552,26 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
+          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>9700000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>245</v>
+        <v>800</v>
       </c>
       <c r="E1469" t="n">
-        <v>647</v>
+        <v>1335</v>
       </c>
       <c r="F1469" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1469" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1469" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1470">
@@ -41580,26 +41580,26 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
+          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>4280000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>262</v>
+        <v>2100</v>
       </c>
       <c r="E1470" t="n">
-        <v>85</v>
+        <v>1025</v>
       </c>
       <c r="F1470" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1470" t="n">
         <v>5</v>
       </c>
       <c r="H1470" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1471">
@@ -41608,26 +41608,26 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Puri Rinda Residence</t>
+          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>1960000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="E1471" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F1471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1472">
@@ -41636,26 +41636,26 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>19500000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>580</v>
+        <v>800</v>
       </c>
       <c r="E1472" t="n">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="F1472" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G1472" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="H1472" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1473">
@@ -41664,26 +41664,26 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Kemang Siap Huni Best Price</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>32000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="E1473" t="n">
-        <v>2138</v>
+        <v>425</v>
       </c>
       <c r="F1473" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1473" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1473" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1474">
@@ -41692,26 +41692,26 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
+          <t>Kemang Jakarta Selatan Harga Dibawah Pasaran</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>1400000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="E1474" t="n">
-        <v>60</v>
+        <v>1075</v>
       </c>
       <c r="F1474" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="G1474" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1474" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1475">
@@ -41720,26 +41720,26 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Aparthouse Crystal</t>
+          <t>Rumah, Pondok Indah 3 Lantai 7 Milyar</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>950000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>42</v>
+        <v>400</v>
       </c>
       <c r="E1475" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G1475" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H1475" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1476">
@@ -41748,26 +41748,26 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
+          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>27000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E1476" t="n">
-        <v>1335</v>
+        <v>275</v>
       </c>
       <c r="F1476" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1476" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H1476" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1477">
@@ -41776,26 +41776,26 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>27000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E1477" t="n">
-        <v>1335</v>
+        <v>2138</v>
       </c>
       <c r="F1477" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1477" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1477" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1478">
@@ -41804,26 +41804,26 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>120000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>2100</v>
+        <v>60</v>
       </c>
       <c r="E1478" t="n">
-        <v>1025</v>
+        <v>74</v>
       </c>
       <c r="F1478" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1478" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1478" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1479">
@@ -41832,26 +41832,26 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Rumah Siap Huni Ada Private Pool di Cilandak Dekat Citos</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>32000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>1200</v>
+        <v>288</v>
       </c>
       <c r="E1479" t="n">
-        <v>2138</v>
+        <v>178</v>
       </c>
       <c r="F1479" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1479" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1480">
@@ -41860,26 +41860,26 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>2100000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="E1480" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1480" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1480" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1480" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1481">
@@ -41888,26 +41888,26 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>Edenhaus Simatupang</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>97000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>800</v>
+        <v>222</v>
       </c>
       <c r="E1481" t="n">
-        <v>650</v>
+        <v>240</v>
       </c>
       <c r="F1481" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1481" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1481" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1482">
@@ -41916,26 +41916,26 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Kemang Siap Huni Best Price</t>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>13500000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="E1482" t="n">
-        <v>425</v>
+        <v>24</v>
       </c>
       <c r="F1482" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G1482" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1482" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1483">
@@ -41944,26 +41944,26 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Kemang Jakarta Selatan Harga Dibawah Pasaran</t>
+          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>26000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="E1483" t="n">
-        <v>1075</v>
+        <v>120</v>
       </c>
       <c r="F1483" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="G1483" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="H1483" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1484">
@@ -41972,26 +41972,26 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Rumah, Pondok Indah 3 Lantai 7 Milyar</t>
+          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>7000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="E1484" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F1484" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G1484" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1484" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1485">
@@ -42000,26 +42000,26 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
+          <t>Dijual Rumah 716m2 Di Badan Jalan Permata Hijau Raya</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>25000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1485" t="n">
-        <v>275</v>
+        <v>716</v>
       </c>
       <c r="F1485" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1485" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1485" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1486">
@@ -42028,26 +42028,26 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>Dijual Rumah Asri Gaya American Country Nyaman dan Strategis Diandara, Cilandak</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>32000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E1486" t="n">
-        <v>2138</v>
+        <v>660</v>
       </c>
       <c r="F1486" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1486" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="H1486" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1487">
@@ -42056,26 +42056,26 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Baru Fully Furnished SHM di Area Senopati Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>7900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>375</v>
+        <v>810</v>
       </c>
       <c r="E1487" t="n">
-        <v>76</v>
+        <v>338</v>
       </c>
       <c r="F1487" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1487" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H1487" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1488">
@@ -42084,26 +42084,26 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>1900000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="E1488" t="n">
-        <v>74</v>
+        <v>515</v>
       </c>
       <c r="F1488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1488" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1488" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1489">
@@ -42112,26 +42112,26 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Ada Private Pool di Cilandak Dekat Citos</t>
+          <t>Rumah 2 Lantai Dalam Town House Harga Dibawah di Bawah NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>6250000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>288</v>
+        <v>1200</v>
       </c>
       <c r="E1489" t="n">
-        <v>178</v>
+        <v>1800</v>
       </c>
       <c r="F1489" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1489" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1489" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1490">
@@ -42140,26 +42140,26 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>2900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>90</v>
+        <v>881</v>
       </c>
       <c r="E1490" t="n">
-        <v>91</v>
+        <v>1066</v>
       </c>
       <c r="F1490" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G1490" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H1490" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1491">
@@ -42168,26 +42168,26 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Edenhaus Simatupang</t>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>9900000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>222</v>
+        <v>1100</v>
       </c>
       <c r="E1491" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="F1491" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1491" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1491" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1492">
@@ -42196,26 +42196,26 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Area Favorit Tenang Jalan Lebar Dalam Portal</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>850000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="E1492" t="n">
-        <v>24</v>
+        <v>425</v>
       </c>
       <c r="F1492" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1492" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1492" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1493">
@@ -42224,26 +42224,26 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
+          <t>Area Tenang Depan Taman Jalan Lebar Siap Huni</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>4900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
       <c r="E1493" t="n">
-        <v>120</v>
+        <v>238</v>
       </c>
       <c r="F1493" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1493" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="H1493" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1494">
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
+          <t>Rumah Mewah Spesifikasi Premium Lokasi Eksklusif di Pondok Indah</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>4900000000</v>
+        <v>26900000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>260</v>
+        <v>800</v>
       </c>
       <c r="E1494" t="n">
-        <v>200</v>
+        <v>430</v>
       </c>
       <c r="F1494" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1494" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="H1494" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Dijual Rumah 716m2 Di Badan Jalan Permata Hijau Raya</t>
+          <t>Rumah Mewah Siap Huni di Jagakarsa Akses Lebar Dekat Tol</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>30000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="E1495" t="n">
-        <v>716</v>
+        <v>70</v>
       </c>
       <c r="F1495" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1495" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1495" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Gaya American Country Nyaman dan Strategis Diandara, Cilandak</t>
+          <t>Rumah Mewah Fully-Furnished Bernuansa Resort di Jagakarsa</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>10000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E1496" t="n">
-        <v>660</v>
+        <v>2138</v>
       </c>
       <c r="F1496" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G1496" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="H1496" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Rumah Baru Fully Furnished SHM di Area Senopati Kebayoran Baru</t>
+          <t>Rumah Jl. Ciniru Kebayoran Baru Jaksel</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>48000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>810</v>
+        <v>300</v>
       </c>
       <c r="E1497" t="n">
-        <v>338</v>
+        <v>450</v>
       </c>
       <c r="F1497" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1497" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H1497" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>Ruma Rempoa</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>12800000000</v>
+        <v>2290000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>400</v>
+        <v>92</v>
       </c>
       <c r="E1498" t="n">
-        <v>515</v>
+        <v>89</v>
       </c>
       <c r="F1498" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1498" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1498" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Dalam Town House Harga Dibawah di Bawah NJOP di Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>30000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="E1499" t="n">
-        <v>1800</v>
+        <v>74</v>
       </c>
       <c r="F1499" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G1499" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1499" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>62000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>881</v>
+        <v>600</v>
       </c>
       <c r="E1500" t="n">
-        <v>1066</v>
+        <v>787</v>
       </c>
       <c r="F1500" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="G1500" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="H1500" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+          <t>Brand New American Classic Style Dijagakarsa</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>17700000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="E1501" t="n">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="F1501" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G1501" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1501" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,26 +42476,26 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Area Favorit Tenang Jalan Lebar Dalam Portal</t>
+          <t>M Living at Puri Pesanggrahan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>28000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>500</v>
+        <v>182</v>
       </c>
       <c r="E1502" t="n">
-        <v>425</v>
+        <v>111</v>
       </c>
       <c r="F1502" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
       </c>
       <c r="H1502" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1503">
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Area Tenang Depan Taman Jalan Lebar Siap Huni</t>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>15000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1503" t="n">
-        <v>238</v>
+        <v>1018</v>
       </c>
       <c r="F1503" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G1503" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1503" t="n">
-        <v>2</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Rumah Mewah Spesifikasi Premium Lokasi Eksklusif di Pondok Indah</t>
+          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>26900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>800</v>
+        <v>765</v>
       </c>
       <c r="E1504" t="n">
-        <v>430</v>
+        <v>765</v>
       </c>
       <c r="F1504" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G1504" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="H1504" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Precium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>62000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>881</v>
+        <v>220</v>
       </c>
       <c r="E1505" t="n">
-        <v>1066</v>
+        <v>334</v>
       </c>
       <c r="F1505" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1505" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1505" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,23 +42588,23 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Jagakarsa Akses Lebar Dekat Tol</t>
+          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>1700000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>120</v>
+        <v>417</v>
       </c>
       <c r="E1506" t="n">
-        <v>70</v>
+        <v>417</v>
       </c>
       <c r="F1506" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1506" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1506" t="n">
         <v>22</v>
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Rumah Mewah Fully-Furnished Bernuansa Resort di Jagakarsa</t>
+          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>32000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="E1507" t="n">
-        <v>2138</v>
+        <v>695</v>
       </c>
       <c r="F1507" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G1507" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H1507" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Rumah Jl. Ciniru Kebayoran Baru Jaksel</t>
+          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>36000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="E1508" t="n">
-        <v>450</v>
+        <v>168</v>
       </c>
       <c r="F1508" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1508" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,23 +42672,23 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Ruma Rempoa</t>
+          <t>67 Kebagusan</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>2290000000</v>
+        <v>1470000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E1509" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F1509" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1509" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1509" t="n">
         <v>1</v>
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>1900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="E1510" t="n">
-        <v>74</v>
+        <v>2360</v>
       </c>
       <c r="F1510" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="G1510" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1510" t="n">
-        <v>11</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
+          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>24000000000</v>
+        <v>9980000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1511" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F1511" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1511" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H1511" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Brand New American Classic Style Dijagakarsa</t>
+          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>2400000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E1512" t="n">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="F1512" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1512" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1512" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>M Living at Puri Pesanggrahan</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>2900000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E1513" t="n">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="F1513" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1513" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1513" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,26 +42812,26 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Dijual Jalan Tebet Barat Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>39000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="E1514" t="n">
-        <v>403</v>
+        <v>90</v>
       </c>
       <c r="F1514" t="n">
         <v>4</v>
       </c>
       <c r="G1514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1514" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1515">
@@ -42840,26 +42840,26 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah dijual bangunan lama dekat Pakubuwono dan Senayan City</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>53000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E1515" t="n">
-        <v>1018</v>
+        <v>328</v>
       </c>
       <c r="F1515" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="G1515" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H1515" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
+          <t>Dijual Rumah Elite Cipaku Kebayoran Baru, Dekat Scbd &amp; Senopati</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>21000000000</v>
+        <v>33000000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>765</v>
+        <v>500</v>
       </c>
       <c r="E1516" t="n">
-        <v>765</v>
+        <v>410</v>
       </c>
       <c r="F1516" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1516" t="n">
         <v>4</v>
       </c>
       <c r="H1516" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Precium Kebayoran Baru</t>
+          <t>Dijual Rumah Hook di Cipaku, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>13500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E1517" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="F1517" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1517" t="n">
         <v>3</v>
       </c>
       <c r="H1517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
+          <t>Dijual Rumah Komersial di Jalan Wijaya, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>23000000000</v>
+        <v>88000000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>417</v>
+        <v>750</v>
       </c>
       <c r="E1518" t="n">
-        <v>417</v>
+        <v>1035</v>
       </c>
       <c r="F1518" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G1518" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H1518" t="n">
-        <v>22</v>
+        <v>810</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
+          <t>Dijual - Rumah Komersial di Jl. Cikajang, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>16000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>450</v>
+        <v>257</v>
       </c>
       <c r="E1519" t="n">
-        <v>695</v>
+        <v>283</v>
       </c>
       <c r="F1519" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G1519" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1519" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1520">
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>6800000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="E1520" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="F1520" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1520" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1520" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>67 Kebagusan</t>
+          <t>Dijual Rumah Baru Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>1470000000</v>
+        <v>39000000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>74</v>
+        <v>850</v>
       </c>
       <c r="E1521" t="n">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="F1521" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1521" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1521" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>48000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E1522" t="n">
-        <v>2360</v>
+        <v>584</v>
       </c>
       <c r="F1522" t="n">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="G1522" t="n">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="H1522" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>9980000000</v>
+        <v>85000000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="E1523" t="n">
-        <v>785</v>
+        <v>634</v>
       </c>
       <c r="F1523" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G1523" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1523" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>12000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>850</v>
+        <v>308</v>
       </c>
       <c r="E1524" t="n">
-        <v>353</v>
+        <v>160</v>
       </c>
       <c r="F1524" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1524" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H1524" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,26 +43120,978 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
+          <t>Dijual Rumah Seperti Ddalam Komplek(Gated) Dikebayoran Baru. Luas 340M.(Fisik 360M) Rp.21.5 M</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>18000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="E1525" t="n">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="F1525" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Dijual Murah Rumah Istana Super Lux Di Pondok Indah Luas 2382m Hanya Rp 89 M ( Hanya 37 Juta/m2 )</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>89000000000</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>2382</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Rumah 100% Brand New Super Lux di Kebayoran Baru. 380M 3Lt Rp 38 Mly</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>380</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1527" t="n">
         <v>42</v>
       </c>
-      <c r="G1525" t="n">
+    </row>
+    <row r="1528">
+      <c r="A1528" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Timur Raya. Luas 1192M2. NJOP 27 M Jual Hanya Rp 24 M</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>1192</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>864</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Dijual Murah Rumah Area Senopati Scbd. Luas 523 Hanya Rp.29 M Jalan Lebar Tenang Dalam Portal</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>29000000000</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>523</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1530" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1531" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1531" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>Dijual Rp 50Jt/M2. Rumah di Bukit Golf (Pondok Indah) Luas 4189Meter2. Langka.</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>209000000000</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>1841</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1532" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>39000000000</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>403</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1533" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1533" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>353</v>
+      </c>
+      <c r="F1534" t="n">
         <v>41</v>
       </c>
-      <c r="H1525" t="n">
+      <c r="G1534" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1534" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="n">
+        <v>1534</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1535" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1535" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Rumah Murah American Classic Cluster Cipete Kolam Renang Lift</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>358</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1536" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1536" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni di Veteran Bintaro, Strategis &amp; Harga Terbaik!</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="D1537" t="n">
+        <v>180</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1537" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1537" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Rumah di Cipete, Jakarta Selatan Area Strategis</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>215</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1538" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Rumah Modern dan Ekslusif di Setiabudi Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>898000000</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1539" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Harga Terbaik Unit Terbatas Rumah di Kemang Cilandak</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>3870000000</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>178</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1540" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Rumah Mewah di Kemang Cilandak Harga Terbaik Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>3870000000</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>178</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1541" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Renovasi Total Dekat MRT dan Apartemen Esence di Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>475</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1542" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1542" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="n">
+        <v>1543</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>395</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>172</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1544" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1545" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1545" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Rumah Kartika Utama Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>516</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>607</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1546" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1546" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="n">
+        <v>1546</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1547" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Cilandak, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1548" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Rumah Bernuansa Villa di Jagakarsa, Jakarta Selatan di Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>488</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1549" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1549" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Rumah di Tirtayasa Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>97600000000</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>1206</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1550" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1550" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Kemang Huis Townhouse</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>247</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1551" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1551" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>261M² Siap Huni di Bawah 14M Dekat Senopati Blok M Scbd- Harga Segini Makin Susah Dicari.</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>261</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1552" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="n">
+        <v>1552</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Di Ciniru Kebayoran Baru LT 252 M², Jalan 2 Mobil, Bebas Banjir, SHM Barang Langka</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>16500000000</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>252</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1553" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Rumah Classic Modern Area Senopati 335M2- Jalan Lebar &amp; Prestisius Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>335</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1554" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="n">
+        <v>1554</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Hakasan Residence</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>190</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1555" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>9.6M di Senopati, 100M Dari Gunawarman - Buat yang Beli Lokasi, Bukan Bangunan.</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>9600000000</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>201</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1556" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="n">
+        <v>1556</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>393M² SHM di Cipaku - Lahan Sebesar Ini di Kebayoran Baru Cepat Habis.</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>366</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>393</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1557" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Dekat Senayan &amp; Scbd! Rumah 4Kt di Kebayoran Lama, Harga Menarik</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1558" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1559" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1559"/>
+  <dimension ref="A1:H1582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40404,26 +40404,26 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>2600000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E1428" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="F1428" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1428" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H1428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1429">
@@ -40432,26 +40432,26 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>5200000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>100</v>
+        <v>442</v>
       </c>
       <c r="E1429" t="n">
-        <v>120</v>
+        <v>644</v>
       </c>
       <c r="F1429" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G1429" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1430">
@@ -40460,26 +40460,26 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah di Jalan Utama Pondok Indah, Harga Sedikit di Atas NJOP</t>
+          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>23500000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E1430" t="n">
-        <v>644</v>
+        <v>500</v>
       </c>
       <c r="F1430" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1430" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H1430" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1431">
@@ -40488,26 +40488,26 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Lokasi Sangat Strategis Pusat Kota</t>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>36000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="E1431" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="F1431" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G1431" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="H1431" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1432">
@@ -40516,26 +40516,26 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>9000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>340</v>
+        <v>560</v>
       </c>
       <c r="E1432" t="n">
-        <v>290</v>
+        <v>674</v>
       </c>
       <c r="F1432" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G1432" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H1432" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1433">
@@ -40544,26 +40544,26 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>20000000000</v>
+        <v>25800000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>560</v>
+        <v>1374</v>
       </c>
       <c r="E1433" t="n">
-        <v>674</v>
+        <v>1493</v>
       </c>
       <c r="F1433" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="G1433" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="H1433" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1434">
@@ -40572,26 +40572,26 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lelang 0 Jalan Raya Kemang Utara</t>
+          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>25800000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>1374</v>
+        <v>70</v>
       </c>
       <c r="E1434" t="n">
-        <v>1493</v>
+        <v>123</v>
       </c>
       <c r="F1434" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1435">
@@ -40600,26 +40600,26 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah Tua Langka Area Tenang di Pondok Indah</t>
+          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>4700000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="E1435" t="n">
-        <v>123</v>
+        <v>580</v>
       </c>
       <c r="F1435" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1435" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1436">
@@ -40628,26 +40628,26 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Radio Dalam Kebayoran Baru Ada 7 Kamar Kost SHM</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>11500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="E1436" t="n">
-        <v>580</v>
+        <v>68</v>
       </c>
       <c r="F1436" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1436" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1436" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1437">
@@ -40656,26 +40656,26 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>2500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="E1437" t="n">
-        <v>68</v>
+        <v>260</v>
       </c>
       <c r="F1437" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1437" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1437" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1438">
@@ -40684,26 +40684,26 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>6500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="E1438" t="n">
-        <v>260</v>
+        <v>71</v>
       </c>
       <c r="F1438" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1438" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1438" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1439">
@@ -40712,17 +40712,17 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>1500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1439" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F1439" t="n">
         <v>3</v>
@@ -40740,26 +40740,26 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>1400000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>120</v>
+        <v>685</v>
       </c>
       <c r="E1440" t="n">
-        <v>65</v>
+        <v>685</v>
       </c>
       <c r="F1440" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1440" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1441">
@@ -40768,26 +40768,26 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
+          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>11000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>685</v>
+        <v>300</v>
       </c>
       <c r="E1441" t="n">
-        <v>685</v>
+        <v>293</v>
       </c>
       <c r="F1441" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1441" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1442">
@@ -40796,26 +40796,26 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
+          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>4900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1442" t="n">
-        <v>293</v>
+        <v>497</v>
       </c>
       <c r="F1442" t="n">
         <v>4</v>
       </c>
       <c r="G1442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1442" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1443">
@@ -40824,17 +40824,17 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>12000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1443" t="n">
-        <v>497</v>
+        <v>155</v>
       </c>
       <c r="F1443" t="n">
         <v>4</v>
@@ -40843,7 +40843,7 @@
         <v>4</v>
       </c>
       <c r="H1443" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1444">
@@ -40852,26 +40852,26 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>2900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>200</v>
+        <v>630</v>
       </c>
       <c r="E1444" t="n">
-        <v>155</v>
+        <v>750</v>
       </c>
       <c r="F1444" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G1444" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1444" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1445">
@@ -40880,26 +40880,26 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Elite Posisi Hook Cocok untuk Hunian dan Office di Pondok Indah</t>
+          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>25000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="E1445" t="n">
-        <v>750</v>
+        <v>257</v>
       </c>
       <c r="F1445" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1445" t="n">
         <v>41</v>
       </c>
       <c r="H1445" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1446">
@@ -40908,26 +40908,26 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>22500000000</v>
+        <v>209000000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>500</v>
+        <v>1841</v>
       </c>
       <c r="E1446" t="n">
-        <v>366</v>
+        <v>4189</v>
       </c>
       <c r="F1446" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="G1446" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="H1446" t="n">
-        <v>21</v>
+        <v>910</v>
       </c>
     </row>
     <row r="1447">
@@ -40936,26 +40936,26 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Turun Harga~ Good Investasi Disewakan. Harga Murah.</t>
+          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>9500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="E1447" t="n">
-        <v>257</v>
+        <v>750</v>
       </c>
       <c r="F1447" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G1447" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1447" t="n">
-        <v>21</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1448">
@@ -40964,26 +40964,26 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Bukit Golf Pondok Indah | LT 4.189 M2 Rp 50 Jt M2</t>
+          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>209000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>1841</v>
+        <v>250</v>
       </c>
       <c r="E1448" t="n">
-        <v>4189</v>
+        <v>320</v>
       </c>
       <c r="F1448" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="G1448" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="H1448" t="n">
-        <v>910</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1449">
@@ -40992,26 +40992,26 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>South Grove</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>7600000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>325</v>
+        <v>720</v>
       </c>
       <c r="E1449" t="n">
-        <v>177</v>
+        <v>634</v>
       </c>
       <c r="F1449" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1449" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1449" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1450">
@@ -41020,26 +41020,26 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>24000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="E1450" t="n">
-        <v>518</v>
+        <v>936</v>
       </c>
       <c r="F1450" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1450" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="H1450" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1451">
@@ -41048,26 +41048,26 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah Mewah The 9 Nine Residence Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>12500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>520</v>
+        <v>100</v>
       </c>
       <c r="E1451" t="n">
-        <v>750</v>
+        <v>182</v>
       </c>
       <c r="F1451" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="G1451" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1451" t="n">
-        <v>310</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1452">
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
+          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>11500000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E1452" t="n">
-        <v>320</v>
+        <v>201</v>
       </c>
       <c r="F1452" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1452" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H1452" t="n">
         <v>11</v>
@@ -41104,26 +41104,26 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>32000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>720</v>
+        <v>280</v>
       </c>
       <c r="E1453" t="n">
-        <v>634</v>
+        <v>157</v>
       </c>
       <c r="F1453" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1453" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1453" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1454">
@@ -41132,26 +41132,26 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
+          <t>1 Park Homes</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>21500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>780</v>
+        <v>380</v>
       </c>
       <c r="E1454" t="n">
-        <v>936</v>
+        <v>200</v>
       </c>
       <c r="F1454" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1454" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="H1454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1455">
@@ -41160,26 +41160,26 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
+          <t>12 Merle Bintaro</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>2900000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E1455" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="F1455" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1455" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1455" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1456">
@@ -41188,26 +41188,26 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
+          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>5200000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>225</v>
+        <v>550</v>
       </c>
       <c r="E1456" t="n">
-        <v>201</v>
+        <v>1094</v>
       </c>
       <c r="F1456" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1456" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H1456" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1457">
@@ -41216,26 +41216,26 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
+          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>3900000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="E1457" t="n">
-        <v>157</v>
+        <v>647</v>
       </c>
       <c r="F1457" t="n">
         <v>4</v>
       </c>
       <c r="G1457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1457" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1458">
@@ -41244,26 +41244,26 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>1 Park Homes</t>
+          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>20000000000</v>
+        <v>4280000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>380</v>
+        <v>262</v>
       </c>
       <c r="E1458" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="F1458" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1458" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1458" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1459">
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>12 Merle Bintaro</t>
+          <t>Puri Rinda Residence</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>3950000000</v>
+        <v>1960000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="E1459" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="F1459" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1459" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,26 +41300,26 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>19000000000</v>
+        <v>19500000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="E1460" t="n">
-        <v>1094</v>
+        <v>673</v>
       </c>
       <c r="F1460" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1460" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H1460" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1461">
@@ -41328,26 +41328,26 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>9700000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>245</v>
+        <v>1200</v>
       </c>
       <c r="E1461" t="n">
-        <v>647</v>
+        <v>2138</v>
       </c>
       <c r="F1461" t="n">
         <v>4</v>
       </c>
       <c r="G1461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1461" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1462">
@@ -41356,26 +41356,26 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
+          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>4280000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>262</v>
+        <v>120</v>
       </c>
       <c r="E1462" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F1462" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1462" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1462" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1463">
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Puri Rinda Residence</t>
+          <t>Aparthouse Crystal</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>1960000000</v>
+        <v>950000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="E1463" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="F1463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
+          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>19500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>580</v>
+        <v>800</v>
       </c>
       <c r="E1464" t="n">
-        <v>673</v>
+        <v>1335</v>
       </c>
       <c r="F1464" t="n">
         <v>7</v>
       </c>
       <c r="G1464" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1464" t="n">
         <v>42</v>
@@ -41440,26 +41440,26 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>32000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E1465" t="n">
-        <v>2138</v>
+        <v>1335</v>
       </c>
       <c r="F1465" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1465" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1465" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1466">
@@ -41468,26 +41468,26 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
+          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>1400000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="E1466" t="n">
-        <v>60</v>
+        <v>1025</v>
       </c>
       <c r="F1466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1466" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1467">
@@ -41496,26 +41496,26 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Aparthouse Crystal</t>
+          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>950000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="E1467" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F1467" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1467" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1468">
@@ -41524,26 +41524,26 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>27000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1468" t="n">
         <v>800</v>
       </c>
       <c r="E1468" t="n">
-        <v>1335</v>
+        <v>650</v>
       </c>
       <c r="F1468" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G1468" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H1468" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1469">
@@ -41552,26 +41552,26 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
+          <t>Kemang Siap Huni Best Price</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>27000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="E1469" t="n">
-        <v>1335</v>
+        <v>425</v>
       </c>
       <c r="F1469" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G1469" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1469" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1470">
@@ -41580,26 +41580,26 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
+          <t>Kemang Jakarta Selatan Harga Dibawah Pasaran</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>120000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>2100</v>
+        <v>460</v>
       </c>
       <c r="E1470" t="n">
-        <v>1025</v>
+        <v>1075</v>
       </c>
       <c r="F1470" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="G1470" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1470" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1471">
@@ -41608,26 +41608,26 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
+          <t>Rumah, Pondok Indah 3 Lantai 7 Milyar</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>2100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="E1471" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="F1471" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G1471" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1471" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1472">
@@ -41636,26 +41636,26 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>97000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E1472" t="n">
-        <v>650</v>
+        <v>2138</v>
       </c>
       <c r="F1472" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1472" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="H1472" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1473">
@@ -41664,26 +41664,26 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Kemang Siap Huni Best Price</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>13500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="E1473" t="n">
-        <v>425</v>
+        <v>91</v>
       </c>
       <c r="F1473" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1473" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1473" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1474">
@@ -41692,26 +41692,26 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Kemang Jakarta Selatan Harga Dibawah Pasaran</t>
+          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>26000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>460</v>
+        <v>260</v>
       </c>
       <c r="E1474" t="n">
-        <v>1075</v>
+        <v>200</v>
       </c>
       <c r="F1474" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="G1474" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1474" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1475">
@@ -41720,26 +41720,26 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Rumah, Pondok Indah 3 Lantai 7 Milyar</t>
+          <t>Dijual Rumah 716m2 Di Badan Jalan Permata Hijau Raya</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>7000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1475" t="n">
         <v>400</v>
       </c>
       <c r="E1475" t="n">
-        <v>120</v>
+        <v>716</v>
       </c>
       <c r="F1475" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G1475" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H1475" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1476">
@@ -41748,26 +41748,26 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
+          <t>Dijual Rumah Asri Gaya American Country Nyaman dan Strategis Diandara, Cilandak</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>25000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1476" t="n">
-        <v>275</v>
+        <v>660</v>
       </c>
       <c r="F1476" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1476" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="H1476" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1477">
@@ -41776,26 +41776,26 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>Rumah Baru Fully Furnished SHM di Area Senopati Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>32000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>1200</v>
+        <v>810</v>
       </c>
       <c r="E1477" t="n">
-        <v>2138</v>
+        <v>338</v>
       </c>
       <c r="F1477" t="n">
         <v>41</v>
       </c>
       <c r="G1477" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H1477" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1478">
@@ -41804,26 +41804,26 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>1900000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="E1478" t="n">
-        <v>74</v>
+        <v>515</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1478" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1478" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1479">
@@ -41832,26 +41832,26 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Ada Private Pool di Cilandak Dekat Citos</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>6250000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>288</v>
+        <v>881</v>
       </c>
       <c r="E1479" t="n">
-        <v>178</v>
+        <v>1066</v>
       </c>
       <c r="F1479" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="G1479" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="H1479" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1480">
@@ -41860,26 +41860,26 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>2900000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>90</v>
+        <v>1100</v>
       </c>
       <c r="E1480" t="n">
-        <v>91</v>
+        <v>360</v>
       </c>
       <c r="F1480" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G1480" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="H1480" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1481">
@@ -41888,26 +41888,26 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Edenhaus Simatupang</t>
+          <t>Area Favorit Tenang Jalan Lebar Dalam Portal</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>9900000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>222</v>
+        <v>500</v>
       </c>
       <c r="E1481" t="n">
-        <v>240</v>
+        <v>425</v>
       </c>
       <c r="F1481" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1481" t="n">
         <v>4</v>
       </c>
       <c r="H1481" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1482">
@@ -41916,26 +41916,26 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Area Tenang Depan Taman Jalan Lebar Siap Huni</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>850000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="E1482" t="n">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="F1482" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1482" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1482" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1483">
@@ -41944,26 +41944,26 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>American Classic Luxury Home 4 Lantai Jagakarsa</t>
+          <t>Rumah Mewah Spesifikasi Premium Lokasi Eksklusif di Pondok Indah</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>4900000000</v>
+        <v>26900000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>370</v>
+        <v>800</v>
       </c>
       <c r="E1483" t="n">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="F1483" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G1483" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="H1483" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1484">
@@ -41972,17 +41972,17 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
+          <t>Rumah Mewah Siap Huni di Jagakarsa Akses Lebar Dekat Tol</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>4900000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="E1484" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="F1484" t="n">
         <v>4</v>
@@ -41991,7 +41991,7 @@
         <v>4</v>
       </c>
       <c r="H1484" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1485">
@@ -42000,26 +42000,26 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Dijual Rumah 716m2 Di Badan Jalan Permata Hijau Raya</t>
+          <t>Rumah Mewah Fully-Furnished Bernuansa Resort di Jagakarsa</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>30000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="E1485" t="n">
-        <v>716</v>
+        <v>2138</v>
       </c>
       <c r="F1485" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G1485" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H1485" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1486">
@@ -42028,26 +42028,26 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Dijual Rumah Asri Gaya American Country Nyaman dan Strategis Diandara, Cilandak</t>
+          <t>Ruma Rempoa</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>10000000000</v>
+        <v>2290000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>500</v>
+        <v>92</v>
       </c>
       <c r="E1486" t="n">
-        <v>660</v>
+        <v>89</v>
       </c>
       <c r="F1486" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1486" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1486" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1487">
@@ -42056,26 +42056,26 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Baru Fully Furnished SHM di Area Senopati Kebayoran Baru</t>
+          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>48000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>810</v>
+        <v>600</v>
       </c>
       <c r="E1487" t="n">
-        <v>338</v>
+        <v>787</v>
       </c>
       <c r="F1487" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1487" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H1487" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1488">
@@ -42084,26 +42084,26 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>Brand New American Classic Style Dijagakarsa</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>12800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1488" t="n">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="F1488" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1488" t="n">
         <v>4</v>
       </c>
       <c r="H1488" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1489">
@@ -42112,26 +42112,26 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Dalam Town House Harga Dibawah di Bawah NJOP di Kemang Jakarta Selatan</t>
+          <t>M Living at Puri Pesanggrahan</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>30000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>1200</v>
+        <v>182</v>
       </c>
       <c r="E1489" t="n">
-        <v>1800</v>
+        <v>111</v>
       </c>
       <c r="F1489" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1489" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1489" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1490">
@@ -42140,26 +42140,26 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>62000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>881</v>
+        <v>600</v>
       </c>
       <c r="E1490" t="n">
-        <v>1066</v>
+        <v>1018</v>
       </c>
       <c r="F1490" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G1490" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H1490" t="n">
-        <v>68</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1491">
@@ -42168,26 +42168,26 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>17700000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>1100</v>
+        <v>765</v>
       </c>
       <c r="E1491" t="n">
-        <v>360</v>
+        <v>765</v>
       </c>
       <c r="F1491" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G1491" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1491" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1492">
@@ -42196,26 +42196,26 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Area Favorit Tenang Jalan Lebar Dalam Portal</t>
+          <t>Precium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>28000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="E1492" t="n">
-        <v>425</v>
+        <v>334</v>
       </c>
       <c r="F1492" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1492" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1492" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1493">
@@ -42224,26 +42224,26 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Area Tenang Depan Taman Jalan Lebar Siap Huni</t>
+          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>15000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>250</v>
+        <v>417</v>
       </c>
       <c r="E1493" t="n">
-        <v>238</v>
+        <v>417</v>
       </c>
       <c r="F1493" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1493" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1493" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1494">
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Rumah Mewah Spesifikasi Premium Lokasi Eksklusif di Pondok Indah</t>
+          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>26900000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="E1494" t="n">
-        <v>430</v>
+        <v>695</v>
       </c>
       <c r="F1494" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1494" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1494" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Jagakarsa Akses Lebar Dekat Tol</t>
+          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>1700000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="E1495" t="n">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="F1495" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1495" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1495" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Rumah Mewah Fully-Furnished Bernuansa Resort di Jagakarsa</t>
+          <t>67 Kebagusan</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>32000000000</v>
+        <v>1470000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>1200</v>
+        <v>74</v>
       </c>
       <c r="E1496" t="n">
-        <v>2138</v>
+        <v>56</v>
       </c>
       <c r="F1496" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="G1496" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H1496" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Rumah Jl. Ciniru Kebayoran Baru Jaksel</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>36000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E1497" t="n">
-        <v>450</v>
+        <v>2360</v>
       </c>
       <c r="F1497" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="G1497" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H1497" t="n">
-        <v>1</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Ruma Rempoa</t>
+          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>2290000000</v>
+        <v>9980000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>92</v>
+        <v>400</v>
       </c>
       <c r="E1498" t="n">
-        <v>89</v>
+        <v>785</v>
       </c>
       <c r="F1498" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1498" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H1498" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>1900000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="E1499" t="n">
-        <v>74</v>
+        <v>412</v>
       </c>
       <c r="F1499" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1499" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1499" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>24000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>600</v>
+        <v>185</v>
       </c>
       <c r="E1500" t="n">
-        <v>787</v>
+        <v>300</v>
       </c>
       <c r="F1500" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G1500" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1500" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Brand New American Classic Style Dijagakarsa</t>
+          <t>Rumah Dijual Jalan Tebet Barat Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>2400000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1501" t="n">
         <v>200</v>
       </c>
       <c r="E1501" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F1501" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1501" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,23 +42476,23 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>M Living at Puri Pesanggrahan</t>
+          <t>Rumah dijual bangunan lama dekat Pakubuwono dan Senayan City</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>2900000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>182</v>
+        <v>500</v>
       </c>
       <c r="E1502" t="n">
-        <v>111</v>
+        <v>328</v>
       </c>
       <c r="F1502" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="G1502" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1502" t="n">
         <v>1</v>
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Elite Cipaku Kebayoran Baru, Dekat Scbd &amp; Senopati</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>53000000000</v>
+        <v>33000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E1503" t="n">
-        <v>1018</v>
+        <v>410</v>
       </c>
       <c r="F1503" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G1503" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1503" t="n">
-        <v>213</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,23 +42532,23 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
+          <t>Dijual Rumah Hook di Cipaku, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>21000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>765</v>
+        <v>229</v>
       </c>
       <c r="E1504" t="n">
-        <v>765</v>
+        <v>359</v>
       </c>
       <c r="F1504" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1504" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1504" t="n">
         <v>2</v>
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Precium Kebayoran Baru</t>
+          <t>Dijual Rumah Komersial di Jalan Wijaya, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>13500000000</v>
+        <v>88000000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>220</v>
+        <v>750</v>
       </c>
       <c r="E1505" t="n">
-        <v>334</v>
+        <v>1035</v>
       </c>
       <c r="F1505" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1505" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1505" t="n">
-        <v>1</v>
+        <v>810</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
+          <t>Dijual - Rumah Komersial di Jl. Cikajang, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>23000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>417</v>
+        <v>257</v>
       </c>
       <c r="E1506" t="n">
-        <v>417</v>
+        <v>283</v>
       </c>
       <c r="F1506" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1506" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1506" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
+          <t>Dijual Rumah Baru Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>16000000000</v>
+        <v>39000000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1507" t="n">
-        <v>695</v>
+        <v>380</v>
       </c>
       <c r="F1507" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1507" t="n">
         <v>42</v>
-      </c>
-      <c r="G1507" t="n">
-        <v>42</v>
-      </c>
-      <c r="H1507" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus. Hanya Rp.40 M</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>6800000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>220</v>
+        <v>1200</v>
       </c>
       <c r="E1508" t="n">
-        <v>168</v>
+        <v>584</v>
       </c>
       <c r="F1508" t="n">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="G1508" t="n">
-        <v>31</v>
+        <v>182</v>
       </c>
       <c r="H1508" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>67 Kebagusan</t>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>1470000000</v>
+        <v>85000000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>74</v>
+        <v>1500</v>
       </c>
       <c r="E1509" t="n">
-        <v>56</v>
+        <v>634</v>
       </c>
       <c r="F1509" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1509" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1509" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Seperti Ddalam Komplek(Gated) Dikebayoran Baru. Luas 340M.(Fisik 360M) Rp.21.5 M</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>48000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E1510" t="n">
-        <v>2360</v>
+        <v>340</v>
       </c>
       <c r="F1510" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G1510" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1510" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Murah Rumah Istana Super Lux Di Pondok Indah Luas 2382m Hanya Rp 89 M ( Hanya 37 Juta/m2 )</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>9980000000</v>
+        <v>89000000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="E1511" t="n">
-        <v>785</v>
+        <v>2382</v>
       </c>
       <c r="F1511" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1511" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1511" t="n">
-        <v>11</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
+          <t>Rumah 100% Brand New Super Lux di Kebayoran Baru. 380M 3Lt Rp 38 Mly</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>18000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>480</v>
+        <v>850</v>
       </c>
       <c r="E1512" t="n">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="F1512" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1512" t="n">
         <v>42</v>
-      </c>
-      <c r="G1512" t="n">
-        <v>41</v>
-      </c>
-      <c r="H1512" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Timur Raya. Luas 1192M2. NJOP 27 M Jual Hanya Rp 24 M</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>16500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>185</v>
+        <v>800</v>
       </c>
       <c r="E1513" t="n">
-        <v>300</v>
+        <v>1192</v>
       </c>
       <c r="F1513" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G1513" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1513" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,26 +42812,26 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Rumah Dijual Jalan Tebet Barat Dalam Jakarta Selatan</t>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>4200000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E1514" t="n">
-        <v>90</v>
+        <v>864</v>
       </c>
       <c r="F1514" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1515">
@@ -42840,26 +42840,26 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Rumah dijual bangunan lama dekat Pakubuwono dan Senayan City</t>
+          <t>Dijual Murah Rumah Area Senopati Scbd. Luas 523 Hanya Rp.29 M Jalan Lebar Tenang Dalam Portal</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>20000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E1515" t="n">
-        <v>328</v>
+        <v>523</v>
       </c>
       <c r="F1515" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="G1515" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="H1515" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Dijual Rumah Elite Cipaku Kebayoran Baru, Dekat Scbd &amp; Senopati</t>
+          <t>Dijual Rp 50Jt/M2. Rumah di Bukit Golf (Pondok Indah) Luas 4189Meter2. Langka.</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>33000000000</v>
+        <v>209000000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>500</v>
+        <v>1841</v>
       </c>
       <c r="E1516" t="n">
-        <v>410</v>
+        <v>4189</v>
       </c>
       <c r="F1516" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1516" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1516" t="n">
-        <v>22</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hook di Cipaku, Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>30000000000</v>
+        <v>39000000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>229</v>
+        <v>850</v>
       </c>
       <c r="E1517" t="n">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="F1517" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1517" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1517" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Dijual Rumah Komersial di Jalan Wijaya, Kebayoran Baru Jakarta Selatan</t>
+          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>88000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="E1518" t="n">
-        <v>1035</v>
+        <v>353</v>
       </c>
       <c r="F1518" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G1518" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H1518" t="n">
-        <v>810</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
      